--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>37500</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>3.21000003814697</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>3.15000009536743</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>3.22000002861023</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -62894,7 +62894,7 @@
         <v>37500</v>
       </c>
       <c r="C2719" t="n">
-        <v>3.21000003814697</v>
+        <v>3.22000002861023</v>
       </c>
       <c r="D2719" t="n">
         <v>3.15000009536743</v>
@@ -62906,6 +62906,29 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>3.22000002861023</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G2720" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>57500</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>3.22000002861023</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>3.22000002861023</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>17000</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>3.21000003814697</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>3.16000008583069</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>3.21000003814697</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>12000</v>
+        <v>40500</v>
       </c>
       <c r="C2715" t="n">
-        <v>3.22000002861023</v>
+        <v>3.25</v>
       </c>
       <c r="D2715" t="n">
-        <v>3.13000011444092</v>
+        <v>3.0699999332428</v>
       </c>
       <c r="E2715" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="F2715" t="n">
         <v>3.20000004768372</v>
-      </c>
-      <c r="F2715" t="n">
-        <v>3.22000002861023</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>22500</v>
+        <v>12000</v>
       </c>
       <c r="C2716" t="n">
-        <v>3.21000003814697</v>
+        <v>3.22000002861023</v>
       </c>
       <c r="D2716" t="n">
-        <v>3.10999989509583</v>
+        <v>3.13000011444092</v>
       </c>
       <c r="E2716" t="n">
-        <v>3.21000003814697</v>
+        <v>3.20000004768372</v>
       </c>
       <c r="F2716" t="n">
-        <v>3.17000007629395</v>
+        <v>3.22000002861023</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>16500</v>
+        <v>22500</v>
       </c>
       <c r="C2717" t="n">
-        <v>3.23000001907349</v>
+        <v>3.21000003814697</v>
       </c>
       <c r="D2717" t="n">
+        <v>3.10999989509583</v>
+      </c>
+      <c r="E2717" t="n">
+        <v>3.21000003814697</v>
+      </c>
+      <c r="F2717" t="n">
         <v>3.17000007629395</v>
-      </c>
-      <c r="E2717" t="n">
-        <v>3.17000007629395</v>
-      </c>
-      <c r="F2717" t="n">
-        <v>3.22000002861023</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>34000</v>
+        <v>16500</v>
       </c>
       <c r="C2718" t="n">
-        <v>3.25</v>
+        <v>3.23000001907349</v>
       </c>
       <c r="D2718" t="n">
-        <v>3.1800000667572</v>
+        <v>3.17000007629395</v>
       </c>
       <c r="E2718" t="n">
-        <v>3.1800000667572</v>
+        <v>3.17000007629395</v>
       </c>
       <c r="F2718" t="n">
-        <v>3.1800000667572</v>
+        <v>3.22000002861023</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>37500</v>
+        <v>34000</v>
       </c>
       <c r="C2719" t="n">
-        <v>3.22000002861023</v>
+        <v>3.25</v>
       </c>
       <c r="D2719" t="n">
-        <v>3.15000009536743</v>
+        <v>3.1800000667572</v>
       </c>
       <c r="E2719" t="n">
-        <v>3.20000004768372</v>
+        <v>3.1800000667572</v>
       </c>
       <c r="F2719" t="n">
-        <v>3.22000002861023</v>
+        <v>3.1800000667572</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>20000</v>
+        <v>37500</v>
       </c>
       <c r="C2720" t="n">
         <v>3.22000002861023</v>
       </c>
       <c r="D2720" t="n">
-        <v>3.1800000667572</v>
+        <v>3.15000009536743</v>
       </c>
       <c r="E2720" t="n">
         <v>3.20000004768372</v>
       </c>
       <c r="F2720" t="n">
-        <v>3.19000005722046</v>
+        <v>3.22000002861023</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>57500</v>
+        <v>20000</v>
       </c>
       <c r="C2721" t="n">
         <v>3.22000002861023</v>
       </c>
       <c r="D2721" t="n">
-        <v>3.14000010490417</v>
+        <v>3.1800000667572</v>
       </c>
       <c r="E2721" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="F2721" t="n">
         <v>3.19000005722046</v>
-      </c>
-      <c r="F2721" t="n">
-        <v>3.22000002861023</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>17000</v>
+        <v>57500</v>
       </c>
       <c r="C2722" t="n">
+        <v>3.22000002861023</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>3.22000002861023</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>28000</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>3.23000001907349</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E2723" t="n">
         <v>3.21000003814697</v>
       </c>
-      <c r="D2722" t="n">
-        <v>3.16000008583069</v>
-      </c>
-      <c r="E2722" t="n">
-        <v>3.20000004768372</v>
-      </c>
-      <c r="F2722" t="n">
+      <c r="F2723" t="n">
         <v>3.21000003814697</v>
       </c>
-      <c r="G2722" t="s">
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -71225,6 +71225,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>12500</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>3.21000003814697</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>3.15000009536743</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="H2726" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -71251,6 +71251,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2727">
+      <c r="A2727" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2727" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C2727" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="D2727" t="n">
+        <v>3.16000008583069</v>
+      </c>
+      <c r="E2727" t="n">
+        <v>3.16000008583069</v>
+      </c>
+      <c r="F2727" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="G2727" t="n">
+        <v>3.19000005722046</v>
+      </c>
+      <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G2" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G3" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G5" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G6" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.90521001815796</v>
       </c>
       <c r="G32" t="n">
-        <v>2.76729702949524</v>
+        <v>2.76729679107666</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.85984706878662</v>
       </c>
       <c r="G34" t="n">
-        <v>2.72408723831177</v>
+        <v>2.72408747673035</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.90718293190002</v>
       </c>
       <c r="G37" t="n">
-        <v>2.76917624473572</v>
+        <v>2.76917600631714</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.90718293190002</v>
       </c>
       <c r="G38" t="n">
-        <v>2.76917624473572</v>
+        <v>2.76917600631714</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.90718293190002</v>
       </c>
       <c r="G39" t="n">
-        <v>2.76917624473572</v>
+        <v>2.76917600631714</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G45" t="n">
-        <v>2.66772723197937</v>
+        <v>2.66772699356079</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G124" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G125" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G126" t="n">
-        <v>2.66772723197937</v>
+        <v>2.66772699356079</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G127" t="n">
-        <v>2.66772723197937</v>
+        <v>2.66772699356079</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G128" t="n">
-        <v>2.66772723197937</v>
+        <v>2.66772699356079</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G129" t="n">
-        <v>2.66772723197937</v>
+        <v>2.66772699356079</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G130" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.72967505455017</v>
       </c>
       <c r="G131" t="n">
-        <v>2.60009479522705</v>
+        <v>2.60009455680847</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.72967505455017</v>
       </c>
       <c r="G132" t="n">
-        <v>2.60009479522705</v>
+        <v>2.60009455680847</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G133" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G136" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G137" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G138" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G139" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G140" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G141" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G142" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.58372402191162</v>
       </c>
       <c r="G143" t="n">
-        <v>2.46107220649719</v>
+        <v>2.46107196807861</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.58372402191162</v>
       </c>
       <c r="G144" t="n">
-        <v>2.46107220649719</v>
+        <v>2.46107196807861</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.48905301094055</v>
       </c>
       <c r="G145" t="n">
-        <v>2.37089514732361</v>
+        <v>2.37089538574219</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.48905301094055</v>
       </c>
       <c r="G146" t="n">
-        <v>2.37089514732361</v>
+        <v>2.37089538574219</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.35690808296204</v>
       </c>
       <c r="G148" t="n">
-        <v>2.24502348899841</v>
+        <v>2.24502325057983</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G154" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G155" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G156" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G157" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G158" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G159" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.56400108337402</v>
       </c>
       <c r="G173" t="n">
-        <v>2.44228529930115</v>
+        <v>2.44228553771973</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.58372402191162</v>
       </c>
       <c r="G181" t="n">
-        <v>2.46107220649719</v>
+        <v>2.46107196807861</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.56400108337402</v>
       </c>
       <c r="G202" t="n">
-        <v>2.44228529930115</v>
+        <v>2.44228553771973</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.56991791725159</v>
       </c>
       <c r="G203" t="n">
-        <v>2.44792127609253</v>
+        <v>2.44792151451111</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G205" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G206" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G207" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G208" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G209" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G210" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.46144104003906</v>
       </c>
       <c r="G214" t="n">
-        <v>2.3445942401886</v>
+        <v>2.34459400177002</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G237" t="n">
-        <v>2.20744967460632</v>
+        <v>2.2074499130249</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G238" t="n">
-        <v>2.20744967460632</v>
+        <v>2.2074499130249</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G239" t="n">
-        <v>2.20744967460632</v>
+        <v>2.2074499130249</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G240" t="n">
-        <v>2.20744967460632</v>
+        <v>2.2074499130249</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G241" t="n">
-        <v>2.20744967460632</v>
+        <v>2.2074499130249</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.36874198913574</v>
       </c>
       <c r="G255" t="n">
-        <v>2.25629568099976</v>
+        <v>2.25629544258118</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.17151093482971</v>
       </c>
       <c r="G259" t="n">
-        <v>2.06842732429504</v>
+        <v>2.06842708587646</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.09853601455688</v>
       </c>
       <c r="G260" t="n">
-        <v>1.99891650676727</v>
+        <v>1.99891638755798</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G262" t="n">
-        <v>2.08345723152161</v>
+        <v>2.08345699310303</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G263" t="n">
-        <v>2.08345723152161</v>
+        <v>2.08345699310303</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G264" t="n">
-        <v>2.08345723152161</v>
+        <v>2.08345699310303</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G265" t="n">
-        <v>2.08345723152161</v>
+        <v>2.08345699310303</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G266" t="n">
-        <v>2.01958131790161</v>
+        <v>2.01958155632019</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G267" t="n">
-        <v>2.01958131790161</v>
+        <v>2.01958155632019</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G280" t="n">
-        <v>2.01958131790161</v>
+        <v>2.01958155632019</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G281" t="n">
-        <v>2.01958131790161</v>
+        <v>2.01958155632019</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G282" t="n">
-        <v>2.01958131790161</v>
+        <v>2.01958155632019</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G283" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G284" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G285" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.18531799316406</v>
       </c>
       <c r="G305" t="n">
-        <v>2.08157896995544</v>
+        <v>2.08157873153687</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>1.98216998577118</v>
       </c>
       <c r="G308" t="n">
-        <v>1.88807451725006</v>
+        <v>1.88807439804077</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>1.94272398948669</v>
       </c>
       <c r="G309" t="n">
-        <v>1.85050106048584</v>
+        <v>1.85050094127655</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.15770506858826</v>
       </c>
       <c r="G326" t="n">
-        <v>2.05527663230896</v>
+        <v>2.05527687072754</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.18926191329956</v>
       </c>
       <c r="G332" t="n">
-        <v>2.08533573150635</v>
+        <v>2.08533549308777</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.18926191329956</v>
       </c>
       <c r="G333" t="n">
-        <v>2.08533573150635</v>
+        <v>2.08533549308777</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G340" t="n">
-        <v>2.02521753311157</v>
+        <v>2.02521777153015</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G344" t="n">
-        <v>2.02521753311157</v>
+        <v>2.02521777153015</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G345" t="n">
-        <v>2.02521753311157</v>
+        <v>2.02521777153015</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G346" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G347" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.00189304351807</v>
       </c>
       <c r="G365" t="n">
-        <v>1.90686118602753</v>
+        <v>1.90686130523682</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.71981310844421</v>
       </c>
       <c r="G368" t="n">
-        <v>2.59070110321045</v>
+        <v>2.59070086479187</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.41607809066772</v>
       </c>
       <c r="G369" t="n">
-        <v>2.30138444900513</v>
+        <v>2.30138468742371</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.25829291343689</v>
       </c>
       <c r="G370" t="n">
-        <v>2.15108966827393</v>
+        <v>2.15108942985535</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.17940092086792</v>
       </c>
       <c r="G374" t="n">
-        <v>2.07594275474548</v>
+        <v>2.0759425163269</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.17940092086792</v>
       </c>
       <c r="G376" t="n">
-        <v>2.07594275474548</v>
+        <v>2.0759425163269</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.20701289176941</v>
       </c>
       <c r="G378" t="n">
-        <v>2.10224366188049</v>
+        <v>2.10224390029907</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.44369006156921</v>
       </c>
       <c r="G383" t="n">
-        <v>2.32768583297729</v>
+        <v>2.32768559455872</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.30957293510437</v>
       </c>
       <c r="G384" t="n">
-        <v>2.1999351978302</v>
+        <v>2.19993543624878</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.3628249168396</v>
       </c>
       <c r="G393" t="n">
-        <v>2.25065946578979</v>
+        <v>2.25065922737122</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.27604389190674</v>
       </c>
       <c r="G395" t="n">
-        <v>2.16799807548523</v>
+        <v>2.16799783706665</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.10445308685303</v>
       </c>
       <c r="G398" t="n">
-        <v>2.00455284118652</v>
+        <v>2.00455260276794</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.0472559928894</v>
       </c>
       <c r="G399" t="n">
-        <v>1.95007061958313</v>
+        <v>1.95007073879242</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.19123506546021</v>
       </c>
       <c r="G401" t="n">
-        <v>2.08721518516541</v>
+        <v>2.08721494674683</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G402" t="n">
-        <v>2.02521753311157</v>
+        <v>2.02521777153015</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.10839796066284</v>
       </c>
       <c r="G403" t="n">
-        <v>2.00831007957458</v>
+        <v>2.00831031799316</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G406" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.00189304351807</v>
       </c>
       <c r="G416" t="n">
-        <v>1.90686118602753</v>
+        <v>1.90686130523682</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>1.98019802570343</v>
       </c>
       <c r="G417" t="n">
-        <v>1.88619613647461</v>
+        <v>1.88619601726532</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.00189304351807</v>
       </c>
       <c r="G418" t="n">
-        <v>1.90686118602753</v>
+        <v>1.90686130523682</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.03936696052551</v>
       </c>
       <c r="G419" t="n">
-        <v>1.94255614280701</v>
+        <v>1.9425562620163</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.03936696052551</v>
       </c>
       <c r="G420" t="n">
-        <v>1.94255614280701</v>
+        <v>1.9425562620163</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>1.98808705806732</v>
       </c>
       <c r="G421" t="n">
-        <v>1.89371073246002</v>
+        <v>1.89371061325073</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.03936696052551</v>
       </c>
       <c r="G422" t="n">
-        <v>1.94255614280701</v>
+        <v>1.9425562620163</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.01569890975952</v>
       </c>
       <c r="G423" t="n">
-        <v>1.92001175880432</v>
+        <v>1.92001163959503</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>1.98019802570343</v>
       </c>
       <c r="G428" t="n">
-        <v>1.88619613647461</v>
+        <v>1.88619601726532</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>1.98019802570343</v>
       </c>
       <c r="G429" t="n">
-        <v>1.88619613647461</v>
+        <v>1.88619601726532</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>1.91313898563385</v>
       </c>
       <c r="G434" t="n">
-        <v>1.8223203420639</v>
+        <v>1.82232046127319</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>1.87960994243622</v>
       </c>
       <c r="G435" t="n">
-        <v>1.79038298130035</v>
+        <v>1.79038310050964</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>1.85397005081177</v>
       </c>
       <c r="G439" t="n">
-        <v>1.76596033573151</v>
+        <v>1.76596021652222</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>1.85791397094727</v>
       </c>
       <c r="G441" t="n">
-        <v>1.76971709728241</v>
+        <v>1.76971697807312</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>1.77507698535919</v>
       </c>
       <c r="G445" t="n">
-        <v>1.69081246852875</v>
+        <v>1.69081234931946</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>1.77507698535919</v>
       </c>
       <c r="G446" t="n">
-        <v>1.69081246852875</v>
+        <v>1.69081234931946</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>1.53840005397797</v>
       </c>
       <c r="G451" t="n">
-        <v>1.4653707742691</v>
+        <v>1.46537065505981</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G454" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>1.82241296768188</v>
       </c>
       <c r="G456" t="n">
-        <v>1.73590123653412</v>
+        <v>1.73590135574341</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>1.47528600692749</v>
       </c>
       <c r="G466" t="n">
-        <v>1.40525269508362</v>
+        <v>1.40525281429291</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>1.50684297084808</v>
       </c>
       <c r="G468" t="n">
-        <v>1.43531179428101</v>
+        <v>1.43531167507172</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G469" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G474" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>1.48909294605255</v>
       </c>
       <c r="G475" t="n">
-        <v>1.41840434074402</v>
+        <v>1.41840422153473</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>1.54431700706482</v>
       </c>
       <c r="G477" t="n">
-        <v>1.47100687026978</v>
+        <v>1.47100675106049</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G478" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>1.48909294605255</v>
       </c>
       <c r="G479" t="n">
-        <v>1.41840434074402</v>
+        <v>1.41840422153473</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>1.49205100536346</v>
       </c>
       <c r="G488" t="n">
-        <v>1.42122197151184</v>
+        <v>1.42122185230255</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>1.53840005397797</v>
       </c>
       <c r="G489" t="n">
-        <v>1.4653707742691</v>
+        <v>1.46537065505981</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G490" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G492" t="n">
-        <v>1.44658386707306</v>
+        <v>1.44658398628235</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G493" t="n">
-        <v>1.44658386707306</v>
+        <v>1.44658398628235</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>1.54234504699707</v>
       </c>
       <c r="G494" t="n">
-        <v>1.46912848949432</v>
+        <v>1.46912837028503</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>1.55615103244781</v>
       </c>
       <c r="G498" t="n">
-        <v>1.48227894306183</v>
+        <v>1.48227906227112</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G499" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>1.55220699310303</v>
       </c>
       <c r="G501" t="n">
-        <v>1.47852218151093</v>
+        <v>1.47852230072021</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>1.50684297084808</v>
       </c>
       <c r="G502" t="n">
-        <v>1.43531179428101</v>
+        <v>1.43531167507172</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G504" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>1.44175696372986</v>
       </c>
       <c r="G505" t="n">
-        <v>1.37331533432007</v>
+        <v>1.37331545352936</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>1.4013249874115</v>
       </c>
       <c r="G507" t="n">
-        <v>1.33480274677277</v>
+        <v>1.33480262756348</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G508" t="n">
-        <v>1.33386361598969</v>
+        <v>1.3338634967804</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G515" t="n">
-        <v>1.33386361598969</v>
+        <v>1.3338634967804</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G520" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>1.48909294605255</v>
       </c>
       <c r="G521" t="n">
-        <v>1.41840434074402</v>
+        <v>1.41840422153473</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>1.5531929731369</v>
       </c>
       <c r="G524" t="n">
-        <v>1.47946131229401</v>
+        <v>1.4794614315033</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G526" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G527" t="n">
-        <v>1.44658386707306</v>
+        <v>1.44658398628235</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>1.5531929731369</v>
       </c>
       <c r="G529" t="n">
-        <v>1.47946131229401</v>
+        <v>1.4794614315033</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G533" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G535" t="n">
-        <v>1.44658386707306</v>
+        <v>1.44658398628235</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G538" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G539" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G543" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G544" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G546" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G547" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G548" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G555" t="n">
-        <v>1.30568289756775</v>
+        <v>1.30568301677704</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G561" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G567" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G568" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G576" t="n">
-        <v>1.29629015922546</v>
+        <v>1.29629004001617</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G577" t="n">
-        <v>1.31977272033691</v>
+        <v>1.3197728395462</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G579" t="n">
-        <v>1.31977272033691</v>
+        <v>1.3197728395462</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G591" t="n">
-        <v>1.29629015922546</v>
+        <v>1.29629004001617</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G597" t="n">
-        <v>1.31977272033691</v>
+        <v>1.3197728395462</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G603" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G604" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G607" t="n">
-        <v>1.2352329492569</v>
+        <v>1.23523306846619</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G611" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G612" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G614" t="n">
-        <v>1.20705246925354</v>
+        <v>1.20705235004425</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G621" t="n">
-        <v>1.30568289756775</v>
+        <v>1.30568301677704</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G630" t="n">
-        <v>1.30568289756775</v>
+        <v>1.30568301677704</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G635" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>1.85397005081177</v>
       </c>
       <c r="G638" t="n">
-        <v>1.76596033573151</v>
+        <v>1.76596021652222</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G645" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>1.56798505783081</v>
       </c>
       <c r="G652" t="n">
-        <v>1.49355125427246</v>
+        <v>1.49355137348175</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G656" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G658" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G660" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G662" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G663" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G664" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G665" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G668" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G669" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G670" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G671" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G673" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G676" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G679" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G680" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G685" t="n">
-        <v>1.29629015922546</v>
+        <v>1.29629004001617</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G686" t="n">
-        <v>1.29629015922546</v>
+        <v>1.29629004001617</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G691" t="n">
-        <v>1.33386361598969</v>
+        <v>1.3338634967804</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G694" t="n">
-        <v>1.33386361598969</v>
+        <v>1.3338634967804</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G696" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G700" t="n">
-        <v>1.30568289756775</v>
+        <v>1.30568301677704</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G701" t="n">
-        <v>1.2352329492569</v>
+        <v>1.23523306846619</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G702" t="n">
-        <v>1.2352329492569</v>
+        <v>1.23523306846619</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.2179000377655</v>
       </c>
       <c r="G707" t="n">
-        <v>1.16008520126343</v>
+        <v>1.16008508205414</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G712" t="n">
-        <v>1.089635014534</v>
+        <v>1.08963513374329</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>1.17845404148102</v>
       </c>
       <c r="G714" t="n">
-        <v>1.12251174449921</v>
+        <v>1.12251162528992</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.12914597988129</v>
       </c>
       <c r="G716" t="n">
-        <v>1.0755443572998</v>
+        <v>1.07554423809052</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.01573896408081</v>
       </c>
       <c r="G719" t="n">
-        <v>0.967520892620087</v>
+        <v>0.967520833015442</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.11435401439667</v>
       </c>
       <c r="G723" t="n">
-        <v>1.06145453453064</v>
+        <v>1.06145465373993</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.10449194908142</v>
       </c>
       <c r="G724" t="n">
-        <v>1.05206072330475</v>
+        <v>1.05206060409546</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>0.938817977905273</v>
       </c>
       <c r="G739" t="n">
-        <v>0.894251346588135</v>
+        <v>0.89425140619278</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>0.938817977905273</v>
       </c>
       <c r="G740" t="n">
-        <v>0.894251346588135</v>
+        <v>0.89425140619278</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>0.926985025405884</v>
       </c>
       <c r="G742" t="n">
-        <v>0.882980167865753</v>
+        <v>0.882980108261108</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G743" t="n">
-        <v>0.911159813404083</v>
+        <v>0.911159753799438</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G744" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G748" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G753" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>0.926985025405884</v>
       </c>
       <c r="G755" t="n">
-        <v>0.882980167865753</v>
+        <v>0.882980108261108</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>0.867815017700195</v>
       </c>
       <c r="G757" t="n">
-        <v>0.826619029045105</v>
+        <v>0.82661896944046</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>0.887538015842438</v>
       </c>
       <c r="G758" t="n">
-        <v>0.845405757427216</v>
+        <v>0.845405697822571</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>0.879648983478546</v>
       </c>
       <c r="G759" t="n">
-        <v>0.837891221046448</v>
+        <v>0.837891161441803</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>0.887538015842438</v>
       </c>
       <c r="G760" t="n">
-        <v>0.845405757427216</v>
+        <v>0.845405697822571</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G770" t="n">
-        <v>0.911159813404083</v>
+        <v>0.911159753799438</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G775" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G777" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G778" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G779" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G780" t="n">
-        <v>0.911159813404083</v>
+        <v>0.911159753799438</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>0.942762970924377</v>
       </c>
       <c r="G781" t="n">
-        <v>0.898009121417999</v>
+        <v>0.898009061813354</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>0.938817977905273</v>
       </c>
       <c r="G787" t="n">
-        <v>0.894251346588135</v>
+        <v>0.89425140619278</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.01573896408081</v>
       </c>
       <c r="G789" t="n">
-        <v>0.967520892620087</v>
+        <v>0.967520833015442</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>0.962486028671265</v>
       </c>
       <c r="G790" t="n">
-        <v>0.91679584980011</v>
+        <v>0.916795909404755</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G791" t="n">
-        <v>0.911159813404083</v>
+        <v>0.911159753799438</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>1.09956204891205</v>
       </c>
       <c r="G804" t="n">
-        <v>1.04736471176147</v>
+        <v>1.04736483097076</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G823" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G824" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G826" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>0.972347974777222</v>
       </c>
       <c r="G828" t="n">
-        <v>0.926189720630646</v>
+        <v>0.926189661026001</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>0.978264987468719</v>
       </c>
       <c r="G829" t="n">
-        <v>0.931825757026672</v>
+        <v>0.931825816631317</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>1.04039204120636</v>
       </c>
       <c r="G836" t="n">
-        <v>0.991003632545471</v>
+        <v>0.991003572940826</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>1.01573896408081</v>
       </c>
       <c r="G839" t="n">
-        <v>0.967520892620087</v>
+        <v>0.967520833015442</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>0.99108499288559</v>
       </c>
       <c r="G840" t="n">
-        <v>0.944037258625031</v>
+        <v>0.944037199020386</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>0.982209026813507</v>
       </c>
       <c r="G842" t="n">
-        <v>0.93558257818222</v>
+        <v>0.935582637786865</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>0.982209026813507</v>
       </c>
       <c r="G843" t="n">
-        <v>0.93558257818222</v>
+        <v>0.935582637786865</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>0.99108499288559</v>
       </c>
       <c r="G845" t="n">
-        <v>0.944037258625031</v>
+        <v>0.944037199020386</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G853" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G855" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>0.982209026813507</v>
       </c>
       <c r="G856" t="n">
-        <v>0.93558257818222</v>
+        <v>0.935582637786865</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G857" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>0.978264987468719</v>
       </c>
       <c r="G863" t="n">
-        <v>0.931825757026672</v>
+        <v>0.931825816631317</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>0.978264987468719</v>
       </c>
       <c r="G864" t="n">
-        <v>0.931825757026672</v>
+        <v>0.931825816631317</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>0.950652003288269</v>
       </c>
       <c r="G867" t="n">
-        <v>0.905523657798767</v>
+        <v>0.905523598194122</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>0.90923398733139</v>
       </c>
       <c r="G873" t="n">
-        <v>0.866071760654449</v>
+        <v>0.866071820259094</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>0.915151000022888</v>
       </c>
       <c r="G874" t="n">
-        <v>0.871707856655121</v>
+        <v>0.871707916259766</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G878" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>0.769200026988983</v>
       </c>
       <c r="G879" t="n">
-        <v>0.732685387134552</v>
+        <v>0.732685327529907</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>0.769200026988983</v>
       </c>
       <c r="G880" t="n">
-        <v>0.732685387134552</v>
+        <v>0.732685327529907</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G884" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G886" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G888" t="n">
-        <v>0.723291456699371</v>
+        <v>0.723291516304016</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>0.745531976222992</v>
       </c>
       <c r="G889" t="n">
-        <v>0.710140824317932</v>
+        <v>0.710140883922577</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G890" t="n">
-        <v>0.723291456699371</v>
+        <v>0.723291516304016</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G891" t="n">
-        <v>0.723291456699371</v>
+        <v>0.723291516304016</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>0.77708899974823</v>
       </c>
       <c r="G893" t="n">
-        <v>0.740199863910675</v>
+        <v>0.74019980430603</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G896" t="n">
-        <v>0.723291456699371</v>
+        <v>0.723291516304016</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>0.729753971099854</v>
       </c>
       <c r="G898" t="n">
-        <v>0.695111811161041</v>
+        <v>0.695111870765686</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G899" t="n">
-        <v>0.702626347541809</v>
+        <v>0.702626407146454</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G904" t="n">
-        <v>0.548574805259705</v>
+        <v>0.548574864864349</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>0.508854985237122</v>
       </c>
       <c r="G907" t="n">
-        <v>0.484699130058289</v>
+        <v>0.484699159860611</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>0.492091000080109</v>
       </c>
       <c r="G912" t="n">
-        <v>0.468730956315994</v>
+        <v>0.468730986118317</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>0.492091000080109</v>
       </c>
       <c r="G913" t="n">
-        <v>0.468730956315994</v>
+        <v>0.468730986118317</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G918" t="n">
-        <v>0.432096689939499</v>
+        <v>0.432096719741821</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G920" t="n">
-        <v>0.418945103883743</v>
+        <v>0.418945133686066</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>0.481243014335632</v>
       </c>
       <c r="G922" t="n">
-        <v>0.458397924900055</v>
+        <v>0.458397954702377</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>0.44574099779129</v>
       </c>
       <c r="G925" t="n">
-        <v>0.424581259489059</v>
+        <v>0.424581229686737</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>0.449685990810394</v>
       </c>
       <c r="G927" t="n">
-        <v>0.428338944911957</v>
+        <v>0.428338974714279</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G930" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>0.469408988952637</v>
       </c>
       <c r="G931" t="n">
-        <v>0.447125673294067</v>
+        <v>0.44712570309639</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G938" t="n">
-        <v>0.494093000888824</v>
+        <v>0.494093030691147</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G939" t="n">
-        <v>0.494093000888824</v>
+        <v>0.494093030691147</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G940" t="n">
-        <v>0.494093000888824</v>
+        <v>0.494093030691147</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>0.506883025169373</v>
       </c>
       <c r="G943" t="n">
-        <v>0.482820808887482</v>
+        <v>0.482820779085159</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>0.489131987094879</v>
       </c>
       <c r="G948" t="n">
-        <v>0.4659124314785</v>
+        <v>0.465912401676178</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G954" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G955" t="n">
-        <v>0.41988530755043</v>
+        <v>0.419885277748108</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G961" t="n">
-        <v>0.437731891870499</v>
+        <v>0.437731862068176</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G963" t="n">
-        <v>0.462154686450958</v>
+        <v>0.462154716253281</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G978" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G981" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G983" t="n">
-        <v>0.432096689939499</v>
+        <v>0.432096719741821</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>0.469408988952637</v>
       </c>
       <c r="G987" t="n">
-        <v>0.447125673294067</v>
+        <v>0.44712570309639</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G990" t="n">
-        <v>0.432096689939499</v>
+        <v>0.432096719741821</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G991" t="n">
-        <v>0.432096689939499</v>
+        <v>0.432096719741821</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G992" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G993" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G994" t="n">
-        <v>0.41988530755043</v>
+        <v>0.419885277748108</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G995" t="n">
-        <v>0.418945103883743</v>
+        <v>0.418945133686066</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>0.449685990810394</v>
       </c>
       <c r="G996" t="n">
-        <v>0.428338944911957</v>
+        <v>0.428338974714279</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G997" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>0.55224597454071</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.526030361652374</v>
+        <v>0.526030302047729</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>0.603525996208191</v>
       </c>
       <c r="G1006" t="n">
-        <v>0.574876010417938</v>
+        <v>0.574876070022583</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>0.694252014160156</v>
       </c>
       <c r="G1008" t="n">
-        <v>0.661295175552368</v>
+        <v>0.661295235157013</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>0.639028012752533</v>
       </c>
       <c r="G1012" t="n">
-        <v>0.608692705631256</v>
+        <v>0.608692765235901</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.63499391078949</v>
+        <v>0.634993970394135</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1017" t="n">
-        <v>0.604935050010681</v>
+        <v>0.604934990406036</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>0.611415028572083</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.582390546798706</v>
+        <v>0.582390606403351</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>0.765254974365234</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.728927552700043</v>
+        <v>0.728927612304688</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>0.706085979938507</v>
       </c>
       <c r="G1031" t="n">
-        <v>0.672567427158356</v>
+        <v>0.672567367553711</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>0.668612003326416</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.636872291564941</v>
+        <v>0.636872351169586</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>0.69819700717926</v>
       </c>
       <c r="G1043" t="n">
-        <v>0.665052950382233</v>
+        <v>0.665052890777588</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>0.550274014472961</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.524151921272278</v>
+        <v>0.524151980876923</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>0.571968972682953</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.544817090034485</v>
+        <v>0.54481703042984</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>0.55224597454071</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.526030361652374</v>
+        <v>0.526030302047729</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>0.520689010620117</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.495971381664276</v>
+        <v>0.495971411466599</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>0.36191800236702</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.344737410545349</v>
+        <v>0.344737380743027</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>0.318527013063431</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.303406208753586</v>
+        <v>0.303406238555908</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.309981524944305</v>
+        <v>0.309981554746628</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>0.400377988815308</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.381371676921844</v>
+        <v>0.381371647119522</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>0.384600013494492</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.366342693567276</v>
+        <v>0.366342663764954</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.336283713579178</v>
+        <v>0.336283683776855</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1103" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1106" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>0.369807004928589</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.352251917123795</v>
+        <v>0.352251887321472</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.432096689939499</v>
+        <v>0.432096719741821</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.392643928527832</v>
+        <v>0.39264389872551</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>0.398405998945236</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.379493296146393</v>
+        <v>0.37949326634407</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>0.475326001644135</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.452761828899384</v>
+        <v>0.452761799097061</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>0.484201014041901</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.461215525865555</v>
+        <v>0.461215496063232</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G1135" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G1137" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.462154686450958</v>
+        <v>0.462154716253281</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>0.475326001644135</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.452761828899384</v>
+        <v>0.452761799097061</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1141" t="n">
-        <v>0.437731891870499</v>
+        <v>0.437731862068176</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1143" t="n">
-        <v>0.548574805259705</v>
+        <v>0.548574864864349</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>0.524634003639221</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.499729126691818</v>
+        <v>0.499729096889496</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.462154686450958</v>
+        <v>0.462154716253281</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>0.489131987094879</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.4659124314785</v>
+        <v>0.465912401676178</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.437731891870499</v>
+        <v>0.437731862068176</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>0.449685990810394</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.428338944911957</v>
+        <v>0.428338974714279</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.41988530755043</v>
+        <v>0.419885277748108</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.418945103883743</v>
+        <v>0.418945133686066</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.418945103883743</v>
+        <v>0.418945133686066</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.418945103883743</v>
+        <v>0.418945133686066</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>0.429962992668152</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.409552246332169</v>
+        <v>0.409552216529846</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.392643928527832</v>
+        <v>0.39264389872551</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>0.429962992668152</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.409552246332169</v>
+        <v>0.409552216529846</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>0.402350008487701</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.383250057697296</v>
+        <v>0.383250087499619</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.392643928527832</v>
+        <v>0.39264389872551</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.494093000888824</v>
+        <v>0.494093030691147</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.462154686450958</v>
+        <v>0.462154716253281</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.437731891870499</v>
+        <v>0.437731862068176</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>0.44574099779129</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.424581259489059</v>
+        <v>0.424581229686737</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.437731891870499</v>
+        <v>0.437731862068176</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.41988530755043</v>
+        <v>0.419885277748108</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1298" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>0.418128997087479</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.398279994726181</v>
+        <v>0.398280024528503</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1325" t="n">
-        <v>0.392643928527832</v>
+        <v>0.39264389872551</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1332" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1337" t="n">
-        <v>0.392643928527832</v>
+        <v>0.39264389872551</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1339" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1341" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1343" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1353" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>0.429962992668152</v>
       </c>
       <c r="G1357" t="n">
-        <v>0.409552246332169</v>
+        <v>0.409552216529846</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>0.398405998945236</v>
       </c>
       <c r="G1363" t="n">
-        <v>0.379493296146393</v>
+        <v>0.37949326634407</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>0.398405998945236</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.379493296146393</v>
+        <v>0.37949326634407</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1368" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1370" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1377" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>0.402350008487701</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.383250057697296</v>
+        <v>0.383250087499619</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1385" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.36070653796196</v>
+        <v>0.360706567764282</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1391" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.361645728349686</v>
+        <v>0.361645758152008</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.36070653796196</v>
+        <v>0.360706567764282</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1398" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>0.368820995092392</v>
       </c>
       <c r="G1407" t="n">
-        <v>0.351312726736069</v>
+        <v>0.351312696933746</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.347555905580521</v>
+        <v>0.347555935382843</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1414" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.336283713579178</v>
+        <v>0.336283683776855</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>0.34909799695015</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.332525968551636</v>
+        <v>0.332525998353958</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1436" t="n">
-        <v>0.347555905580521</v>
+        <v>0.347555935382843</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1450" t="n">
-        <v>0.361645728349686</v>
+        <v>0.361645758152008</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.361645728349686</v>
+        <v>0.361645758152008</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1462" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1467" t="n">
-        <v>0.36070653796196</v>
+        <v>0.360706567764282</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.347555905580521</v>
+        <v>0.347555935382843</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1478" t="n">
-        <v>0.36070653796196</v>
+        <v>0.360706567764282</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.361645728349686</v>
+        <v>0.361645758152008</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>0.384600013494492</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.366342693567276</v>
+        <v>0.366342663764954</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>0.384600013494492</v>
       </c>
       <c r="G1485" t="n">
-        <v>0.366342693567276</v>
+        <v>0.366342663764954</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1487" t="n">
-        <v>0.361645728349686</v>
+        <v>0.361645758152008</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1488" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1489" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1490" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.321253776550293</v>
+        <v>0.321253746747971</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.336283713579178</v>
+        <v>0.336283683776855</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1508" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1517" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1518" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>0.319514006376266</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.304346352815628</v>
+        <v>0.30434638261795</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>0.347126007080078</v>
       </c>
       <c r="G1525" t="n">
-        <v>0.330647587776184</v>
+        <v>0.330647617578506</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1529" t="n">
-        <v>0.321253776550293</v>
+        <v>0.321253746747971</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>0.330361008644104</v>
       </c>
       <c r="G1531" t="n">
-        <v>0.314678460359573</v>
+        <v>0.314678430557251</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>0.347126007080078</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.330647587776184</v>
+        <v>0.330647617578506</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>0.333319991827011</v>
       </c>
       <c r="G1542" t="n">
-        <v>0.317496955394745</v>
+        <v>0.317496985197067</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>0.333319991827011</v>
       </c>
       <c r="G1543" t="n">
-        <v>0.317496955394745</v>
+        <v>0.317496985197067</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>0.334306001663208</v>
       </c>
       <c r="G1545" t="n">
-        <v>0.318436145782471</v>
+        <v>0.318436175584793</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>0.334306001663208</v>
       </c>
       <c r="G1546" t="n">
-        <v>0.318436145782471</v>
+        <v>0.318436175584793</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1547" t="n">
-        <v>0.309981524944305</v>
+        <v>0.309981554746628</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.309981524944305</v>
+        <v>0.309981554746628</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>0.333319991827011</v>
       </c>
       <c r="G1557" t="n">
-        <v>0.317496955394745</v>
+        <v>0.317496985197067</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>0.366849005222321</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.349434345960617</v>
+        <v>0.349434316158295</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.321253776550293</v>
+        <v>0.321253746747971</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1563" t="n">
-        <v>0.309981524944305</v>
+        <v>0.309981554746628</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>0.330361008644104</v>
       </c>
       <c r="G1569" t="n">
-        <v>0.314678460359573</v>
+        <v>0.314678430557251</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>0.330361008644104</v>
       </c>
       <c r="G1570" t="n">
-        <v>0.314678460359573</v>
+        <v>0.314678430557251</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>0.307680010795593</v>
       </c>
       <c r="G1574" t="n">
-        <v>0.293074160814285</v>
+        <v>0.293074131011963</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>0.301762998104095</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.287438005208969</v>
+        <v>0.287438035011292</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>0.304720997810364</v>
       </c>
       <c r="G1576" t="n">
-        <v>0.290255576372147</v>
+        <v>0.290255606174469</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>0.316554993391037</v>
       </c>
       <c r="G1583" t="n">
-        <v>0.301527827978134</v>
+        <v>0.301527798175812</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>0.304720997810364</v>
       </c>
       <c r="G1584" t="n">
-        <v>0.290255576372147</v>
+        <v>0.290255606174469</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1587" t="n">
-        <v>0.309981524944305</v>
+        <v>0.309981554746628</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>0.323457986116409</v>
       </c>
       <c r="G1592" t="n">
-        <v>0.308103144168854</v>
+        <v>0.308103114366531</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>0.321485996246338</v>
       </c>
       <c r="G1594" t="n">
-        <v>0.306224763393402</v>
+        <v>0.30622473359108</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>0.307680010795593</v>
       </c>
       <c r="G1604" t="n">
-        <v>0.293074160814285</v>
+        <v>0.293074131011963</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>0.307680010795593</v>
       </c>
       <c r="G1605" t="n">
-        <v>0.293074160814285</v>
+        <v>0.293074131011963</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>0.308665990829468</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.294013321399689</v>
+        <v>0.294013291597366</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>0.301762998104095</v>
       </c>
       <c r="G1607" t="n">
-        <v>0.287438005208969</v>
+        <v>0.287438035011292</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>0.34909799695015</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.332525968551636</v>
+        <v>0.332525998353958</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.321253776550293</v>
+        <v>0.321253746747971</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1617" t="n">
-        <v>0.347555905580521</v>
+        <v>0.347555935382843</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.336283713579178</v>
+        <v>0.336283683776855</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>0.363889992237091</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.346615761518478</v>
+        <v>0.346615791320801</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>0.368820995092392</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.351312726736069</v>
+        <v>0.351312696933746</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1624" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>0.674529016017914</v>
       </c>
       <c r="G1632" t="n">
-        <v>0.642508447170258</v>
+        <v>0.642508506774902</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>0.639028012752533</v>
       </c>
       <c r="G1634" t="n">
-        <v>0.608692705631256</v>
+        <v>0.608692765235901</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>0.611415028572083</v>
       </c>
       <c r="G1638" t="n">
-        <v>0.582390546798706</v>
+        <v>0.582390606403351</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1639" t="n">
-        <v>0.548574805259705</v>
+        <v>0.548574864864349</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1642" t="n">
-        <v>0.548574805259705</v>
+        <v>0.548574864864349</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>0.571968972682953</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.544817090034485</v>
+        <v>0.54481703042984</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>0.702140986919403</v>
       </c>
       <c r="G1655" t="n">
-        <v>0.668809652328491</v>
+        <v>0.668809711933136</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>0.615360021591187</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.586148321628571</v>
+        <v>0.586148262023926</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>0.639028012752533</v>
       </c>
       <c r="G1667" t="n">
-        <v>0.608692705631256</v>
+        <v>0.608692765235901</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>0.64691698551178</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.616207182407379</v>
+        <v>0.616207242012024</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.604935050010681</v>
+        <v>0.604934990406036</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1674" t="n">
-        <v>0.604935050010681</v>
+        <v>0.604934990406036</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>0.615360021591187</v>
       </c>
       <c r="G1682" t="n">
-        <v>0.586148321628571</v>
+        <v>0.586148262023926</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>0.583802998065948</v>
       </c>
       <c r="G1683" t="n">
-        <v>0.556089282035828</v>
+        <v>0.556089341640472</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>0.571968972682953</v>
       </c>
       <c r="G1686" t="n">
-        <v>0.544817090034485</v>
+        <v>0.54481703042984</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1689" t="n">
-        <v>0.548574805259705</v>
+        <v>0.548574864864349</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>0.595637023448944</v>
       </c>
       <c r="G1691" t="n">
-        <v>0.567361533641815</v>
+        <v>0.56736159324646</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>0.603525996208191</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.574876010417938</v>
+        <v>0.574876070022583</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>0.595637023448944</v>
       </c>
       <c r="G1697" t="n">
-        <v>0.567361533641815</v>
+        <v>0.56736159324646</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>0.607470989227295</v>
       </c>
       <c r="G1700" t="n">
-        <v>0.578633785247803</v>
+        <v>0.578633725643158</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>0.607470989227295</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.578633785247803</v>
+        <v>0.578633725643158</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.604935050010681</v>
+        <v>0.604934990406036</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>0.662694990634918</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.631236255168915</v>
+        <v>0.63123619556427</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>0.702140986919403</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.668809652328491</v>
+        <v>0.668809711933136</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1717" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>0.702140986919403</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.668809652328491</v>
+        <v>0.668809711933136</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1726" t="n">
-        <v>0.63499391078949</v>
+        <v>0.634993970394135</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>0.668612003326416</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.636872291564941</v>
+        <v>0.636872351169586</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1729" t="n">
-        <v>0.63499391078949</v>
+        <v>0.634993970394135</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>0.674529016017914</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.642508447170258</v>
+        <v>0.642508506774902</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1742" t="n">
-        <v>0.63499391078949</v>
+        <v>0.634993970394135</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>0.662694990634918</v>
       </c>
       <c r="G1744" t="n">
-        <v>0.631236255168915</v>
+        <v>0.63123619556427</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>0.64691698551178</v>
       </c>
       <c r="G1750" t="n">
-        <v>0.616207182407379</v>
+        <v>0.616207242012024</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>0.694252014160156</v>
       </c>
       <c r="G1755" t="n">
-        <v>0.661295175552368</v>
+        <v>0.661295235157013</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1763" t="n">
-        <v>0.63499391078949</v>
+        <v>0.634993970394135</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>0.69819700717926</v>
       </c>
       <c r="G1770" t="n">
-        <v>0.665052950382233</v>
+        <v>0.665052890777588</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>0.674529016017914</v>
       </c>
       <c r="G1790" t="n">
-        <v>0.642508447170258</v>
+        <v>0.642508506774902</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>0.694252014160156</v>
       </c>
       <c r="G1792" t="n">
-        <v>0.661295175552368</v>
+        <v>0.661295235157013</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>0.69819700717926</v>
       </c>
       <c r="G1803" t="n">
-        <v>0.665052950382233</v>
+        <v>0.665052890777588</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1809" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>0.706085979938507</v>
       </c>
       <c r="G1810" t="n">
-        <v>0.672567427158356</v>
+        <v>0.672567367553711</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>0.733698010444641</v>
       </c>
       <c r="G1824" t="n">
-        <v>0.698868691921234</v>
+        <v>0.698868632316589</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>0.729753971099854</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.695111811161041</v>
+        <v>0.695111870765686</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>0.745531976222992</v>
       </c>
       <c r="G1829" t="n">
-        <v>0.710140824317932</v>
+        <v>0.710140883922577</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>0.745531976222992</v>
       </c>
       <c r="G1830" t="n">
-        <v>0.710140824317932</v>
+        <v>0.710140883922577</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1832" t="n">
-        <v>0.712020218372345</v>
+        <v>0.71202027797699</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1834" t="n">
-        <v>0.712020218372345</v>
+        <v>0.71202027797699</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G1835" t="n">
-        <v>0.702626347541809</v>
+        <v>0.702626407146454</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.702626347541809</v>
+        <v>0.702626407146454</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G1837" t="n">
-        <v>0.702626347541809</v>
+        <v>0.702626407146454</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1839" t="n">
-        <v>0.712020218372345</v>
+        <v>0.71202027797699</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.712020218372345</v>
+        <v>0.71202027797699</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>0.796811997890472</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.758986592292786</v>
+        <v>0.758986532688141</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>0.942762970924377</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.898009121417999</v>
+        <v>0.898009061813354</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1861" t="n">
-        <v>1.089635014534</v>
+        <v>1.08963513374329</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>1.10449194908142</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.05206072330475</v>
+        <v>1.05206060409546</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.089635014534</v>
+        <v>1.08963513374329</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>1.10449194908142</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.05206072330475</v>
+        <v>1.05206060409546</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.089635014534</v>
+        <v>1.08963513374329</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>1.15873098373413</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.10372483730316</v>
+        <v>1.10372495651245</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.089635014534</v>
+        <v>1.08963513374329</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>1.15873098373413</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.10372483730316</v>
+        <v>1.10372495651245</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>1.2179000377655</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.16008520126343</v>
+        <v>1.16008508205414</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.20705246925354</v>
+        <v>1.20705235004425</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>1.25734603404999</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.19765853881836</v>
+        <v>1.19765865802765</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.20705246925354</v>
+        <v>1.20705235004425</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>1.27213895320892</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.21174931526184</v>
+        <v>1.21174919605255</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49977,7 +49977,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.20705246925354</v>
+        <v>1.20705235004425</v>
       </c>
       <c r="H1908" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.31977272033691</v>
+        <v>1.3197728395462</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.33386361598969</v>
+        <v>1.3338634967804</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.30568289756775</v>
+        <v>1.30568301677704</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.2352329492569</v>
+        <v>1.23523306846619</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50601,7 +50601,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G1932" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H1932" t="s">
         <v>8</v>
@@ -71274,6 +71274,32 @@
         <v>3.19000005722046</v>
       </c>
       <c r="H2727" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2728">
+      <c r="A2728" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2728" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C2728" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="D2728" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="E2728" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="F2728" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="G2728" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="H2728" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G2" t="n">
-        <v>2.78796315193176</v>
+        <v>2.78796291351318</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G3" t="n">
-        <v>2.78796315193176</v>
+        <v>2.78796291351318</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78796315193176</v>
+        <v>2.78796291351318</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G5" t="n">
-        <v>2.78796315193176</v>
+        <v>2.78796291351318</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G6" t="n">
-        <v>2.78796315193176</v>
+        <v>2.78796291351318</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.90521001815796</v>
       </c>
       <c r="G32" t="n">
-        <v>2.76729679107666</v>
+        <v>2.76729702949524</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.85984706878662</v>
       </c>
       <c r="G34" t="n">
-        <v>2.72408747673035</v>
+        <v>2.72408723831177</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.90718293190002</v>
       </c>
       <c r="G37" t="n">
-        <v>2.76917600631714</v>
+        <v>2.76917624473572</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.90718293190002</v>
       </c>
       <c r="G38" t="n">
-        <v>2.76917600631714</v>
+        <v>2.76917624473572</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.90718293190002</v>
       </c>
       <c r="G39" t="n">
-        <v>2.76917600631714</v>
+        <v>2.76917624473572</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G45" t="n">
-        <v>2.66772699356079</v>
+        <v>2.66772723197937</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G124" t="n">
-        <v>2.78796315193176</v>
+        <v>2.78796291351318</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G125" t="n">
-        <v>2.78796315193176</v>
+        <v>2.78796291351318</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G126" t="n">
-        <v>2.66772699356079</v>
+        <v>2.66772723197937</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G127" t="n">
-        <v>2.66772699356079</v>
+        <v>2.66772723197937</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G128" t="n">
-        <v>2.66772699356079</v>
+        <v>2.66772723197937</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G129" t="n">
-        <v>2.66772699356079</v>
+        <v>2.66772723197937</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G130" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.72967505455017</v>
       </c>
       <c r="G131" t="n">
-        <v>2.60009455680847</v>
+        <v>2.60009479522705</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.72967505455017</v>
       </c>
       <c r="G132" t="n">
-        <v>2.60009455680847</v>
+        <v>2.60009479522705</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G133" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G136" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G137" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G138" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G139" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G140" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G141" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G142" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.58372402191162</v>
       </c>
       <c r="G143" t="n">
-        <v>2.46107196807861</v>
+        <v>2.46107220649719</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.58372402191162</v>
       </c>
       <c r="G144" t="n">
-        <v>2.46107196807861</v>
+        <v>2.46107220649719</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.48905301094055</v>
       </c>
       <c r="G145" t="n">
-        <v>2.37089538574219</v>
+        <v>2.37089514732361</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.48905301094055</v>
       </c>
       <c r="G146" t="n">
-        <v>2.37089538574219</v>
+        <v>2.37089514732361</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.35690808296204</v>
       </c>
       <c r="G148" t="n">
-        <v>2.24502325057983</v>
+        <v>2.24502348899841</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G154" t="n">
-        <v>2.47046613693237</v>
+        <v>2.47046589851379</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G155" t="n">
-        <v>2.47046613693237</v>
+        <v>2.47046589851379</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G156" t="n">
-        <v>2.47046613693237</v>
+        <v>2.47046589851379</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G157" t="n">
-        <v>2.47046613693237</v>
+        <v>2.47046589851379</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G158" t="n">
-        <v>2.47046613693237</v>
+        <v>2.47046589851379</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G159" t="n">
-        <v>2.47046613693237</v>
+        <v>2.47046589851379</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.56400108337402</v>
       </c>
       <c r="G173" t="n">
-        <v>2.44228553771973</v>
+        <v>2.44228529930115</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.58372402191162</v>
       </c>
       <c r="G181" t="n">
-        <v>2.46107196807861</v>
+        <v>2.46107220649719</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.56400108337402</v>
       </c>
       <c r="G202" t="n">
-        <v>2.44228553771973</v>
+        <v>2.44228529930115</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.56991791725159</v>
       </c>
       <c r="G203" t="n">
-        <v>2.44792151451111</v>
+        <v>2.44792127609253</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G205" t="n">
-        <v>2.36525917053223</v>
+        <v>2.36525893211365</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G206" t="n">
-        <v>2.36525917053223</v>
+        <v>2.36525893211365</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G207" t="n">
-        <v>2.36525917053223</v>
+        <v>2.36525893211365</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G208" t="n">
-        <v>2.36525917053223</v>
+        <v>2.36525893211365</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G209" t="n">
-        <v>2.36525917053223</v>
+        <v>2.36525893211365</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G210" t="n">
-        <v>2.36525917053223</v>
+        <v>2.36525893211365</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.46144104003906</v>
       </c>
       <c r="G214" t="n">
-        <v>2.34459400177002</v>
+        <v>2.3445942401886</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G237" t="n">
-        <v>2.2074499130249</v>
+        <v>2.20744967460632</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G238" t="n">
-        <v>2.2074499130249</v>
+        <v>2.20744967460632</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G239" t="n">
-        <v>2.2074499130249</v>
+        <v>2.20744967460632</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G240" t="n">
-        <v>2.2074499130249</v>
+        <v>2.20744967460632</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G241" t="n">
-        <v>2.2074499130249</v>
+        <v>2.20744967460632</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.36874198913574</v>
       </c>
       <c r="G255" t="n">
-        <v>2.25629544258118</v>
+        <v>2.25629568099976</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.17151093482971</v>
       </c>
       <c r="G259" t="n">
-        <v>2.06842708587646</v>
+        <v>2.06842732429504</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.09853601455688</v>
       </c>
       <c r="G260" t="n">
-        <v>1.99891638755798</v>
+        <v>1.99891650676727</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G262" t="n">
-        <v>2.08345699310303</v>
+        <v>2.08345723152161</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G263" t="n">
-        <v>2.08345699310303</v>
+        <v>2.08345723152161</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G264" t="n">
-        <v>2.08345699310303</v>
+        <v>2.08345723152161</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G265" t="n">
-        <v>2.08345699310303</v>
+        <v>2.08345723152161</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G266" t="n">
-        <v>2.01958155632019</v>
+        <v>2.01958131790161</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G267" t="n">
-        <v>2.01958155632019</v>
+        <v>2.01958131790161</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G280" t="n">
-        <v>2.01958155632019</v>
+        <v>2.01958131790161</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G281" t="n">
-        <v>2.01958155632019</v>
+        <v>2.01958131790161</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G282" t="n">
-        <v>2.01958155632019</v>
+        <v>2.01958131790161</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G283" t="n">
-        <v>1.98200809955597</v>
+        <v>1.98200821876526</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G284" t="n">
-        <v>1.98200809955597</v>
+        <v>1.98200821876526</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G285" t="n">
-        <v>1.98200809955597</v>
+        <v>1.98200821876526</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.18531799316406</v>
       </c>
       <c r="G305" t="n">
-        <v>2.08157873153687</v>
+        <v>2.08157896995544</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>1.98216998577118</v>
       </c>
       <c r="G308" t="n">
-        <v>1.88807439804077</v>
+        <v>1.88807451725006</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>1.94272398948669</v>
       </c>
       <c r="G309" t="n">
-        <v>1.85050094127655</v>
+        <v>1.85050106048584</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.15770506858826</v>
       </c>
       <c r="G326" t="n">
-        <v>2.05527687072754</v>
+        <v>2.05527663230896</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.18926191329956</v>
       </c>
       <c r="G332" t="n">
-        <v>2.08533549308777</v>
+        <v>2.08533573150635</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.18926191329956</v>
       </c>
       <c r="G333" t="n">
-        <v>2.08533549308777</v>
+        <v>2.08533573150635</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G340" t="n">
-        <v>2.02521777153015</v>
+        <v>2.02521753311157</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G344" t="n">
-        <v>2.02521777153015</v>
+        <v>2.02521753311157</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G345" t="n">
-        <v>2.02521777153015</v>
+        <v>2.02521753311157</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G346" t="n">
-        <v>1.98200809955597</v>
+        <v>1.98200821876526</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G347" t="n">
-        <v>1.98200809955597</v>
+        <v>1.98200821876526</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.00189304351807</v>
       </c>
       <c r="G365" t="n">
-        <v>1.90686130523682</v>
+        <v>1.90686118602753</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.71981310844421</v>
       </c>
       <c r="G368" t="n">
-        <v>2.59070086479187</v>
+        <v>2.59070110321045</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.41607809066772</v>
       </c>
       <c r="G369" t="n">
-        <v>2.30138468742371</v>
+        <v>2.30138444900513</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.25829291343689</v>
       </c>
       <c r="G370" t="n">
-        <v>2.15108942985535</v>
+        <v>2.15108966827393</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.17940092086792</v>
       </c>
       <c r="G374" t="n">
-        <v>2.0759425163269</v>
+        <v>2.07594275474548</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.17940092086792</v>
       </c>
       <c r="G376" t="n">
-        <v>2.0759425163269</v>
+        <v>2.07594275474548</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.20701289176941</v>
       </c>
       <c r="G378" t="n">
-        <v>2.10224390029907</v>
+        <v>2.10224366188049</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.44369006156921</v>
       </c>
       <c r="G383" t="n">
-        <v>2.32768559455872</v>
+        <v>2.32768583297729</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.30957293510437</v>
       </c>
       <c r="G384" t="n">
-        <v>2.19993543624878</v>
+        <v>2.1999351978302</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.3628249168396</v>
       </c>
       <c r="G393" t="n">
-        <v>2.25065922737122</v>
+        <v>2.25065946578979</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.27604389190674</v>
       </c>
       <c r="G395" t="n">
-        <v>2.16799783706665</v>
+        <v>2.16799807548523</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.10445308685303</v>
       </c>
       <c r="G398" t="n">
-        <v>2.00455260276794</v>
+        <v>2.00455284118652</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.0472559928894</v>
       </c>
       <c r="G399" t="n">
-        <v>1.95007073879242</v>
+        <v>1.95007061958313</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.19123506546021</v>
       </c>
       <c r="G401" t="n">
-        <v>2.08721494674683</v>
+        <v>2.08721518516541</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G402" t="n">
-        <v>2.02521777153015</v>
+        <v>2.02521753311157</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.10839796066284</v>
       </c>
       <c r="G403" t="n">
-        <v>2.00831031799316</v>
+        <v>2.00831007957458</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G406" t="n">
-        <v>1.98200809955597</v>
+        <v>1.98200821876526</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.00189304351807</v>
       </c>
       <c r="G416" t="n">
-        <v>1.90686130523682</v>
+        <v>1.90686118602753</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>1.98019802570343</v>
       </c>
       <c r="G417" t="n">
-        <v>1.88619601726532</v>
+        <v>1.88619613647461</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.00189304351807</v>
       </c>
       <c r="G418" t="n">
-        <v>1.90686130523682</v>
+        <v>1.90686118602753</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.03936696052551</v>
       </c>
       <c r="G419" t="n">
-        <v>1.9425562620163</v>
+        <v>1.94255614280701</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.03936696052551</v>
       </c>
       <c r="G420" t="n">
-        <v>1.9425562620163</v>
+        <v>1.94255614280701</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>1.98808705806732</v>
       </c>
       <c r="G421" t="n">
-        <v>1.89371061325073</v>
+        <v>1.89371073246002</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.03936696052551</v>
       </c>
       <c r="G422" t="n">
-        <v>1.9425562620163</v>
+        <v>1.94255614280701</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.01569890975952</v>
       </c>
       <c r="G423" t="n">
-        <v>1.92001163959503</v>
+        <v>1.92001175880432</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>1.98019802570343</v>
       </c>
       <c r="G428" t="n">
-        <v>1.88619601726532</v>
+        <v>1.88619613647461</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>1.98019802570343</v>
       </c>
       <c r="G429" t="n">
-        <v>1.88619601726532</v>
+        <v>1.88619613647461</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>1.91313898563385</v>
       </c>
       <c r="G434" t="n">
-        <v>1.82232046127319</v>
+        <v>1.8223203420639</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>1.87960994243622</v>
       </c>
       <c r="G435" t="n">
-        <v>1.79038310050964</v>
+        <v>1.79038298130035</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>1.85397005081177</v>
       </c>
       <c r="G439" t="n">
-        <v>1.76596021652222</v>
+        <v>1.76596033573151</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>1.85791397094727</v>
       </c>
       <c r="G441" t="n">
-        <v>1.76971697807312</v>
+        <v>1.76971709728241</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>1.77507698535919</v>
       </c>
       <c r="G445" t="n">
-        <v>1.69081234931946</v>
+        <v>1.69081246852875</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>1.77507698535919</v>
       </c>
       <c r="G446" t="n">
-        <v>1.69081234931946</v>
+        <v>1.69081246852875</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>1.53840005397797</v>
       </c>
       <c r="G451" t="n">
-        <v>1.46537065505981</v>
+        <v>1.4653707742691</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G454" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>1.82241296768188</v>
       </c>
       <c r="G456" t="n">
-        <v>1.73590135574341</v>
+        <v>1.73590123653412</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>1.47528600692749</v>
       </c>
       <c r="G466" t="n">
-        <v>1.40525281429291</v>
+        <v>1.40525269508362</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>1.50684297084808</v>
       </c>
       <c r="G468" t="n">
-        <v>1.43531167507172</v>
+        <v>1.43531179428101</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G469" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G474" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>1.48909294605255</v>
       </c>
       <c r="G475" t="n">
-        <v>1.41840422153473</v>
+        <v>1.41840434074402</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>1.54431700706482</v>
       </c>
       <c r="G477" t="n">
-        <v>1.47100675106049</v>
+        <v>1.47100687026978</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G478" t="n">
-        <v>1.474764585495</v>
+        <v>1.47476446628571</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>1.48909294605255</v>
       </c>
       <c r="G479" t="n">
-        <v>1.41840422153473</v>
+        <v>1.41840434074402</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>1.49205100536346</v>
       </c>
       <c r="G488" t="n">
-        <v>1.42122185230255</v>
+        <v>1.42122197151184</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>1.53840005397797</v>
       </c>
       <c r="G489" t="n">
-        <v>1.46537065505981</v>
+        <v>1.4653707742691</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G490" t="n">
-        <v>1.474764585495</v>
+        <v>1.47476446628571</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G492" t="n">
-        <v>1.44658398628235</v>
+        <v>1.44658386707306</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G493" t="n">
-        <v>1.44658398628235</v>
+        <v>1.44658386707306</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>1.54234504699707</v>
       </c>
       <c r="G494" t="n">
-        <v>1.46912837028503</v>
+        <v>1.46912848949432</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>1.55615103244781</v>
       </c>
       <c r="G498" t="n">
-        <v>1.48227906227112</v>
+        <v>1.48227894306183</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G499" t="n">
-        <v>1.474764585495</v>
+        <v>1.47476446628571</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>1.55220699310303</v>
       </c>
       <c r="G501" t="n">
-        <v>1.47852230072021</v>
+        <v>1.47852218151093</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>1.50684297084808</v>
       </c>
       <c r="G502" t="n">
-        <v>1.43531167507172</v>
+        <v>1.43531179428101</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G504" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>1.44175696372986</v>
       </c>
       <c r="G505" t="n">
-        <v>1.37331545352936</v>
+        <v>1.37331533432007</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>1.4013249874115</v>
       </c>
       <c r="G507" t="n">
-        <v>1.33480262756348</v>
+        <v>1.33480274677277</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G508" t="n">
-        <v>1.3338634967804</v>
+        <v>1.33386361598969</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G515" t="n">
-        <v>1.3338634967804</v>
+        <v>1.33386361598969</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G520" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>1.48909294605255</v>
       </c>
       <c r="G521" t="n">
-        <v>1.41840422153473</v>
+        <v>1.41840434074402</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>1.5531929731369</v>
       </c>
       <c r="G524" t="n">
-        <v>1.4794614315033</v>
+        <v>1.47946131229401</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G526" t="n">
-        <v>1.474764585495</v>
+        <v>1.47476446628571</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G527" t="n">
-        <v>1.44658398628235</v>
+        <v>1.44658386707306</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>1.5531929731369</v>
       </c>
       <c r="G529" t="n">
-        <v>1.4794614315033</v>
+        <v>1.47946131229401</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G533" t="n">
-        <v>1.474764585495</v>
+        <v>1.47476446628571</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G535" t="n">
-        <v>1.44658398628235</v>
+        <v>1.44658386707306</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G538" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G539" t="n">
-        <v>1.474764585495</v>
+        <v>1.47476446628571</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G543" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G544" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G546" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G547" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G548" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G555" t="n">
-        <v>1.30568301677704</v>
+        <v>1.30568289756775</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G561" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G567" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G568" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G576" t="n">
-        <v>1.29629004001617</v>
+        <v>1.29629015922546</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G577" t="n">
-        <v>1.3197728395462</v>
+        <v>1.31977272033691</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G579" t="n">
-        <v>1.3197728395462</v>
+        <v>1.31977272033691</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G591" t="n">
-        <v>1.29629004001617</v>
+        <v>1.29629015922546</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G597" t="n">
-        <v>1.3197728395462</v>
+        <v>1.31977272033691</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G603" t="n">
-        <v>1.24932265281677</v>
+        <v>1.24932277202606</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G604" t="n">
-        <v>1.24932265281677</v>
+        <v>1.24932277202606</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G607" t="n">
-        <v>1.23523306846619</v>
+        <v>1.2352329492569</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G611" t="n">
-        <v>1.24932265281677</v>
+        <v>1.24932277202606</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G612" t="n">
-        <v>1.24932265281677</v>
+        <v>1.24932277202606</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G614" t="n">
-        <v>1.20705235004425</v>
+        <v>1.20705246925354</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G621" t="n">
-        <v>1.30568301677704</v>
+        <v>1.30568289756775</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G630" t="n">
-        <v>1.30568301677704</v>
+        <v>1.30568289756775</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G635" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>1.85397005081177</v>
       </c>
       <c r="G638" t="n">
-        <v>1.76596021652222</v>
+        <v>1.76596033573151</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G645" t="n">
-        <v>1.474764585495</v>
+        <v>1.47476446628571</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>1.56798505783081</v>
       </c>
       <c r="G652" t="n">
-        <v>1.49355137348175</v>
+        <v>1.49355125427246</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G656" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G658" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G660" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G662" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G663" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G664" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G665" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G668" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G669" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G670" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G671" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G673" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G676" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G679" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G680" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G685" t="n">
-        <v>1.29629004001617</v>
+        <v>1.29629015922546</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G686" t="n">
-        <v>1.29629004001617</v>
+        <v>1.29629015922546</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G691" t="n">
-        <v>1.3338634967804</v>
+        <v>1.33386361598969</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G694" t="n">
-        <v>1.3338634967804</v>
+        <v>1.33386361598969</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G696" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G700" t="n">
-        <v>1.30568301677704</v>
+        <v>1.30568289756775</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G701" t="n">
-        <v>1.23523306846619</v>
+        <v>1.2352329492569</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G702" t="n">
-        <v>1.23523306846619</v>
+        <v>1.2352329492569</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.2179000377655</v>
       </c>
       <c r="G707" t="n">
-        <v>1.16008508205414</v>
+        <v>1.16008520126343</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G712" t="n">
-        <v>1.08963513374329</v>
+        <v>1.089635014534</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>1.17845404148102</v>
       </c>
       <c r="G714" t="n">
-        <v>1.12251162528992</v>
+        <v>1.12251174449921</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.12914597988129</v>
       </c>
       <c r="G716" t="n">
-        <v>1.07554423809052</v>
+        <v>1.0755443572998</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.01573896408081</v>
       </c>
       <c r="G719" t="n">
-        <v>0.967520833015442</v>
+        <v>0.967520892620087</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.11435401439667</v>
       </c>
       <c r="G723" t="n">
-        <v>1.06145465373993</v>
+        <v>1.06145453453064</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.10449194908142</v>
       </c>
       <c r="G724" t="n">
-        <v>1.05206060409546</v>
+        <v>1.05206072330475</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>0.938817977905273</v>
       </c>
       <c r="G739" t="n">
-        <v>0.89425140619278</v>
+        <v>0.894251346588135</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>0.938817977905273</v>
       </c>
       <c r="G740" t="n">
-        <v>0.89425140619278</v>
+        <v>0.894251346588135</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>0.926985025405884</v>
       </c>
       <c r="G742" t="n">
-        <v>0.882980108261108</v>
+        <v>0.882980167865753</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G743" t="n">
-        <v>0.911159753799438</v>
+        <v>0.911159813404083</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G744" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G748" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G753" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>0.926985025405884</v>
       </c>
       <c r="G755" t="n">
-        <v>0.882980108261108</v>
+        <v>0.882980167865753</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>0.867815017700195</v>
       </c>
       <c r="G757" t="n">
-        <v>0.82661896944046</v>
+        <v>0.826619029045105</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>0.887538015842438</v>
       </c>
       <c r="G758" t="n">
-        <v>0.845405697822571</v>
+        <v>0.845405757427216</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>0.879648983478546</v>
       </c>
       <c r="G759" t="n">
-        <v>0.837891161441803</v>
+        <v>0.837891221046448</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>0.887538015842438</v>
       </c>
       <c r="G760" t="n">
-        <v>0.845405697822571</v>
+        <v>0.845405757427216</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G770" t="n">
-        <v>0.911159753799438</v>
+        <v>0.911159813404083</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G775" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G777" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G778" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G779" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G780" t="n">
-        <v>0.911159753799438</v>
+        <v>0.911159813404083</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>0.942762970924377</v>
       </c>
       <c r="G781" t="n">
-        <v>0.898009061813354</v>
+        <v>0.898009121417999</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>0.938817977905273</v>
       </c>
       <c r="G787" t="n">
-        <v>0.89425140619278</v>
+        <v>0.894251346588135</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.01573896408081</v>
       </c>
       <c r="G789" t="n">
-        <v>0.967520833015442</v>
+        <v>0.967520892620087</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>0.962486028671265</v>
       </c>
       <c r="G790" t="n">
-        <v>0.916795909404755</v>
+        <v>0.91679584980011</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G791" t="n">
-        <v>0.911159753799438</v>
+        <v>0.911159813404083</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>1.09956204891205</v>
       </c>
       <c r="G804" t="n">
-        <v>1.04736483097076</v>
+        <v>1.04736471176147</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G823" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G824" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G826" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>0.972347974777222</v>
       </c>
       <c r="G828" t="n">
-        <v>0.926189661026001</v>
+        <v>0.926189720630646</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>0.978264987468719</v>
       </c>
       <c r="G829" t="n">
-        <v>0.931825816631317</v>
+        <v>0.931825757026672</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>1.04039204120636</v>
       </c>
       <c r="G836" t="n">
-        <v>0.991003572940826</v>
+        <v>0.991003632545471</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>1.01573896408081</v>
       </c>
       <c r="G839" t="n">
-        <v>0.967520833015442</v>
+        <v>0.967520892620087</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>0.99108499288559</v>
       </c>
       <c r="G840" t="n">
-        <v>0.944037199020386</v>
+        <v>0.944037258625031</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>0.982209026813507</v>
       </c>
       <c r="G842" t="n">
-        <v>0.935582637786865</v>
+        <v>0.93558257818222</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>0.982209026813507</v>
       </c>
       <c r="G843" t="n">
-        <v>0.935582637786865</v>
+        <v>0.93558257818222</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>0.99108499288559</v>
       </c>
       <c r="G845" t="n">
-        <v>0.944037199020386</v>
+        <v>0.944037258625031</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G853" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G855" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>0.982209026813507</v>
       </c>
       <c r="G856" t="n">
-        <v>0.935582637786865</v>
+        <v>0.93558257818222</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G857" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>0.978264987468719</v>
       </c>
       <c r="G863" t="n">
-        <v>0.931825816631317</v>
+        <v>0.931825757026672</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>0.978264987468719</v>
       </c>
       <c r="G864" t="n">
-        <v>0.931825816631317</v>
+        <v>0.931825757026672</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>0.950652003288269</v>
       </c>
       <c r="G867" t="n">
-        <v>0.905523598194122</v>
+        <v>0.905523657798767</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>0.90923398733139</v>
       </c>
       <c r="G873" t="n">
-        <v>0.866071820259094</v>
+        <v>0.866071760654449</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>0.915151000022888</v>
       </c>
       <c r="G874" t="n">
-        <v>0.871707916259766</v>
+        <v>0.871707856655121</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G878" t="n">
-        <v>0.674445748329163</v>
+        <v>0.674445807933807</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>0.769200026988983</v>
       </c>
       <c r="G879" t="n">
-        <v>0.732685327529907</v>
+        <v>0.732685387134552</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>0.769200026988983</v>
       </c>
       <c r="G880" t="n">
-        <v>0.732685327529907</v>
+        <v>0.732685387134552</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G884" t="n">
-        <v>0.674445748329163</v>
+        <v>0.674445807933807</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G886" t="n">
-        <v>0.674445748329163</v>
+        <v>0.674445807933807</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G888" t="n">
-        <v>0.723291516304016</v>
+        <v>0.723291456699371</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>0.745531976222992</v>
       </c>
       <c r="G889" t="n">
-        <v>0.710140883922577</v>
+        <v>0.710140824317932</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G890" t="n">
-        <v>0.723291516304016</v>
+        <v>0.723291456699371</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G891" t="n">
-        <v>0.723291516304016</v>
+        <v>0.723291456699371</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>0.77708899974823</v>
       </c>
       <c r="G893" t="n">
-        <v>0.74019980430603</v>
+        <v>0.740199863910675</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G896" t="n">
-        <v>0.723291516304016</v>
+        <v>0.723291456699371</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>0.729753971099854</v>
       </c>
       <c r="G898" t="n">
-        <v>0.695111870765686</v>
+        <v>0.695111811161041</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G899" t="n">
-        <v>0.702626407146454</v>
+        <v>0.702626347541809</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G904" t="n">
-        <v>0.548574864864349</v>
+        <v>0.548574805259705</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>0.508854985237122</v>
       </c>
       <c r="G907" t="n">
-        <v>0.484699159860611</v>
+        <v>0.484699130058289</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>0.492091000080109</v>
       </c>
       <c r="G912" t="n">
-        <v>0.468730986118317</v>
+        <v>0.468730956315994</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>0.492091000080109</v>
       </c>
       <c r="G913" t="n">
-        <v>0.468730986118317</v>
+        <v>0.468730956315994</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G918" t="n">
-        <v>0.432096719741821</v>
+        <v>0.432096689939499</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G920" t="n">
-        <v>0.418945133686066</v>
+        <v>0.418945103883743</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>0.481243014335632</v>
       </c>
       <c r="G922" t="n">
-        <v>0.458397954702377</v>
+        <v>0.458397924900055</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>0.44574099779129</v>
       </c>
       <c r="G925" t="n">
-        <v>0.424581229686737</v>
+        <v>0.424581259489059</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>0.449685990810394</v>
       </c>
       <c r="G927" t="n">
-        <v>0.428338974714279</v>
+        <v>0.428338944911957</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G930" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>0.469408988952637</v>
       </c>
       <c r="G931" t="n">
-        <v>0.44712570309639</v>
+        <v>0.447125673294067</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G938" t="n">
-        <v>0.494093030691147</v>
+        <v>0.494093000888824</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G939" t="n">
-        <v>0.494093030691147</v>
+        <v>0.494093000888824</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G940" t="n">
-        <v>0.494093030691147</v>
+        <v>0.494093000888824</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>0.506883025169373</v>
       </c>
       <c r="G943" t="n">
-        <v>0.482820779085159</v>
+        <v>0.482820808887482</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>0.489131987094879</v>
       </c>
       <c r="G948" t="n">
-        <v>0.465912401676178</v>
+        <v>0.4659124314785</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G954" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G955" t="n">
-        <v>0.419885277748108</v>
+        <v>0.41988530755043</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G961" t="n">
-        <v>0.437731862068176</v>
+        <v>0.437731891870499</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G963" t="n">
-        <v>0.462154716253281</v>
+        <v>0.462154686450958</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G978" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G981" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G983" t="n">
-        <v>0.432096719741821</v>
+        <v>0.432096689939499</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>0.469408988952637</v>
       </c>
       <c r="G987" t="n">
-        <v>0.44712570309639</v>
+        <v>0.447125673294067</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G990" t="n">
-        <v>0.432096719741821</v>
+        <v>0.432096689939499</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G991" t="n">
-        <v>0.432096719741821</v>
+        <v>0.432096689939499</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G992" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G993" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G994" t="n">
-        <v>0.419885277748108</v>
+        <v>0.41988530755043</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G995" t="n">
-        <v>0.418945133686066</v>
+        <v>0.418945103883743</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>0.449685990810394</v>
       </c>
       <c r="G996" t="n">
-        <v>0.428338974714279</v>
+        <v>0.428338944911957</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G997" t="n">
-        <v>0.422702848911285</v>
+        <v>0.422702878713608</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>0.55224597454071</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.526030302047729</v>
+        <v>0.526030361652374</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>0.603525996208191</v>
       </c>
       <c r="G1006" t="n">
-        <v>0.574876070022583</v>
+        <v>0.574876010417938</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>0.694252014160156</v>
       </c>
       <c r="G1008" t="n">
-        <v>0.661295235157013</v>
+        <v>0.661295175552368</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>0.639028012752533</v>
       </c>
       <c r="G1012" t="n">
-        <v>0.608692765235901</v>
+        <v>0.608692705631256</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.634993970394135</v>
+        <v>0.63499391078949</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1017" t="n">
-        <v>0.604934990406036</v>
+        <v>0.604935050010681</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>0.611415028572083</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.582390606403351</v>
+        <v>0.582390546798706</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>0.765254974365234</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.728927612304688</v>
+        <v>0.728927552700043</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>0.706085979938507</v>
       </c>
       <c r="G1031" t="n">
-        <v>0.672567367553711</v>
+        <v>0.672567427158356</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>0.668612003326416</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.636872351169586</v>
+        <v>0.636872291564941</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>0.69819700717926</v>
       </c>
       <c r="G1043" t="n">
-        <v>0.665052890777588</v>
+        <v>0.665052950382233</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>0.550274014472961</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.524151980876923</v>
+        <v>0.524151921272278</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>0.571968972682953</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.54481703042984</v>
+        <v>0.544817090034485</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>0.55224597454071</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.526030302047729</v>
+        <v>0.526030361652374</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>0.520689010620117</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.495971411466599</v>
+        <v>0.495971381664276</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>0.36191800236702</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.344737380743027</v>
+        <v>0.344737410545349</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>0.318527013063431</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.303406238555908</v>
+        <v>0.303406208753586</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.309981554746628</v>
+        <v>0.309981524944305</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.345676630735397</v>
+        <v>0.345676600933075</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.394522279500961</v>
+        <v>0.394522309303284</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.387946963310242</v>
+        <v>0.387946993112564</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.387946963310242</v>
+        <v>0.387946993112564</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>0.400377988815308</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.381371647119522</v>
+        <v>0.381371676921844</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>0.384600013494492</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.366342663764954</v>
+        <v>0.366342693567276</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.336283683776855</v>
+        <v>0.336283713579178</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.337222874164581</v>
+        <v>0.337222903966904</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1103" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1106" t="n">
-        <v>0.337222874164581</v>
+        <v>0.337222903966904</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>0.369807004928589</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.352251887321472</v>
+        <v>0.352251917123795</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.432096719741821</v>
+        <v>0.432096689939499</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.39264389872551</v>
+        <v>0.392643928527832</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.394522279500961</v>
+        <v>0.394522309303284</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>0.398405998945236</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.37949326634407</v>
+        <v>0.379493296146393</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>0.475326001644135</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.452761799097061</v>
+        <v>0.452761828899384</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>0.484201014041901</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.461215496063232</v>
+        <v>0.461215525865555</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G1135" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G1137" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.462154716253281</v>
+        <v>0.462154686450958</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>0.475326001644135</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.452761799097061</v>
+        <v>0.452761828899384</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1141" t="n">
-        <v>0.437731862068176</v>
+        <v>0.437731891870499</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1143" t="n">
-        <v>0.548574864864349</v>
+        <v>0.548574805259705</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>0.524634003639221</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.499729096889496</v>
+        <v>0.499729126691818</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.462154716253281</v>
+        <v>0.462154686450958</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>0.489131987094879</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.465912401676178</v>
+        <v>0.4659124314785</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.437731862068176</v>
+        <v>0.437731891870499</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.422702848911285</v>
+        <v>0.422702878713608</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>0.449685990810394</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.428338974714279</v>
+        <v>0.428338944911957</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.387946963310242</v>
+        <v>0.387946993112564</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.419885277748108</v>
+        <v>0.41988530755043</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.422702848911285</v>
+        <v>0.422702878713608</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.422702848911285</v>
+        <v>0.422702878713608</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.418945133686066</v>
+        <v>0.418945103883743</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.418945133686066</v>
+        <v>0.418945103883743</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.418945133686066</v>
+        <v>0.418945103883743</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>0.429962992668152</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.409552216529846</v>
+        <v>0.409552246332169</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.39264389872551</v>
+        <v>0.392643928527832</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>0.429962992668152</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.409552216529846</v>
+        <v>0.409552246332169</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>0.402350008487701</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.383250087499619</v>
+        <v>0.383250057697296</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.39264389872551</v>
+        <v>0.392643928527832</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.394522279500961</v>
+        <v>0.394522309303284</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.394522279500961</v>
+        <v>0.394522309303284</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.422702848911285</v>
+        <v>0.422702878713608</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.494093030691147</v>
+        <v>0.494093000888824</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.462154716253281</v>
+        <v>0.462154686450958</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.437731862068176</v>
+        <v>0.437731891870499</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>0.44574099779129</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.424581229686737</v>
+        <v>0.424581259489059</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.437731862068176</v>
+        <v>0.437731891870499</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.422702848911285</v>
+        <v>0.422702878713608</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.419885277748108</v>
+        <v>0.41988530755043</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.394522279500961</v>
+        <v>0.394522309303284</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1298" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>0.418128997087479</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.398280024528503</v>
+        <v>0.398279994726181</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.387946963310242</v>
+        <v>0.387946993112564</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.387946963310242</v>
+        <v>0.387946993112564</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1325" t="n">
-        <v>0.39264389872551</v>
+        <v>0.392643928527832</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1332" t="n">
-        <v>0.394522279500961</v>
+        <v>0.394522309303284</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1337" t="n">
-        <v>0.39264389872551</v>
+        <v>0.392643928527832</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1339" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1341" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1343" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.387946963310242</v>
+        <v>0.387946993112564</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.394522279500961</v>
+        <v>0.394522309303284</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1353" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>0.429962992668152</v>
       </c>
       <c r="G1357" t="n">
-        <v>0.409552216529846</v>
+        <v>0.409552246332169</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>0.398405998945236</v>
       </c>
       <c r="G1363" t="n">
-        <v>0.37949326634407</v>
+        <v>0.379493296146393</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>0.398405998945236</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.37949326634407</v>
+        <v>0.379493296146393</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1368" t="n">
-        <v>0.387946963310242</v>
+        <v>0.387946993112564</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1370" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1377" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>0.402350008487701</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.383250087499619</v>
+        <v>0.383250057697296</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1385" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.364463329315186</v>
+        <v>0.364463359117508</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.360706567764282</v>
+        <v>0.36070653796196</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1391" t="n">
-        <v>0.364463329315186</v>
+        <v>0.364463359117508</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.361645758152008</v>
+        <v>0.361645728349686</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.360706567764282</v>
+        <v>0.36070653796196</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1398" t="n">
-        <v>0.364463329315186</v>
+        <v>0.364463359117508</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.364463329315186</v>
+        <v>0.364463359117508</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>0.368820995092392</v>
       </c>
       <c r="G1407" t="n">
-        <v>0.351312696933746</v>
+        <v>0.351312726736069</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.347555935382843</v>
+        <v>0.347555905580521</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1414" t="n">
-        <v>0.337222874164581</v>
+        <v>0.337222903966904</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.337222874164581</v>
+        <v>0.337222903966904</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.337222874164581</v>
+        <v>0.337222903966904</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.337222874164581</v>
+        <v>0.337222903966904</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.336283683776855</v>
+        <v>0.336283713579178</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>0.34909799695015</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.332525998353958</v>
+        <v>0.332525968551636</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.345676630735397</v>
+        <v>0.345676600933075</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.345676630735397</v>
+        <v>0.345676600933075</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.345676630735397</v>
+        <v>0.345676600933075</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1436" t="n">
-        <v>0.347555935382843</v>
+        <v>0.347555905580521</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.355070441961288</v>
+        <v>0.355070412158966</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.355070441961288</v>
+        <v>0.355070412158966</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1450" t="n">
-        <v>0.361645758152008</v>
+        <v>0.361645728349686</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.361645758152008</v>
+        <v>0.361645728349686</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.364463329315186</v>
+        <v>0.364463359117508</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1462" t="n">
-        <v>0.364463329315186</v>
+        <v>0.364463359117508</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1467" t="n">
-        <v>0.360706567764282</v>
+        <v>0.36070653796196</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.355070441961288</v>
+        <v>0.355070412158966</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.347555935382843</v>
+        <v>0.347555905580521</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1478" t="n">
-        <v>0.360706567764282</v>
+        <v>0.36070653796196</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.361645758152008</v>
+        <v>0.361645728349686</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>0.384600013494492</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.366342663764954</v>
+        <v>0.366342693567276</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>0.384600013494492</v>
       </c>
       <c r="G1485" t="n">
-        <v>0.366342663764954</v>
+        <v>0.366342693567276</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1487" t="n">
-        <v>0.361645758152008</v>
+        <v>0.361645728349686</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1488" t="n">
-        <v>0.355070441961288</v>
+        <v>0.355070412158966</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1489" t="n">
-        <v>0.355070441961288</v>
+        <v>0.355070412158966</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1490" t="n">
-        <v>0.355070441961288</v>
+        <v>0.355070412158966</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.345676630735397</v>
+        <v>0.345676600933075</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.345676630735397</v>
+        <v>0.345676600933075</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.321253746747971</v>
+        <v>0.321253776550293</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.336283683776855</v>
+        <v>0.336283713579178</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1508" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1517" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1518" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>0.319514006376266</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.30434638261795</v>
+        <v>0.304346352815628</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>0.347126007080078</v>
       </c>
       <c r="G1525" t="n">
-        <v>0.330647617578506</v>
+        <v>0.330647587776184</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1529" t="n">
-        <v>0.321253746747971</v>
+        <v>0.321253776550293</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>0.330361008644104</v>
       </c>
       <c r="G1531" t="n">
-        <v>0.314678430557251</v>
+        <v>0.314678460359573</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>0.347126007080078</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.330647617578506</v>
+        <v>0.330647587776184</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>0.333319991827011</v>
       </c>
       <c r="G1542" t="n">
-        <v>0.317496985197067</v>
+        <v>0.317496955394745</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>0.333319991827011</v>
       </c>
       <c r="G1543" t="n">
-        <v>0.317496985197067</v>
+        <v>0.317496955394745</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>0.334306001663208</v>
       </c>
       <c r="G1545" t="n">
-        <v>0.318436175584793</v>
+        <v>0.318436145782471</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>0.334306001663208</v>
       </c>
       <c r="G1546" t="n">
-        <v>0.318436175584793</v>
+        <v>0.318436145782471</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1547" t="n">
-        <v>0.309981554746628</v>
+        <v>0.309981524944305</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.309981554746628</v>
+        <v>0.309981524944305</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>0.333319991827011</v>
       </c>
       <c r="G1557" t="n">
-        <v>0.317496985197067</v>
+        <v>0.317496955394745</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>0.366849005222321</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.349434316158295</v>
+        <v>0.349434345960617</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.321253746747971</v>
+        <v>0.321253776550293</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1563" t="n">
-        <v>0.309981554746628</v>
+        <v>0.309981524944305</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>0.330361008644104</v>
       </c>
       <c r="G1569" t="n">
-        <v>0.314678430557251</v>
+        <v>0.314678460359573</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>0.330361008644104</v>
       </c>
       <c r="G1570" t="n">
-        <v>0.314678430557251</v>
+        <v>0.314678460359573</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>0.307680010795593</v>
       </c>
       <c r="G1574" t="n">
-        <v>0.293074131011963</v>
+        <v>0.293074160814285</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>0.301762998104095</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.287438035011292</v>
+        <v>0.287438005208969</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>0.304720997810364</v>
       </c>
       <c r="G1576" t="n">
-        <v>0.290255606174469</v>
+        <v>0.290255576372147</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>0.316554993391037</v>
       </c>
       <c r="G1583" t="n">
-        <v>0.301527798175812</v>
+        <v>0.301527827978134</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>0.304720997810364</v>
       </c>
       <c r="G1584" t="n">
-        <v>0.290255606174469</v>
+        <v>0.290255576372147</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1587" t="n">
-        <v>0.309981554746628</v>
+        <v>0.309981524944305</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>0.323457986116409</v>
       </c>
       <c r="G1592" t="n">
-        <v>0.308103114366531</v>
+        <v>0.308103144168854</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>0.321485996246338</v>
       </c>
       <c r="G1594" t="n">
-        <v>0.30622473359108</v>
+        <v>0.306224763393402</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>0.307680010795593</v>
       </c>
       <c r="G1604" t="n">
-        <v>0.293074131011963</v>
+        <v>0.293074160814285</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>0.307680010795593</v>
       </c>
       <c r="G1605" t="n">
-        <v>0.293074131011963</v>
+        <v>0.293074160814285</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>0.308665990829468</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.294013291597366</v>
+        <v>0.294013321399689</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>0.301762998104095</v>
       </c>
       <c r="G1607" t="n">
-        <v>0.287438035011292</v>
+        <v>0.287438005208969</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>0.34909799695015</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.332525998353958</v>
+        <v>0.332525968551636</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.321253746747971</v>
+        <v>0.321253776550293</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1617" t="n">
-        <v>0.347555935382843</v>
+        <v>0.347555905580521</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.336283683776855</v>
+        <v>0.336283713579178</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>0.363889992237091</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.346615791320801</v>
+        <v>0.346615761518478</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>0.368820995092392</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.351312696933746</v>
+        <v>0.351312726736069</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1624" t="n">
-        <v>0.364463329315186</v>
+        <v>0.364463359117508</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>0.674529016017914</v>
       </c>
       <c r="G1632" t="n">
-        <v>0.642508506774902</v>
+        <v>0.642508447170258</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>0.639028012752533</v>
       </c>
       <c r="G1634" t="n">
-        <v>0.608692765235901</v>
+        <v>0.608692705631256</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>0.611415028572083</v>
       </c>
       <c r="G1638" t="n">
-        <v>0.582390606403351</v>
+        <v>0.582390546798706</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1639" t="n">
-        <v>0.548574864864349</v>
+        <v>0.548574805259705</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1642" t="n">
-        <v>0.548574864864349</v>
+        <v>0.548574805259705</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>0.571968972682953</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.54481703042984</v>
+        <v>0.544817090034485</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>0.702140986919403</v>
       </c>
       <c r="G1655" t="n">
-        <v>0.668809711933136</v>
+        <v>0.668809652328491</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>0.615360021591187</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.586148262023926</v>
+        <v>0.586148321628571</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>0.639028012752533</v>
       </c>
       <c r="G1667" t="n">
-        <v>0.608692765235901</v>
+        <v>0.608692705631256</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>0.64691698551178</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.616207242012024</v>
+        <v>0.616207182407379</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.604934990406036</v>
+        <v>0.604935050010681</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1674" t="n">
-        <v>0.604934990406036</v>
+        <v>0.604935050010681</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>0.615360021591187</v>
       </c>
       <c r="G1682" t="n">
-        <v>0.586148262023926</v>
+        <v>0.586148321628571</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>0.583802998065948</v>
       </c>
       <c r="G1683" t="n">
-        <v>0.556089341640472</v>
+        <v>0.556089282035828</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>0.571968972682953</v>
       </c>
       <c r="G1686" t="n">
-        <v>0.54481703042984</v>
+        <v>0.544817090034485</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1689" t="n">
-        <v>0.548574864864349</v>
+        <v>0.548574805259705</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>0.595637023448944</v>
       </c>
       <c r="G1691" t="n">
-        <v>0.56736159324646</v>
+        <v>0.567361533641815</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>0.603525996208191</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.574876070022583</v>
+        <v>0.574876010417938</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>0.595637023448944</v>
       </c>
       <c r="G1697" t="n">
-        <v>0.56736159324646</v>
+        <v>0.567361533641815</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>0.607470989227295</v>
       </c>
       <c r="G1700" t="n">
-        <v>0.578633725643158</v>
+        <v>0.578633785247803</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>0.607470989227295</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.578633725643158</v>
+        <v>0.578633785247803</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.604934990406036</v>
+        <v>0.604935050010681</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>0.662694990634918</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.63123619556427</v>
+        <v>0.631236255168915</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>0.702140986919403</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.668809711933136</v>
+        <v>0.668809652328491</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1717" t="n">
-        <v>0.674445748329163</v>
+        <v>0.674445807933807</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>0.702140986919403</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.668809711933136</v>
+        <v>0.668809652328491</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1726" t="n">
-        <v>0.634993970394135</v>
+        <v>0.63499391078949</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>0.668612003326416</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.636872351169586</v>
+        <v>0.636872291564941</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1729" t="n">
-        <v>0.634993970394135</v>
+        <v>0.63499391078949</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.674445748329163</v>
+        <v>0.674445807933807</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>0.674529016017914</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.642508506774902</v>
+        <v>0.642508447170258</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1742" t="n">
-        <v>0.634993970394135</v>
+        <v>0.63499391078949</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>0.662694990634918</v>
       </c>
       <c r="G1744" t="n">
-        <v>0.63123619556427</v>
+        <v>0.631236255168915</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>0.64691698551178</v>
       </c>
       <c r="G1750" t="n">
-        <v>0.616207242012024</v>
+        <v>0.616207182407379</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>0.694252014160156</v>
       </c>
       <c r="G1755" t="n">
-        <v>0.661295235157013</v>
+        <v>0.661295175552368</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1763" t="n">
-        <v>0.634993970394135</v>
+        <v>0.63499391078949</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>0.69819700717926</v>
       </c>
       <c r="G1770" t="n">
-        <v>0.665052890777588</v>
+        <v>0.665052950382233</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>0.674529016017914</v>
       </c>
       <c r="G1790" t="n">
-        <v>0.642508506774902</v>
+        <v>0.642508447170258</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>0.694252014160156</v>
       </c>
       <c r="G1792" t="n">
-        <v>0.661295235157013</v>
+        <v>0.661295175552368</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>0.69819700717926</v>
       </c>
       <c r="G1803" t="n">
-        <v>0.665052890777588</v>
+        <v>0.665052950382233</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1809" t="n">
-        <v>0.674445748329163</v>
+        <v>0.674445807933807</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>0.706085979938507</v>
       </c>
       <c r="G1810" t="n">
-        <v>0.672567367553711</v>
+        <v>0.672567427158356</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.674445748329163</v>
+        <v>0.674445807933807</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>0.733698010444641</v>
       </c>
       <c r="G1824" t="n">
-        <v>0.698868632316589</v>
+        <v>0.698868691921234</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>0.729753971099854</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.695111870765686</v>
+        <v>0.695111811161041</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>0.745531976222992</v>
       </c>
       <c r="G1829" t="n">
-        <v>0.710140883922577</v>
+        <v>0.710140824317932</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>0.745531976222992</v>
       </c>
       <c r="G1830" t="n">
-        <v>0.710140883922577</v>
+        <v>0.710140824317932</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1832" t="n">
-        <v>0.71202027797699</v>
+        <v>0.712020218372345</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1834" t="n">
-        <v>0.71202027797699</v>
+        <v>0.712020218372345</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G1835" t="n">
-        <v>0.702626407146454</v>
+        <v>0.702626347541809</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.702626407146454</v>
+        <v>0.702626347541809</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G1837" t="n">
-        <v>0.702626407146454</v>
+        <v>0.702626347541809</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1839" t="n">
-        <v>0.71202027797699</v>
+        <v>0.712020218372345</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.71202027797699</v>
+        <v>0.712020218372345</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>0.796811997890472</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.758986532688141</v>
+        <v>0.758986592292786</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>0.942762970924377</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.898009061813354</v>
+        <v>0.898009121417999</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1861" t="n">
-        <v>1.08963513374329</v>
+        <v>1.089635014534</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>1.10449194908142</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.05206060409546</v>
+        <v>1.05206072330475</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.08963513374329</v>
+        <v>1.089635014534</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>1.10449194908142</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.05206060409546</v>
+        <v>1.05206072330475</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.08963513374329</v>
+        <v>1.089635014534</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>1.15873098373413</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.10372495651245</v>
+        <v>1.10372483730316</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.08963513374329</v>
+        <v>1.089635014534</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>1.15873098373413</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.10372495651245</v>
+        <v>1.10372483730316</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>1.2179000377655</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.16008508205414</v>
+        <v>1.16008520126343</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.20705235004425</v>
+        <v>1.20705246925354</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>1.25734603404999</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.19765865802765</v>
+        <v>1.19765853881836</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.20705235004425</v>
+        <v>1.20705246925354</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>1.27213895320892</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.21174919605255</v>
+        <v>1.21174931526184</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49977,7 +49977,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.20705235004425</v>
+        <v>1.20705246925354</v>
       </c>
       <c r="H1908" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.24932265281677</v>
+        <v>1.24932277202606</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.3197728395462</v>
+        <v>1.31977272033691</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.3338634967804</v>
+        <v>1.33386361598969</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.30568301677704</v>
+        <v>1.30568289756775</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.23523306846619</v>
+        <v>1.2352329492569</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50601,7 +50601,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G1932" t="n">
-        <v>1.24932265281677</v>
+        <v>1.24932277202606</v>
       </c>
       <c r="H1932" t="s">
         <v>8</v>
@@ -71285,7 +71285,7 @@
         <v>1000</v>
       </c>
       <c r="C2728" t="n">
-        <v>3.11999988555908</v>
+        <v>3.17000007629395</v>
       </c>
       <c r="D2728" t="n">
         <v>3.11999988555908</v>
@@ -71300,6 +71300,32 @@
         <v>3.17000007629395</v>
       </c>
       <c r="H2728" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>62000</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G2729" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="H2729" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -421,7 +421,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G2" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G3" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G5" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G6" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.90521001815796</v>
       </c>
       <c r="G32" t="n">
-        <v>2.76729702949524</v>
+        <v>2.76729679107666</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>2.85984706878662</v>
       </c>
       <c r="G34" t="n">
-        <v>2.72408723831177</v>
+        <v>2.72408747673035</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>2.90718293190002</v>
       </c>
       <c r="G37" t="n">
-        <v>2.76917624473572</v>
+        <v>2.76917600631714</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>2.90718293190002</v>
       </c>
       <c r="G38" t="n">
-        <v>2.76917624473572</v>
+        <v>2.76917600631714</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>2.90718293190002</v>
       </c>
       <c r="G39" t="n">
-        <v>2.76917624473572</v>
+        <v>2.76917600631714</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G45" t="n">
-        <v>2.66772723197937</v>
+        <v>2.66772699356079</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G124" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G125" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G126" t="n">
-        <v>2.66772723197937</v>
+        <v>2.66772699356079</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G127" t="n">
-        <v>2.66772723197937</v>
+        <v>2.66772699356079</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G128" t="n">
-        <v>2.66772723197937</v>
+        <v>2.66772699356079</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G129" t="n">
-        <v>2.66772723197937</v>
+        <v>2.66772699356079</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G130" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.72967505455017</v>
       </c>
       <c r="G131" t="n">
-        <v>2.60009479522705</v>
+        <v>2.60009455680847</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.72967505455017</v>
       </c>
       <c r="G132" t="n">
-        <v>2.60009479522705</v>
+        <v>2.60009455680847</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G133" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G136" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G137" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G138" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G139" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G140" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G141" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G142" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.58372402191162</v>
       </c>
       <c r="G143" t="n">
-        <v>2.46107220649719</v>
+        <v>2.46107196807861</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.58372402191162</v>
       </c>
       <c r="G144" t="n">
-        <v>2.46107220649719</v>
+        <v>2.46107196807861</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>2.48905301094055</v>
       </c>
       <c r="G145" t="n">
-        <v>2.37089514732361</v>
+        <v>2.37089538574219</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.48905301094055</v>
       </c>
       <c r="G146" t="n">
-        <v>2.37089514732361</v>
+        <v>2.37089538574219</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.35690808296204</v>
       </c>
       <c r="G148" t="n">
-        <v>2.24502348899841</v>
+        <v>2.24502325057983</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G154" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G155" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G156" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G157" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G158" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G159" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.56400108337402</v>
       </c>
       <c r="G173" t="n">
-        <v>2.44228529930115</v>
+        <v>2.44228553771973</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.58372402191162</v>
       </c>
       <c r="G181" t="n">
-        <v>2.46107220649719</v>
+        <v>2.46107196807861</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.56400108337402</v>
       </c>
       <c r="G202" t="n">
-        <v>2.44228529930115</v>
+        <v>2.44228553771973</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>2.56991791725159</v>
       </c>
       <c r="G203" t="n">
-        <v>2.44792127609253</v>
+        <v>2.44792151451111</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G205" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G206" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G207" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G208" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G209" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G210" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.46144104003906</v>
       </c>
       <c r="G214" t="n">
-        <v>2.3445942401886</v>
+        <v>2.34459400177002</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G237" t="n">
-        <v>2.20744967460632</v>
+        <v>2.2074499130249</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G238" t="n">
-        <v>2.20744967460632</v>
+        <v>2.2074499130249</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G239" t="n">
-        <v>2.20744967460632</v>
+        <v>2.2074499130249</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G240" t="n">
-        <v>2.20744967460632</v>
+        <v>2.2074499130249</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G241" t="n">
-        <v>2.20744967460632</v>
+        <v>2.2074499130249</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.36874198913574</v>
       </c>
       <c r="G255" t="n">
-        <v>2.25629568099976</v>
+        <v>2.25629544258118</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.17151093482971</v>
       </c>
       <c r="G259" t="n">
-        <v>2.06842732429504</v>
+        <v>2.06842708587646</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.09853601455688</v>
       </c>
       <c r="G260" t="n">
-        <v>1.99891650676727</v>
+        <v>1.99891638755798</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G262" t="n">
-        <v>2.08345723152161</v>
+        <v>2.08345699310303</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G263" t="n">
-        <v>2.08345723152161</v>
+        <v>2.08345699310303</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G264" t="n">
-        <v>2.08345723152161</v>
+        <v>2.08345699310303</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G265" t="n">
-        <v>2.08345723152161</v>
+        <v>2.08345699310303</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G266" t="n">
-        <v>2.01958131790161</v>
+        <v>2.01958155632019</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G267" t="n">
-        <v>2.01958131790161</v>
+        <v>2.01958155632019</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G280" t="n">
-        <v>2.01958131790161</v>
+        <v>2.01958155632019</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G281" t="n">
-        <v>2.01958131790161</v>
+        <v>2.01958155632019</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G282" t="n">
-        <v>2.01958131790161</v>
+        <v>2.01958155632019</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G283" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G284" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G285" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.18531799316406</v>
       </c>
       <c r="G305" t="n">
-        <v>2.08157896995544</v>
+        <v>2.08157873153687</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>1.98216998577118</v>
       </c>
       <c r="G308" t="n">
-        <v>1.88807451725006</v>
+        <v>1.88807439804077</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>1.94272398948669</v>
       </c>
       <c r="G309" t="n">
-        <v>1.85050106048584</v>
+        <v>1.85050094127655</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.15770506858826</v>
       </c>
       <c r="G326" t="n">
-        <v>2.05527663230896</v>
+        <v>2.05527687072754</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.18926191329956</v>
       </c>
       <c r="G332" t="n">
-        <v>2.08533573150635</v>
+        <v>2.08533549308777</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.18926191329956</v>
       </c>
       <c r="G333" t="n">
-        <v>2.08533573150635</v>
+        <v>2.08533549308777</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G340" t="n">
-        <v>2.02521753311157</v>
+        <v>2.02521777153015</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G344" t="n">
-        <v>2.02521753311157</v>
+        <v>2.02521777153015</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G345" t="n">
-        <v>2.02521753311157</v>
+        <v>2.02521777153015</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G346" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G347" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.00189304351807</v>
       </c>
       <c r="G365" t="n">
-        <v>1.90686118602753</v>
+        <v>1.90686130523682</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.71981310844421</v>
       </c>
       <c r="G368" t="n">
-        <v>2.59070110321045</v>
+        <v>2.59070086479187</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.41607809066772</v>
       </c>
       <c r="G369" t="n">
-        <v>2.30138444900513</v>
+        <v>2.30138468742371</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.25829291343689</v>
       </c>
       <c r="G370" t="n">
-        <v>2.15108966827393</v>
+        <v>2.15108942985535</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.17940092086792</v>
       </c>
       <c r="G374" t="n">
-        <v>2.07594275474548</v>
+        <v>2.0759425163269</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.17940092086792</v>
       </c>
       <c r="G376" t="n">
-        <v>2.07594275474548</v>
+        <v>2.0759425163269</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.20701289176941</v>
       </c>
       <c r="G378" t="n">
-        <v>2.10224366188049</v>
+        <v>2.10224390029907</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>2.44369006156921</v>
       </c>
       <c r="G383" t="n">
-        <v>2.32768583297729</v>
+        <v>2.32768559455872</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>2.30957293510437</v>
       </c>
       <c r="G384" t="n">
-        <v>2.1999351978302</v>
+        <v>2.19993543624878</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>2.3628249168396</v>
       </c>
       <c r="G393" t="n">
-        <v>2.25065946578979</v>
+        <v>2.25065922737122</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>2.27604389190674</v>
       </c>
       <c r="G395" t="n">
-        <v>2.16799807548523</v>
+        <v>2.16799783706665</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.10445308685303</v>
       </c>
       <c r="G398" t="n">
-        <v>2.00455284118652</v>
+        <v>2.00455260276794</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.0472559928894</v>
       </c>
       <c r="G399" t="n">
-        <v>1.95007061958313</v>
+        <v>1.95007073879242</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.19123506546021</v>
       </c>
       <c r="G401" t="n">
-        <v>2.08721518516541</v>
+        <v>2.08721494674683</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G402" t="n">
-        <v>2.02521753311157</v>
+        <v>2.02521777153015</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.10839796066284</v>
       </c>
       <c r="G403" t="n">
-        <v>2.00831007957458</v>
+        <v>2.00831031799316</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G406" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.00189304351807</v>
       </c>
       <c r="G416" t="n">
-        <v>1.90686118602753</v>
+        <v>1.90686130523682</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>1.98019802570343</v>
       </c>
       <c r="G417" t="n">
-        <v>1.88619613647461</v>
+        <v>1.88619601726532</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.00189304351807</v>
       </c>
       <c r="G418" t="n">
-        <v>1.90686118602753</v>
+        <v>1.90686130523682</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>2.03936696052551</v>
       </c>
       <c r="G419" t="n">
-        <v>1.94255614280701</v>
+        <v>1.9425562620163</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.03936696052551</v>
       </c>
       <c r="G420" t="n">
-        <v>1.94255614280701</v>
+        <v>1.9425562620163</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>1.98808705806732</v>
       </c>
       <c r="G421" t="n">
-        <v>1.89371073246002</v>
+        <v>1.89371061325073</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.03936696052551</v>
       </c>
       <c r="G422" t="n">
-        <v>1.94255614280701</v>
+        <v>1.9425562620163</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.01569890975952</v>
       </c>
       <c r="G423" t="n">
-        <v>1.92001175880432</v>
+        <v>1.92001163959503</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>1.98019802570343</v>
       </c>
       <c r="G428" t="n">
-        <v>1.88619613647461</v>
+        <v>1.88619601726532</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>1.98019802570343</v>
       </c>
       <c r="G429" t="n">
-        <v>1.88619613647461</v>
+        <v>1.88619601726532</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>1.91313898563385</v>
       </c>
       <c r="G434" t="n">
-        <v>1.8223203420639</v>
+        <v>1.82232046127319</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>1.87960994243622</v>
       </c>
       <c r="G435" t="n">
-        <v>1.79038298130035</v>
+        <v>1.79038310050964</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>1.85397005081177</v>
       </c>
       <c r="G439" t="n">
-        <v>1.76596033573151</v>
+        <v>1.76596021652222</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>1.85791397094727</v>
       </c>
       <c r="G441" t="n">
-        <v>1.76971709728241</v>
+        <v>1.76971697807312</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>1.77507698535919</v>
       </c>
       <c r="G445" t="n">
-        <v>1.69081246852875</v>
+        <v>1.69081234931946</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>1.77507698535919</v>
       </c>
       <c r="G446" t="n">
-        <v>1.69081246852875</v>
+        <v>1.69081234931946</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>1.53840005397797</v>
       </c>
       <c r="G451" t="n">
-        <v>1.4653707742691</v>
+        <v>1.46537065505981</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G454" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>1.82241296768188</v>
       </c>
       <c r="G456" t="n">
-        <v>1.73590123653412</v>
+        <v>1.73590135574341</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>1.47528600692749</v>
       </c>
       <c r="G466" t="n">
-        <v>1.40525269508362</v>
+        <v>1.40525281429291</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>1.50684297084808</v>
       </c>
       <c r="G468" t="n">
-        <v>1.43531179428101</v>
+        <v>1.43531167507172</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G469" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G474" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>1.48909294605255</v>
       </c>
       <c r="G475" t="n">
-        <v>1.41840434074402</v>
+        <v>1.41840422153473</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>1.54431700706482</v>
       </c>
       <c r="G477" t="n">
-        <v>1.47100687026978</v>
+        <v>1.47100675106049</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G478" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>1.48909294605255</v>
       </c>
       <c r="G479" t="n">
-        <v>1.41840434074402</v>
+        <v>1.41840422153473</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>1.49205100536346</v>
       </c>
       <c r="G488" t="n">
-        <v>1.42122197151184</v>
+        <v>1.42122185230255</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>1.53840005397797</v>
       </c>
       <c r="G489" t="n">
-        <v>1.4653707742691</v>
+        <v>1.46537065505981</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G490" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G492" t="n">
-        <v>1.44658386707306</v>
+        <v>1.44658398628235</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G493" t="n">
-        <v>1.44658386707306</v>
+        <v>1.44658398628235</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>1.54234504699707</v>
       </c>
       <c r="G494" t="n">
-        <v>1.46912848949432</v>
+        <v>1.46912837028503</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>1.55615103244781</v>
       </c>
       <c r="G498" t="n">
-        <v>1.48227894306183</v>
+        <v>1.48227906227112</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G499" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>1.55220699310303</v>
       </c>
       <c r="G501" t="n">
-        <v>1.47852218151093</v>
+        <v>1.47852230072021</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>1.50684297084808</v>
       </c>
       <c r="G502" t="n">
-        <v>1.43531179428101</v>
+        <v>1.43531167507172</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G504" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>1.44175696372986</v>
       </c>
       <c r="G505" t="n">
-        <v>1.37331533432007</v>
+        <v>1.37331545352936</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>1.4013249874115</v>
       </c>
       <c r="G507" t="n">
-        <v>1.33480274677277</v>
+        <v>1.33480262756348</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G508" t="n">
-        <v>1.33386361598969</v>
+        <v>1.3338634967804</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G515" t="n">
-        <v>1.33386361598969</v>
+        <v>1.3338634967804</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G520" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>1.48909294605255</v>
       </c>
       <c r="G521" t="n">
-        <v>1.41840434074402</v>
+        <v>1.41840422153473</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>1.5531929731369</v>
       </c>
       <c r="G524" t="n">
-        <v>1.47946131229401</v>
+        <v>1.4794614315033</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G526" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G527" t="n">
-        <v>1.44658386707306</v>
+        <v>1.44658398628235</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>1.5531929731369</v>
       </c>
       <c r="G529" t="n">
-        <v>1.47946131229401</v>
+        <v>1.4794614315033</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G533" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G535" t="n">
-        <v>1.44658386707306</v>
+        <v>1.44658398628235</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G538" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G539" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G543" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G544" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G546" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G547" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G548" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G555" t="n">
-        <v>1.30568289756775</v>
+        <v>1.30568301677704</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G561" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G567" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G568" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G576" t="n">
-        <v>1.29629015922546</v>
+        <v>1.29629004001617</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G577" t="n">
-        <v>1.31977272033691</v>
+        <v>1.3197728395462</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G579" t="n">
-        <v>1.31977272033691</v>
+        <v>1.3197728395462</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G591" t="n">
-        <v>1.29629015922546</v>
+        <v>1.29629004001617</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G597" t="n">
-        <v>1.31977272033691</v>
+        <v>1.3197728395462</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G603" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G604" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G607" t="n">
-        <v>1.2352329492569</v>
+        <v>1.23523306846619</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G611" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G612" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G614" t="n">
-        <v>1.20705246925354</v>
+        <v>1.20705235004425</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G621" t="n">
-        <v>1.30568289756775</v>
+        <v>1.30568301677704</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G630" t="n">
-        <v>1.30568289756775</v>
+        <v>1.30568301677704</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G635" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>1.85397005081177</v>
       </c>
       <c r="G638" t="n">
-        <v>1.76596033573151</v>
+        <v>1.76596021652222</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G645" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>1.56798505783081</v>
       </c>
       <c r="G652" t="n">
-        <v>1.49355125427246</v>
+        <v>1.49355137348175</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G656" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G658" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G660" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G662" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G663" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G664" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G665" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G668" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G669" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G670" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G671" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G673" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G676" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G679" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G680" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G685" t="n">
-        <v>1.29629015922546</v>
+        <v>1.29629004001617</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G686" t="n">
-        <v>1.29629015922546</v>
+        <v>1.29629004001617</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G691" t="n">
-        <v>1.33386361598969</v>
+        <v>1.3338634967804</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G694" t="n">
-        <v>1.33386361598969</v>
+        <v>1.3338634967804</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G696" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G700" t="n">
-        <v>1.30568289756775</v>
+        <v>1.30568301677704</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G701" t="n">
-        <v>1.2352329492569</v>
+        <v>1.23523306846619</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G702" t="n">
-        <v>1.2352329492569</v>
+        <v>1.23523306846619</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.2179000377655</v>
       </c>
       <c r="G707" t="n">
-        <v>1.16008520126343</v>
+        <v>1.16008508205414</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G712" t="n">
-        <v>1.089635014534</v>
+        <v>1.08963513374329</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>1.17845404148102</v>
       </c>
       <c r="G714" t="n">
-        <v>1.12251174449921</v>
+        <v>1.12251162528992</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.12914597988129</v>
       </c>
       <c r="G716" t="n">
-        <v>1.0755443572998</v>
+        <v>1.07554423809052</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.01573896408081</v>
       </c>
       <c r="G719" t="n">
-        <v>0.967520892620087</v>
+        <v>0.967520833015442</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.11435401439667</v>
       </c>
       <c r="G723" t="n">
-        <v>1.06145453453064</v>
+        <v>1.06145465373993</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>1.10449194908142</v>
       </c>
       <c r="G724" t="n">
-        <v>1.05206072330475</v>
+        <v>1.05206060409546</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>0.938817977905273</v>
       </c>
       <c r="G739" t="n">
-        <v>0.894251346588135</v>
+        <v>0.89425140619278</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>0.938817977905273</v>
       </c>
       <c r="G740" t="n">
-        <v>0.894251346588135</v>
+        <v>0.89425140619278</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>0.926985025405884</v>
       </c>
       <c r="G742" t="n">
-        <v>0.882980167865753</v>
+        <v>0.882980108261108</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G743" t="n">
-        <v>0.911159813404083</v>
+        <v>0.911159753799438</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G744" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G748" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G753" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>0.926985025405884</v>
       </c>
       <c r="G755" t="n">
-        <v>0.882980167865753</v>
+        <v>0.882980108261108</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>0.867815017700195</v>
       </c>
       <c r="G757" t="n">
-        <v>0.826619029045105</v>
+        <v>0.82661896944046</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>0.887538015842438</v>
       </c>
       <c r="G758" t="n">
-        <v>0.845405757427216</v>
+        <v>0.845405697822571</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>0.879648983478546</v>
       </c>
       <c r="G759" t="n">
-        <v>0.837891221046448</v>
+        <v>0.837891161441803</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>0.887538015842438</v>
       </c>
       <c r="G760" t="n">
-        <v>0.845405757427216</v>
+        <v>0.845405697822571</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G770" t="n">
-        <v>0.911159813404083</v>
+        <v>0.911159753799438</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G775" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G777" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G778" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G779" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G780" t="n">
-        <v>0.911159813404083</v>
+        <v>0.911159753799438</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>0.942762970924377</v>
       </c>
       <c r="G781" t="n">
-        <v>0.898009121417999</v>
+        <v>0.898009061813354</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>0.938817977905273</v>
       </c>
       <c r="G787" t="n">
-        <v>0.894251346588135</v>
+        <v>0.89425140619278</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>1.01573896408081</v>
       </c>
       <c r="G789" t="n">
-        <v>0.967520892620087</v>
+        <v>0.967520833015442</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>0.962486028671265</v>
       </c>
       <c r="G790" t="n">
-        <v>0.91679584980011</v>
+        <v>0.916795909404755</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G791" t="n">
-        <v>0.911159813404083</v>
+        <v>0.911159753799438</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>1.09956204891205</v>
       </c>
       <c r="G804" t="n">
-        <v>1.04736471176147</v>
+        <v>1.04736483097076</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G823" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G824" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G826" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>0.972347974777222</v>
       </c>
       <c r="G828" t="n">
-        <v>0.926189720630646</v>
+        <v>0.926189661026001</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>0.978264987468719</v>
       </c>
       <c r="G829" t="n">
-        <v>0.931825757026672</v>
+        <v>0.931825816631317</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>1.04039204120636</v>
       </c>
       <c r="G836" t="n">
-        <v>0.991003632545471</v>
+        <v>0.991003572940826</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>1.01573896408081</v>
       </c>
       <c r="G839" t="n">
-        <v>0.967520892620087</v>
+        <v>0.967520833015442</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>0.99108499288559</v>
       </c>
       <c r="G840" t="n">
-        <v>0.944037258625031</v>
+        <v>0.944037199020386</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>0.982209026813507</v>
       </c>
       <c r="G842" t="n">
-        <v>0.93558257818222</v>
+        <v>0.935582637786865</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>0.982209026813507</v>
       </c>
       <c r="G843" t="n">
-        <v>0.93558257818222</v>
+        <v>0.935582637786865</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>0.99108499288559</v>
       </c>
       <c r="G845" t="n">
-        <v>0.944037258625031</v>
+        <v>0.944037199020386</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G853" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G855" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>0.982209026813507</v>
       </c>
       <c r="G856" t="n">
-        <v>0.93558257818222</v>
+        <v>0.935582637786865</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G857" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>0.978264987468719</v>
       </c>
       <c r="G863" t="n">
-        <v>0.931825757026672</v>
+        <v>0.931825816631317</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>0.978264987468719</v>
       </c>
       <c r="G864" t="n">
-        <v>0.931825757026672</v>
+        <v>0.931825816631317</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>0.950652003288269</v>
       </c>
       <c r="G867" t="n">
-        <v>0.905523657798767</v>
+        <v>0.905523598194122</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>0.90923398733139</v>
       </c>
       <c r="G873" t="n">
-        <v>0.866071760654449</v>
+        <v>0.866071820259094</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>0.915151000022888</v>
       </c>
       <c r="G874" t="n">
-        <v>0.871707856655121</v>
+        <v>0.871707916259766</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G878" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>0.769200026988983</v>
       </c>
       <c r="G879" t="n">
-        <v>0.732685387134552</v>
+        <v>0.732685327529907</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>0.769200026988983</v>
       </c>
       <c r="G880" t="n">
-        <v>0.732685387134552</v>
+        <v>0.732685327529907</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G884" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G886" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G888" t="n">
-        <v>0.723291456699371</v>
+        <v>0.723291516304016</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>0.745531976222992</v>
       </c>
       <c r="G889" t="n">
-        <v>0.710140824317932</v>
+        <v>0.710140883922577</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G890" t="n">
-        <v>0.723291456699371</v>
+        <v>0.723291516304016</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G891" t="n">
-        <v>0.723291456699371</v>
+        <v>0.723291516304016</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>0.77708899974823</v>
       </c>
       <c r="G893" t="n">
-        <v>0.740199863910675</v>
+        <v>0.74019980430603</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G896" t="n">
-        <v>0.723291456699371</v>
+        <v>0.723291516304016</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>0.729753971099854</v>
       </c>
       <c r="G898" t="n">
-        <v>0.695111811161041</v>
+        <v>0.695111870765686</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G899" t="n">
-        <v>0.702626347541809</v>
+        <v>0.702626407146454</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G904" t="n">
-        <v>0.548574805259705</v>
+        <v>0.548574864864349</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>0.508854985237122</v>
       </c>
       <c r="G907" t="n">
-        <v>0.484699130058289</v>
+        <v>0.484699159860611</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>0.492091000080109</v>
       </c>
       <c r="G912" t="n">
-        <v>0.468730956315994</v>
+        <v>0.468730986118317</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>0.492091000080109</v>
       </c>
       <c r="G913" t="n">
-        <v>0.468730956315994</v>
+        <v>0.468730986118317</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G918" t="n">
-        <v>0.432096689939499</v>
+        <v>0.432096719741821</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G920" t="n">
-        <v>0.418945103883743</v>
+        <v>0.418945133686066</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>0.481243014335632</v>
       </c>
       <c r="G922" t="n">
-        <v>0.458397924900055</v>
+        <v>0.458397954702377</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>0.44574099779129</v>
       </c>
       <c r="G925" t="n">
-        <v>0.424581259489059</v>
+        <v>0.424581229686737</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>0.449685990810394</v>
       </c>
       <c r="G927" t="n">
-        <v>0.428338944911957</v>
+        <v>0.428338974714279</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G930" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>0.469408988952637</v>
       </c>
       <c r="G931" t="n">
-        <v>0.447125673294067</v>
+        <v>0.44712570309639</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G938" t="n">
-        <v>0.494093000888824</v>
+        <v>0.494093030691147</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G939" t="n">
-        <v>0.494093000888824</v>
+        <v>0.494093030691147</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G940" t="n">
-        <v>0.494093000888824</v>
+        <v>0.494093030691147</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>0.506883025169373</v>
       </c>
       <c r="G943" t="n">
-        <v>0.482820808887482</v>
+        <v>0.482820779085159</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>0.489131987094879</v>
       </c>
       <c r="G948" t="n">
-        <v>0.4659124314785</v>
+        <v>0.465912401676178</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G954" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G955" t="n">
-        <v>0.41988530755043</v>
+        <v>0.419885277748108</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G961" t="n">
-        <v>0.437731891870499</v>
+        <v>0.437731862068176</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G963" t="n">
-        <v>0.462154686450958</v>
+        <v>0.462154716253281</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G978" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G981" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G983" t="n">
-        <v>0.432096689939499</v>
+        <v>0.432096719741821</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>0.469408988952637</v>
       </c>
       <c r="G987" t="n">
-        <v>0.447125673294067</v>
+        <v>0.44712570309639</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G990" t="n">
-        <v>0.432096689939499</v>
+        <v>0.432096719741821</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G991" t="n">
-        <v>0.432096689939499</v>
+        <v>0.432096719741821</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G992" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G993" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G994" t="n">
-        <v>0.41988530755043</v>
+        <v>0.419885277748108</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G995" t="n">
-        <v>0.418945103883743</v>
+        <v>0.418945133686066</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>0.449685990810394</v>
       </c>
       <c r="G996" t="n">
-        <v>0.428338944911957</v>
+        <v>0.428338974714279</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G997" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>0.55224597454071</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.526030361652374</v>
+        <v>0.526030302047729</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>0.603525996208191</v>
       </c>
       <c r="G1006" t="n">
-        <v>0.574876010417938</v>
+        <v>0.574876070022583</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>0.694252014160156</v>
       </c>
       <c r="G1008" t="n">
-        <v>0.661295175552368</v>
+        <v>0.661295235157013</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>0.639028012752533</v>
       </c>
       <c r="G1012" t="n">
-        <v>0.608692705631256</v>
+        <v>0.608692765235901</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.63499391078949</v>
+        <v>0.634993970394135</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1017" t="n">
-        <v>0.604935050010681</v>
+        <v>0.604934990406036</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>0.611415028572083</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.582390546798706</v>
+        <v>0.582390606403351</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>0.765254974365234</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.728927552700043</v>
+        <v>0.728927612304688</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>0.706085979938507</v>
       </c>
       <c r="G1031" t="n">
-        <v>0.672567427158356</v>
+        <v>0.672567367553711</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>0.668612003326416</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.636872291564941</v>
+        <v>0.636872351169586</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>0.69819700717926</v>
       </c>
       <c r="G1043" t="n">
-        <v>0.665052950382233</v>
+        <v>0.665052890777588</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>0.550274014472961</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.524151921272278</v>
+        <v>0.524151980876923</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>0.571968972682953</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.544817090034485</v>
+        <v>0.54481703042984</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>0.55224597454071</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.526030361652374</v>
+        <v>0.526030302047729</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>0.520689010620117</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.495971381664276</v>
+        <v>0.495971411466599</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>0.36191800236702</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.344737410545349</v>
+        <v>0.344737380743027</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>0.318527013063431</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.303406208753586</v>
+        <v>0.303406238555908</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.309981524944305</v>
+        <v>0.309981554746628</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>0.400377988815308</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.381371676921844</v>
+        <v>0.381371647119522</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>0.384600013494492</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.366342693567276</v>
+        <v>0.366342663764954</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.336283713579178</v>
+        <v>0.336283683776855</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1103" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1106" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>0.369807004928589</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.352251917123795</v>
+        <v>0.352251887321472</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.432096689939499</v>
+        <v>0.432096719741821</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.392643928527832</v>
+        <v>0.39264389872551</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>0.398405998945236</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.379493296146393</v>
+        <v>0.37949326634407</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>0.475326001644135</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.452761828899384</v>
+        <v>0.452761799097061</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>0.484201014041901</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.461215525865555</v>
+        <v>0.461215496063232</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G1135" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G1137" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.462154686450958</v>
+        <v>0.462154716253281</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>0.475326001644135</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.452761828899384</v>
+        <v>0.452761799097061</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1141" t="n">
-        <v>0.437731891870499</v>
+        <v>0.437731862068176</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1143" t="n">
-        <v>0.548574805259705</v>
+        <v>0.548574864864349</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>0.524634003639221</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.499729126691818</v>
+        <v>0.499729096889496</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.462154686450958</v>
+        <v>0.462154716253281</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>0.489131987094879</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.4659124314785</v>
+        <v>0.465912401676178</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.437731891870499</v>
+        <v>0.437731862068176</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>0.449685990810394</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.428338944911957</v>
+        <v>0.428338974714279</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.41988530755043</v>
+        <v>0.419885277748108</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.418945103883743</v>
+        <v>0.418945133686066</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.418945103883743</v>
+        <v>0.418945133686066</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.418945103883743</v>
+        <v>0.418945133686066</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>0.429962992668152</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.409552246332169</v>
+        <v>0.409552216529846</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.392643928527832</v>
+        <v>0.39264389872551</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>0.429962992668152</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.409552246332169</v>
+        <v>0.409552216529846</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>0.402350008487701</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.383250057697296</v>
+        <v>0.383250087499619</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.392643928527832</v>
+        <v>0.39264389872551</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.494093000888824</v>
+        <v>0.494093030691147</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.462154686450958</v>
+        <v>0.462154716253281</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.437731891870499</v>
+        <v>0.437731862068176</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>0.44574099779129</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.424581259489059</v>
+        <v>0.424581229686737</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.437731891870499</v>
+        <v>0.437731862068176</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.41988530755043</v>
+        <v>0.419885277748108</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1298" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>0.418128997087479</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.398279994726181</v>
+        <v>0.398280024528503</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1325" t="n">
-        <v>0.392643928527832</v>
+        <v>0.39264389872551</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1332" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1337" t="n">
-        <v>0.392643928527832</v>
+        <v>0.39264389872551</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1339" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1341" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1343" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1353" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>0.429962992668152</v>
       </c>
       <c r="G1357" t="n">
-        <v>0.409552246332169</v>
+        <v>0.409552216529846</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>0.398405998945236</v>
       </c>
       <c r="G1363" t="n">
-        <v>0.379493296146393</v>
+        <v>0.37949326634407</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>0.398405998945236</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.379493296146393</v>
+        <v>0.37949326634407</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1368" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1370" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1377" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>0.402350008487701</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.383250057697296</v>
+        <v>0.383250087499619</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1385" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.36070653796196</v>
+        <v>0.360706567764282</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1391" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.361645728349686</v>
+        <v>0.361645758152008</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.36070653796196</v>
+        <v>0.360706567764282</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1398" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>0.368820995092392</v>
       </c>
       <c r="G1407" t="n">
-        <v>0.351312726736069</v>
+        <v>0.351312696933746</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.347555905580521</v>
+        <v>0.347555935382843</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1414" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.336283713579178</v>
+        <v>0.336283683776855</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>0.34909799695015</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.332525968551636</v>
+        <v>0.332525998353958</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1436" t="n">
-        <v>0.347555905580521</v>
+        <v>0.347555935382843</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1450" t="n">
-        <v>0.361645728349686</v>
+        <v>0.361645758152008</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.361645728349686</v>
+        <v>0.361645758152008</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1462" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1467" t="n">
-        <v>0.36070653796196</v>
+        <v>0.360706567764282</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.347555905580521</v>
+        <v>0.347555935382843</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1478" t="n">
-        <v>0.36070653796196</v>
+        <v>0.360706567764282</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.361645728349686</v>
+        <v>0.361645758152008</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>0.384600013494492</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.366342693567276</v>
+        <v>0.366342663764954</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>0.384600013494492</v>
       </c>
       <c r="G1485" t="n">
-        <v>0.366342693567276</v>
+        <v>0.366342663764954</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1487" t="n">
-        <v>0.361645728349686</v>
+        <v>0.361645758152008</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1488" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1489" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1490" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.321253776550293</v>
+        <v>0.321253746747971</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.336283713579178</v>
+        <v>0.336283683776855</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1508" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1517" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1518" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>0.319514006376266</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.304346352815628</v>
+        <v>0.30434638261795</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40019,7 +40019,7 @@
         <v>0.347126007080078</v>
       </c>
       <c r="G1525" t="n">
-        <v>0.330647587776184</v>
+        <v>0.330647617578506</v>
       </c>
       <c r="H1525" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1529" t="n">
-        <v>0.321253776550293</v>
+        <v>0.321253746747971</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>0.330361008644104</v>
       </c>
       <c r="G1531" t="n">
-        <v>0.314678460359573</v>
+        <v>0.314678430557251</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>0.347126007080078</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.330647587776184</v>
+        <v>0.330647617578506</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>0.333319991827011</v>
       </c>
       <c r="G1542" t="n">
-        <v>0.317496955394745</v>
+        <v>0.317496985197067</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>0.333319991827011</v>
       </c>
       <c r="G1543" t="n">
-        <v>0.317496955394745</v>
+        <v>0.317496985197067</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>0.334306001663208</v>
       </c>
       <c r="G1545" t="n">
-        <v>0.318436145782471</v>
+        <v>0.318436175584793</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>0.334306001663208</v>
       </c>
       <c r="G1546" t="n">
-        <v>0.318436145782471</v>
+        <v>0.318436175584793</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1547" t="n">
-        <v>0.309981524944305</v>
+        <v>0.309981554746628</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.309981524944305</v>
+        <v>0.309981554746628</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>0.333319991827011</v>
       </c>
       <c r="G1557" t="n">
-        <v>0.317496955394745</v>
+        <v>0.317496985197067</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>0.366849005222321</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.349434345960617</v>
+        <v>0.349434316158295</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.321253776550293</v>
+        <v>0.321253746747971</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1563" t="n">
-        <v>0.309981524944305</v>
+        <v>0.309981554746628</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>0.330361008644104</v>
       </c>
       <c r="G1569" t="n">
-        <v>0.314678460359573</v>
+        <v>0.314678430557251</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>0.330361008644104</v>
       </c>
       <c r="G1570" t="n">
-        <v>0.314678460359573</v>
+        <v>0.314678430557251</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>0.307680010795593</v>
       </c>
       <c r="G1574" t="n">
-        <v>0.293074160814285</v>
+        <v>0.293074131011963</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>0.301762998104095</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.287438005208969</v>
+        <v>0.287438035011292</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41345,7 +41345,7 @@
         <v>0.304720997810364</v>
       </c>
       <c r="G1576" t="n">
-        <v>0.290255576372147</v>
+        <v>0.290255606174469</v>
       </c>
       <c r="H1576" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>0.316554993391037</v>
       </c>
       <c r="G1583" t="n">
-        <v>0.301527827978134</v>
+        <v>0.301527798175812</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>0.304720997810364</v>
       </c>
       <c r="G1584" t="n">
-        <v>0.290255576372147</v>
+        <v>0.290255606174469</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1587" t="n">
-        <v>0.309981524944305</v>
+        <v>0.309981554746628</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>0.323457986116409</v>
       </c>
       <c r="G1592" t="n">
-        <v>0.308103144168854</v>
+        <v>0.308103114366531</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41813,7 +41813,7 @@
         <v>0.321485996246338</v>
       </c>
       <c r="G1594" t="n">
-        <v>0.306224763393402</v>
+        <v>0.30622473359108</v>
       </c>
       <c r="H1594" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>0.307680010795593</v>
       </c>
       <c r="G1604" t="n">
-        <v>0.293074160814285</v>
+        <v>0.293074131011963</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>0.307680010795593</v>
       </c>
       <c r="G1605" t="n">
-        <v>0.293074160814285</v>
+        <v>0.293074131011963</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>0.308665990829468</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.294013321399689</v>
+        <v>0.294013291597366</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>0.301762998104095</v>
       </c>
       <c r="G1607" t="n">
-        <v>0.287438005208969</v>
+        <v>0.287438035011292</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>0.34909799695015</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.332525968551636</v>
+        <v>0.332525998353958</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.321253776550293</v>
+        <v>0.321253746747971</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1617" t="n">
-        <v>0.347555905580521</v>
+        <v>0.347555935382843</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.336283713579178</v>
+        <v>0.336283683776855</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>0.363889992237091</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.346615761518478</v>
+        <v>0.346615791320801</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>0.368820995092392</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.351312726736069</v>
+        <v>0.351312696933746</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1624" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>0.674529016017914</v>
       </c>
       <c r="G1632" t="n">
-        <v>0.642508447170258</v>
+        <v>0.642508506774902</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>0.639028012752533</v>
       </c>
       <c r="G1634" t="n">
-        <v>0.608692705631256</v>
+        <v>0.608692765235901</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>0.611415028572083</v>
       </c>
       <c r="G1638" t="n">
-        <v>0.582390546798706</v>
+        <v>0.582390606403351</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -42983,7 +42983,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1639" t="n">
-        <v>0.548574805259705</v>
+        <v>0.548574864864349</v>
       </c>
       <c r="H1639" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1642" t="n">
-        <v>0.548574805259705</v>
+        <v>0.548574864864349</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>0.571968972682953</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.544817090034485</v>
+        <v>0.54481703042984</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>0.702140986919403</v>
       </c>
       <c r="G1655" t="n">
-        <v>0.668809652328491</v>
+        <v>0.668809711933136</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>0.615360021591187</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.586148321628571</v>
+        <v>0.586148262023926</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>0.639028012752533</v>
       </c>
       <c r="G1667" t="n">
-        <v>0.608692705631256</v>
+        <v>0.608692765235901</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>0.64691698551178</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.616207182407379</v>
+        <v>0.616207242012024</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.604935050010681</v>
+        <v>0.604934990406036</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1674" t="n">
-        <v>0.604935050010681</v>
+        <v>0.604934990406036</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>0.615360021591187</v>
       </c>
       <c r="G1682" t="n">
-        <v>0.586148321628571</v>
+        <v>0.586148262023926</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>0.583802998065948</v>
       </c>
       <c r="G1683" t="n">
-        <v>0.556089282035828</v>
+        <v>0.556089341640472</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>0.571968972682953</v>
       </c>
       <c r="G1686" t="n">
-        <v>0.544817090034485</v>
+        <v>0.54481703042984</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1689" t="n">
-        <v>0.548574805259705</v>
+        <v>0.548574864864349</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>0.595637023448944</v>
       </c>
       <c r="G1691" t="n">
-        <v>0.567361533641815</v>
+        <v>0.56736159324646</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>0.603525996208191</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.574876010417938</v>
+        <v>0.574876070022583</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>0.595637023448944</v>
       </c>
       <c r="G1697" t="n">
-        <v>0.567361533641815</v>
+        <v>0.56736159324646</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>0.607470989227295</v>
       </c>
       <c r="G1700" t="n">
-        <v>0.578633785247803</v>
+        <v>0.578633725643158</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>0.607470989227295</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.578633785247803</v>
+        <v>0.578633725643158</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.604935050010681</v>
+        <v>0.604934990406036</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>0.662694990634918</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.631236255168915</v>
+        <v>0.63123619556427</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>0.702140986919403</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.668809652328491</v>
+        <v>0.668809711933136</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1717" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>0.702140986919403</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.668809652328491</v>
+        <v>0.668809711933136</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1726" t="n">
-        <v>0.63499391078949</v>
+        <v>0.634993970394135</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>0.668612003326416</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.636872291564941</v>
+        <v>0.636872351169586</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1729" t="n">
-        <v>0.63499391078949</v>
+        <v>0.634993970394135</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>0.674529016017914</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.642508447170258</v>
+        <v>0.642508506774902</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1742" t="n">
-        <v>0.63499391078949</v>
+        <v>0.634993970394135</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>0.662694990634918</v>
       </c>
       <c r="G1744" t="n">
-        <v>0.631236255168915</v>
+        <v>0.63123619556427</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>0.64691698551178</v>
       </c>
       <c r="G1750" t="n">
-        <v>0.616207182407379</v>
+        <v>0.616207242012024</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>0.694252014160156</v>
       </c>
       <c r="G1755" t="n">
-        <v>0.661295175552368</v>
+        <v>0.661295235157013</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1763" t="n">
-        <v>0.63499391078949</v>
+        <v>0.634993970394135</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>0.69819700717926</v>
       </c>
       <c r="G1770" t="n">
-        <v>0.665052950382233</v>
+        <v>0.665052890777588</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>0.674529016017914</v>
       </c>
       <c r="G1790" t="n">
-        <v>0.642508447170258</v>
+        <v>0.642508506774902</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>0.694252014160156</v>
       </c>
       <c r="G1792" t="n">
-        <v>0.661295175552368</v>
+        <v>0.661295235157013</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47247,7 +47247,7 @@
         <v>0.69819700717926</v>
       </c>
       <c r="G1803" t="n">
-        <v>0.665052950382233</v>
+        <v>0.665052890777588</v>
       </c>
       <c r="H1803" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1809" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>0.706085979938507</v>
       </c>
       <c r="G1810" t="n">
-        <v>0.672567427158356</v>
+        <v>0.672567367553711</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47793,7 +47793,7 @@
         <v>0.733698010444641</v>
       </c>
       <c r="G1824" t="n">
-        <v>0.698868691921234</v>
+        <v>0.698868632316589</v>
       </c>
       <c r="H1824" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>0.729753971099854</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.695111811161041</v>
+        <v>0.695111870765686</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47923,7 +47923,7 @@
         <v>0.745531976222992</v>
       </c>
       <c r="G1829" t="n">
-        <v>0.710140824317932</v>
+        <v>0.710140883922577</v>
       </c>
       <c r="H1829" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>0.745531976222992</v>
       </c>
       <c r="G1830" t="n">
-        <v>0.710140824317932</v>
+        <v>0.710140883922577</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1832" t="n">
-        <v>0.712020218372345</v>
+        <v>0.71202027797699</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1834" t="n">
-        <v>0.712020218372345</v>
+        <v>0.71202027797699</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G1835" t="n">
-        <v>0.702626347541809</v>
+        <v>0.702626407146454</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.702626347541809</v>
+        <v>0.702626407146454</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G1837" t="n">
-        <v>0.702626347541809</v>
+        <v>0.702626407146454</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1839" t="n">
-        <v>0.712020218372345</v>
+        <v>0.71202027797699</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.712020218372345</v>
+        <v>0.71202027797699</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48443,7 +48443,7 @@
         <v>0.796811997890472</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.758986592292786</v>
+        <v>0.758986532688141</v>
       </c>
       <c r="H1849" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>0.942762970924377</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.898009121417999</v>
+        <v>0.898009061813354</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1861" t="n">
-        <v>1.089635014534</v>
+        <v>1.08963513374329</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>1.10449194908142</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.05206072330475</v>
+        <v>1.05206060409546</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.089635014534</v>
+        <v>1.08963513374329</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>1.10449194908142</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.05206072330475</v>
+        <v>1.05206060409546</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.089635014534</v>
+        <v>1.08963513374329</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>1.15873098373413</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.10372483730316</v>
+        <v>1.10372495651245</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.089635014534</v>
+        <v>1.08963513374329</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>1.15873098373413</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.10372483730316</v>
+        <v>1.10372495651245</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49327,7 +49327,7 @@
         <v>1.2179000377655</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.16008520126343</v>
+        <v>1.16008508205414</v>
       </c>
       <c r="H1883" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.20705246925354</v>
+        <v>1.20705235004425</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>1.25734603404999</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.19765853881836</v>
+        <v>1.19765865802765</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.20705246925354</v>
+        <v>1.20705235004425</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49743,7 +49743,7 @@
         <v>1.27213895320892</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.21174931526184</v>
+        <v>1.21174919605255</v>
       </c>
       <c r="H1899" t="s">
         <v>8</v>
@@ -49977,7 +49977,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.20705246925354</v>
+        <v>1.20705235004425</v>
       </c>
       <c r="H1908" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.31977272033691</v>
+        <v>1.3197728395462</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.33386361598969</v>
+        <v>1.3338634967804</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50523,7 +50523,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.30568289756775</v>
+        <v>1.30568301677704</v>
       </c>
       <c r="H1929" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.2352329492569</v>
+        <v>1.23523306846619</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50601,7 +50601,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G1932" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H1932" t="s">
         <v>8</v>
@@ -71378,6 +71378,32 @@
         <v>3.25</v>
       </c>
       <c r="H2731" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2732">
+      <c r="A2732" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2732" t="n">
+        <v>25000</v>
+      </c>
+      <c r="C2732" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D2732" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="E2732" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="F2732" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G2732" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="H2732" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>3.26999998092651</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>3.46000003814697</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>88500</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>3.58999991416931</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>3.41000008583069</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>3.41000008583069</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>3.41000008583069</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>3.5699999332428</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>18500</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>3.58999991416931</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>3.54999995231628</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>3.58999991416931</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>3.58999991416931</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>3.54999995231628</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>31500</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>3.45000004768372</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>3.50999999046326</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>3.50999999046326</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>3.53999996185303</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>11000</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>3.52999997138977</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>3.45000004768372</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>3.52999997138977</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>3.49000000953674</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>3.4300000667572</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>3.49000000953674</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>3.47000002861023</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -71667,6 +71667,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="2743">
+      <c r="A2743" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2743" t="n">
+        <v>46500</v>
+      </c>
+      <c r="C2743" t="n">
+        <v>3.48000001907349</v>
+      </c>
+      <c r="D2743" t="n">
+        <v>3.3199999332428</v>
+      </c>
+      <c r="E2743" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="F2743" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G2743" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -71675,7 +71675,7 @@
         <v>46500</v>
       </c>
       <c r="C2743" t="n">
-        <v>3.48000001907349</v>
+        <v>3.53999996185303</v>
       </c>
       <c r="D2743" t="n">
         <v>3.3199999332428</v>
@@ -71690,6 +71690,32 @@
         <v>3.5</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>3.45000004768372</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>3.49000000953674</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>3.47000002861023</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>3.47000002861023</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -79983,6 +79983,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2746">
+      <c r="A2746" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2746" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2746" t="n">
+        <v>3.39000010490417</v>
+      </c>
+      <c r="D2746" t="n">
+        <v>3.48000001907349</v>
+      </c>
+      <c r="E2746" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="F2746" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="G2746" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="H2746" t="n">
+        <v>14500</v>
+      </c>
+      <c r="I2746" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -80012,6 +80012,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2747">
+      <c r="A2747" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2747" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2747" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="D2747" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="E2747" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="F2747" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="G2747" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="H2747" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I2747" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -80041,6 +80041,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2748">
+      <c r="A2748" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2748" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C2748" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="D2748" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="E2748" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="F2748" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="G2748" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="H2748" t="n">
+        <v>3500</v>
+      </c>
+      <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G2" t="n">
-        <v>2.78796315193176</v>
+        <v>2.78796291351318</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -456,7 +456,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G3" t="n">
-        <v>2.78796315193176</v>
+        <v>2.78796291351318</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -485,7 +485,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78796315193176</v>
+        <v>2.78796291351318</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -514,7 +514,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G5" t="n">
-        <v>2.78796315193176</v>
+        <v>2.78796291351318</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -543,7 +543,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G6" t="n">
-        <v>2.78796315193176</v>
+        <v>2.78796291351318</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>2.90521001815796</v>
       </c>
       <c r="G32" t="n">
-        <v>2.76729679107666</v>
+        <v>2.76729702949524</v>
       </c>
       <c r="H32" t="n">
         <v>1521</v>
@@ -1355,7 +1355,7 @@
         <v>2.85984706878662</v>
       </c>
       <c r="G34" t="n">
-        <v>2.72408747673035</v>
+        <v>2.72408723831177</v>
       </c>
       <c r="H34" t="n">
         <v>5070</v>
@@ -1442,7 +1442,7 @@
         <v>2.90718293190002</v>
       </c>
       <c r="G37" t="n">
-        <v>2.76917600631714</v>
+        <v>2.76917624473572</v>
       </c>
       <c r="H37" t="n">
         <v>1014</v>
@@ -1471,7 +1471,7 @@
         <v>2.90718293190002</v>
       </c>
       <c r="G38" t="n">
-        <v>2.76917600631714</v>
+        <v>2.76917624473572</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>2.90718293190002</v>
       </c>
       <c r="G39" t="n">
-        <v>2.76917600631714</v>
+        <v>2.76917624473572</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G45" t="n">
-        <v>2.66772699356079</v>
+        <v>2.66772723197937</v>
       </c>
       <c r="H45" t="n">
         <v>2028</v>
@@ -3965,7 +3965,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G124" t="n">
-        <v>2.78796315193176</v>
+        <v>2.78796291351318</v>
       </c>
       <c r="H124" t="n">
         <v>507</v>
@@ -3994,7 +3994,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G125" t="n">
-        <v>2.78796315193176</v>
+        <v>2.78796291351318</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G126" t="n">
-        <v>2.66772699356079</v>
+        <v>2.66772723197937</v>
       </c>
       <c r="H126" t="n">
         <v>10140</v>
@@ -4052,7 +4052,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G127" t="n">
-        <v>2.66772699356079</v>
+        <v>2.66772723197937</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G128" t="n">
-        <v>2.66772699356079</v>
+        <v>2.66772723197937</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G129" t="n">
-        <v>2.66772699356079</v>
+        <v>2.66772723197937</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G130" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H130" t="n">
         <v>2028</v>
@@ -4168,7 +4168,7 @@
         <v>2.72967505455017</v>
       </c>
       <c r="G131" t="n">
-        <v>2.60009455680847</v>
+        <v>2.60009479522705</v>
       </c>
       <c r="H131" t="n">
         <v>507</v>
@@ -4197,7 +4197,7 @@
         <v>2.72967505455017</v>
       </c>
       <c r="G132" t="n">
-        <v>2.60009455680847</v>
+        <v>2.60009479522705</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4226,7 +4226,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G133" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H133" t="n">
         <v>6591</v>
@@ -4255,7 +4255,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G136" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G137" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G138" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G139" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G140" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G141" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G142" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>2.58372402191162</v>
       </c>
       <c r="G143" t="n">
-        <v>2.46107196807861</v>
+        <v>2.46107220649719</v>
       </c>
       <c r="H143" t="n">
         <v>1014</v>
@@ -4545,7 +4545,7 @@
         <v>2.58372402191162</v>
       </c>
       <c r="G144" t="n">
-        <v>2.46107196807861</v>
+        <v>2.46107220649719</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>2.48905301094055</v>
       </c>
       <c r="G145" t="n">
-        <v>2.37089538574219</v>
+        <v>2.37089514732361</v>
       </c>
       <c r="H145" t="n">
         <v>507</v>
@@ -4603,7 +4603,7 @@
         <v>2.48905301094055</v>
       </c>
       <c r="G146" t="n">
-        <v>2.37089538574219</v>
+        <v>2.37089514732361</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>2.35690808296204</v>
       </c>
       <c r="G148" t="n">
-        <v>2.24502325057983</v>
+        <v>2.24502348899841</v>
       </c>
       <c r="H148" t="n">
         <v>2028</v>
@@ -4835,7 +4835,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G154" t="n">
-        <v>2.47046613693237</v>
+        <v>2.47046589851379</v>
       </c>
       <c r="H154" t="n">
         <v>1014</v>
@@ -4864,7 +4864,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G155" t="n">
-        <v>2.47046613693237</v>
+        <v>2.47046589851379</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G156" t="n">
-        <v>2.47046613693237</v>
+        <v>2.47046589851379</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G157" t="n">
-        <v>2.47046613693237</v>
+        <v>2.47046589851379</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G158" t="n">
-        <v>2.47046613693237</v>
+        <v>2.47046589851379</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G159" t="n">
-        <v>2.47046613693237</v>
+        <v>2.47046589851379</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>2.56400108337402</v>
       </c>
       <c r="G173" t="n">
-        <v>2.44228553771973</v>
+        <v>2.44228529930115</v>
       </c>
       <c r="H173" t="n">
         <v>1014</v>
@@ -5618,7 +5618,7 @@
         <v>2.58372402191162</v>
       </c>
       <c r="G181" t="n">
-        <v>2.46107196807861</v>
+        <v>2.46107220649719</v>
       </c>
       <c r="H181" t="n">
         <v>2028</v>
@@ -6227,7 +6227,7 @@
         <v>2.56400108337402</v>
       </c>
       <c r="G202" t="n">
-        <v>2.44228553771973</v>
+        <v>2.44228529930115</v>
       </c>
       <c r="H202" t="n">
         <v>10140</v>
@@ -6256,7 +6256,7 @@
         <v>2.56991791725159</v>
       </c>
       <c r="G203" t="n">
-        <v>2.44792151451111</v>
+        <v>2.44792127609253</v>
       </c>
       <c r="H203" t="n">
         <v>3549</v>
@@ -6314,7 +6314,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G205" t="n">
-        <v>2.36525917053223</v>
+        <v>2.36525893211365</v>
       </c>
       <c r="H205" t="n">
         <v>2028</v>
@@ -6343,7 +6343,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G206" t="n">
-        <v>2.36525917053223</v>
+        <v>2.36525893211365</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -6372,7 +6372,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G207" t="n">
-        <v>2.36525917053223</v>
+        <v>2.36525893211365</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G208" t="n">
-        <v>2.36525917053223</v>
+        <v>2.36525893211365</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G209" t="n">
-        <v>2.36525917053223</v>
+        <v>2.36525893211365</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G210" t="n">
-        <v>2.36525917053223</v>
+        <v>2.36525893211365</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>2.46144104003906</v>
       </c>
       <c r="G214" t="n">
-        <v>2.34459400177002</v>
+        <v>2.3445942401886</v>
       </c>
       <c r="H214" t="n">
         <v>7605</v>
@@ -7242,7 +7242,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G237" t="n">
-        <v>2.2074499130249</v>
+        <v>2.20744967460632</v>
       </c>
       <c r="H237" t="n">
         <v>2028</v>
@@ -7271,7 +7271,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G238" t="n">
-        <v>2.2074499130249</v>
+        <v>2.20744967460632</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G239" t="n">
-        <v>2.2074499130249</v>
+        <v>2.20744967460632</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G240" t="n">
-        <v>2.2074499130249</v>
+        <v>2.20744967460632</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G241" t="n">
-        <v>2.2074499130249</v>
+        <v>2.20744967460632</v>
       </c>
       <c r="H241" t="n">
         <v>1521</v>
@@ -7764,7 +7764,7 @@
         <v>2.36874198913574</v>
       </c>
       <c r="G255" t="n">
-        <v>2.25629544258118</v>
+        <v>2.25629568099976</v>
       </c>
       <c r="H255" t="n">
         <v>21294</v>
@@ -7880,7 +7880,7 @@
         <v>2.17151093482971</v>
       </c>
       <c r="G259" t="n">
-        <v>2.06842708587646</v>
+        <v>2.06842732429504</v>
       </c>
       <c r="H259" t="n">
         <v>1014</v>
@@ -7909,7 +7909,7 @@
         <v>2.09853601455688</v>
       </c>
       <c r="G260" t="n">
-        <v>1.99891638755798</v>
+        <v>1.99891650676727</v>
       </c>
       <c r="H260" t="n">
         <v>5577</v>
@@ -7967,7 +7967,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G262" t="n">
-        <v>2.08345699310303</v>
+        <v>2.08345723152161</v>
       </c>
       <c r="H262" t="n">
         <v>507</v>
@@ -7996,7 +7996,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G263" t="n">
-        <v>2.08345699310303</v>
+        <v>2.08345723152161</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G264" t="n">
-        <v>2.08345699310303</v>
+        <v>2.08345723152161</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G265" t="n">
-        <v>2.08345699310303</v>
+        <v>2.08345723152161</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G266" t="n">
-        <v>2.01958155632019</v>
+        <v>2.01958131790161</v>
       </c>
       <c r="H266" t="n">
         <v>2535</v>
@@ -8112,7 +8112,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G267" t="n">
-        <v>2.01958155632019</v>
+        <v>2.01958131790161</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G280" t="n">
-        <v>2.01958155632019</v>
+        <v>2.01958131790161</v>
       </c>
       <c r="H280" t="n">
         <v>507</v>
@@ -8518,7 +8518,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G281" t="n">
-        <v>2.01958155632019</v>
+        <v>2.01958131790161</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G282" t="n">
-        <v>2.01958155632019</v>
+        <v>2.01958131790161</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G283" t="n">
-        <v>1.98200809955597</v>
+        <v>1.98200821876526</v>
       </c>
       <c r="H283" t="n">
         <v>1014</v>
@@ -8605,7 +8605,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G284" t="n">
-        <v>1.98200809955597</v>
+        <v>1.98200821876526</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G285" t="n">
-        <v>1.98200809955597</v>
+        <v>1.98200821876526</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>2.18531799316406</v>
       </c>
       <c r="G305" t="n">
-        <v>2.08157873153687</v>
+        <v>2.08157896995544</v>
       </c>
       <c r="H305" t="n">
         <v>7605</v>
@@ -9301,7 +9301,7 @@
         <v>1.98216998577118</v>
       </c>
       <c r="G308" t="n">
-        <v>1.88807439804077</v>
+        <v>1.88807451725006</v>
       </c>
       <c r="H308" t="n">
         <v>8112</v>
@@ -9330,7 +9330,7 @@
         <v>1.94272398948669</v>
       </c>
       <c r="G309" t="n">
-        <v>1.85050094127655</v>
+        <v>1.85050106048584</v>
       </c>
       <c r="H309" t="n">
         <v>1014</v>
@@ -9823,7 +9823,7 @@
         <v>2.15770506858826</v>
       </c>
       <c r="G326" t="n">
-        <v>2.05527687072754</v>
+        <v>2.05527663230896</v>
       </c>
       <c r="H326" t="n">
         <v>12675</v>
@@ -9997,7 +9997,7 @@
         <v>2.18926191329956</v>
       </c>
       <c r="G332" t="n">
-        <v>2.08533549308777</v>
+        <v>2.08533573150635</v>
       </c>
       <c r="H332" t="n">
         <v>2535</v>
@@ -10026,7 +10026,7 @@
         <v>2.18926191329956</v>
       </c>
       <c r="G333" t="n">
-        <v>2.08533549308777</v>
+        <v>2.08533573150635</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G340" t="n">
-        <v>2.02521777153015</v>
+        <v>2.02521753311157</v>
       </c>
       <c r="H340" t="n">
         <v>507</v>
@@ -10345,7 +10345,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G344" t="n">
-        <v>2.02521777153015</v>
+        <v>2.02521753311157</v>
       </c>
       <c r="H344" t="n">
         <v>2535</v>
@@ -10374,7 +10374,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G345" t="n">
-        <v>2.02521777153015</v>
+        <v>2.02521753311157</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G346" t="n">
-        <v>1.98200809955597</v>
+        <v>1.98200821876526</v>
       </c>
       <c r="H346" t="n">
         <v>3042</v>
@@ -10432,7 +10432,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G347" t="n">
-        <v>1.98200809955597</v>
+        <v>1.98200821876526</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>2.00189304351807</v>
       </c>
       <c r="G365" t="n">
-        <v>1.90686130523682</v>
+        <v>1.90686118602753</v>
       </c>
       <c r="H365" t="n">
         <v>507</v>
@@ -11041,7 +11041,7 @@
         <v>2.71981310844421</v>
       </c>
       <c r="G368" t="n">
-        <v>2.59070086479187</v>
+        <v>2.59070110321045</v>
       </c>
       <c r="H368" t="n">
         <v>70475</v>
@@ -11070,7 +11070,7 @@
         <v>2.41607809066772</v>
       </c>
       <c r="G369" t="n">
-        <v>2.30138468742371</v>
+        <v>2.30138444900513</v>
       </c>
       <c r="H369" t="n">
         <v>39040</v>
@@ -11099,7 +11099,7 @@
         <v>2.25829291343689</v>
       </c>
       <c r="G370" t="n">
-        <v>2.15108942985535</v>
+        <v>2.15108966827393</v>
       </c>
       <c r="H370" t="n">
         <v>18759</v>
@@ -11215,7 +11215,7 @@
         <v>2.17940092086792</v>
       </c>
       <c r="G374" t="n">
-        <v>2.0759425163269</v>
+        <v>2.07594275474548</v>
       </c>
       <c r="H374" t="n">
         <v>7098</v>
@@ -11273,7 +11273,7 @@
         <v>2.17940092086792</v>
       </c>
       <c r="G376" t="n">
-        <v>2.0759425163269</v>
+        <v>2.07594275474548</v>
       </c>
       <c r="H376" t="n">
         <v>3549</v>
@@ -11331,7 +11331,7 @@
         <v>2.20701289176941</v>
       </c>
       <c r="G378" t="n">
-        <v>2.10224390029907</v>
+        <v>2.10224366188049</v>
       </c>
       <c r="H378" t="n">
         <v>507</v>
@@ -11476,7 +11476,7 @@
         <v>2.44369006156921</v>
       </c>
       <c r="G383" t="n">
-        <v>2.32768559455872</v>
+        <v>2.32768583297729</v>
       </c>
       <c r="H383" t="n">
         <v>179992</v>
@@ -11505,7 +11505,7 @@
         <v>2.30957293510437</v>
       </c>
       <c r="G384" t="n">
-        <v>2.19993543624878</v>
+        <v>2.1999351978302</v>
       </c>
       <c r="H384" t="n">
         <v>109516</v>
@@ -11766,7 +11766,7 @@
         <v>2.3628249168396</v>
       </c>
       <c r="G393" t="n">
-        <v>2.25065922737122</v>
+        <v>2.25065946578979</v>
       </c>
       <c r="H393" t="n">
         <v>19266</v>
@@ -11824,7 +11824,7 @@
         <v>2.27604389190674</v>
       </c>
       <c r="G395" t="n">
-        <v>2.16799783706665</v>
+        <v>2.16799807548523</v>
       </c>
       <c r="H395" t="n">
         <v>20280</v>
@@ -11911,7 +11911,7 @@
         <v>2.10445308685303</v>
       </c>
       <c r="G398" t="n">
-        <v>2.00455260276794</v>
+        <v>2.00455284118652</v>
       </c>
       <c r="H398" t="n">
         <v>142979</v>
@@ -11940,7 +11940,7 @@
         <v>2.0472559928894</v>
       </c>
       <c r="G399" t="n">
-        <v>1.95007073879242</v>
+        <v>1.95007061958313</v>
       </c>
       <c r="H399" t="n">
         <v>25858</v>
@@ -11998,7 +11998,7 @@
         <v>2.19123506546021</v>
       </c>
       <c r="G401" t="n">
-        <v>2.08721494674683</v>
+        <v>2.08721518516541</v>
       </c>
       <c r="H401" t="n">
         <v>99882</v>
@@ -12027,7 +12027,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G402" t="n">
-        <v>2.02521777153015</v>
+        <v>2.02521753311157</v>
       </c>
       <c r="H402" t="n">
         <v>30421</v>
@@ -12056,7 +12056,7 @@
         <v>2.10839796066284</v>
       </c>
       <c r="G403" t="n">
-        <v>2.00831031799316</v>
+        <v>2.00831007957458</v>
       </c>
       <c r="H403" t="n">
         <v>20280</v>
@@ -12143,7 +12143,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G406" t="n">
-        <v>1.98200809955597</v>
+        <v>1.98200821876526</v>
       </c>
       <c r="H406" t="n">
         <v>9633</v>
@@ -12433,7 +12433,7 @@
         <v>2.00189304351807</v>
       </c>
       <c r="G416" t="n">
-        <v>1.90686130523682</v>
+        <v>1.90686118602753</v>
       </c>
       <c r="H416" t="n">
         <v>8112</v>
@@ -12462,7 +12462,7 @@
         <v>1.98019802570343</v>
       </c>
       <c r="G417" t="n">
-        <v>1.88619601726532</v>
+        <v>1.88619613647461</v>
       </c>
       <c r="H417" t="n">
         <v>4563</v>
@@ -12491,7 +12491,7 @@
         <v>2.00189304351807</v>
       </c>
       <c r="G418" t="n">
-        <v>1.90686130523682</v>
+        <v>1.90686118602753</v>
       </c>
       <c r="H418" t="n">
         <v>11661</v>
@@ -12520,7 +12520,7 @@
         <v>2.03936696052551</v>
       </c>
       <c r="G419" t="n">
-        <v>1.9425562620163</v>
+        <v>1.94255614280701</v>
       </c>
       <c r="H419" t="n">
         <v>1014</v>
@@ -12549,7 +12549,7 @@
         <v>2.03936696052551</v>
       </c>
       <c r="G420" t="n">
-        <v>1.9425562620163</v>
+        <v>1.94255614280701</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>1.98808705806732</v>
       </c>
       <c r="G421" t="n">
-        <v>1.89371061325073</v>
+        <v>1.89371073246002</v>
       </c>
       <c r="H421" t="n">
         <v>2028</v>
@@ -12607,7 +12607,7 @@
         <v>2.03936696052551</v>
       </c>
       <c r="G422" t="n">
-        <v>1.9425562620163</v>
+        <v>1.94255614280701</v>
       </c>
       <c r="H422" t="n">
         <v>5070</v>
@@ -12636,7 +12636,7 @@
         <v>2.01569890975952</v>
       </c>
       <c r="G423" t="n">
-        <v>1.92001163959503</v>
+        <v>1.92001175880432</v>
       </c>
       <c r="H423" t="n">
         <v>17745</v>
@@ -12781,7 +12781,7 @@
         <v>1.98019802570343</v>
       </c>
       <c r="G428" t="n">
-        <v>1.88619601726532</v>
+        <v>1.88619613647461</v>
       </c>
       <c r="H428" t="n">
         <v>1521</v>
@@ -12810,7 +12810,7 @@
         <v>1.98019802570343</v>
       </c>
       <c r="G429" t="n">
-        <v>1.88619601726532</v>
+        <v>1.88619613647461</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>1.91313898563385</v>
       </c>
       <c r="G434" t="n">
-        <v>1.82232046127319</v>
+        <v>1.8223203420639</v>
       </c>
       <c r="H434" t="n">
         <v>5070</v>
@@ -12984,7 +12984,7 @@
         <v>1.87960994243622</v>
       </c>
       <c r="G435" t="n">
-        <v>1.79038310050964</v>
+        <v>1.79038298130035</v>
       </c>
       <c r="H435" t="n">
         <v>44617</v>
@@ -13100,7 +13100,7 @@
         <v>1.85397005081177</v>
       </c>
       <c r="G439" t="n">
-        <v>1.76596021652222</v>
+        <v>1.76596033573151</v>
       </c>
       <c r="H439" t="n">
         <v>16731</v>
@@ -13158,7 +13158,7 @@
         <v>1.85791397094727</v>
       </c>
       <c r="G441" t="n">
-        <v>1.76971697807312</v>
+        <v>1.76971709728241</v>
       </c>
       <c r="H441" t="n">
         <v>10140</v>
@@ -13274,7 +13274,7 @@
         <v>1.77507698535919</v>
       </c>
       <c r="G445" t="n">
-        <v>1.69081234931946</v>
+        <v>1.69081246852875</v>
       </c>
       <c r="H445" t="n">
         <v>24843</v>
@@ -13303,7 +13303,7 @@
         <v>1.77507698535919</v>
       </c>
       <c r="G446" t="n">
-        <v>1.69081234931946</v>
+        <v>1.69081246852875</v>
       </c>
       <c r="H446" t="n">
         <v>12675</v>
@@ -13448,7 +13448,7 @@
         <v>1.53840005397797</v>
       </c>
       <c r="G451" t="n">
-        <v>1.46537065505981</v>
+        <v>1.4653707742691</v>
       </c>
       <c r="H451" t="n">
         <v>38533</v>
@@ -13535,7 +13535,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G454" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H454" t="n">
         <v>19266</v>
@@ -13593,7 +13593,7 @@
         <v>1.82241296768188</v>
       </c>
       <c r="G456" t="n">
-        <v>1.73590135574341</v>
+        <v>1.73590123653412</v>
       </c>
       <c r="H456" t="n">
         <v>45631</v>
@@ -13883,7 +13883,7 @@
         <v>1.47528600692749</v>
       </c>
       <c r="G466" t="n">
-        <v>1.40525281429291</v>
+        <v>1.40525269508362</v>
       </c>
       <c r="H466" t="n">
         <v>28393</v>
@@ -13941,7 +13941,7 @@
         <v>1.50684297084808</v>
       </c>
       <c r="G468" t="n">
-        <v>1.43531167507172</v>
+        <v>1.43531179428101</v>
       </c>
       <c r="H468" t="n">
         <v>35998</v>
@@ -13970,7 +13970,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G469" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H469" t="n">
         <v>31435</v>
@@ -14115,7 +14115,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G474" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H474" t="n">
         <v>7098</v>
@@ -14144,7 +14144,7 @@
         <v>1.48909294605255</v>
       </c>
       <c r="G475" t="n">
-        <v>1.41840422153473</v>
+        <v>1.41840434074402</v>
       </c>
       <c r="H475" t="n">
         <v>50702</v>
@@ -14202,7 +14202,7 @@
         <v>1.54431700706482</v>
       </c>
       <c r="G477" t="n">
-        <v>1.47100675106049</v>
+        <v>1.47100687026978</v>
       </c>
       <c r="H477" t="n">
         <v>92784</v>
@@ -14231,7 +14231,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G478" t="n">
-        <v>1.474764585495</v>
+        <v>1.47476446628571</v>
       </c>
       <c r="H478" t="n">
         <v>51716</v>
@@ -14260,7 +14260,7 @@
         <v>1.48909294605255</v>
       </c>
       <c r="G479" t="n">
-        <v>1.41840422153473</v>
+        <v>1.41840434074402</v>
       </c>
       <c r="H479" t="n">
         <v>3042</v>
@@ -14521,7 +14521,7 @@
         <v>1.49205100536346</v>
       </c>
       <c r="G488" t="n">
-        <v>1.42122185230255</v>
+        <v>1.42122197151184</v>
       </c>
       <c r="H488" t="n">
         <v>104446</v>
@@ -14550,7 +14550,7 @@
         <v>1.53840005397797</v>
       </c>
       <c r="G489" t="n">
-        <v>1.46537065505981</v>
+        <v>1.4653707742691</v>
       </c>
       <c r="H489" t="n">
         <v>117121</v>
@@ -14579,7 +14579,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G490" t="n">
-        <v>1.474764585495</v>
+        <v>1.47476446628571</v>
       </c>
       <c r="H490" t="n">
         <v>201793</v>
@@ -14637,7 +14637,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G492" t="n">
-        <v>1.44658398628235</v>
+        <v>1.44658386707306</v>
       </c>
       <c r="H492" t="n">
         <v>31435</v>
@@ -14666,7 +14666,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G493" t="n">
-        <v>1.44658398628235</v>
+        <v>1.44658386707306</v>
       </c>
       <c r="H493" t="n">
         <v>0</v>
@@ -14695,7 +14695,7 @@
         <v>1.54234504699707</v>
       </c>
       <c r="G494" t="n">
-        <v>1.46912837028503</v>
+        <v>1.46912848949432</v>
       </c>
       <c r="H494" t="n">
         <v>14196</v>
@@ -14811,7 +14811,7 @@
         <v>1.55615103244781</v>
       </c>
       <c r="G498" t="n">
-        <v>1.48227906227112</v>
+        <v>1.48227894306183</v>
       </c>
       <c r="H498" t="n">
         <v>2535</v>
@@ -14840,7 +14840,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G499" t="n">
-        <v>1.474764585495</v>
+        <v>1.47476446628571</v>
       </c>
       <c r="H499" t="n">
         <v>3549</v>
@@ -14898,7 +14898,7 @@
         <v>1.55220699310303</v>
       </c>
       <c r="G501" t="n">
-        <v>1.47852230072021</v>
+        <v>1.47852218151093</v>
       </c>
       <c r="H501" t="n">
         <v>2028</v>
@@ -14927,7 +14927,7 @@
         <v>1.50684297084808</v>
       </c>
       <c r="G502" t="n">
-        <v>1.43531167507172</v>
+        <v>1.43531179428101</v>
       </c>
       <c r="H502" t="n">
         <v>3549</v>
@@ -14985,7 +14985,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G504" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H504" t="n">
         <v>23322</v>
@@ -15014,7 +15014,7 @@
         <v>1.44175696372986</v>
       </c>
       <c r="G505" t="n">
-        <v>1.37331545352936</v>
+        <v>1.37331533432007</v>
       </c>
       <c r="H505" t="n">
         <v>8619</v>
@@ -15072,7 +15072,7 @@
         <v>1.4013249874115</v>
       </c>
       <c r="G507" t="n">
-        <v>1.33480262756348</v>
+        <v>1.33480274677277</v>
       </c>
       <c r="H507" t="n">
         <v>5070</v>
@@ -15101,7 +15101,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G508" t="n">
-        <v>1.3338634967804</v>
+        <v>1.33386361598969</v>
       </c>
       <c r="H508" t="n">
         <v>2028</v>
@@ -15304,7 +15304,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G515" t="n">
-        <v>1.3338634967804</v>
+        <v>1.33386361598969</v>
       </c>
       <c r="H515" t="n">
         <v>5577</v>
@@ -15449,7 +15449,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G520" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H520" t="n">
         <v>39040</v>
@@ -15478,7 +15478,7 @@
         <v>1.48909294605255</v>
       </c>
       <c r="G521" t="n">
-        <v>1.41840422153473</v>
+        <v>1.41840434074402</v>
       </c>
       <c r="H521" t="n">
         <v>4056</v>
@@ -15565,7 +15565,7 @@
         <v>1.5531929731369</v>
       </c>
       <c r="G524" t="n">
-        <v>1.4794614315033</v>
+        <v>1.47946131229401</v>
       </c>
       <c r="H524" t="n">
         <v>313845</v>
@@ -15623,7 +15623,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G526" t="n">
-        <v>1.474764585495</v>
+        <v>1.47476446628571</v>
       </c>
       <c r="H526" t="n">
         <v>37012</v>
@@ -15652,7 +15652,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G527" t="n">
-        <v>1.44658398628235</v>
+        <v>1.44658386707306</v>
       </c>
       <c r="H527" t="n">
         <v>17238</v>
@@ -15710,7 +15710,7 @@
         <v>1.5531929731369</v>
       </c>
       <c r="G529" t="n">
-        <v>1.4794614315033</v>
+        <v>1.47946131229401</v>
       </c>
       <c r="H529" t="n">
         <v>11154</v>
@@ -15826,7 +15826,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G533" t="n">
-        <v>1.474764585495</v>
+        <v>1.47476446628571</v>
       </c>
       <c r="H533" t="n">
         <v>20280</v>
@@ -15884,7 +15884,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G535" t="n">
-        <v>1.44658398628235</v>
+        <v>1.44658386707306</v>
       </c>
       <c r="H535" t="n">
         <v>5070</v>
@@ -15971,7 +15971,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G538" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H538" t="n">
         <v>11661</v>
@@ -16000,7 +16000,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G539" t="n">
-        <v>1.474764585495</v>
+        <v>1.47476446628571</v>
       </c>
       <c r="H539" t="n">
         <v>17238</v>
@@ -16116,7 +16116,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G543" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H543" t="n">
         <v>507</v>
@@ -16145,7 +16145,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G544" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H544" t="n">
         <v>1014</v>
@@ -16203,7 +16203,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G546" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H546" t="n">
         <v>7098</v>
@@ -16232,7 +16232,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G547" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H547" t="n">
         <v>6084</v>
@@ -16261,7 +16261,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G548" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H548" t="n">
         <v>2028</v>
@@ -16464,7 +16464,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G555" t="n">
-        <v>1.30568301677704</v>
+        <v>1.30568289756775</v>
       </c>
       <c r="H555" t="n">
         <v>9633</v>
@@ -16638,7 +16638,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G561" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H561" t="n">
         <v>4056</v>
@@ -16812,7 +16812,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G567" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H567" t="n">
         <v>24843</v>
@@ -16841,7 +16841,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G568" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H568" t="n">
         <v>2028</v>
@@ -17073,7 +17073,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G576" t="n">
-        <v>1.29629004001617</v>
+        <v>1.29629015922546</v>
       </c>
       <c r="H576" t="n">
         <v>4056</v>
@@ -17102,7 +17102,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G577" t="n">
-        <v>1.3197728395462</v>
+        <v>1.31977272033691</v>
       </c>
       <c r="H577" t="n">
         <v>6084</v>
@@ -17160,7 +17160,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G579" t="n">
-        <v>1.3197728395462</v>
+        <v>1.31977272033691</v>
       </c>
       <c r="H579" t="n">
         <v>3549</v>
@@ -17508,7 +17508,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G591" t="n">
-        <v>1.29629004001617</v>
+        <v>1.29629015922546</v>
       </c>
       <c r="H591" t="n">
         <v>17745</v>
@@ -17682,7 +17682,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G597" t="n">
-        <v>1.3197728395462</v>
+        <v>1.31977272033691</v>
       </c>
       <c r="H597" t="n">
         <v>5577</v>
@@ -17856,7 +17856,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G603" t="n">
-        <v>1.24932265281677</v>
+        <v>1.24932277202606</v>
       </c>
       <c r="H603" t="n">
         <v>1014</v>
@@ -17885,7 +17885,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G604" t="n">
-        <v>1.24932265281677</v>
+        <v>1.24932277202606</v>
       </c>
       <c r="H604" t="n">
         <v>1521</v>
@@ -17972,7 +17972,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G607" t="n">
-        <v>1.23523306846619</v>
+        <v>1.2352329492569</v>
       </c>
       <c r="H607" t="n">
         <v>15717</v>
@@ -18088,7 +18088,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G611" t="n">
-        <v>1.24932265281677</v>
+        <v>1.24932277202606</v>
       </c>
       <c r="H611" t="n">
         <v>2028</v>
@@ -18117,7 +18117,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G612" t="n">
-        <v>1.24932265281677</v>
+        <v>1.24932277202606</v>
       </c>
       <c r="H612" t="n">
         <v>1014</v>
@@ -18175,7 +18175,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G614" t="n">
-        <v>1.20705235004425</v>
+        <v>1.20705246925354</v>
       </c>
       <c r="H614" t="n">
         <v>12168</v>
@@ -18378,7 +18378,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G621" t="n">
-        <v>1.30568301677704</v>
+        <v>1.30568289756775</v>
       </c>
       <c r="H621" t="n">
         <v>16731</v>
@@ -18639,7 +18639,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G630" t="n">
-        <v>1.30568301677704</v>
+        <v>1.30568289756775</v>
       </c>
       <c r="H630" t="n">
         <v>10647</v>
@@ -18784,7 +18784,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G635" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H635" t="n">
         <v>53237</v>
@@ -18871,7 +18871,7 @@
         <v>1.85397005081177</v>
       </c>
       <c r="G638" t="n">
-        <v>1.76596021652222</v>
+        <v>1.76596033573151</v>
       </c>
       <c r="H638" t="n">
         <v>456825</v>
@@ -19074,7 +19074,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G645" t="n">
-        <v>1.474764585495</v>
+        <v>1.47476446628571</v>
       </c>
       <c r="H645" t="n">
         <v>142979</v>
@@ -19277,7 +19277,7 @@
         <v>1.56798505783081</v>
       </c>
       <c r="G652" t="n">
-        <v>1.49355137348175</v>
+        <v>1.49355125427246</v>
       </c>
       <c r="H652" t="n">
         <v>129797</v>
@@ -19393,7 +19393,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G656" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H656" t="n">
         <v>6591</v>
@@ -19451,7 +19451,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G658" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H658" t="n">
         <v>46138</v>
@@ -19509,7 +19509,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G660" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H660" t="n">
         <v>2028</v>
@@ -19567,7 +19567,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G662" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H662" t="n">
         <v>2535</v>
@@ -19596,7 +19596,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G663" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H663" t="n">
         <v>0</v>
@@ -19625,7 +19625,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G664" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H664" t="n">
         <v>0</v>
@@ -19654,7 +19654,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G665" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H665" t="n">
         <v>0</v>
@@ -19741,7 +19741,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G668" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H668" t="n">
         <v>17238</v>
@@ -19770,7 +19770,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G669" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H669" t="n">
         <v>30421</v>
@@ -19799,7 +19799,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G670" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H670" t="n">
         <v>3042</v>
@@ -19828,7 +19828,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G671" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H671" t="n">
         <v>9126</v>
@@ -19886,7 +19886,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G673" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H673" t="n">
         <v>4563</v>
@@ -19973,7 +19973,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G676" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H676" t="n">
         <v>20280</v>
@@ -20060,7 +20060,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G679" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H679" t="n">
         <v>5070</v>
@@ -20089,7 +20089,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G680" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H680" t="n">
         <v>4056</v>
@@ -20234,7 +20234,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G685" t="n">
-        <v>1.29629004001617</v>
+        <v>1.29629015922546</v>
       </c>
       <c r="H685" t="n">
         <v>5070</v>
@@ -20263,7 +20263,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G686" t="n">
-        <v>1.29629004001617</v>
+        <v>1.29629015922546</v>
       </c>
       <c r="H686" t="n">
         <v>507</v>
@@ -20408,7 +20408,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G691" t="n">
-        <v>1.3338634967804</v>
+        <v>1.33386361598969</v>
       </c>
       <c r="H691" t="n">
         <v>9633</v>
@@ -20495,7 +20495,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G694" t="n">
-        <v>1.3338634967804</v>
+        <v>1.33386361598969</v>
       </c>
       <c r="H694" t="n">
         <v>10140</v>
@@ -20553,7 +20553,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G696" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H696" t="n">
         <v>44110</v>
@@ -20669,7 +20669,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G700" t="n">
-        <v>1.30568301677704</v>
+        <v>1.30568289756775</v>
       </c>
       <c r="H700" t="n">
         <v>67433</v>
@@ -20698,7 +20698,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G701" t="n">
-        <v>1.23523306846619</v>
+        <v>1.2352329492569</v>
       </c>
       <c r="H701" t="n">
         <v>81123</v>
@@ -20727,7 +20727,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G702" t="n">
-        <v>1.23523306846619</v>
+        <v>1.2352329492569</v>
       </c>
       <c r="H702" t="n">
         <v>14703</v>
@@ -20872,7 +20872,7 @@
         <v>1.2179000377655</v>
       </c>
       <c r="G707" t="n">
-        <v>1.16008508205414</v>
+        <v>1.16008520126343</v>
       </c>
       <c r="H707" t="n">
         <v>17745</v>
@@ -21017,7 +21017,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G712" t="n">
-        <v>1.08963513374329</v>
+        <v>1.089635014534</v>
       </c>
       <c r="H712" t="n">
         <v>20787</v>
@@ -21075,7 +21075,7 @@
         <v>1.17845404148102</v>
       </c>
       <c r="G714" t="n">
-        <v>1.12251162528992</v>
+        <v>1.12251174449921</v>
       </c>
       <c r="H714" t="n">
         <v>32956</v>
@@ -21133,7 +21133,7 @@
         <v>1.12914597988129</v>
       </c>
       <c r="G716" t="n">
-        <v>1.07554423809052</v>
+        <v>1.0755443572998</v>
       </c>
       <c r="H716" t="n">
         <v>28393</v>
@@ -21220,7 +21220,7 @@
         <v>1.01573896408081</v>
       </c>
       <c r="G719" t="n">
-        <v>0.967520833015442</v>
+        <v>0.967520892620087</v>
       </c>
       <c r="H719" t="n">
         <v>25858</v>
@@ -21336,7 +21336,7 @@
         <v>1.11435401439667</v>
       </c>
       <c r="G723" t="n">
-        <v>1.06145465373993</v>
+        <v>1.06145453453064</v>
       </c>
       <c r="H723" t="n">
         <v>4563</v>
@@ -21365,7 +21365,7 @@
         <v>1.10449194908142</v>
       </c>
       <c r="G724" t="n">
-        <v>1.05206060409546</v>
+        <v>1.05206072330475</v>
       </c>
       <c r="H724" t="n">
         <v>3042</v>
@@ -21800,7 +21800,7 @@
         <v>0.938817977905273</v>
       </c>
       <c r="G739" t="n">
-        <v>0.89425140619278</v>
+        <v>0.894251346588135</v>
       </c>
       <c r="H739" t="n">
         <v>507</v>
@@ -21829,7 +21829,7 @@
         <v>0.938817977905273</v>
       </c>
       <c r="G740" t="n">
-        <v>0.89425140619278</v>
+        <v>0.894251346588135</v>
       </c>
       <c r="H740" t="n">
         <v>1521</v>
@@ -21887,7 +21887,7 @@
         <v>0.926985025405884</v>
       </c>
       <c r="G742" t="n">
-        <v>0.882980108261108</v>
+        <v>0.882980167865753</v>
       </c>
       <c r="H742" t="n">
         <v>11661</v>
@@ -21916,7 +21916,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G743" t="n">
-        <v>0.911159753799438</v>
+        <v>0.911159813404083</v>
       </c>
       <c r="H743" t="n">
         <v>9126</v>
@@ -21945,7 +21945,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G744" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H744" t="n">
         <v>12168</v>
@@ -22061,7 +22061,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G748" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H748" t="n">
         <v>1521</v>
@@ -22206,7 +22206,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G753" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H753" t="n">
         <v>6591</v>
@@ -22264,7 +22264,7 @@
         <v>0.926985025405884</v>
       </c>
       <c r="G755" t="n">
-        <v>0.882980108261108</v>
+        <v>0.882980167865753</v>
       </c>
       <c r="H755" t="n">
         <v>8112</v>
@@ -22322,7 +22322,7 @@
         <v>0.867815017700195</v>
       </c>
       <c r="G757" t="n">
-        <v>0.82661896944046</v>
+        <v>0.826619029045105</v>
       </c>
       <c r="H757" t="n">
         <v>3042</v>
@@ -22351,7 +22351,7 @@
         <v>0.887538015842438</v>
       </c>
       <c r="G758" t="n">
-        <v>0.845405697822571</v>
+        <v>0.845405757427216</v>
       </c>
       <c r="H758" t="n">
         <v>11154</v>
@@ -22380,7 +22380,7 @@
         <v>0.879648983478546</v>
       </c>
       <c r="G759" t="n">
-        <v>0.837891161441803</v>
+        <v>0.837891221046448</v>
       </c>
       <c r="H759" t="n">
         <v>10140</v>
@@ -22409,7 +22409,7 @@
         <v>0.887538015842438</v>
       </c>
       <c r="G760" t="n">
-        <v>0.845405697822571</v>
+        <v>0.845405757427216</v>
       </c>
       <c r="H760" t="n">
         <v>1521</v>
@@ -22699,7 +22699,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G770" t="n">
-        <v>0.911159753799438</v>
+        <v>0.911159813404083</v>
       </c>
       <c r="H770" t="n">
         <v>2028</v>
@@ -22844,7 +22844,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G775" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H775" t="n">
         <v>6591</v>
@@ -22902,7 +22902,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G777" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H777" t="n">
         <v>19266</v>
@@ -22931,7 +22931,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G778" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H778" t="n">
         <v>10140</v>
@@ -22960,7 +22960,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G779" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H779" t="n">
         <v>0</v>
@@ -22989,7 +22989,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G780" t="n">
-        <v>0.911159753799438</v>
+        <v>0.911159813404083</v>
       </c>
       <c r="H780" t="n">
         <v>1521</v>
@@ -23018,7 +23018,7 @@
         <v>0.942762970924377</v>
       </c>
       <c r="G781" t="n">
-        <v>0.898009061813354</v>
+        <v>0.898009121417999</v>
       </c>
       <c r="H781" t="n">
         <v>7098</v>
@@ -23192,7 +23192,7 @@
         <v>0.938817977905273</v>
       </c>
       <c r="G787" t="n">
-        <v>0.89425140619278</v>
+        <v>0.894251346588135</v>
       </c>
       <c r="H787" t="n">
         <v>1014</v>
@@ -23250,7 +23250,7 @@
         <v>1.01573896408081</v>
       </c>
       <c r="G789" t="n">
-        <v>0.967520833015442</v>
+        <v>0.967520892620087</v>
       </c>
       <c r="H789" t="n">
         <v>1521</v>
@@ -23279,7 +23279,7 @@
         <v>0.962486028671265</v>
       </c>
       <c r="G790" t="n">
-        <v>0.916795909404755</v>
+        <v>0.91679584980011</v>
       </c>
       <c r="H790" t="n">
         <v>32449</v>
@@ -23308,7 +23308,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G791" t="n">
-        <v>0.911159753799438</v>
+        <v>0.911159813404083</v>
       </c>
       <c r="H791" t="n">
         <v>16224</v>
@@ -23685,7 +23685,7 @@
         <v>1.09956204891205</v>
       </c>
       <c r="G804" t="n">
-        <v>1.04736483097076</v>
+        <v>1.04736471176147</v>
       </c>
       <c r="H804" t="n">
         <v>18252</v>
@@ -24236,7 +24236,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G823" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H823" t="n">
         <v>23322</v>
@@ -24265,7 +24265,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G824" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -24323,7 +24323,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G826" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H826" t="n">
         <v>3549</v>
@@ -24381,7 +24381,7 @@
         <v>0.972347974777222</v>
       </c>
       <c r="G828" t="n">
-        <v>0.926189661026001</v>
+        <v>0.926189720630646</v>
       </c>
       <c r="H828" t="n">
         <v>25858</v>
@@ -24410,7 +24410,7 @@
         <v>0.978264987468719</v>
       </c>
       <c r="G829" t="n">
-        <v>0.931825816631317</v>
+        <v>0.931825757026672</v>
       </c>
       <c r="H829" t="n">
         <v>10647</v>
@@ -24613,7 +24613,7 @@
         <v>1.04039204120636</v>
       </c>
       <c r="G836" t="n">
-        <v>0.991003572940826</v>
+        <v>0.991003632545471</v>
       </c>
       <c r="H836" t="n">
         <v>55772</v>
@@ -24700,7 +24700,7 @@
         <v>1.01573896408081</v>
       </c>
       <c r="G839" t="n">
-        <v>0.967520833015442</v>
+        <v>0.967520892620087</v>
       </c>
       <c r="H839" t="n">
         <v>14703</v>
@@ -24729,7 +24729,7 @@
         <v>0.99108499288559</v>
       </c>
       <c r="G840" t="n">
-        <v>0.944037199020386</v>
+        <v>0.944037258625031</v>
       </c>
       <c r="H840" t="n">
         <v>19773</v>
@@ -24787,7 +24787,7 @@
         <v>0.982209026813507</v>
       </c>
       <c r="G842" t="n">
-        <v>0.935582637786865</v>
+        <v>0.93558257818222</v>
       </c>
       <c r="H842" t="n">
         <v>6591</v>
@@ -24816,7 +24816,7 @@
         <v>0.982209026813507</v>
       </c>
       <c r="G843" t="n">
-        <v>0.935582637786865</v>
+        <v>0.93558257818222</v>
       </c>
       <c r="H843" t="n">
         <v>0</v>
@@ -24874,7 +24874,7 @@
         <v>0.99108499288559</v>
       </c>
       <c r="G845" t="n">
-        <v>0.944037199020386</v>
+        <v>0.944037258625031</v>
       </c>
       <c r="H845" t="n">
         <v>12168</v>
@@ -25106,7 +25106,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G853" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H853" t="n">
         <v>18759</v>
@@ -25164,7 +25164,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G855" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H855" t="n">
         <v>3549</v>
@@ -25193,7 +25193,7 @@
         <v>0.982209026813507</v>
       </c>
       <c r="G856" t="n">
-        <v>0.935582637786865</v>
+        <v>0.93558257818222</v>
       </c>
       <c r="H856" t="n">
         <v>5070</v>
@@ -25222,7 +25222,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G857" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H857" t="n">
         <v>12675</v>
@@ -25396,7 +25396,7 @@
         <v>0.978264987468719</v>
       </c>
       <c r="G863" t="n">
-        <v>0.931825816631317</v>
+        <v>0.931825757026672</v>
       </c>
       <c r="H863" t="n">
         <v>17745</v>
@@ -25425,7 +25425,7 @@
         <v>0.978264987468719</v>
       </c>
       <c r="G864" t="n">
-        <v>0.931825816631317</v>
+        <v>0.931825757026672</v>
       </c>
       <c r="H864" t="n">
         <v>0</v>
@@ -25512,7 +25512,7 @@
         <v>0.950652003288269</v>
       </c>
       <c r="G867" t="n">
-        <v>0.905523598194122</v>
+        <v>0.905523657798767</v>
       </c>
       <c r="H867" t="n">
         <v>9126</v>
@@ -25686,7 +25686,7 @@
         <v>0.90923398733139</v>
       </c>
       <c r="G873" t="n">
-        <v>0.866071820259094</v>
+        <v>0.866071760654449</v>
       </c>
       <c r="H873" t="n">
         <v>7098</v>
@@ -25715,7 +25715,7 @@
         <v>0.915151000022888</v>
       </c>
       <c r="G874" t="n">
-        <v>0.871707916259766</v>
+        <v>0.871707856655121</v>
       </c>
       <c r="H874" t="n">
         <v>7098</v>
@@ -25831,7 +25831,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G878" t="n">
-        <v>0.674445748329163</v>
+        <v>0.674445807933807</v>
       </c>
       <c r="H878" t="n">
         <v>31435</v>
@@ -25860,7 +25860,7 @@
         <v>0.769200026988983</v>
       </c>
       <c r="G879" t="n">
-        <v>0.732685327529907</v>
+        <v>0.732685387134552</v>
       </c>
       <c r="H879" t="n">
         <v>49687</v>
@@ -25889,7 +25889,7 @@
         <v>0.769200026988983</v>
       </c>
       <c r="G880" t="n">
-        <v>0.732685327529907</v>
+        <v>0.732685387134552</v>
       </c>
       <c r="H880" t="n">
         <v>21801</v>
@@ -26005,7 +26005,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G884" t="n">
-        <v>0.674445748329163</v>
+        <v>0.674445807933807</v>
       </c>
       <c r="H884" t="n">
         <v>10647</v>
@@ -26063,7 +26063,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G886" t="n">
-        <v>0.674445748329163</v>
+        <v>0.674445807933807</v>
       </c>
       <c r="H886" t="n">
         <v>7605</v>
@@ -26121,7 +26121,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G888" t="n">
-        <v>0.723291516304016</v>
+        <v>0.723291456699371</v>
       </c>
       <c r="H888" t="n">
         <v>12168</v>
@@ -26150,7 +26150,7 @@
         <v>0.745531976222992</v>
       </c>
       <c r="G889" t="n">
-        <v>0.710140883922577</v>
+        <v>0.710140824317932</v>
       </c>
       <c r="H889" t="n">
         <v>10647</v>
@@ -26179,7 +26179,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G890" t="n">
-        <v>0.723291516304016</v>
+        <v>0.723291456699371</v>
       </c>
       <c r="H890" t="n">
         <v>1521</v>
@@ -26208,7 +26208,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G891" t="n">
-        <v>0.723291516304016</v>
+        <v>0.723291456699371</v>
       </c>
       <c r="H891" t="n">
         <v>0</v>
@@ -26266,7 +26266,7 @@
         <v>0.77708899974823</v>
       </c>
       <c r="G893" t="n">
-        <v>0.74019980430603</v>
+        <v>0.740199863910675</v>
       </c>
       <c r="H893" t="n">
         <v>29914</v>
@@ -26353,7 +26353,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G896" t="n">
-        <v>0.723291516304016</v>
+        <v>0.723291456699371</v>
       </c>
       <c r="H896" t="n">
         <v>30928</v>
@@ -26411,7 +26411,7 @@
         <v>0.729753971099854</v>
       </c>
       <c r="G898" t="n">
-        <v>0.695111870765686</v>
+        <v>0.695111811161041</v>
       </c>
       <c r="H898" t="n">
         <v>15210</v>
@@ -26440,7 +26440,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G899" t="n">
-        <v>0.702626407146454</v>
+        <v>0.702626347541809</v>
       </c>
       <c r="H899" t="n">
         <v>52223</v>
@@ -26585,7 +26585,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G904" t="n">
-        <v>0.548574864864349</v>
+        <v>0.548574805259705</v>
       </c>
       <c r="H904" t="n">
         <v>50702</v>
@@ -26672,7 +26672,7 @@
         <v>0.508854985237122</v>
       </c>
       <c r="G907" t="n">
-        <v>0.484699159860611</v>
+        <v>0.484699130058289</v>
       </c>
       <c r="H907" t="n">
         <v>76053</v>
@@ -26817,7 +26817,7 @@
         <v>0.492091000080109</v>
       </c>
       <c r="G912" t="n">
-        <v>0.468730986118317</v>
+        <v>0.468730956315994</v>
       </c>
       <c r="H912" t="n">
         <v>19773</v>
@@ -26846,7 +26846,7 @@
         <v>0.492091000080109</v>
       </c>
       <c r="G913" t="n">
-        <v>0.468730986118317</v>
+        <v>0.468730956315994</v>
       </c>
       <c r="H913" t="n">
         <v>507</v>
@@ -26991,7 +26991,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G918" t="n">
-        <v>0.432096719741821</v>
+        <v>0.432096689939499</v>
       </c>
       <c r="H918" t="n">
         <v>18759</v>
@@ -27049,7 +27049,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G920" t="n">
-        <v>0.418945133686066</v>
+        <v>0.418945103883743</v>
       </c>
       <c r="H920" t="n">
         <v>7098</v>
@@ -27107,7 +27107,7 @@
         <v>0.481243014335632</v>
       </c>
       <c r="G922" t="n">
-        <v>0.458397954702377</v>
+        <v>0.458397924900055</v>
       </c>
       <c r="H922" t="n">
         <v>51209</v>
@@ -27194,7 +27194,7 @@
         <v>0.44574099779129</v>
       </c>
       <c r="G925" t="n">
-        <v>0.424581229686737</v>
+        <v>0.424581259489059</v>
       </c>
       <c r="H925" t="n">
         <v>198751</v>
@@ -27252,7 +27252,7 @@
         <v>0.449685990810394</v>
       </c>
       <c r="G927" t="n">
-        <v>0.428338974714279</v>
+        <v>0.428338944911957</v>
       </c>
       <c r="H927" t="n">
         <v>507</v>
@@ -27339,7 +27339,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G930" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H930" t="n">
         <v>36505</v>
@@ -27368,7 +27368,7 @@
         <v>0.469408988952637</v>
       </c>
       <c r="G931" t="n">
-        <v>0.44712570309639</v>
+        <v>0.447125673294067</v>
       </c>
       <c r="H931" t="n">
         <v>24843</v>
@@ -27571,7 +27571,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G938" t="n">
-        <v>0.494093030691147</v>
+        <v>0.494093000888824</v>
       </c>
       <c r="H938" t="n">
         <v>40561</v>
@@ -27600,7 +27600,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G939" t="n">
-        <v>0.494093030691147</v>
+        <v>0.494093000888824</v>
       </c>
       <c r="H939" t="n">
         <v>19773</v>
@@ -27629,7 +27629,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G940" t="n">
-        <v>0.494093030691147</v>
+        <v>0.494093000888824</v>
       </c>
       <c r="H940" t="n">
         <v>20787</v>
@@ -27716,7 +27716,7 @@
         <v>0.506883025169373</v>
       </c>
       <c r="G943" t="n">
-        <v>0.482820779085159</v>
+        <v>0.482820808887482</v>
       </c>
       <c r="H943" t="n">
         <v>100389</v>
@@ -27861,7 +27861,7 @@
         <v>0.489131987094879</v>
       </c>
       <c r="G948" t="n">
-        <v>0.465912401676178</v>
+        <v>0.4659124314785</v>
       </c>
       <c r="H948" t="n">
         <v>3549</v>
@@ -28035,7 +28035,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G954" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H954" t="n">
         <v>103939</v>
@@ -28064,7 +28064,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G955" t="n">
-        <v>0.419885277748108</v>
+        <v>0.41988530755043</v>
       </c>
       <c r="H955" t="n">
         <v>17238</v>
@@ -28238,7 +28238,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G961" t="n">
-        <v>0.437731862068176</v>
+        <v>0.437731891870499</v>
       </c>
       <c r="H961" t="n">
         <v>415756</v>
@@ -28296,7 +28296,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G963" t="n">
-        <v>0.462154716253281</v>
+        <v>0.462154686450958</v>
       </c>
       <c r="H963" t="n">
         <v>130811</v>
@@ -28731,7 +28731,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G978" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H978" t="n">
         <v>47659</v>
@@ -28818,7 +28818,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G981" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H981" t="n">
         <v>45631</v>
@@ -28876,7 +28876,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G983" t="n">
-        <v>0.432096719741821</v>
+        <v>0.432096689939499</v>
       </c>
       <c r="H983" t="n">
         <v>39547</v>
@@ -28992,7 +28992,7 @@
         <v>0.469408988952637</v>
       </c>
       <c r="G987" t="n">
-        <v>0.44712570309639</v>
+        <v>0.447125673294067</v>
       </c>
       <c r="H987" t="n">
         <v>6084</v>
@@ -29079,7 +29079,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G990" t="n">
-        <v>0.432096719741821</v>
+        <v>0.432096689939499</v>
       </c>
       <c r="H990" t="n">
         <v>19266</v>
@@ -29108,7 +29108,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G991" t="n">
-        <v>0.432096719741821</v>
+        <v>0.432096689939499</v>
       </c>
       <c r="H991" t="n">
         <v>19266</v>
@@ -29137,7 +29137,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G992" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H992" t="n">
         <v>9633</v>
@@ -29166,7 +29166,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G993" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H993" t="n">
         <v>104446</v>
@@ -29195,7 +29195,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G994" t="n">
-        <v>0.419885277748108</v>
+        <v>0.41988530755043</v>
       </c>
       <c r="H994" t="n">
         <v>175935</v>
@@ -29224,7 +29224,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G995" t="n">
-        <v>0.418945133686066</v>
+        <v>0.418945103883743</v>
       </c>
       <c r="H995" t="n">
         <v>67940</v>
@@ -29253,7 +29253,7 @@
         <v>0.449685990810394</v>
       </c>
       <c r="G996" t="n">
-        <v>0.428338974714279</v>
+        <v>0.428338944911957</v>
       </c>
       <c r="H996" t="n">
         <v>116107</v>
@@ -29282,7 +29282,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G997" t="n">
-        <v>0.422702848911285</v>
+        <v>0.422702878713608</v>
       </c>
       <c r="H997" t="n">
         <v>52730</v>
@@ -29398,7 +29398,7 @@
         <v>0.55224597454071</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.526030302047729</v>
+        <v>0.526030361652374</v>
       </c>
       <c r="H1001" t="n">
         <v>693096</v>
@@ -29543,7 +29543,7 @@
         <v>0.603525996208191</v>
       </c>
       <c r="G1006" t="n">
-        <v>0.574876070022583</v>
+        <v>0.574876010417938</v>
       </c>
       <c r="H1006" t="n">
         <v>259594</v>
@@ -29601,7 +29601,7 @@
         <v>0.694252014160156</v>
       </c>
       <c r="G1008" t="n">
-        <v>0.661295235157013</v>
+        <v>0.661295175552368</v>
       </c>
       <c r="H1008" t="n">
         <v>497893</v>
@@ -29717,7 +29717,7 @@
         <v>0.639028012752533</v>
       </c>
       <c r="G1012" t="n">
-        <v>0.608692765235901</v>
+        <v>0.608692705631256</v>
       </c>
       <c r="H1012" t="n">
         <v>271255</v>
@@ -29775,7 +29775,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.634993970394135</v>
+        <v>0.63499391078949</v>
       </c>
       <c r="H1014" t="n">
         <v>67433</v>
@@ -29862,7 +29862,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1017" t="n">
-        <v>0.604934990406036</v>
+        <v>0.604935050010681</v>
       </c>
       <c r="H1017" t="n">
         <v>279875</v>
@@ -29949,7 +29949,7 @@
         <v>0.611415028572083</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.582390606403351</v>
+        <v>0.582390546798706</v>
       </c>
       <c r="H1020" t="n">
         <v>99882</v>
@@ -30094,7 +30094,7 @@
         <v>0.765254974365234</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.728927612304688</v>
+        <v>0.728927552700043</v>
       </c>
       <c r="H1025" t="n">
         <v>870046</v>
@@ -30268,7 +30268,7 @@
         <v>0.706085979938507</v>
       </c>
       <c r="G1031" t="n">
-        <v>0.672567367553711</v>
+        <v>0.672567427158356</v>
       </c>
       <c r="H1031" t="n">
         <v>155148</v>
@@ -30471,7 +30471,7 @@
         <v>0.668612003326416</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.636872351169586</v>
+        <v>0.636872291564941</v>
       </c>
       <c r="H1038" t="n">
         <v>98361</v>
@@ -30616,7 +30616,7 @@
         <v>0.69819700717926</v>
       </c>
       <c r="G1043" t="n">
-        <v>0.665052890777588</v>
+        <v>0.665052950382233</v>
       </c>
       <c r="H1043" t="n">
         <v>186583</v>
@@ -30906,7 +30906,7 @@
         <v>0.550274014472961</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.524151980876923</v>
+        <v>0.524151921272278</v>
       </c>
       <c r="H1053" t="n">
         <v>205850</v>
@@ -30935,7 +30935,7 @@
         <v>0.571968972682953</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.54481703042984</v>
+        <v>0.544817090034485</v>
       </c>
       <c r="H1054" t="n">
         <v>95826</v>
@@ -30964,7 +30964,7 @@
         <v>0.55224597454071</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.526030302047729</v>
+        <v>0.526030361652374</v>
       </c>
       <c r="H1055" t="n">
         <v>104953</v>
@@ -31051,7 +31051,7 @@
         <v>0.520689010620117</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.495971411466599</v>
+        <v>0.495971381664276</v>
       </c>
       <c r="H1058" t="n">
         <v>18759</v>
@@ -31225,7 +31225,7 @@
         <v>0.36191800236702</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.344737380743027</v>
+        <v>0.344737410545349</v>
       </c>
       <c r="H1064" t="n">
         <v>127769</v>
@@ -31312,7 +31312,7 @@
         <v>0.318527013063431</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.303406238555908</v>
+        <v>0.303406208753586</v>
       </c>
       <c r="H1067" t="n">
         <v>33463</v>
@@ -31370,7 +31370,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.309981554746628</v>
+        <v>0.309981524944305</v>
       </c>
       <c r="H1069" t="n">
         <v>42082</v>
@@ -31399,7 +31399,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1070" t="n">
         <v>74531</v>
@@ -31515,7 +31515,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.345676630735397</v>
+        <v>0.345676600933075</v>
       </c>
       <c r="H1074" t="n">
         <v>38026</v>
@@ -31718,7 +31718,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.394522279500961</v>
+        <v>0.394522309303284</v>
       </c>
       <c r="H1081" t="n">
         <v>79095</v>
@@ -31776,7 +31776,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.387946963310242</v>
+        <v>0.387946993112564</v>
       </c>
       <c r="H1083" t="n">
         <v>106474</v>
@@ -31863,7 +31863,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.387946963310242</v>
+        <v>0.387946993112564</v>
       </c>
       <c r="H1086" t="n">
         <v>16224</v>
@@ -31892,7 +31892,7 @@
         <v>0.400377988815308</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.381371647119522</v>
+        <v>0.381371676921844</v>
       </c>
       <c r="H1087" t="n">
         <v>33463</v>
@@ -31921,7 +31921,7 @@
         <v>0.384600013494492</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.366342663764954</v>
+        <v>0.366342693567276</v>
       </c>
       <c r="H1088" t="n">
         <v>21294</v>
@@ -32066,7 +32066,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1093" t="n">
         <v>9633</v>
@@ -32124,7 +32124,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1095" t="n">
         <v>16224</v>
@@ -32211,7 +32211,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1098" t="n">
         <v>44617</v>
@@ -32269,7 +32269,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.336283683776855</v>
+        <v>0.336283713579178</v>
       </c>
       <c r="H1100" t="n">
         <v>250974</v>
@@ -32298,7 +32298,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.337222874164581</v>
+        <v>0.337222903966904</v>
       </c>
       <c r="H1101" t="n">
         <v>48673</v>
@@ -32356,7 +32356,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1103" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1103" t="n">
         <v>9126</v>
@@ -32385,7 +32385,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1104" t="n">
         <v>12168</v>
@@ -32443,7 +32443,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1106" t="n">
-        <v>0.337222874164581</v>
+        <v>0.337222903966904</v>
       </c>
       <c r="H1106" t="n">
         <v>25351</v>
@@ -32472,7 +32472,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1107" t="n">
         <v>7605</v>
@@ -32530,7 +32530,7 @@
         <v>0.369807004928589</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.352251887321472</v>
+        <v>0.352251917123795</v>
       </c>
       <c r="H1109" t="n">
         <v>23829</v>
@@ -32559,7 +32559,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.432096719741821</v>
+        <v>0.432096689939499</v>
       </c>
       <c r="H1110" t="n">
         <v>456825</v>
@@ -32617,7 +32617,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.39264389872551</v>
+        <v>0.392643928527832</v>
       </c>
       <c r="H1112" t="n">
         <v>188104</v>
@@ -32646,7 +32646,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.394522279500961</v>
+        <v>0.394522309303284</v>
       </c>
       <c r="H1113" t="n">
         <v>101911</v>
@@ -32704,7 +32704,7 @@
         <v>0.398405998945236</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.37949326634407</v>
+        <v>0.379493296146393</v>
       </c>
       <c r="H1115" t="n">
         <v>63377</v>
@@ -32849,7 +32849,7 @@
         <v>0.475326001644135</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.452761799097061</v>
+        <v>0.452761828899384</v>
       </c>
       <c r="H1120" t="n">
         <v>63884</v>
@@ -33110,7 +33110,7 @@
         <v>0.484201014041901</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.461215496063232</v>
+        <v>0.461215525865555</v>
       </c>
       <c r="H1129" t="n">
         <v>51209</v>
@@ -33284,7 +33284,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G1135" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H1135" t="n">
         <v>11154</v>
@@ -33342,7 +33342,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G1137" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H1137" t="n">
         <v>3549</v>
@@ -33371,7 +33371,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.462154716253281</v>
+        <v>0.462154686450958</v>
       </c>
       <c r="H1138" t="n">
         <v>16224</v>
@@ -33400,7 +33400,7 @@
         <v>0.475326001644135</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.452761799097061</v>
+        <v>0.452761828899384</v>
       </c>
       <c r="H1139" t="n">
         <v>8619</v>
@@ -33458,7 +33458,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1141" t="n">
-        <v>0.437731862068176</v>
+        <v>0.437731891870499</v>
       </c>
       <c r="H1141" t="n">
         <v>9126</v>
@@ -33516,7 +33516,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1143" t="n">
-        <v>0.548574864864349</v>
+        <v>0.548574805259705</v>
       </c>
       <c r="H1143" t="n">
         <v>882214</v>
@@ -33545,7 +33545,7 @@
         <v>0.524634003639221</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.499729096889496</v>
+        <v>0.499729126691818</v>
       </c>
       <c r="H1144" t="n">
         <v>914157</v>
@@ -33748,7 +33748,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.462154716253281</v>
+        <v>0.462154686450958</v>
       </c>
       <c r="H1151" t="n">
         <v>49687</v>
@@ -33806,7 +33806,7 @@
         <v>0.489131987094879</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.465912401676178</v>
+        <v>0.4659124314785</v>
       </c>
       <c r="H1153" t="n">
         <v>48673</v>
@@ -33980,7 +33980,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.437731862068176</v>
+        <v>0.437731891870499</v>
       </c>
       <c r="H1159" t="n">
         <v>34984</v>
@@ -34009,7 +34009,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.422702848911285</v>
+        <v>0.422702878713608</v>
       </c>
       <c r="H1160" t="n">
         <v>45124</v>
@@ -34096,7 +34096,7 @@
         <v>0.449685990810394</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.428338974714279</v>
+        <v>0.428338944911957</v>
       </c>
       <c r="H1163" t="n">
         <v>51716</v>
@@ -34241,7 +34241,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.387946963310242</v>
+        <v>0.387946993112564</v>
       </c>
       <c r="H1168" t="n">
         <v>12168</v>
@@ -34357,7 +34357,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.419885277748108</v>
+        <v>0.41988530755043</v>
       </c>
       <c r="H1172" t="n">
         <v>116107</v>
@@ -34386,7 +34386,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.422702848911285</v>
+        <v>0.422702878713608</v>
       </c>
       <c r="H1173" t="n">
         <v>52730</v>
@@ -34415,7 +34415,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.422702848911285</v>
+        <v>0.422702878713608</v>
       </c>
       <c r="H1174" t="n">
         <v>0</v>
@@ -34473,7 +34473,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.418945133686066</v>
+        <v>0.418945103883743</v>
       </c>
       <c r="H1176" t="n">
         <v>15717</v>
@@ -34502,7 +34502,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.418945133686066</v>
+        <v>0.418945103883743</v>
       </c>
       <c r="H1177" t="n">
         <v>8619</v>
@@ -34531,7 +34531,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.418945133686066</v>
+        <v>0.418945103883743</v>
       </c>
       <c r="H1178" t="n">
         <v>1014</v>
@@ -34676,7 +34676,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1183" t="n">
         <v>10140</v>
@@ -35024,7 +35024,7 @@
         <v>0.429962992668152</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.409552216529846</v>
+        <v>0.409552246332169</v>
       </c>
       <c r="H1195" t="n">
         <v>142472</v>
@@ -35053,7 +35053,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1196" t="n">
         <v>87207</v>
@@ -35256,7 +35256,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1203" t="n">
         <v>65405</v>
@@ -35314,7 +35314,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1205" t="n">
         <v>3042</v>
@@ -35401,7 +35401,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1208" t="n">
         <v>241341</v>
@@ -35430,7 +35430,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.39264389872551</v>
+        <v>0.392643928527832</v>
       </c>
       <c r="H1209" t="n">
         <v>62363</v>
@@ -35575,7 +35575,7 @@
         <v>0.429962992668152</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.409552216529846</v>
+        <v>0.409552246332169</v>
       </c>
       <c r="H1214" t="n">
         <v>40561</v>
@@ -35836,7 +35836,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1223" t="n">
         <v>77067</v>
@@ -35923,7 +35923,7 @@
         <v>0.402350008487701</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.383250087499619</v>
+        <v>0.383250057697296</v>
       </c>
       <c r="H1226" t="n">
         <v>10647</v>
@@ -36097,7 +36097,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.39264389872551</v>
+        <v>0.392643928527832</v>
       </c>
       <c r="H1232" t="n">
         <v>11154</v>
@@ -36184,7 +36184,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1235" t="n">
         <v>115093</v>
@@ -36213,7 +36213,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.394522279500961</v>
+        <v>0.394522309303284</v>
       </c>
       <c r="H1236" t="n">
         <v>85179</v>
@@ -36300,7 +36300,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.394522279500961</v>
+        <v>0.394522309303284</v>
       </c>
       <c r="H1239" t="n">
         <v>109516</v>
@@ -36329,7 +36329,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1240" t="n">
         <v>40561</v>
@@ -36358,7 +36358,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1241" t="n">
         <v>76053</v>
@@ -36416,7 +36416,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.422702848911285</v>
+        <v>0.422702878713608</v>
       </c>
       <c r="H1243" t="n">
         <v>481161</v>
@@ -36561,7 +36561,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H1248" t="n">
         <v>119149</v>
@@ -36648,7 +36648,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.494093030691147</v>
+        <v>0.494093000888824</v>
       </c>
       <c r="H1251" t="n">
         <v>617043</v>
@@ -36822,7 +36822,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.462154716253281</v>
+        <v>0.462154686450958</v>
       </c>
       <c r="H1257" t="n">
         <v>29407</v>
@@ -37054,7 +37054,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.437731862068176</v>
+        <v>0.437731891870499</v>
       </c>
       <c r="H1265" t="n">
         <v>59321</v>
@@ -37170,7 +37170,7 @@
         <v>0.44574099779129</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.424581229686737</v>
+        <v>0.424581259489059</v>
       </c>
       <c r="H1269" t="n">
         <v>12168</v>
@@ -37315,7 +37315,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.437731862068176</v>
+        <v>0.437731891870499</v>
       </c>
       <c r="H1274" t="n">
         <v>93798</v>
@@ -37431,7 +37431,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.422702848911285</v>
+        <v>0.422702878713608</v>
       </c>
       <c r="H1278" t="n">
         <v>9126</v>
@@ -37547,7 +37547,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.419885277748108</v>
+        <v>0.41988530755043</v>
       </c>
       <c r="H1282" t="n">
         <v>6084</v>
@@ -37837,7 +37837,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1292" t="n">
         <v>94305</v>
@@ -37895,7 +37895,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1294" t="n">
         <v>116107</v>
@@ -37924,7 +37924,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1295" t="n">
         <v>29407</v>
@@ -37953,7 +37953,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.394522279500961</v>
+        <v>0.394522309303284</v>
       </c>
       <c r="H1296" t="n">
         <v>84672</v>
@@ -38011,7 +38011,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1298" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1298" t="n">
         <v>76560</v>
@@ -38243,7 +38243,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1306" t="n">
         <v>4056</v>
@@ -38330,7 +38330,7 @@
         <v>0.418128997087479</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.398280024528503</v>
+        <v>0.398279994726181</v>
       </c>
       <c r="H1309" t="n">
         <v>13689</v>
@@ -38359,7 +38359,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1310" t="n">
         <v>1521</v>
@@ -38388,7 +38388,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1311" t="n">
         <v>3042</v>
@@ -38504,7 +38504,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.387946963310242</v>
+        <v>0.387946993112564</v>
       </c>
       <c r="H1315" t="n">
         <v>4563</v>
@@ -38533,7 +38533,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.387946963310242</v>
+        <v>0.387946993112564</v>
       </c>
       <c r="H1316" t="n">
         <v>0</v>
@@ -38591,7 +38591,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1318" t="n">
         <v>115600</v>
@@ -38765,7 +38765,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1324" t="n">
         <v>25858</v>
@@ -38794,7 +38794,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1325" t="n">
-        <v>0.39264389872551</v>
+        <v>0.392643928527832</v>
       </c>
       <c r="H1325" t="n">
         <v>1521</v>
@@ -38968,7 +38968,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1331" t="n">
         <v>29407</v>
@@ -38997,7 +38997,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1332" t="n">
-        <v>0.394522279500961</v>
+        <v>0.394522309303284</v>
       </c>
       <c r="H1332" t="n">
         <v>14703</v>
@@ -39026,7 +39026,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1333" t="n">
         <v>4056</v>
@@ -39113,7 +39113,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1336" t="n">
         <v>39040</v>
@@ -39142,7 +39142,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1337" t="n">
-        <v>0.39264389872551</v>
+        <v>0.392643928527832</v>
       </c>
       <c r="H1337" t="n">
         <v>11154</v>
@@ -39200,7 +39200,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1339" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1339" t="n">
         <v>2028</v>
@@ -39258,7 +39258,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1341" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1341" t="n">
         <v>10647</v>
@@ -39287,7 +39287,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1342" t="n">
         <v>0</v>
@@ -39316,7 +39316,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1343" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1343" t="n">
         <v>11154</v>
@@ -39490,7 +39490,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.387946963310242</v>
+        <v>0.387946993112564</v>
       </c>
       <c r="H1349" t="n">
         <v>7098</v>
@@ -39519,7 +39519,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.394522279500961</v>
+        <v>0.394522309303284</v>
       </c>
       <c r="H1350" t="n">
         <v>19266</v>
@@ -39606,7 +39606,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1353" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1353" t="n">
         <v>41575</v>
@@ -39693,7 +39693,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1356" t="n">
         <v>9633</v>
@@ -39722,7 +39722,7 @@
         <v>0.429962992668152</v>
       </c>
       <c r="G1357" t="n">
-        <v>0.409552216529846</v>
+        <v>0.409552246332169</v>
       </c>
       <c r="H1357" t="n">
         <v>12168</v>
@@ -39896,7 +39896,7 @@
         <v>0.398405998945236</v>
       </c>
       <c r="G1363" t="n">
-        <v>0.37949326634407</v>
+        <v>0.379493296146393</v>
       </c>
       <c r="H1363" t="n">
         <v>57293</v>
@@ -39983,7 +39983,7 @@
         <v>0.398405998945236</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.37949326634407</v>
+        <v>0.379493296146393</v>
       </c>
       <c r="H1366" t="n">
         <v>5577</v>
@@ -40041,7 +40041,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1368" t="n">
-        <v>0.387946963310242</v>
+        <v>0.387946993112564</v>
       </c>
       <c r="H1368" t="n">
         <v>7098</v>
@@ -40070,7 +40070,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1369" t="n">
         <v>49687</v>
@@ -40099,7 +40099,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1370" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1370" t="n">
         <v>171372</v>
@@ -40244,7 +40244,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1375" t="n">
         <v>56786</v>
@@ -40302,7 +40302,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1377" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1377" t="n">
         <v>23829</v>
@@ -40505,7 +40505,7 @@
         <v>0.402350008487701</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.383250087499619</v>
+        <v>0.383250057697296</v>
       </c>
       <c r="H1384" t="n">
         <v>46138</v>
@@ -40534,7 +40534,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1385" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1385" t="n">
         <v>136895</v>
@@ -40621,7 +40621,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.364463329315186</v>
+        <v>0.364463359117508</v>
       </c>
       <c r="H1388" t="n">
         <v>115093</v>
@@ -40650,7 +40650,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.360706567764282</v>
+        <v>0.36070653796196</v>
       </c>
       <c r="H1389" t="n">
         <v>14703</v>
@@ -40708,7 +40708,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1391" t="n">
-        <v>0.364463329315186</v>
+        <v>0.364463359117508</v>
       </c>
       <c r="H1391" t="n">
         <v>68954</v>
@@ -40766,7 +40766,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.361645758152008</v>
+        <v>0.361645728349686</v>
       </c>
       <c r="H1393" t="n">
         <v>43096</v>
@@ -40795,7 +40795,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.360706567764282</v>
+        <v>0.36070653796196</v>
       </c>
       <c r="H1394" t="n">
         <v>37012</v>
@@ -40911,7 +40911,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1398" t="n">
-        <v>0.364463329315186</v>
+        <v>0.364463359117508</v>
       </c>
       <c r="H1398" t="n">
         <v>18759</v>
@@ -40940,7 +40940,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.364463329315186</v>
+        <v>0.364463359117508</v>
       </c>
       <c r="H1399" t="n">
         <v>0</v>
@@ -41172,7 +41172,7 @@
         <v>0.368820995092392</v>
       </c>
       <c r="G1407" t="n">
-        <v>0.351312696933746</v>
+        <v>0.351312726736069</v>
       </c>
       <c r="H1407" t="n">
         <v>23829</v>
@@ -41201,7 +41201,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.347555935382843</v>
+        <v>0.347555905580521</v>
       </c>
       <c r="H1408" t="n">
         <v>35998</v>
@@ -41288,7 +41288,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1411" t="n">
         <v>29407</v>
@@ -41375,7 +41375,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1414" t="n">
-        <v>0.337222874164581</v>
+        <v>0.337222903966904</v>
       </c>
       <c r="H1414" t="n">
         <v>21801</v>
@@ -41404,7 +41404,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.337222874164581</v>
+        <v>0.337222903966904</v>
       </c>
       <c r="H1415" t="n">
         <v>24336</v>
@@ -41433,7 +41433,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.337222874164581</v>
+        <v>0.337222903966904</v>
       </c>
       <c r="H1416" t="n">
         <v>0</v>
@@ -41462,7 +41462,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.337222874164581</v>
+        <v>0.337222903966904</v>
       </c>
       <c r="H1417" t="n">
         <v>5577</v>
@@ -41491,7 +41491,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.336283683776855</v>
+        <v>0.336283713579178</v>
       </c>
       <c r="H1418" t="n">
         <v>29407</v>
@@ -41665,7 +41665,7 @@
         <v>0.34909799695015</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.332525998353958</v>
+        <v>0.332525968551636</v>
       </c>
       <c r="H1424" t="n">
         <v>60842</v>
@@ -41752,7 +41752,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.345676630735397</v>
+        <v>0.345676600933075</v>
       </c>
       <c r="H1427" t="n">
         <v>30928</v>
@@ -41781,7 +41781,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.345676630735397</v>
+        <v>0.345676600933075</v>
       </c>
       <c r="H1428" t="n">
         <v>32956</v>
@@ -41810,7 +41810,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.345676630735397</v>
+        <v>0.345676600933075</v>
       </c>
       <c r="H1429" t="n">
         <v>0</v>
@@ -42013,7 +42013,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1436" t="n">
-        <v>0.347555935382843</v>
+        <v>0.347555905580521</v>
       </c>
       <c r="H1436" t="n">
         <v>8112</v>
@@ -42332,7 +42332,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.355070441961288</v>
+        <v>0.355070412158966</v>
       </c>
       <c r="H1447" t="n">
         <v>14196</v>
@@ -42361,7 +42361,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.355070441961288</v>
+        <v>0.355070412158966</v>
       </c>
       <c r="H1448" t="n">
         <v>31942</v>
@@ -42419,7 +42419,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1450" t="n">
-        <v>0.361645758152008</v>
+        <v>0.361645728349686</v>
       </c>
       <c r="H1450" t="n">
         <v>3549</v>
@@ -42448,7 +42448,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.361645758152008</v>
+        <v>0.361645728349686</v>
       </c>
       <c r="H1451" t="n">
         <v>0</v>
@@ -42680,7 +42680,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.364463329315186</v>
+        <v>0.364463359117508</v>
       </c>
       <c r="H1459" t="n">
         <v>120163</v>
@@ -42767,7 +42767,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1462" t="n">
-        <v>0.364463329315186</v>
+        <v>0.364463359117508</v>
       </c>
       <c r="H1462" t="n">
         <v>46645</v>
@@ -42912,7 +42912,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1467" t="n">
-        <v>0.360706567764282</v>
+        <v>0.36070653796196</v>
       </c>
       <c r="H1467" t="n">
         <v>6591</v>
@@ -42941,7 +42941,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.355070441961288</v>
+        <v>0.355070412158966</v>
       </c>
       <c r="H1468" t="n">
         <v>18759</v>
@@ -43028,7 +43028,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.347555935382843</v>
+        <v>0.347555905580521</v>
       </c>
       <c r="H1471" t="n">
         <v>5070</v>
@@ -43231,7 +43231,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1478" t="n">
-        <v>0.360706567764282</v>
+        <v>0.36070653796196</v>
       </c>
       <c r="H1478" t="n">
         <v>1521</v>
@@ -43260,7 +43260,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.361645758152008</v>
+        <v>0.361645728349686</v>
       </c>
       <c r="H1479" t="n">
         <v>5070</v>
@@ -43405,7 +43405,7 @@
         <v>0.384600013494492</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.366342663764954</v>
+        <v>0.366342693567276</v>
       </c>
       <c r="H1484" t="n">
         <v>2535</v>
@@ -43434,7 +43434,7 @@
         <v>0.384600013494492</v>
       </c>
       <c r="G1485" t="n">
-        <v>0.366342663764954</v>
+        <v>0.366342693567276</v>
       </c>
       <c r="H1485" t="n">
         <v>0</v>
@@ -43492,7 +43492,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1487" t="n">
-        <v>0.361645758152008</v>
+        <v>0.361645728349686</v>
       </c>
       <c r="H1487" t="n">
         <v>11661</v>
@@ -43521,7 +43521,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1488" t="n">
-        <v>0.355070441961288</v>
+        <v>0.355070412158966</v>
       </c>
       <c r="H1488" t="n">
         <v>17745</v>
@@ -43550,7 +43550,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1489" t="n">
-        <v>0.355070441961288</v>
+        <v>0.355070412158966</v>
       </c>
       <c r="H1489" t="n">
         <v>0</v>
@@ -43579,7 +43579,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1490" t="n">
-        <v>0.355070441961288</v>
+        <v>0.355070412158966</v>
       </c>
       <c r="H1490" t="n">
         <v>0</v>
@@ -43695,7 +43695,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.345676630735397</v>
+        <v>0.345676600933075</v>
       </c>
       <c r="H1494" t="n">
         <v>40561</v>
@@ -43724,7 +43724,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.345676630735397</v>
+        <v>0.345676600933075</v>
       </c>
       <c r="H1495" t="n">
         <v>31435</v>
@@ -44014,7 +44014,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.321253746747971</v>
+        <v>0.321253776550293</v>
       </c>
       <c r="H1505" t="n">
         <v>17238</v>
@@ -44072,7 +44072,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.336283683776855</v>
+        <v>0.336283713579178</v>
       </c>
       <c r="H1507" t="n">
         <v>8112</v>
@@ -44101,7 +44101,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1508" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1508" t="n">
         <v>9126</v>
@@ -44362,7 +44362,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1517" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1517" t="n">
         <v>41068</v>
@@ -44391,7 +44391,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1518" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1518" t="n">
         <v>15717</v>
@@ -44565,7 +44565,7 @@
         <v>0.319514006376266</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.30434638261795</v>
+        <v>0.304346352815628</v>
       </c>
       <c r="H1524" t="n">
         <v>88728</v>
@@ -44594,7 +44594,7 @@
         <v>0.347126007080078</v>
       </c>
       <c r="G1525" t="n">
-        <v>0.330647617578506</v>
+        <v>0.330647587776184</v>
       </c>
       <c r="H1525" t="n">
         <v>83151</v>
@@ -44710,7 +44710,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1529" t="n">
-        <v>0.321253746747971</v>
+        <v>0.321253776550293</v>
       </c>
       <c r="H1529" t="n">
         <v>28393</v>
@@ -44768,7 +44768,7 @@
         <v>0.330361008644104</v>
       </c>
       <c r="G1531" t="n">
-        <v>0.314678430557251</v>
+        <v>0.314678460359573</v>
       </c>
       <c r="H1531" t="n">
         <v>50194</v>
@@ -45029,7 +45029,7 @@
         <v>0.347126007080078</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.330647617578506</v>
+        <v>0.330647587776184</v>
       </c>
       <c r="H1540" t="n">
         <v>26365</v>
@@ -45087,7 +45087,7 @@
         <v>0.333319991827011</v>
       </c>
       <c r="G1542" t="n">
-        <v>0.317496985197067</v>
+        <v>0.317496955394745</v>
       </c>
       <c r="H1542" t="n">
         <v>20280</v>
@@ -45116,7 +45116,7 @@
         <v>0.333319991827011</v>
       </c>
       <c r="G1543" t="n">
-        <v>0.317496985197067</v>
+        <v>0.317496955394745</v>
       </c>
       <c r="H1543" t="n">
         <v>41068</v>
@@ -45174,7 +45174,7 @@
         <v>0.334306001663208</v>
       </c>
       <c r="G1545" t="n">
-        <v>0.318436175584793</v>
+        <v>0.318436145782471</v>
       </c>
       <c r="H1545" t="n">
         <v>1521</v>
@@ -45203,7 +45203,7 @@
         <v>0.334306001663208</v>
       </c>
       <c r="G1546" t="n">
-        <v>0.318436175584793</v>
+        <v>0.318436145782471</v>
       </c>
       <c r="H1546" t="n">
         <v>0</v>
@@ -45232,7 +45232,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1547" t="n">
-        <v>0.309981554746628</v>
+        <v>0.309981524944305</v>
       </c>
       <c r="H1547" t="n">
         <v>12168</v>
@@ -45261,7 +45261,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.309981554746628</v>
+        <v>0.309981524944305</v>
       </c>
       <c r="H1548" t="n">
         <v>8619</v>
@@ -45522,7 +45522,7 @@
         <v>0.333319991827011</v>
       </c>
       <c r="G1557" t="n">
-        <v>0.317496985197067</v>
+        <v>0.317496955394745</v>
       </c>
       <c r="H1557" t="n">
         <v>13182</v>
@@ -45551,7 +45551,7 @@
         <v>0.366849005222321</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.349434316158295</v>
+        <v>0.349434345960617</v>
       </c>
       <c r="H1558" t="n">
         <v>454289</v>
@@ -45667,7 +45667,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.321253746747971</v>
+        <v>0.321253776550293</v>
       </c>
       <c r="H1562" t="n">
         <v>39547</v>
@@ -45696,7 +45696,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1563" t="n">
-        <v>0.309981554746628</v>
+        <v>0.309981524944305</v>
       </c>
       <c r="H1563" t="n">
         <v>19266</v>
@@ -45870,7 +45870,7 @@
         <v>0.330361008644104</v>
       </c>
       <c r="G1569" t="n">
-        <v>0.314678430557251</v>
+        <v>0.314678460359573</v>
       </c>
       <c r="H1569" t="n">
         <v>24843</v>
@@ -45899,7 +45899,7 @@
         <v>0.330361008644104</v>
       </c>
       <c r="G1570" t="n">
-        <v>0.314678430557251</v>
+        <v>0.314678460359573</v>
       </c>
       <c r="H1570" t="n">
         <v>0</v>
@@ -46015,7 +46015,7 @@
         <v>0.307680010795593</v>
       </c>
       <c r="G1574" t="n">
-        <v>0.293074131011963</v>
+        <v>0.293074160814285</v>
       </c>
       <c r="H1574" t="n">
         <v>35491</v>
@@ -46044,7 +46044,7 @@
         <v>0.301762998104095</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.287438035011292</v>
+        <v>0.287438005208969</v>
       </c>
       <c r="H1575" t="n">
         <v>19266</v>
@@ -46073,7 +46073,7 @@
         <v>0.304720997810364</v>
       </c>
       <c r="G1576" t="n">
-        <v>0.290255606174469</v>
+        <v>0.290255576372147</v>
       </c>
       <c r="H1576" t="n">
         <v>5070</v>
@@ -46276,7 +46276,7 @@
         <v>0.316554993391037</v>
       </c>
       <c r="G1583" t="n">
-        <v>0.301527798175812</v>
+        <v>0.301527827978134</v>
       </c>
       <c r="H1583" t="n">
         <v>4056</v>
@@ -46305,7 +46305,7 @@
         <v>0.304720997810364</v>
       </c>
       <c r="G1584" t="n">
-        <v>0.290255606174469</v>
+        <v>0.290255576372147</v>
       </c>
       <c r="H1584" t="n">
         <v>19773</v>
@@ -46392,7 +46392,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1587" t="n">
-        <v>0.309981554746628</v>
+        <v>0.309981524944305</v>
       </c>
       <c r="H1587" t="n">
         <v>9633</v>
@@ -46537,7 +46537,7 @@
         <v>0.323457986116409</v>
       </c>
       <c r="G1592" t="n">
-        <v>0.308103114366531</v>
+        <v>0.308103144168854</v>
       </c>
       <c r="H1592" t="n">
         <v>3042</v>
@@ -46595,7 +46595,7 @@
         <v>0.321485996246338</v>
       </c>
       <c r="G1594" t="n">
-        <v>0.30622473359108</v>
+        <v>0.306224763393402</v>
       </c>
       <c r="H1594" t="n">
         <v>12168</v>
@@ -46885,7 +46885,7 @@
         <v>0.307680010795593</v>
       </c>
       <c r="G1604" t="n">
-        <v>0.293074131011963</v>
+        <v>0.293074160814285</v>
       </c>
       <c r="H1604" t="n">
         <v>6591</v>
@@ -46914,7 +46914,7 @@
         <v>0.307680010795593</v>
       </c>
       <c r="G1605" t="n">
-        <v>0.293074131011963</v>
+        <v>0.293074160814285</v>
       </c>
       <c r="H1605" t="n">
         <v>0</v>
@@ -46943,7 +46943,7 @@
         <v>0.308665990829468</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.294013291597366</v>
+        <v>0.294013321399689</v>
       </c>
       <c r="H1606" t="n">
         <v>6084</v>
@@ -46972,7 +46972,7 @@
         <v>0.301762998104095</v>
       </c>
       <c r="G1607" t="n">
-        <v>0.287438035011292</v>
+        <v>0.287438005208969</v>
       </c>
       <c r="H1607" t="n">
         <v>6084</v>
@@ -47146,7 +47146,7 @@
         <v>0.34909799695015</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.332525998353958</v>
+        <v>0.332525968551636</v>
       </c>
       <c r="H1613" t="n">
         <v>2028</v>
@@ -47175,7 +47175,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.321253746747971</v>
+        <v>0.321253776550293</v>
       </c>
       <c r="H1614" t="n">
         <v>13689</v>
@@ -47262,7 +47262,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1617" t="n">
-        <v>0.347555935382843</v>
+        <v>0.347555905580521</v>
       </c>
       <c r="H1617" t="n">
         <v>191653</v>
@@ -47320,7 +47320,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.336283683776855</v>
+        <v>0.336283713579178</v>
       </c>
       <c r="H1619" t="n">
         <v>56279</v>
@@ -47349,7 +47349,7 @@
         <v>0.363889992237091</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.346615791320801</v>
+        <v>0.346615761518478</v>
       </c>
       <c r="H1620" t="n">
         <v>17238</v>
@@ -47407,7 +47407,7 @@
         <v>0.368820995092392</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.351312696933746</v>
+        <v>0.351312726736069</v>
       </c>
       <c r="H1622" t="n">
         <v>476598</v>
@@ -47465,7 +47465,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1624" t="n">
-        <v>0.364463329315186</v>
+        <v>0.364463359117508</v>
       </c>
       <c r="H1624" t="n">
         <v>62363</v>
@@ -47697,7 +47697,7 @@
         <v>0.674529016017914</v>
       </c>
       <c r="G1632" t="n">
-        <v>0.642508506774902</v>
+        <v>0.642508447170258</v>
       </c>
       <c r="H1632" t="n">
         <v>674336</v>
@@ -47755,7 +47755,7 @@
         <v>0.639028012752533</v>
       </c>
       <c r="G1634" t="n">
-        <v>0.608692765235901</v>
+        <v>0.608692705631256</v>
       </c>
       <c r="H1634" t="n">
         <v>336661</v>
@@ -47871,7 +47871,7 @@
         <v>0.611415028572083</v>
       </c>
       <c r="G1638" t="n">
-        <v>0.582390606403351</v>
+        <v>0.582390546798706</v>
       </c>
       <c r="H1638" t="n">
         <v>162246</v>
@@ -47900,7 +47900,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1639" t="n">
-        <v>0.548574864864349</v>
+        <v>0.548574805259705</v>
       </c>
       <c r="H1639" t="n">
         <v>162246</v>
@@ -47987,7 +47987,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1642" t="n">
-        <v>0.548574864864349</v>
+        <v>0.548574805259705</v>
       </c>
       <c r="H1642" t="n">
         <v>111037</v>
@@ -48045,7 +48045,7 @@
         <v>0.571968972682953</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.54481703042984</v>
+        <v>0.544817090034485</v>
       </c>
       <c r="H1644" t="n">
         <v>66926</v>
@@ -48364,7 +48364,7 @@
         <v>0.702140986919403</v>
       </c>
       <c r="G1655" t="n">
-        <v>0.668809711933136</v>
+        <v>0.668809652328491</v>
       </c>
       <c r="H1655" t="n">
         <v>78081</v>
@@ -48625,7 +48625,7 @@
         <v>0.615360021591187</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.586148262023926</v>
+        <v>0.586148321628571</v>
       </c>
       <c r="H1664" t="n">
         <v>8619</v>
@@ -48712,7 +48712,7 @@
         <v>0.639028012752533</v>
       </c>
       <c r="G1667" t="n">
-        <v>0.608692765235901</v>
+        <v>0.608692705631256</v>
       </c>
       <c r="H1667" t="n">
         <v>56786</v>
@@ -48741,7 +48741,7 @@
         <v>0.64691698551178</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.616207242012024</v>
+        <v>0.616207182407379</v>
       </c>
       <c r="H1668" t="n">
         <v>59321</v>
@@ -48857,7 +48857,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.604934990406036</v>
+        <v>0.604935050010681</v>
       </c>
       <c r="H1672" t="n">
         <v>31942</v>
@@ -48915,7 +48915,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1674" t="n">
-        <v>0.604934990406036</v>
+        <v>0.604935050010681</v>
       </c>
       <c r="H1674" t="n">
         <v>70982</v>
@@ -49147,7 +49147,7 @@
         <v>0.615360021591187</v>
       </c>
       <c r="G1682" t="n">
-        <v>0.586148262023926</v>
+        <v>0.586148321628571</v>
       </c>
       <c r="H1682" t="n">
         <v>13689</v>
@@ -49176,7 +49176,7 @@
         <v>0.583802998065948</v>
       </c>
       <c r="G1683" t="n">
-        <v>0.556089341640472</v>
+        <v>0.556089282035828</v>
       </c>
       <c r="H1683" t="n">
         <v>214976</v>
@@ -49263,7 +49263,7 @@
         <v>0.571968972682953</v>
       </c>
       <c r="G1686" t="n">
-        <v>0.54481703042984</v>
+        <v>0.544817090034485</v>
       </c>
       <c r="H1686" t="n">
         <v>9126</v>
@@ -49350,7 +49350,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1689" t="n">
-        <v>0.548574864864349</v>
+        <v>0.548574805259705</v>
       </c>
       <c r="H1689" t="n">
         <v>25858</v>
@@ -49408,7 +49408,7 @@
         <v>0.595637023448944</v>
       </c>
       <c r="G1691" t="n">
-        <v>0.56736159324646</v>
+        <v>0.567361533641815</v>
       </c>
       <c r="H1691" t="n">
         <v>12675</v>
@@ -49524,7 +49524,7 @@
         <v>0.603525996208191</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.574876070022583</v>
+        <v>0.574876010417938</v>
       </c>
       <c r="H1695" t="n">
         <v>28900</v>
@@ -49582,7 +49582,7 @@
         <v>0.595637023448944</v>
       </c>
       <c r="G1697" t="n">
-        <v>0.56736159324646</v>
+        <v>0.567361533641815</v>
       </c>
       <c r="H1697" t="n">
         <v>3549</v>
@@ -49669,7 +49669,7 @@
         <v>0.607470989227295</v>
       </c>
       <c r="G1700" t="n">
-        <v>0.578633725643158</v>
+        <v>0.578633785247803</v>
       </c>
       <c r="H1700" t="n">
         <v>25351</v>
@@ -49698,7 +49698,7 @@
         <v>0.607470989227295</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.578633725643158</v>
+        <v>0.578633785247803</v>
       </c>
       <c r="H1701" t="n">
         <v>19773</v>
@@ -49727,7 +49727,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.604934990406036</v>
+        <v>0.604935050010681</v>
       </c>
       <c r="H1702" t="n">
         <v>64391</v>
@@ -49872,7 +49872,7 @@
         <v>0.662694990634918</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.63123619556427</v>
+        <v>0.631236255168915</v>
       </c>
       <c r="H1707" t="n">
         <v>123712</v>
@@ -50075,7 +50075,7 @@
         <v>0.702140986919403</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.668809711933136</v>
+        <v>0.668809652328491</v>
       </c>
       <c r="H1714" t="n">
         <v>115093</v>
@@ -50162,7 +50162,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1717" t="n">
-        <v>0.674445748329163</v>
+        <v>0.674445807933807</v>
       </c>
       <c r="H1717" t="n">
         <v>1126598</v>
@@ -50249,7 +50249,7 @@
         <v>0.702140986919403</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.668809711933136</v>
+        <v>0.668809652328491</v>
       </c>
       <c r="H1720" t="n">
         <v>385842</v>
@@ -50423,7 +50423,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1726" t="n">
-        <v>0.634993970394135</v>
+        <v>0.63499391078949</v>
       </c>
       <c r="H1726" t="n">
         <v>82644</v>
@@ -50481,7 +50481,7 @@
         <v>0.668612003326416</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.636872351169586</v>
+        <v>0.636872291564941</v>
       </c>
       <c r="H1728" t="n">
         <v>132332</v>
@@ -50510,7 +50510,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1729" t="n">
-        <v>0.634993970394135</v>
+        <v>0.63499391078949</v>
       </c>
       <c r="H1729" t="n">
         <v>9126</v>
@@ -50713,7 +50713,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.674445748329163</v>
+        <v>0.674445807933807</v>
       </c>
       <c r="H1736" t="n">
         <v>307254</v>
@@ -50800,7 +50800,7 @@
         <v>0.674529016017914</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.642508506774902</v>
+        <v>0.642508447170258</v>
       </c>
       <c r="H1739" t="n">
         <v>100389</v>
@@ -50887,7 +50887,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1742" t="n">
-        <v>0.634993970394135</v>
+        <v>0.63499391078949</v>
       </c>
       <c r="H1742" t="n">
         <v>41575</v>
@@ -50945,7 +50945,7 @@
         <v>0.662694990634918</v>
       </c>
       <c r="G1744" t="n">
-        <v>0.63123619556427</v>
+        <v>0.631236255168915</v>
       </c>
       <c r="H1744" t="n">
         <v>26365</v>
@@ -51119,7 +51119,7 @@
         <v>0.64691698551178</v>
       </c>
       <c r="G1750" t="n">
-        <v>0.616207242012024</v>
+        <v>0.616207182407379</v>
       </c>
       <c r="H1750" t="n">
         <v>328548</v>
@@ -51264,7 +51264,7 @@
         <v>0.694252014160156</v>
       </c>
       <c r="G1755" t="n">
-        <v>0.661295235157013</v>
+        <v>0.661295175552368</v>
       </c>
       <c r="H1755" t="n">
         <v>19773</v>
@@ -51496,7 +51496,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1763" t="n">
-        <v>0.634993970394135</v>
+        <v>0.63499391078949</v>
       </c>
       <c r="H1763" t="n">
         <v>228159</v>
@@ -51699,7 +51699,7 @@
         <v>0.69819700717926</v>
       </c>
       <c r="G1770" t="n">
-        <v>0.665052890777588</v>
+        <v>0.665052950382233</v>
       </c>
       <c r="H1770" t="n">
         <v>90249</v>
@@ -52279,7 +52279,7 @@
         <v>0.674529016017914</v>
       </c>
       <c r="G1790" t="n">
-        <v>0.642508506774902</v>
+        <v>0.642508447170258</v>
       </c>
       <c r="H1790" t="n">
         <v>5577</v>
@@ -52337,7 +52337,7 @@
         <v>0.694252014160156</v>
       </c>
       <c r="G1792" t="n">
-        <v>0.661295235157013</v>
+        <v>0.661295175552368</v>
       </c>
       <c r="H1792" t="n">
         <v>99882</v>
@@ -52656,7 +52656,7 @@
         <v>0.69819700717926</v>
       </c>
       <c r="G1803" t="n">
-        <v>0.665052890777588</v>
+        <v>0.665052950382233</v>
       </c>
       <c r="H1803" t="n">
         <v>735179</v>
@@ -52830,7 +52830,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1809" t="n">
-        <v>0.674445748329163</v>
+        <v>0.674445807933807</v>
       </c>
       <c r="H1809" t="n">
         <v>43603</v>
@@ -52859,7 +52859,7 @@
         <v>0.706085979938507</v>
       </c>
       <c r="G1810" t="n">
-        <v>0.672567367553711</v>
+        <v>0.672567427158356</v>
       </c>
       <c r="H1810" t="n">
         <v>60335</v>
@@ -53207,7 +53207,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.674445748329163</v>
+        <v>0.674445807933807</v>
       </c>
       <c r="H1822" t="n">
         <v>42589</v>
@@ -53265,7 +53265,7 @@
         <v>0.733698010444641</v>
       </c>
       <c r="G1824" t="n">
-        <v>0.698868632316589</v>
+        <v>0.698868691921234</v>
       </c>
       <c r="H1824" t="n">
         <v>185569</v>
@@ -53323,7 +53323,7 @@
         <v>0.729753971099854</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.695111870765686</v>
+        <v>0.695111811161041</v>
       </c>
       <c r="H1826" t="n">
         <v>63884</v>
@@ -53410,7 +53410,7 @@
         <v>0.745531976222992</v>
       </c>
       <c r="G1829" t="n">
-        <v>0.710140883922577</v>
+        <v>0.710140824317932</v>
       </c>
       <c r="H1829" t="n">
         <v>101911</v>
@@ -53439,7 +53439,7 @@
         <v>0.745531976222992</v>
       </c>
       <c r="G1830" t="n">
-        <v>0.710140883922577</v>
+        <v>0.710140824317932</v>
       </c>
       <c r="H1830" t="n">
         <v>85179</v>
@@ -53497,7 +53497,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1832" t="n">
-        <v>0.71202027797699</v>
+        <v>0.712020218372345</v>
       </c>
       <c r="H1832" t="n">
         <v>27886</v>
@@ -53555,7 +53555,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1834" t="n">
-        <v>0.71202027797699</v>
+        <v>0.712020218372345</v>
       </c>
       <c r="H1834" t="n">
         <v>23829</v>
@@ -53584,7 +53584,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G1835" t="n">
-        <v>0.702626407146454</v>
+        <v>0.702626347541809</v>
       </c>
       <c r="H1835" t="n">
         <v>106981</v>
@@ -53613,7 +53613,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.702626407146454</v>
+        <v>0.702626347541809</v>
       </c>
       <c r="H1836" t="n">
         <v>2535</v>
@@ -53642,7 +53642,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G1837" t="n">
-        <v>0.702626407146454</v>
+        <v>0.702626347541809</v>
       </c>
       <c r="H1837" t="n">
         <v>14703</v>
@@ -53700,7 +53700,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1839" t="n">
-        <v>0.71202027797699</v>
+        <v>0.712020218372345</v>
       </c>
       <c r="H1839" t="n">
         <v>37519</v>
@@ -53729,7 +53729,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.71202027797699</v>
+        <v>0.712020218372345</v>
       </c>
       <c r="H1840" t="n">
         <v>5577</v>
@@ -53990,7 +53990,7 @@
         <v>0.796811997890472</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.758986532688141</v>
+        <v>0.758986592292786</v>
       </c>
       <c r="H1849" t="n">
         <v>942043</v>
@@ -54193,7 +54193,7 @@
         <v>0.942762970924377</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.898009061813354</v>
+        <v>0.898009121417999</v>
       </c>
       <c r="H1856" t="n">
         <v>243876</v>
@@ -54338,7 +54338,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1861" t="n">
-        <v>1.08963513374329</v>
+        <v>1.089635014534</v>
       </c>
       <c r="H1861" t="n">
         <v>336661</v>
@@ -54425,7 +54425,7 @@
         <v>1.10449194908142</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.05206060409546</v>
+        <v>1.05206072330475</v>
       </c>
       <c r="H1864" t="n">
         <v>324999</v>
@@ -54512,7 +54512,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.08963513374329</v>
+        <v>1.089635014534</v>
       </c>
       <c r="H1867" t="n">
         <v>737207</v>
@@ -54599,7 +54599,7 @@
         <v>1.10449194908142</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.05206060409546</v>
+        <v>1.05206072330475</v>
       </c>
       <c r="H1870" t="n">
         <v>120163</v>
@@ -54657,7 +54657,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.08963513374329</v>
+        <v>1.089635014534</v>
       </c>
       <c r="H1872" t="n">
         <v>374180</v>
@@ -54744,7 +54744,7 @@
         <v>1.15873098373413</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.10372495651245</v>
+        <v>1.10372483730316</v>
       </c>
       <c r="H1875" t="n">
         <v>117121</v>
@@ -54773,7 +54773,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.08963513374329</v>
+        <v>1.089635014534</v>
       </c>
       <c r="H1876" t="n">
         <v>24336</v>
@@ -54860,7 +54860,7 @@
         <v>1.15873098373413</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.10372495651245</v>
+        <v>1.10372483730316</v>
       </c>
       <c r="H1879" t="n">
         <v>75038</v>
@@ -54976,7 +54976,7 @@
         <v>1.2179000377655</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.16008508205414</v>
+        <v>1.16008520126343</v>
       </c>
       <c r="H1883" t="n">
         <v>52730</v>
@@ -55324,7 +55324,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.20705235004425</v>
+        <v>1.20705246925354</v>
       </c>
       <c r="H1895" t="n">
         <v>59321</v>
@@ -55382,7 +55382,7 @@
         <v>1.25734603404999</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.19765865802765</v>
+        <v>1.19765853881836</v>
       </c>
       <c r="H1897" t="n">
         <v>146021</v>
@@ -55411,7 +55411,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.20705235004425</v>
+        <v>1.20705246925354</v>
       </c>
       <c r="H1898" t="n">
         <v>88221</v>
@@ -55440,7 +55440,7 @@
         <v>1.27213895320892</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.21174919605255</v>
+        <v>1.21174931526184</v>
       </c>
       <c r="H1899" t="n">
         <v>80616</v>
@@ -55701,7 +55701,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.20705235004425</v>
+        <v>1.20705246925354</v>
       </c>
       <c r="H1908" t="n">
         <v>396489</v>
@@ -56020,7 +56020,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.24932265281677</v>
+        <v>1.24932277202606</v>
       </c>
       <c r="H1919" t="n">
         <v>359984</v>
@@ -56049,7 +56049,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.3197728395462</v>
+        <v>1.31977272033691</v>
       </c>
       <c r="H1920" t="n">
         <v>571411</v>
@@ -56107,7 +56107,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.3338634967804</v>
+        <v>1.33386361598969</v>
       </c>
       <c r="H1922" t="n">
         <v>187090</v>
@@ -56310,7 +56310,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.30568301677704</v>
+        <v>1.30568289756775</v>
       </c>
       <c r="H1929" t="n">
         <v>545553</v>
@@ -56368,7 +56368,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.23523306846619</v>
+        <v>1.2352329492569</v>
       </c>
       <c r="H1931" t="n">
         <v>329055</v>
@@ -56397,7 +56397,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G1932" t="n">
-        <v>1.24932265281677</v>
+        <v>1.24932277202606</v>
       </c>
       <c r="H1932" t="n">
         <v>112558</v>
@@ -80052,7 +80052,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="D2748" t="n">
-        <v>3.38000011444092</v>
+        <v>3.42000007629395</v>
       </c>
       <c r="E2748" t="n">
         <v>3.38000011444092</v>
@@ -80067,6 +80067,35 @@
         <v>3500</v>
       </c>
       <c r="I2748" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2749">
+      <c r="A2749" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2749" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C2749" t="n">
+        <v>3.41000008583069</v>
+      </c>
+      <c r="D2749" t="n">
+        <v>3.41000008583069</v>
+      </c>
+      <c r="E2749" t="n">
+        <v>3.22000002861023</v>
+      </c>
+      <c r="F2749" t="n">
+        <v>3.36999988555908</v>
+      </c>
+      <c r="G2749" t="n">
+        <v>3.36999988555908</v>
+      </c>
+      <c r="H2749" t="n">
+        <v>42000</v>
+      </c>
+      <c r="I2749" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -80099,6 +80099,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>3.42000007629395</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>3.44000005722046</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>3.33999991416931</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>17500</v>
+      </c>
+      <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G2" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -456,7 +456,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G3" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -485,7 +485,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -514,7 +514,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G5" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -543,7 +543,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G6" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>2.90521001815796</v>
       </c>
       <c r="G32" t="n">
-        <v>2.76729702949524</v>
+        <v>2.76729679107666</v>
       </c>
       <c r="H32" t="n">
         <v>1521</v>
@@ -1355,7 +1355,7 @@
         <v>2.85984706878662</v>
       </c>
       <c r="G34" t="n">
-        <v>2.72408723831177</v>
+        <v>2.72408747673035</v>
       </c>
       <c r="H34" t="n">
         <v>5070</v>
@@ -1442,7 +1442,7 @@
         <v>2.90718293190002</v>
       </c>
       <c r="G37" t="n">
-        <v>2.76917624473572</v>
+        <v>2.76917600631714</v>
       </c>
       <c r="H37" t="n">
         <v>1014</v>
@@ -1471,7 +1471,7 @@
         <v>2.90718293190002</v>
       </c>
       <c r="G38" t="n">
-        <v>2.76917624473572</v>
+        <v>2.76917600631714</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>2.90718293190002</v>
       </c>
       <c r="G39" t="n">
-        <v>2.76917624473572</v>
+        <v>2.76917600631714</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G45" t="n">
-        <v>2.66772723197937</v>
+        <v>2.66772699356079</v>
       </c>
       <c r="H45" t="n">
         <v>2028</v>
@@ -3965,7 +3965,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G124" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H124" t="n">
         <v>507</v>
@@ -3994,7 +3994,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G125" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G126" t="n">
-        <v>2.66772723197937</v>
+        <v>2.66772699356079</v>
       </c>
       <c r="H126" t="n">
         <v>10140</v>
@@ -4052,7 +4052,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G127" t="n">
-        <v>2.66772723197937</v>
+        <v>2.66772699356079</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G128" t="n">
-        <v>2.66772723197937</v>
+        <v>2.66772699356079</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G129" t="n">
-        <v>2.66772723197937</v>
+        <v>2.66772699356079</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G130" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H130" t="n">
         <v>2028</v>
@@ -4168,7 +4168,7 @@
         <v>2.72967505455017</v>
       </c>
       <c r="G131" t="n">
-        <v>2.60009479522705</v>
+        <v>2.60009455680847</v>
       </c>
       <c r="H131" t="n">
         <v>507</v>
@@ -4197,7 +4197,7 @@
         <v>2.72967505455017</v>
       </c>
       <c r="G132" t="n">
-        <v>2.60009479522705</v>
+        <v>2.60009455680847</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4226,7 +4226,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G133" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H133" t="n">
         <v>6591</v>
@@ -4255,7 +4255,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G136" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G137" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G138" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G139" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G140" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G141" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G142" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>2.58372402191162</v>
       </c>
       <c r="G143" t="n">
-        <v>2.46107220649719</v>
+        <v>2.46107196807861</v>
       </c>
       <c r="H143" t="n">
         <v>1014</v>
@@ -4545,7 +4545,7 @@
         <v>2.58372402191162</v>
       </c>
       <c r="G144" t="n">
-        <v>2.46107220649719</v>
+        <v>2.46107196807861</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>2.48905301094055</v>
       </c>
       <c r="G145" t="n">
-        <v>2.37089514732361</v>
+        <v>2.37089538574219</v>
       </c>
       <c r="H145" t="n">
         <v>507</v>
@@ -4603,7 +4603,7 @@
         <v>2.48905301094055</v>
       </c>
       <c r="G146" t="n">
-        <v>2.37089514732361</v>
+        <v>2.37089538574219</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>2.35690808296204</v>
       </c>
       <c r="G148" t="n">
-        <v>2.24502348899841</v>
+        <v>2.24502325057983</v>
       </c>
       <c r="H148" t="n">
         <v>2028</v>
@@ -4835,7 +4835,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G154" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H154" t="n">
         <v>1014</v>
@@ -4864,7 +4864,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G155" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G156" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G157" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G158" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G159" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>2.56400108337402</v>
       </c>
       <c r="G173" t="n">
-        <v>2.44228529930115</v>
+        <v>2.44228553771973</v>
       </c>
       <c r="H173" t="n">
         <v>1014</v>
@@ -5618,7 +5618,7 @@
         <v>2.58372402191162</v>
       </c>
       <c r="G181" t="n">
-        <v>2.46107220649719</v>
+        <v>2.46107196807861</v>
       </c>
       <c r="H181" t="n">
         <v>2028</v>
@@ -6227,7 +6227,7 @@
         <v>2.56400108337402</v>
       </c>
       <c r="G202" t="n">
-        <v>2.44228529930115</v>
+        <v>2.44228553771973</v>
       </c>
       <c r="H202" t="n">
         <v>10140</v>
@@ -6256,7 +6256,7 @@
         <v>2.56991791725159</v>
       </c>
       <c r="G203" t="n">
-        <v>2.44792127609253</v>
+        <v>2.44792151451111</v>
       </c>
       <c r="H203" t="n">
         <v>3549</v>
@@ -6314,7 +6314,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G205" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H205" t="n">
         <v>2028</v>
@@ -6343,7 +6343,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G206" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -6372,7 +6372,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G207" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G208" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G209" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G210" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>2.46144104003906</v>
       </c>
       <c r="G214" t="n">
-        <v>2.3445942401886</v>
+        <v>2.34459400177002</v>
       </c>
       <c r="H214" t="n">
         <v>7605</v>
@@ -7242,7 +7242,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G237" t="n">
-        <v>2.20744967460632</v>
+        <v>2.2074499130249</v>
       </c>
       <c r="H237" t="n">
         <v>2028</v>
@@ -7271,7 +7271,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G238" t="n">
-        <v>2.20744967460632</v>
+        <v>2.2074499130249</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G239" t="n">
-        <v>2.20744967460632</v>
+        <v>2.2074499130249</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G240" t="n">
-        <v>2.20744967460632</v>
+        <v>2.2074499130249</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G241" t="n">
-        <v>2.20744967460632</v>
+        <v>2.2074499130249</v>
       </c>
       <c r="H241" t="n">
         <v>1521</v>
@@ -7764,7 +7764,7 @@
         <v>2.36874198913574</v>
       </c>
       <c r="G255" t="n">
-        <v>2.25629568099976</v>
+        <v>2.25629544258118</v>
       </c>
       <c r="H255" t="n">
         <v>21294</v>
@@ -7880,7 +7880,7 @@
         <v>2.17151093482971</v>
       </c>
       <c r="G259" t="n">
-        <v>2.06842732429504</v>
+        <v>2.06842708587646</v>
       </c>
       <c r="H259" t="n">
         <v>1014</v>
@@ -7909,7 +7909,7 @@
         <v>2.09853601455688</v>
       </c>
       <c r="G260" t="n">
-        <v>1.99891650676727</v>
+        <v>1.99891638755798</v>
       </c>
       <c r="H260" t="n">
         <v>5577</v>
@@ -7967,7 +7967,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G262" t="n">
-        <v>2.08345723152161</v>
+        <v>2.08345699310303</v>
       </c>
       <c r="H262" t="n">
         <v>507</v>
@@ -7996,7 +7996,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G263" t="n">
-        <v>2.08345723152161</v>
+        <v>2.08345699310303</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G264" t="n">
-        <v>2.08345723152161</v>
+        <v>2.08345699310303</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G265" t="n">
-        <v>2.08345723152161</v>
+        <v>2.08345699310303</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G266" t="n">
-        <v>2.01958131790161</v>
+        <v>2.01958155632019</v>
       </c>
       <c r="H266" t="n">
         <v>2535</v>
@@ -8112,7 +8112,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G267" t="n">
-        <v>2.01958131790161</v>
+        <v>2.01958155632019</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G280" t="n">
-        <v>2.01958131790161</v>
+        <v>2.01958155632019</v>
       </c>
       <c r="H280" t="n">
         <v>507</v>
@@ -8518,7 +8518,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G281" t="n">
-        <v>2.01958131790161</v>
+        <v>2.01958155632019</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G282" t="n">
-        <v>2.01958131790161</v>
+        <v>2.01958155632019</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G283" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H283" t="n">
         <v>1014</v>
@@ -8605,7 +8605,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G284" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G285" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>2.18531799316406</v>
       </c>
       <c r="G305" t="n">
-        <v>2.08157896995544</v>
+        <v>2.08157873153687</v>
       </c>
       <c r="H305" t="n">
         <v>7605</v>
@@ -9301,7 +9301,7 @@
         <v>1.98216998577118</v>
       </c>
       <c r="G308" t="n">
-        <v>1.88807451725006</v>
+        <v>1.88807439804077</v>
       </c>
       <c r="H308" t="n">
         <v>8112</v>
@@ -9330,7 +9330,7 @@
         <v>1.94272398948669</v>
       </c>
       <c r="G309" t="n">
-        <v>1.85050106048584</v>
+        <v>1.85050094127655</v>
       </c>
       <c r="H309" t="n">
         <v>1014</v>
@@ -9823,7 +9823,7 @@
         <v>2.15770506858826</v>
       </c>
       <c r="G326" t="n">
-        <v>2.05527663230896</v>
+        <v>2.05527687072754</v>
       </c>
       <c r="H326" t="n">
         <v>12675</v>
@@ -9997,7 +9997,7 @@
         <v>2.18926191329956</v>
       </c>
       <c r="G332" t="n">
-        <v>2.08533573150635</v>
+        <v>2.08533549308777</v>
       </c>
       <c r="H332" t="n">
         <v>2535</v>
@@ -10026,7 +10026,7 @@
         <v>2.18926191329956</v>
       </c>
       <c r="G333" t="n">
-        <v>2.08533573150635</v>
+        <v>2.08533549308777</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G340" t="n">
-        <v>2.02521753311157</v>
+        <v>2.02521777153015</v>
       </c>
       <c r="H340" t="n">
         <v>507</v>
@@ -10345,7 +10345,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G344" t="n">
-        <v>2.02521753311157</v>
+        <v>2.02521777153015</v>
       </c>
       <c r="H344" t="n">
         <v>2535</v>
@@ -10374,7 +10374,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G345" t="n">
-        <v>2.02521753311157</v>
+        <v>2.02521777153015</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G346" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H346" t="n">
         <v>3042</v>
@@ -10432,7 +10432,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G347" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>2.00189304351807</v>
       </c>
       <c r="G365" t="n">
-        <v>1.90686118602753</v>
+        <v>1.90686130523682</v>
       </c>
       <c r="H365" t="n">
         <v>507</v>
@@ -11041,7 +11041,7 @@
         <v>2.71981310844421</v>
       </c>
       <c r="G368" t="n">
-        <v>2.59070110321045</v>
+        <v>2.59070086479187</v>
       </c>
       <c r="H368" t="n">
         <v>70475</v>
@@ -11070,7 +11070,7 @@
         <v>2.41607809066772</v>
       </c>
       <c r="G369" t="n">
-        <v>2.30138444900513</v>
+        <v>2.30138468742371</v>
       </c>
       <c r="H369" t="n">
         <v>39040</v>
@@ -11099,7 +11099,7 @@
         <v>2.25829291343689</v>
       </c>
       <c r="G370" t="n">
-        <v>2.15108966827393</v>
+        <v>2.15108942985535</v>
       </c>
       <c r="H370" t="n">
         <v>18759</v>
@@ -11215,7 +11215,7 @@
         <v>2.17940092086792</v>
       </c>
       <c r="G374" t="n">
-        <v>2.07594275474548</v>
+        <v>2.0759425163269</v>
       </c>
       <c r="H374" t="n">
         <v>7098</v>
@@ -11273,7 +11273,7 @@
         <v>2.17940092086792</v>
       </c>
       <c r="G376" t="n">
-        <v>2.07594275474548</v>
+        <v>2.0759425163269</v>
       </c>
       <c r="H376" t="n">
         <v>3549</v>
@@ -11331,7 +11331,7 @@
         <v>2.20701289176941</v>
       </c>
       <c r="G378" t="n">
-        <v>2.10224366188049</v>
+        <v>2.10224390029907</v>
       </c>
       <c r="H378" t="n">
         <v>507</v>
@@ -11476,7 +11476,7 @@
         <v>2.44369006156921</v>
       </c>
       <c r="G383" t="n">
-        <v>2.32768583297729</v>
+        <v>2.32768559455872</v>
       </c>
       <c r="H383" t="n">
         <v>179992</v>
@@ -11505,7 +11505,7 @@
         <v>2.30957293510437</v>
       </c>
       <c r="G384" t="n">
-        <v>2.1999351978302</v>
+        <v>2.19993543624878</v>
       </c>
       <c r="H384" t="n">
         <v>109516</v>
@@ -11766,7 +11766,7 @@
         <v>2.3628249168396</v>
       </c>
       <c r="G393" t="n">
-        <v>2.25065946578979</v>
+        <v>2.25065922737122</v>
       </c>
       <c r="H393" t="n">
         <v>19266</v>
@@ -11824,7 +11824,7 @@
         <v>2.27604389190674</v>
       </c>
       <c r="G395" t="n">
-        <v>2.16799807548523</v>
+        <v>2.16799783706665</v>
       </c>
       <c r="H395" t="n">
         <v>20280</v>
@@ -11911,7 +11911,7 @@
         <v>2.10445308685303</v>
       </c>
       <c r="G398" t="n">
-        <v>2.00455284118652</v>
+        <v>2.00455260276794</v>
       </c>
       <c r="H398" t="n">
         <v>142979</v>
@@ -11940,7 +11940,7 @@
         <v>2.0472559928894</v>
       </c>
       <c r="G399" t="n">
-        <v>1.95007061958313</v>
+        <v>1.95007073879242</v>
       </c>
       <c r="H399" t="n">
         <v>25858</v>
@@ -11998,7 +11998,7 @@
         <v>2.19123506546021</v>
       </c>
       <c r="G401" t="n">
-        <v>2.08721518516541</v>
+        <v>2.08721494674683</v>
       </c>
       <c r="H401" t="n">
         <v>99882</v>
@@ -12027,7 +12027,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G402" t="n">
-        <v>2.02521753311157</v>
+        <v>2.02521777153015</v>
       </c>
       <c r="H402" t="n">
         <v>30421</v>
@@ -12056,7 +12056,7 @@
         <v>2.10839796066284</v>
       </c>
       <c r="G403" t="n">
-        <v>2.00831007957458</v>
+        <v>2.00831031799316</v>
       </c>
       <c r="H403" t="n">
         <v>20280</v>
@@ -12143,7 +12143,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G406" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H406" t="n">
         <v>9633</v>
@@ -12433,7 +12433,7 @@
         <v>2.00189304351807</v>
       </c>
       <c r="G416" t="n">
-        <v>1.90686118602753</v>
+        <v>1.90686130523682</v>
       </c>
       <c r="H416" t="n">
         <v>8112</v>
@@ -12462,7 +12462,7 @@
         <v>1.98019802570343</v>
       </c>
       <c r="G417" t="n">
-        <v>1.88619613647461</v>
+        <v>1.88619601726532</v>
       </c>
       <c r="H417" t="n">
         <v>4563</v>
@@ -12491,7 +12491,7 @@
         <v>2.00189304351807</v>
       </c>
       <c r="G418" t="n">
-        <v>1.90686118602753</v>
+        <v>1.90686130523682</v>
       </c>
       <c r="H418" t="n">
         <v>11661</v>
@@ -12520,7 +12520,7 @@
         <v>2.03936696052551</v>
       </c>
       <c r="G419" t="n">
-        <v>1.94255614280701</v>
+        <v>1.9425562620163</v>
       </c>
       <c r="H419" t="n">
         <v>1014</v>
@@ -12549,7 +12549,7 @@
         <v>2.03936696052551</v>
       </c>
       <c r="G420" t="n">
-        <v>1.94255614280701</v>
+        <v>1.9425562620163</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>1.98808705806732</v>
       </c>
       <c r="G421" t="n">
-        <v>1.89371073246002</v>
+        <v>1.89371061325073</v>
       </c>
       <c r="H421" t="n">
         <v>2028</v>
@@ -12607,7 +12607,7 @@
         <v>2.03936696052551</v>
       </c>
       <c r="G422" t="n">
-        <v>1.94255614280701</v>
+        <v>1.9425562620163</v>
       </c>
       <c r="H422" t="n">
         <v>5070</v>
@@ -12636,7 +12636,7 @@
         <v>2.01569890975952</v>
       </c>
       <c r="G423" t="n">
-        <v>1.92001175880432</v>
+        <v>1.92001163959503</v>
       </c>
       <c r="H423" t="n">
         <v>17745</v>
@@ -12781,7 +12781,7 @@
         <v>1.98019802570343</v>
       </c>
       <c r="G428" t="n">
-        <v>1.88619613647461</v>
+        <v>1.88619601726532</v>
       </c>
       <c r="H428" t="n">
         <v>1521</v>
@@ -12810,7 +12810,7 @@
         <v>1.98019802570343</v>
       </c>
       <c r="G429" t="n">
-        <v>1.88619613647461</v>
+        <v>1.88619601726532</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>1.91313898563385</v>
       </c>
       <c r="G434" t="n">
-        <v>1.8223203420639</v>
+        <v>1.82232046127319</v>
       </c>
       <c r="H434" t="n">
         <v>5070</v>
@@ -12984,7 +12984,7 @@
         <v>1.87960994243622</v>
       </c>
       <c r="G435" t="n">
-        <v>1.79038298130035</v>
+        <v>1.79038310050964</v>
       </c>
       <c r="H435" t="n">
         <v>44617</v>
@@ -13100,7 +13100,7 @@
         <v>1.85397005081177</v>
       </c>
       <c r="G439" t="n">
-        <v>1.76596033573151</v>
+        <v>1.76596021652222</v>
       </c>
       <c r="H439" t="n">
         <v>16731</v>
@@ -13158,7 +13158,7 @@
         <v>1.85791397094727</v>
       </c>
       <c r="G441" t="n">
-        <v>1.76971709728241</v>
+        <v>1.76971697807312</v>
       </c>
       <c r="H441" t="n">
         <v>10140</v>
@@ -13274,7 +13274,7 @@
         <v>1.77507698535919</v>
       </c>
       <c r="G445" t="n">
-        <v>1.69081246852875</v>
+        <v>1.69081234931946</v>
       </c>
       <c r="H445" t="n">
         <v>24843</v>
@@ -13303,7 +13303,7 @@
         <v>1.77507698535919</v>
       </c>
       <c r="G446" t="n">
-        <v>1.69081246852875</v>
+        <v>1.69081234931946</v>
       </c>
       <c r="H446" t="n">
         <v>12675</v>
@@ -13448,7 +13448,7 @@
         <v>1.53840005397797</v>
       </c>
       <c r="G451" t="n">
-        <v>1.4653707742691</v>
+        <v>1.46537065505981</v>
       </c>
       <c r="H451" t="n">
         <v>38533</v>
@@ -13535,7 +13535,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G454" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H454" t="n">
         <v>19266</v>
@@ -13593,7 +13593,7 @@
         <v>1.82241296768188</v>
       </c>
       <c r="G456" t="n">
-        <v>1.73590123653412</v>
+        <v>1.73590135574341</v>
       </c>
       <c r="H456" t="n">
         <v>45631</v>
@@ -13883,7 +13883,7 @@
         <v>1.47528600692749</v>
       </c>
       <c r="G466" t="n">
-        <v>1.40525269508362</v>
+        <v>1.40525281429291</v>
       </c>
       <c r="H466" t="n">
         <v>28393</v>
@@ -13941,7 +13941,7 @@
         <v>1.50684297084808</v>
       </c>
       <c r="G468" t="n">
-        <v>1.43531179428101</v>
+        <v>1.43531167507172</v>
       </c>
       <c r="H468" t="n">
         <v>35998</v>
@@ -13970,7 +13970,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G469" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H469" t="n">
         <v>31435</v>
@@ -14115,7 +14115,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G474" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H474" t="n">
         <v>7098</v>
@@ -14144,7 +14144,7 @@
         <v>1.48909294605255</v>
       </c>
       <c r="G475" t="n">
-        <v>1.41840434074402</v>
+        <v>1.41840422153473</v>
       </c>
       <c r="H475" t="n">
         <v>50702</v>
@@ -14202,7 +14202,7 @@
         <v>1.54431700706482</v>
       </c>
       <c r="G477" t="n">
-        <v>1.47100687026978</v>
+        <v>1.47100675106049</v>
       </c>
       <c r="H477" t="n">
         <v>92784</v>
@@ -14231,7 +14231,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G478" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H478" t="n">
         <v>51716</v>
@@ -14260,7 +14260,7 @@
         <v>1.48909294605255</v>
       </c>
       <c r="G479" t="n">
-        <v>1.41840434074402</v>
+        <v>1.41840422153473</v>
       </c>
       <c r="H479" t="n">
         <v>3042</v>
@@ -14521,7 +14521,7 @@
         <v>1.49205100536346</v>
       </c>
       <c r="G488" t="n">
-        <v>1.42122197151184</v>
+        <v>1.42122185230255</v>
       </c>
       <c r="H488" t="n">
         <v>104446</v>
@@ -14550,7 +14550,7 @@
         <v>1.53840005397797</v>
       </c>
       <c r="G489" t="n">
-        <v>1.4653707742691</v>
+        <v>1.46537065505981</v>
       </c>
       <c r="H489" t="n">
         <v>117121</v>
@@ -14579,7 +14579,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G490" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H490" t="n">
         <v>201793</v>
@@ -14637,7 +14637,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G492" t="n">
-        <v>1.44658386707306</v>
+        <v>1.44658398628235</v>
       </c>
       <c r="H492" t="n">
         <v>31435</v>
@@ -14666,7 +14666,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G493" t="n">
-        <v>1.44658386707306</v>
+        <v>1.44658398628235</v>
       </c>
       <c r="H493" t="n">
         <v>0</v>
@@ -14695,7 +14695,7 @@
         <v>1.54234504699707</v>
       </c>
       <c r="G494" t="n">
-        <v>1.46912848949432</v>
+        <v>1.46912837028503</v>
       </c>
       <c r="H494" t="n">
         <v>14196</v>
@@ -14811,7 +14811,7 @@
         <v>1.55615103244781</v>
       </c>
       <c r="G498" t="n">
-        <v>1.48227894306183</v>
+        <v>1.48227906227112</v>
       </c>
       <c r="H498" t="n">
         <v>2535</v>
@@ -14840,7 +14840,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G499" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H499" t="n">
         <v>3549</v>
@@ -14898,7 +14898,7 @@
         <v>1.55220699310303</v>
       </c>
       <c r="G501" t="n">
-        <v>1.47852218151093</v>
+        <v>1.47852230072021</v>
       </c>
       <c r="H501" t="n">
         <v>2028</v>
@@ -14927,7 +14927,7 @@
         <v>1.50684297084808</v>
       </c>
       <c r="G502" t="n">
-        <v>1.43531179428101</v>
+        <v>1.43531167507172</v>
       </c>
       <c r="H502" t="n">
         <v>3549</v>
@@ -14985,7 +14985,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G504" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H504" t="n">
         <v>23322</v>
@@ -15014,7 +15014,7 @@
         <v>1.44175696372986</v>
       </c>
       <c r="G505" t="n">
-        <v>1.37331533432007</v>
+        <v>1.37331545352936</v>
       </c>
       <c r="H505" t="n">
         <v>8619</v>
@@ -15072,7 +15072,7 @@
         <v>1.4013249874115</v>
       </c>
       <c r="G507" t="n">
-        <v>1.33480274677277</v>
+        <v>1.33480262756348</v>
       </c>
       <c r="H507" t="n">
         <v>5070</v>
@@ -15101,7 +15101,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G508" t="n">
-        <v>1.33386361598969</v>
+        <v>1.3338634967804</v>
       </c>
       <c r="H508" t="n">
         <v>2028</v>
@@ -15304,7 +15304,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G515" t="n">
-        <v>1.33386361598969</v>
+        <v>1.3338634967804</v>
       </c>
       <c r="H515" t="n">
         <v>5577</v>
@@ -15449,7 +15449,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G520" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H520" t="n">
         <v>39040</v>
@@ -15478,7 +15478,7 @@
         <v>1.48909294605255</v>
       </c>
       <c r="G521" t="n">
-        <v>1.41840434074402</v>
+        <v>1.41840422153473</v>
       </c>
       <c r="H521" t="n">
         <v>4056</v>
@@ -15565,7 +15565,7 @@
         <v>1.5531929731369</v>
       </c>
       <c r="G524" t="n">
-        <v>1.47946131229401</v>
+        <v>1.4794614315033</v>
       </c>
       <c r="H524" t="n">
         <v>313845</v>
@@ -15623,7 +15623,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G526" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H526" t="n">
         <v>37012</v>
@@ -15652,7 +15652,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G527" t="n">
-        <v>1.44658386707306</v>
+        <v>1.44658398628235</v>
       </c>
       <c r="H527" t="n">
         <v>17238</v>
@@ -15710,7 +15710,7 @@
         <v>1.5531929731369</v>
       </c>
       <c r="G529" t="n">
-        <v>1.47946131229401</v>
+        <v>1.4794614315033</v>
       </c>
       <c r="H529" t="n">
         <v>11154</v>
@@ -15826,7 +15826,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G533" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H533" t="n">
         <v>20280</v>
@@ -15884,7 +15884,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G535" t="n">
-        <v>1.44658386707306</v>
+        <v>1.44658398628235</v>
       </c>
       <c r="H535" t="n">
         <v>5070</v>
@@ -15971,7 +15971,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G538" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H538" t="n">
         <v>11661</v>
@@ -16000,7 +16000,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G539" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H539" t="n">
         <v>17238</v>
@@ -16116,7 +16116,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G543" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H543" t="n">
         <v>507</v>
@@ -16145,7 +16145,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G544" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H544" t="n">
         <v>1014</v>
@@ -16203,7 +16203,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G546" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H546" t="n">
         <v>7098</v>
@@ -16232,7 +16232,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G547" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H547" t="n">
         <v>6084</v>
@@ -16261,7 +16261,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G548" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H548" t="n">
         <v>2028</v>
@@ -16464,7 +16464,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G555" t="n">
-        <v>1.30568289756775</v>
+        <v>1.30568301677704</v>
       </c>
       <c r="H555" t="n">
         <v>9633</v>
@@ -16638,7 +16638,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G561" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H561" t="n">
         <v>4056</v>
@@ -16812,7 +16812,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G567" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H567" t="n">
         <v>24843</v>
@@ -16841,7 +16841,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G568" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H568" t="n">
         <v>2028</v>
@@ -17073,7 +17073,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G576" t="n">
-        <v>1.29629015922546</v>
+        <v>1.29629004001617</v>
       </c>
       <c r="H576" t="n">
         <v>4056</v>
@@ -17102,7 +17102,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G577" t="n">
-        <v>1.31977272033691</v>
+        <v>1.3197728395462</v>
       </c>
       <c r="H577" t="n">
         <v>6084</v>
@@ -17160,7 +17160,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G579" t="n">
-        <v>1.31977272033691</v>
+        <v>1.3197728395462</v>
       </c>
       <c r="H579" t="n">
         <v>3549</v>
@@ -17508,7 +17508,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G591" t="n">
-        <v>1.29629015922546</v>
+        <v>1.29629004001617</v>
       </c>
       <c r="H591" t="n">
         <v>17745</v>
@@ -17682,7 +17682,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G597" t="n">
-        <v>1.31977272033691</v>
+        <v>1.3197728395462</v>
       </c>
       <c r="H597" t="n">
         <v>5577</v>
@@ -17856,7 +17856,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G603" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H603" t="n">
         <v>1014</v>
@@ -17885,7 +17885,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G604" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H604" t="n">
         <v>1521</v>
@@ -17972,7 +17972,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G607" t="n">
-        <v>1.2352329492569</v>
+        <v>1.23523306846619</v>
       </c>
       <c r="H607" t="n">
         <v>15717</v>
@@ -18088,7 +18088,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G611" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H611" t="n">
         <v>2028</v>
@@ -18117,7 +18117,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G612" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H612" t="n">
         <v>1014</v>
@@ -18175,7 +18175,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G614" t="n">
-        <v>1.20705246925354</v>
+        <v>1.20705235004425</v>
       </c>
       <c r="H614" t="n">
         <v>12168</v>
@@ -18378,7 +18378,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G621" t="n">
-        <v>1.30568289756775</v>
+        <v>1.30568301677704</v>
       </c>
       <c r="H621" t="n">
         <v>16731</v>
@@ -18639,7 +18639,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G630" t="n">
-        <v>1.30568289756775</v>
+        <v>1.30568301677704</v>
       </c>
       <c r="H630" t="n">
         <v>10647</v>
@@ -18784,7 +18784,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G635" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H635" t="n">
         <v>53237</v>
@@ -18871,7 +18871,7 @@
         <v>1.85397005081177</v>
       </c>
       <c r="G638" t="n">
-        <v>1.76596033573151</v>
+        <v>1.76596021652222</v>
       </c>
       <c r="H638" t="n">
         <v>456825</v>
@@ -19074,7 +19074,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G645" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H645" t="n">
         <v>142979</v>
@@ -19277,7 +19277,7 @@
         <v>1.56798505783081</v>
       </c>
       <c r="G652" t="n">
-        <v>1.49355125427246</v>
+        <v>1.49355137348175</v>
       </c>
       <c r="H652" t="n">
         <v>129797</v>
@@ -19393,7 +19393,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G656" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H656" t="n">
         <v>6591</v>
@@ -19451,7 +19451,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G658" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H658" t="n">
         <v>46138</v>
@@ -19509,7 +19509,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G660" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H660" t="n">
         <v>2028</v>
@@ -19567,7 +19567,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G662" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H662" t="n">
         <v>2535</v>
@@ -19596,7 +19596,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G663" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H663" t="n">
         <v>0</v>
@@ -19625,7 +19625,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G664" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H664" t="n">
         <v>0</v>
@@ -19654,7 +19654,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G665" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H665" t="n">
         <v>0</v>
@@ -19741,7 +19741,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G668" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H668" t="n">
         <v>17238</v>
@@ -19770,7 +19770,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G669" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H669" t="n">
         <v>30421</v>
@@ -19799,7 +19799,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G670" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H670" t="n">
         <v>3042</v>
@@ -19828,7 +19828,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G671" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H671" t="n">
         <v>9126</v>
@@ -19886,7 +19886,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G673" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H673" t="n">
         <v>4563</v>
@@ -19973,7 +19973,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G676" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H676" t="n">
         <v>20280</v>
@@ -20060,7 +20060,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G679" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H679" t="n">
         <v>5070</v>
@@ -20089,7 +20089,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G680" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H680" t="n">
         <v>4056</v>
@@ -20234,7 +20234,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G685" t="n">
-        <v>1.29629015922546</v>
+        <v>1.29629004001617</v>
       </c>
       <c r="H685" t="n">
         <v>5070</v>
@@ -20263,7 +20263,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G686" t="n">
-        <v>1.29629015922546</v>
+        <v>1.29629004001617</v>
       </c>
       <c r="H686" t="n">
         <v>507</v>
@@ -20408,7 +20408,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G691" t="n">
-        <v>1.33386361598969</v>
+        <v>1.3338634967804</v>
       </c>
       <c r="H691" t="n">
         <v>9633</v>
@@ -20495,7 +20495,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G694" t="n">
-        <v>1.33386361598969</v>
+        <v>1.3338634967804</v>
       </c>
       <c r="H694" t="n">
         <v>10140</v>
@@ -20553,7 +20553,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G696" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H696" t="n">
         <v>44110</v>
@@ -20669,7 +20669,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G700" t="n">
-        <v>1.30568289756775</v>
+        <v>1.30568301677704</v>
       </c>
       <c r="H700" t="n">
         <v>67433</v>
@@ -20698,7 +20698,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G701" t="n">
-        <v>1.2352329492569</v>
+        <v>1.23523306846619</v>
       </c>
       <c r="H701" t="n">
         <v>81123</v>
@@ -20727,7 +20727,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G702" t="n">
-        <v>1.2352329492569</v>
+        <v>1.23523306846619</v>
       </c>
       <c r="H702" t="n">
         <v>14703</v>
@@ -20872,7 +20872,7 @@
         <v>1.2179000377655</v>
       </c>
       <c r="G707" t="n">
-        <v>1.16008520126343</v>
+        <v>1.16008508205414</v>
       </c>
       <c r="H707" t="n">
         <v>17745</v>
@@ -21017,7 +21017,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G712" t="n">
-        <v>1.089635014534</v>
+        <v>1.08963513374329</v>
       </c>
       <c r="H712" t="n">
         <v>20787</v>
@@ -21075,7 +21075,7 @@
         <v>1.17845404148102</v>
       </c>
       <c r="G714" t="n">
-        <v>1.12251174449921</v>
+        <v>1.12251162528992</v>
       </c>
       <c r="H714" t="n">
         <v>32956</v>
@@ -21133,7 +21133,7 @@
         <v>1.12914597988129</v>
       </c>
       <c r="G716" t="n">
-        <v>1.0755443572998</v>
+        <v>1.07554423809052</v>
       </c>
       <c r="H716" t="n">
         <v>28393</v>
@@ -21220,7 +21220,7 @@
         <v>1.01573896408081</v>
       </c>
       <c r="G719" t="n">
-        <v>0.967520892620087</v>
+        <v>0.967520833015442</v>
       </c>
       <c r="H719" t="n">
         <v>25858</v>
@@ -21336,7 +21336,7 @@
         <v>1.11435401439667</v>
       </c>
       <c r="G723" t="n">
-        <v>1.06145453453064</v>
+        <v>1.06145465373993</v>
       </c>
       <c r="H723" t="n">
         <v>4563</v>
@@ -21365,7 +21365,7 @@
         <v>1.10449194908142</v>
       </c>
       <c r="G724" t="n">
-        <v>1.05206072330475</v>
+        <v>1.05206060409546</v>
       </c>
       <c r="H724" t="n">
         <v>3042</v>
@@ -21800,7 +21800,7 @@
         <v>0.938817977905273</v>
       </c>
       <c r="G739" t="n">
-        <v>0.894251346588135</v>
+        <v>0.89425140619278</v>
       </c>
       <c r="H739" t="n">
         <v>507</v>
@@ -21829,7 +21829,7 @@
         <v>0.938817977905273</v>
       </c>
       <c r="G740" t="n">
-        <v>0.894251346588135</v>
+        <v>0.89425140619278</v>
       </c>
       <c r="H740" t="n">
         <v>1521</v>
@@ -21887,7 +21887,7 @@
         <v>0.926985025405884</v>
       </c>
       <c r="G742" t="n">
-        <v>0.882980167865753</v>
+        <v>0.882980108261108</v>
       </c>
       <c r="H742" t="n">
         <v>11661</v>
@@ -21916,7 +21916,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G743" t="n">
-        <v>0.911159813404083</v>
+        <v>0.911159753799438</v>
       </c>
       <c r="H743" t="n">
         <v>9126</v>
@@ -21945,7 +21945,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G744" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H744" t="n">
         <v>12168</v>
@@ -22061,7 +22061,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G748" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H748" t="n">
         <v>1521</v>
@@ -22206,7 +22206,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G753" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H753" t="n">
         <v>6591</v>
@@ -22264,7 +22264,7 @@
         <v>0.926985025405884</v>
       </c>
       <c r="G755" t="n">
-        <v>0.882980167865753</v>
+        <v>0.882980108261108</v>
       </c>
       <c r="H755" t="n">
         <v>8112</v>
@@ -22322,7 +22322,7 @@
         <v>0.867815017700195</v>
       </c>
       <c r="G757" t="n">
-        <v>0.826619029045105</v>
+        <v>0.82661896944046</v>
       </c>
       <c r="H757" t="n">
         <v>3042</v>
@@ -22351,7 +22351,7 @@
         <v>0.887538015842438</v>
       </c>
       <c r="G758" t="n">
-        <v>0.845405757427216</v>
+        <v>0.845405697822571</v>
       </c>
       <c r="H758" t="n">
         <v>11154</v>
@@ -22380,7 +22380,7 @@
         <v>0.879648983478546</v>
       </c>
       <c r="G759" t="n">
-        <v>0.837891221046448</v>
+        <v>0.837891161441803</v>
       </c>
       <c r="H759" t="n">
         <v>10140</v>
@@ -22409,7 +22409,7 @@
         <v>0.887538015842438</v>
       </c>
       <c r="G760" t="n">
-        <v>0.845405757427216</v>
+        <v>0.845405697822571</v>
       </c>
       <c r="H760" t="n">
         <v>1521</v>
@@ -22699,7 +22699,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G770" t="n">
-        <v>0.911159813404083</v>
+        <v>0.911159753799438</v>
       </c>
       <c r="H770" t="n">
         <v>2028</v>
@@ -22844,7 +22844,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G775" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H775" t="n">
         <v>6591</v>
@@ -22902,7 +22902,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G777" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H777" t="n">
         <v>19266</v>
@@ -22931,7 +22931,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G778" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H778" t="n">
         <v>10140</v>
@@ -22960,7 +22960,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G779" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H779" t="n">
         <v>0</v>
@@ -22989,7 +22989,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G780" t="n">
-        <v>0.911159813404083</v>
+        <v>0.911159753799438</v>
       </c>
       <c r="H780" t="n">
         <v>1521</v>
@@ -23018,7 +23018,7 @@
         <v>0.942762970924377</v>
       </c>
       <c r="G781" t="n">
-        <v>0.898009121417999</v>
+        <v>0.898009061813354</v>
       </c>
       <c r="H781" t="n">
         <v>7098</v>
@@ -23192,7 +23192,7 @@
         <v>0.938817977905273</v>
       </c>
       <c r="G787" t="n">
-        <v>0.894251346588135</v>
+        <v>0.89425140619278</v>
       </c>
       <c r="H787" t="n">
         <v>1014</v>
@@ -23250,7 +23250,7 @@
         <v>1.01573896408081</v>
       </c>
       <c r="G789" t="n">
-        <v>0.967520892620087</v>
+        <v>0.967520833015442</v>
       </c>
       <c r="H789" t="n">
         <v>1521</v>
@@ -23279,7 +23279,7 @@
         <v>0.962486028671265</v>
       </c>
       <c r="G790" t="n">
-        <v>0.91679584980011</v>
+        <v>0.916795909404755</v>
       </c>
       <c r="H790" t="n">
         <v>32449</v>
@@ -23308,7 +23308,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G791" t="n">
-        <v>0.911159813404083</v>
+        <v>0.911159753799438</v>
       </c>
       <c r="H791" t="n">
         <v>16224</v>
@@ -23685,7 +23685,7 @@
         <v>1.09956204891205</v>
       </c>
       <c r="G804" t="n">
-        <v>1.04736471176147</v>
+        <v>1.04736483097076</v>
       </c>
       <c r="H804" t="n">
         <v>18252</v>
@@ -24236,7 +24236,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G823" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H823" t="n">
         <v>23322</v>
@@ -24265,7 +24265,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G824" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -24323,7 +24323,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G826" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H826" t="n">
         <v>3549</v>
@@ -24381,7 +24381,7 @@
         <v>0.972347974777222</v>
       </c>
       <c r="G828" t="n">
-        <v>0.926189720630646</v>
+        <v>0.926189661026001</v>
       </c>
       <c r="H828" t="n">
         <v>25858</v>
@@ -24410,7 +24410,7 @@
         <v>0.978264987468719</v>
       </c>
       <c r="G829" t="n">
-        <v>0.931825757026672</v>
+        <v>0.931825816631317</v>
       </c>
       <c r="H829" t="n">
         <v>10647</v>
@@ -24613,7 +24613,7 @@
         <v>1.04039204120636</v>
       </c>
       <c r="G836" t="n">
-        <v>0.991003632545471</v>
+        <v>0.991003572940826</v>
       </c>
       <c r="H836" t="n">
         <v>55772</v>
@@ -24700,7 +24700,7 @@
         <v>1.01573896408081</v>
       </c>
       <c r="G839" t="n">
-        <v>0.967520892620087</v>
+        <v>0.967520833015442</v>
       </c>
       <c r="H839" t="n">
         <v>14703</v>
@@ -24729,7 +24729,7 @@
         <v>0.99108499288559</v>
       </c>
       <c r="G840" t="n">
-        <v>0.944037258625031</v>
+        <v>0.944037199020386</v>
       </c>
       <c r="H840" t="n">
         <v>19773</v>
@@ -24787,7 +24787,7 @@
         <v>0.982209026813507</v>
       </c>
       <c r="G842" t="n">
-        <v>0.93558257818222</v>
+        <v>0.935582637786865</v>
       </c>
       <c r="H842" t="n">
         <v>6591</v>
@@ -24816,7 +24816,7 @@
         <v>0.982209026813507</v>
       </c>
       <c r="G843" t="n">
-        <v>0.93558257818222</v>
+        <v>0.935582637786865</v>
       </c>
       <c r="H843" t="n">
         <v>0</v>
@@ -24874,7 +24874,7 @@
         <v>0.99108499288559</v>
       </c>
       <c r="G845" t="n">
-        <v>0.944037258625031</v>
+        <v>0.944037199020386</v>
       </c>
       <c r="H845" t="n">
         <v>12168</v>
@@ -25106,7 +25106,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G853" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H853" t="n">
         <v>18759</v>
@@ -25164,7 +25164,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G855" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H855" t="n">
         <v>3549</v>
@@ -25193,7 +25193,7 @@
         <v>0.982209026813507</v>
       </c>
       <c r="G856" t="n">
-        <v>0.93558257818222</v>
+        <v>0.935582637786865</v>
       </c>
       <c r="H856" t="n">
         <v>5070</v>
@@ -25222,7 +25222,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G857" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H857" t="n">
         <v>12675</v>
@@ -25396,7 +25396,7 @@
         <v>0.978264987468719</v>
       </c>
       <c r="G863" t="n">
-        <v>0.931825757026672</v>
+        <v>0.931825816631317</v>
       </c>
       <c r="H863" t="n">
         <v>17745</v>
@@ -25425,7 +25425,7 @@
         <v>0.978264987468719</v>
       </c>
       <c r="G864" t="n">
-        <v>0.931825757026672</v>
+        <v>0.931825816631317</v>
       </c>
       <c r="H864" t="n">
         <v>0</v>
@@ -25512,7 +25512,7 @@
         <v>0.950652003288269</v>
       </c>
       <c r="G867" t="n">
-        <v>0.905523657798767</v>
+        <v>0.905523598194122</v>
       </c>
       <c r="H867" t="n">
         <v>9126</v>
@@ -25686,7 +25686,7 @@
         <v>0.90923398733139</v>
       </c>
       <c r="G873" t="n">
-        <v>0.866071760654449</v>
+        <v>0.866071820259094</v>
       </c>
       <c r="H873" t="n">
         <v>7098</v>
@@ -25715,7 +25715,7 @@
         <v>0.915151000022888</v>
       </c>
       <c r="G874" t="n">
-        <v>0.871707856655121</v>
+        <v>0.871707916259766</v>
       </c>
       <c r="H874" t="n">
         <v>7098</v>
@@ -25831,7 +25831,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G878" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H878" t="n">
         <v>31435</v>
@@ -25860,7 +25860,7 @@
         <v>0.769200026988983</v>
       </c>
       <c r="G879" t="n">
-        <v>0.732685387134552</v>
+        <v>0.732685327529907</v>
       </c>
       <c r="H879" t="n">
         <v>49687</v>
@@ -25889,7 +25889,7 @@
         <v>0.769200026988983</v>
       </c>
       <c r="G880" t="n">
-        <v>0.732685387134552</v>
+        <v>0.732685327529907</v>
       </c>
       <c r="H880" t="n">
         <v>21801</v>
@@ -26005,7 +26005,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G884" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H884" t="n">
         <v>10647</v>
@@ -26063,7 +26063,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G886" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H886" t="n">
         <v>7605</v>
@@ -26121,7 +26121,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G888" t="n">
-        <v>0.723291456699371</v>
+        <v>0.723291516304016</v>
       </c>
       <c r="H888" t="n">
         <v>12168</v>
@@ -26150,7 +26150,7 @@
         <v>0.745531976222992</v>
       </c>
       <c r="G889" t="n">
-        <v>0.710140824317932</v>
+        <v>0.710140883922577</v>
       </c>
       <c r="H889" t="n">
         <v>10647</v>
@@ -26179,7 +26179,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G890" t="n">
-        <v>0.723291456699371</v>
+        <v>0.723291516304016</v>
       </c>
       <c r="H890" t="n">
         <v>1521</v>
@@ -26208,7 +26208,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G891" t="n">
-        <v>0.723291456699371</v>
+        <v>0.723291516304016</v>
       </c>
       <c r="H891" t="n">
         <v>0</v>
@@ -26266,7 +26266,7 @@
         <v>0.77708899974823</v>
       </c>
       <c r="G893" t="n">
-        <v>0.740199863910675</v>
+        <v>0.74019980430603</v>
       </c>
       <c r="H893" t="n">
         <v>29914</v>
@@ -26353,7 +26353,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G896" t="n">
-        <v>0.723291456699371</v>
+        <v>0.723291516304016</v>
       </c>
       <c r="H896" t="n">
         <v>30928</v>
@@ -26411,7 +26411,7 @@
         <v>0.729753971099854</v>
       </c>
       <c r="G898" t="n">
-        <v>0.695111811161041</v>
+        <v>0.695111870765686</v>
       </c>
       <c r="H898" t="n">
         <v>15210</v>
@@ -26440,7 +26440,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G899" t="n">
-        <v>0.702626347541809</v>
+        <v>0.702626407146454</v>
       </c>
       <c r="H899" t="n">
         <v>52223</v>
@@ -26585,7 +26585,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G904" t="n">
-        <v>0.548574805259705</v>
+        <v>0.548574864864349</v>
       </c>
       <c r="H904" t="n">
         <v>50702</v>
@@ -26672,7 +26672,7 @@
         <v>0.508854985237122</v>
       </c>
       <c r="G907" t="n">
-        <v>0.484699130058289</v>
+        <v>0.484699159860611</v>
       </c>
       <c r="H907" t="n">
         <v>76053</v>
@@ -26817,7 +26817,7 @@
         <v>0.492091000080109</v>
       </c>
       <c r="G912" t="n">
-        <v>0.468730956315994</v>
+        <v>0.468730986118317</v>
       </c>
       <c r="H912" t="n">
         <v>19773</v>
@@ -26846,7 +26846,7 @@
         <v>0.492091000080109</v>
       </c>
       <c r="G913" t="n">
-        <v>0.468730956315994</v>
+        <v>0.468730986118317</v>
       </c>
       <c r="H913" t="n">
         <v>507</v>
@@ -26991,7 +26991,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G918" t="n">
-        <v>0.432096689939499</v>
+        <v>0.432096719741821</v>
       </c>
       <c r="H918" t="n">
         <v>18759</v>
@@ -27049,7 +27049,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G920" t="n">
-        <v>0.418945103883743</v>
+        <v>0.418945133686066</v>
       </c>
       <c r="H920" t="n">
         <v>7098</v>
@@ -27107,7 +27107,7 @@
         <v>0.481243014335632</v>
       </c>
       <c r="G922" t="n">
-        <v>0.458397924900055</v>
+        <v>0.458397954702377</v>
       </c>
       <c r="H922" t="n">
         <v>51209</v>
@@ -27194,7 +27194,7 @@
         <v>0.44574099779129</v>
       </c>
       <c r="G925" t="n">
-        <v>0.424581259489059</v>
+        <v>0.424581229686737</v>
       </c>
       <c r="H925" t="n">
         <v>198751</v>
@@ -27252,7 +27252,7 @@
         <v>0.449685990810394</v>
       </c>
       <c r="G927" t="n">
-        <v>0.428338944911957</v>
+        <v>0.428338974714279</v>
       </c>
       <c r="H927" t="n">
         <v>507</v>
@@ -27339,7 +27339,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G930" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H930" t="n">
         <v>36505</v>
@@ -27368,7 +27368,7 @@
         <v>0.469408988952637</v>
       </c>
       <c r="G931" t="n">
-        <v>0.447125673294067</v>
+        <v>0.44712570309639</v>
       </c>
       <c r="H931" t="n">
         <v>24843</v>
@@ -27571,7 +27571,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G938" t="n">
-        <v>0.494093000888824</v>
+        <v>0.494093030691147</v>
       </c>
       <c r="H938" t="n">
         <v>40561</v>
@@ -27600,7 +27600,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G939" t="n">
-        <v>0.494093000888824</v>
+        <v>0.494093030691147</v>
       </c>
       <c r="H939" t="n">
         <v>19773</v>
@@ -27629,7 +27629,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G940" t="n">
-        <v>0.494093000888824</v>
+        <v>0.494093030691147</v>
       </c>
       <c r="H940" t="n">
         <v>20787</v>
@@ -27716,7 +27716,7 @@
         <v>0.506883025169373</v>
       </c>
       <c r="G943" t="n">
-        <v>0.482820808887482</v>
+        <v>0.482820779085159</v>
       </c>
       <c r="H943" t="n">
         <v>100389</v>
@@ -27861,7 +27861,7 @@
         <v>0.489131987094879</v>
       </c>
       <c r="G948" t="n">
-        <v>0.4659124314785</v>
+        <v>0.465912401676178</v>
       </c>
       <c r="H948" t="n">
         <v>3549</v>
@@ -28035,7 +28035,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G954" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H954" t="n">
         <v>103939</v>
@@ -28064,7 +28064,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G955" t="n">
-        <v>0.41988530755043</v>
+        <v>0.419885277748108</v>
       </c>
       <c r="H955" t="n">
         <v>17238</v>
@@ -28238,7 +28238,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G961" t="n">
-        <v>0.437731891870499</v>
+        <v>0.437731862068176</v>
       </c>
       <c r="H961" t="n">
         <v>415756</v>
@@ -28296,7 +28296,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G963" t="n">
-        <v>0.462154686450958</v>
+        <v>0.462154716253281</v>
       </c>
       <c r="H963" t="n">
         <v>130811</v>
@@ -28731,7 +28731,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G978" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H978" t="n">
         <v>47659</v>
@@ -28818,7 +28818,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G981" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H981" t="n">
         <v>45631</v>
@@ -28876,7 +28876,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G983" t="n">
-        <v>0.432096689939499</v>
+        <v>0.432096719741821</v>
       </c>
       <c r="H983" t="n">
         <v>39547</v>
@@ -28992,7 +28992,7 @@
         <v>0.469408988952637</v>
       </c>
       <c r="G987" t="n">
-        <v>0.447125673294067</v>
+        <v>0.44712570309639</v>
       </c>
       <c r="H987" t="n">
         <v>6084</v>
@@ -29079,7 +29079,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G990" t="n">
-        <v>0.432096689939499</v>
+        <v>0.432096719741821</v>
       </c>
       <c r="H990" t="n">
         <v>19266</v>
@@ -29108,7 +29108,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G991" t="n">
-        <v>0.432096689939499</v>
+        <v>0.432096719741821</v>
       </c>
       <c r="H991" t="n">
         <v>19266</v>
@@ -29137,7 +29137,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G992" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H992" t="n">
         <v>9633</v>
@@ -29166,7 +29166,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G993" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H993" t="n">
         <v>104446</v>
@@ -29195,7 +29195,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G994" t="n">
-        <v>0.41988530755043</v>
+        <v>0.419885277748108</v>
       </c>
       <c r="H994" t="n">
         <v>175935</v>
@@ -29224,7 +29224,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G995" t="n">
-        <v>0.418945103883743</v>
+        <v>0.418945133686066</v>
       </c>
       <c r="H995" t="n">
         <v>67940</v>
@@ -29253,7 +29253,7 @@
         <v>0.449685990810394</v>
       </c>
       <c r="G996" t="n">
-        <v>0.428338944911957</v>
+        <v>0.428338974714279</v>
       </c>
       <c r="H996" t="n">
         <v>116107</v>
@@ -29282,7 +29282,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G997" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H997" t="n">
         <v>52730</v>
@@ -29398,7 +29398,7 @@
         <v>0.55224597454071</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.526030361652374</v>
+        <v>0.526030302047729</v>
       </c>
       <c r="H1001" t="n">
         <v>693096</v>
@@ -29543,7 +29543,7 @@
         <v>0.603525996208191</v>
       </c>
       <c r="G1006" t="n">
-        <v>0.574876010417938</v>
+        <v>0.574876070022583</v>
       </c>
       <c r="H1006" t="n">
         <v>259594</v>
@@ -29601,7 +29601,7 @@
         <v>0.694252014160156</v>
       </c>
       <c r="G1008" t="n">
-        <v>0.661295175552368</v>
+        <v>0.661295235157013</v>
       </c>
       <c r="H1008" t="n">
         <v>497893</v>
@@ -29717,7 +29717,7 @@
         <v>0.639028012752533</v>
       </c>
       <c r="G1012" t="n">
-        <v>0.608692705631256</v>
+        <v>0.608692765235901</v>
       </c>
       <c r="H1012" t="n">
         <v>271255</v>
@@ -29775,7 +29775,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.63499391078949</v>
+        <v>0.634993970394135</v>
       </c>
       <c r="H1014" t="n">
         <v>67433</v>
@@ -29862,7 +29862,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1017" t="n">
-        <v>0.604935050010681</v>
+        <v>0.604934990406036</v>
       </c>
       <c r="H1017" t="n">
         <v>279875</v>
@@ -29949,7 +29949,7 @@
         <v>0.611415028572083</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.582390546798706</v>
+        <v>0.582390606403351</v>
       </c>
       <c r="H1020" t="n">
         <v>99882</v>
@@ -30094,7 +30094,7 @@
         <v>0.765254974365234</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.728927552700043</v>
+        <v>0.728927612304688</v>
       </c>
       <c r="H1025" t="n">
         <v>870046</v>
@@ -30268,7 +30268,7 @@
         <v>0.706085979938507</v>
       </c>
       <c r="G1031" t="n">
-        <v>0.672567427158356</v>
+        <v>0.672567367553711</v>
       </c>
       <c r="H1031" t="n">
         <v>155148</v>
@@ -30471,7 +30471,7 @@
         <v>0.668612003326416</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.636872291564941</v>
+        <v>0.636872351169586</v>
       </c>
       <c r="H1038" t="n">
         <v>98361</v>
@@ -30616,7 +30616,7 @@
         <v>0.69819700717926</v>
       </c>
       <c r="G1043" t="n">
-        <v>0.665052950382233</v>
+        <v>0.665052890777588</v>
       </c>
       <c r="H1043" t="n">
         <v>186583</v>
@@ -30906,7 +30906,7 @@
         <v>0.550274014472961</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.524151921272278</v>
+        <v>0.524151980876923</v>
       </c>
       <c r="H1053" t="n">
         <v>205850</v>
@@ -30935,7 +30935,7 @@
         <v>0.571968972682953</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.544817090034485</v>
+        <v>0.54481703042984</v>
       </c>
       <c r="H1054" t="n">
         <v>95826</v>
@@ -30964,7 +30964,7 @@
         <v>0.55224597454071</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.526030361652374</v>
+        <v>0.526030302047729</v>
       </c>
       <c r="H1055" t="n">
         <v>104953</v>
@@ -31051,7 +31051,7 @@
         <v>0.520689010620117</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.495971381664276</v>
+        <v>0.495971411466599</v>
       </c>
       <c r="H1058" t="n">
         <v>18759</v>
@@ -31225,7 +31225,7 @@
         <v>0.36191800236702</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.344737410545349</v>
+        <v>0.344737380743027</v>
       </c>
       <c r="H1064" t="n">
         <v>127769</v>
@@ -31312,7 +31312,7 @@
         <v>0.318527013063431</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.303406208753586</v>
+        <v>0.303406238555908</v>
       </c>
       <c r="H1067" t="n">
         <v>33463</v>
@@ -31370,7 +31370,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.309981524944305</v>
+        <v>0.309981554746628</v>
       </c>
       <c r="H1069" t="n">
         <v>42082</v>
@@ -31399,7 +31399,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1070" t="n">
         <v>74531</v>
@@ -31515,7 +31515,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1074" t="n">
         <v>38026</v>
@@ -31718,7 +31718,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1081" t="n">
         <v>79095</v>
@@ -31776,7 +31776,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1083" t="n">
         <v>106474</v>
@@ -31863,7 +31863,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1086" t="n">
         <v>16224</v>
@@ -31892,7 +31892,7 @@
         <v>0.400377988815308</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.381371676921844</v>
+        <v>0.381371647119522</v>
       </c>
       <c r="H1087" t="n">
         <v>33463</v>
@@ -31921,7 +31921,7 @@
         <v>0.384600013494492</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.366342693567276</v>
+        <v>0.366342663764954</v>
       </c>
       <c r="H1088" t="n">
         <v>21294</v>
@@ -32066,7 +32066,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1093" t="n">
         <v>9633</v>
@@ -32124,7 +32124,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1095" t="n">
         <v>16224</v>
@@ -32211,7 +32211,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1098" t="n">
         <v>44617</v>
@@ -32269,7 +32269,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.336283713579178</v>
+        <v>0.336283683776855</v>
       </c>
       <c r="H1100" t="n">
         <v>250974</v>
@@ -32298,7 +32298,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1101" t="n">
         <v>48673</v>
@@ -32356,7 +32356,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1103" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1103" t="n">
         <v>9126</v>
@@ -32385,7 +32385,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1104" t="n">
         <v>12168</v>
@@ -32443,7 +32443,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1106" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1106" t="n">
         <v>25351</v>
@@ -32472,7 +32472,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1107" t="n">
         <v>7605</v>
@@ -32530,7 +32530,7 @@
         <v>0.369807004928589</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.352251917123795</v>
+        <v>0.352251887321472</v>
       </c>
       <c r="H1109" t="n">
         <v>23829</v>
@@ -32559,7 +32559,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.432096689939499</v>
+        <v>0.432096719741821</v>
       </c>
       <c r="H1110" t="n">
         <v>456825</v>
@@ -32617,7 +32617,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.392643928527832</v>
+        <v>0.39264389872551</v>
       </c>
       <c r="H1112" t="n">
         <v>188104</v>
@@ -32646,7 +32646,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1113" t="n">
         <v>101911</v>
@@ -32704,7 +32704,7 @@
         <v>0.398405998945236</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.379493296146393</v>
+        <v>0.37949326634407</v>
       </c>
       <c r="H1115" t="n">
         <v>63377</v>
@@ -32849,7 +32849,7 @@
         <v>0.475326001644135</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.452761828899384</v>
+        <v>0.452761799097061</v>
       </c>
       <c r="H1120" t="n">
         <v>63884</v>
@@ -33110,7 +33110,7 @@
         <v>0.484201014041901</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.461215525865555</v>
+        <v>0.461215496063232</v>
       </c>
       <c r="H1129" t="n">
         <v>51209</v>
@@ -33284,7 +33284,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G1135" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H1135" t="n">
         <v>11154</v>
@@ -33342,7 +33342,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G1137" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H1137" t="n">
         <v>3549</v>
@@ -33371,7 +33371,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.462154686450958</v>
+        <v>0.462154716253281</v>
       </c>
       <c r="H1138" t="n">
         <v>16224</v>
@@ -33400,7 +33400,7 @@
         <v>0.475326001644135</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.452761828899384</v>
+        <v>0.452761799097061</v>
       </c>
       <c r="H1139" t="n">
         <v>8619</v>
@@ -33458,7 +33458,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1141" t="n">
-        <v>0.437731891870499</v>
+        <v>0.437731862068176</v>
       </c>
       <c r="H1141" t="n">
         <v>9126</v>
@@ -33516,7 +33516,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1143" t="n">
-        <v>0.548574805259705</v>
+        <v>0.548574864864349</v>
       </c>
       <c r="H1143" t="n">
         <v>882214</v>
@@ -33545,7 +33545,7 @@
         <v>0.524634003639221</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.499729126691818</v>
+        <v>0.499729096889496</v>
       </c>
       <c r="H1144" t="n">
         <v>914157</v>
@@ -33748,7 +33748,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.462154686450958</v>
+        <v>0.462154716253281</v>
       </c>
       <c r="H1151" t="n">
         <v>49687</v>
@@ -33806,7 +33806,7 @@
         <v>0.489131987094879</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.4659124314785</v>
+        <v>0.465912401676178</v>
       </c>
       <c r="H1153" t="n">
         <v>48673</v>
@@ -33980,7 +33980,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.437731891870499</v>
+        <v>0.437731862068176</v>
       </c>
       <c r="H1159" t="n">
         <v>34984</v>
@@ -34009,7 +34009,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H1160" t="n">
         <v>45124</v>
@@ -34096,7 +34096,7 @@
         <v>0.449685990810394</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.428338944911957</v>
+        <v>0.428338974714279</v>
       </c>
       <c r="H1163" t="n">
         <v>51716</v>
@@ -34241,7 +34241,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1168" t="n">
         <v>12168</v>
@@ -34357,7 +34357,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.41988530755043</v>
+        <v>0.419885277748108</v>
       </c>
       <c r="H1172" t="n">
         <v>116107</v>
@@ -34386,7 +34386,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H1173" t="n">
         <v>52730</v>
@@ -34415,7 +34415,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H1174" t="n">
         <v>0</v>
@@ -34473,7 +34473,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.418945103883743</v>
+        <v>0.418945133686066</v>
       </c>
       <c r="H1176" t="n">
         <v>15717</v>
@@ -34502,7 +34502,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.418945103883743</v>
+        <v>0.418945133686066</v>
       </c>
       <c r="H1177" t="n">
         <v>8619</v>
@@ -34531,7 +34531,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.418945103883743</v>
+        <v>0.418945133686066</v>
       </c>
       <c r="H1178" t="n">
         <v>1014</v>
@@ -34676,7 +34676,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1183" t="n">
         <v>10140</v>
@@ -35024,7 +35024,7 @@
         <v>0.429962992668152</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.409552246332169</v>
+        <v>0.409552216529846</v>
       </c>
       <c r="H1195" t="n">
         <v>142472</v>
@@ -35053,7 +35053,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1196" t="n">
         <v>87207</v>
@@ -35256,7 +35256,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1203" t="n">
         <v>65405</v>
@@ -35314,7 +35314,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1205" t="n">
         <v>3042</v>
@@ -35401,7 +35401,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1208" t="n">
         <v>241341</v>
@@ -35430,7 +35430,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.392643928527832</v>
+        <v>0.39264389872551</v>
       </c>
       <c r="H1209" t="n">
         <v>62363</v>
@@ -35575,7 +35575,7 @@
         <v>0.429962992668152</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.409552246332169</v>
+        <v>0.409552216529846</v>
       </c>
       <c r="H1214" t="n">
         <v>40561</v>
@@ -35836,7 +35836,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1223" t="n">
         <v>77067</v>
@@ -35923,7 +35923,7 @@
         <v>0.402350008487701</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.383250057697296</v>
+        <v>0.383250087499619</v>
       </c>
       <c r="H1226" t="n">
         <v>10647</v>
@@ -36097,7 +36097,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.392643928527832</v>
+        <v>0.39264389872551</v>
       </c>
       <c r="H1232" t="n">
         <v>11154</v>
@@ -36184,7 +36184,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1235" t="n">
         <v>115093</v>
@@ -36213,7 +36213,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1236" t="n">
         <v>85179</v>
@@ -36300,7 +36300,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1239" t="n">
         <v>109516</v>
@@ -36329,7 +36329,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1240" t="n">
         <v>40561</v>
@@ -36358,7 +36358,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1241" t="n">
         <v>76053</v>
@@ -36416,7 +36416,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H1243" t="n">
         <v>481161</v>
@@ -36561,7 +36561,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H1248" t="n">
         <v>119149</v>
@@ -36648,7 +36648,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.494093000888824</v>
+        <v>0.494093030691147</v>
       </c>
       <c r="H1251" t="n">
         <v>617043</v>
@@ -36822,7 +36822,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.462154686450958</v>
+        <v>0.462154716253281</v>
       </c>
       <c r="H1257" t="n">
         <v>29407</v>
@@ -37054,7 +37054,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.437731891870499</v>
+        <v>0.437731862068176</v>
       </c>
       <c r="H1265" t="n">
         <v>59321</v>
@@ -37170,7 +37170,7 @@
         <v>0.44574099779129</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.424581259489059</v>
+        <v>0.424581229686737</v>
       </c>
       <c r="H1269" t="n">
         <v>12168</v>
@@ -37315,7 +37315,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.437731891870499</v>
+        <v>0.437731862068176</v>
       </c>
       <c r="H1274" t="n">
         <v>93798</v>
@@ -37431,7 +37431,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H1278" t="n">
         <v>9126</v>
@@ -37547,7 +37547,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.41988530755043</v>
+        <v>0.419885277748108</v>
       </c>
       <c r="H1282" t="n">
         <v>6084</v>
@@ -37837,7 +37837,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1292" t="n">
         <v>94305</v>
@@ -37895,7 +37895,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1294" t="n">
         <v>116107</v>
@@ -37924,7 +37924,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1295" t="n">
         <v>29407</v>
@@ -37953,7 +37953,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1296" t="n">
         <v>84672</v>
@@ -38011,7 +38011,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1298" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1298" t="n">
         <v>76560</v>
@@ -38243,7 +38243,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1306" t="n">
         <v>4056</v>
@@ -38330,7 +38330,7 @@
         <v>0.418128997087479</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.398279994726181</v>
+        <v>0.398280024528503</v>
       </c>
       <c r="H1309" t="n">
         <v>13689</v>
@@ -38359,7 +38359,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1310" t="n">
         <v>1521</v>
@@ -38388,7 +38388,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1311" t="n">
         <v>3042</v>
@@ -38504,7 +38504,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1315" t="n">
         <v>4563</v>
@@ -38533,7 +38533,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1316" t="n">
         <v>0</v>
@@ -38591,7 +38591,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1318" t="n">
         <v>115600</v>
@@ -38765,7 +38765,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1324" t="n">
         <v>25858</v>
@@ -38794,7 +38794,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1325" t="n">
-        <v>0.392643928527832</v>
+        <v>0.39264389872551</v>
       </c>
       <c r="H1325" t="n">
         <v>1521</v>
@@ -38968,7 +38968,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1331" t="n">
         <v>29407</v>
@@ -38997,7 +38997,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1332" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1332" t="n">
         <v>14703</v>
@@ -39026,7 +39026,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1333" t="n">
         <v>4056</v>
@@ -39113,7 +39113,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1336" t="n">
         <v>39040</v>
@@ -39142,7 +39142,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1337" t="n">
-        <v>0.392643928527832</v>
+        <v>0.39264389872551</v>
       </c>
       <c r="H1337" t="n">
         <v>11154</v>
@@ -39200,7 +39200,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1339" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1339" t="n">
         <v>2028</v>
@@ -39258,7 +39258,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1341" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1341" t="n">
         <v>10647</v>
@@ -39287,7 +39287,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1342" t="n">
         <v>0</v>
@@ -39316,7 +39316,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1343" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1343" t="n">
         <v>11154</v>
@@ -39490,7 +39490,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1349" t="n">
         <v>7098</v>
@@ -39519,7 +39519,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1350" t="n">
         <v>19266</v>
@@ -39606,7 +39606,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1353" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1353" t="n">
         <v>41575</v>
@@ -39693,7 +39693,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1356" t="n">
         <v>9633</v>
@@ -39722,7 +39722,7 @@
         <v>0.429962992668152</v>
       </c>
       <c r="G1357" t="n">
-        <v>0.409552246332169</v>
+        <v>0.409552216529846</v>
       </c>
       <c r="H1357" t="n">
         <v>12168</v>
@@ -39896,7 +39896,7 @@
         <v>0.398405998945236</v>
       </c>
       <c r="G1363" t="n">
-        <v>0.379493296146393</v>
+        <v>0.37949326634407</v>
       </c>
       <c r="H1363" t="n">
         <v>57293</v>
@@ -39983,7 +39983,7 @@
         <v>0.398405998945236</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.379493296146393</v>
+        <v>0.37949326634407</v>
       </c>
       <c r="H1366" t="n">
         <v>5577</v>
@@ -40041,7 +40041,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1368" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1368" t="n">
         <v>7098</v>
@@ -40070,7 +40070,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1369" t="n">
         <v>49687</v>
@@ -40099,7 +40099,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1370" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1370" t="n">
         <v>171372</v>
@@ -40244,7 +40244,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1375" t="n">
         <v>56786</v>
@@ -40302,7 +40302,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1377" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1377" t="n">
         <v>23829</v>
@@ -40505,7 +40505,7 @@
         <v>0.402350008487701</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.383250057697296</v>
+        <v>0.383250087499619</v>
       </c>
       <c r="H1384" t="n">
         <v>46138</v>
@@ -40534,7 +40534,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1385" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1385" t="n">
         <v>136895</v>
@@ -40621,7 +40621,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1388" t="n">
         <v>115093</v>
@@ -40650,7 +40650,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.36070653796196</v>
+        <v>0.360706567764282</v>
       </c>
       <c r="H1389" t="n">
         <v>14703</v>
@@ -40708,7 +40708,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1391" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1391" t="n">
         <v>68954</v>
@@ -40766,7 +40766,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.361645728349686</v>
+        <v>0.361645758152008</v>
       </c>
       <c r="H1393" t="n">
         <v>43096</v>
@@ -40795,7 +40795,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.36070653796196</v>
+        <v>0.360706567764282</v>
       </c>
       <c r="H1394" t="n">
         <v>37012</v>
@@ -40911,7 +40911,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1398" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1398" t="n">
         <v>18759</v>
@@ -40940,7 +40940,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1399" t="n">
         <v>0</v>
@@ -41172,7 +41172,7 @@
         <v>0.368820995092392</v>
       </c>
       <c r="G1407" t="n">
-        <v>0.351312726736069</v>
+        <v>0.351312696933746</v>
       </c>
       <c r="H1407" t="n">
         <v>23829</v>
@@ -41201,7 +41201,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.347555905580521</v>
+        <v>0.347555935382843</v>
       </c>
       <c r="H1408" t="n">
         <v>35998</v>
@@ -41288,7 +41288,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1411" t="n">
         <v>29407</v>
@@ -41375,7 +41375,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1414" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1414" t="n">
         <v>21801</v>
@@ -41404,7 +41404,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1415" t="n">
         <v>24336</v>
@@ -41433,7 +41433,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1416" t="n">
         <v>0</v>
@@ -41462,7 +41462,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1417" t="n">
         <v>5577</v>
@@ -41491,7 +41491,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.336283713579178</v>
+        <v>0.336283683776855</v>
       </c>
       <c r="H1418" t="n">
         <v>29407</v>
@@ -41665,7 +41665,7 @@
         <v>0.34909799695015</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.332525968551636</v>
+        <v>0.332525998353958</v>
       </c>
       <c r="H1424" t="n">
         <v>60842</v>
@@ -41752,7 +41752,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1427" t="n">
         <v>30928</v>
@@ -41781,7 +41781,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1428" t="n">
         <v>32956</v>
@@ -41810,7 +41810,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1429" t="n">
         <v>0</v>
@@ -42013,7 +42013,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1436" t="n">
-        <v>0.347555905580521</v>
+        <v>0.347555935382843</v>
       </c>
       <c r="H1436" t="n">
         <v>8112</v>
@@ -42332,7 +42332,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1447" t="n">
         <v>14196</v>
@@ -42361,7 +42361,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1448" t="n">
         <v>31942</v>
@@ -42419,7 +42419,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1450" t="n">
-        <v>0.361645728349686</v>
+        <v>0.361645758152008</v>
       </c>
       <c r="H1450" t="n">
         <v>3549</v>
@@ -42448,7 +42448,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.361645728349686</v>
+        <v>0.361645758152008</v>
       </c>
       <c r="H1451" t="n">
         <v>0</v>
@@ -42680,7 +42680,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1459" t="n">
         <v>120163</v>
@@ -42767,7 +42767,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1462" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1462" t="n">
         <v>46645</v>
@@ -42912,7 +42912,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1467" t="n">
-        <v>0.36070653796196</v>
+        <v>0.360706567764282</v>
       </c>
       <c r="H1467" t="n">
         <v>6591</v>
@@ -42941,7 +42941,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1468" t="n">
         <v>18759</v>
@@ -43028,7 +43028,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.347555905580521</v>
+        <v>0.347555935382843</v>
       </c>
       <c r="H1471" t="n">
         <v>5070</v>
@@ -43231,7 +43231,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1478" t="n">
-        <v>0.36070653796196</v>
+        <v>0.360706567764282</v>
       </c>
       <c r="H1478" t="n">
         <v>1521</v>
@@ -43260,7 +43260,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.361645728349686</v>
+        <v>0.361645758152008</v>
       </c>
       <c r="H1479" t="n">
         <v>5070</v>
@@ -43405,7 +43405,7 @@
         <v>0.384600013494492</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.366342693567276</v>
+        <v>0.366342663764954</v>
       </c>
       <c r="H1484" t="n">
         <v>2535</v>
@@ -43434,7 +43434,7 @@
         <v>0.384600013494492</v>
       </c>
       <c r="G1485" t="n">
-        <v>0.366342693567276</v>
+        <v>0.366342663764954</v>
       </c>
       <c r="H1485" t="n">
         <v>0</v>
@@ -43492,7 +43492,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1487" t="n">
-        <v>0.361645728349686</v>
+        <v>0.361645758152008</v>
       </c>
       <c r="H1487" t="n">
         <v>11661</v>
@@ -43521,7 +43521,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1488" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1488" t="n">
         <v>17745</v>
@@ -43550,7 +43550,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1489" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1489" t="n">
         <v>0</v>
@@ -43579,7 +43579,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1490" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1490" t="n">
         <v>0</v>
@@ -43695,7 +43695,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1494" t="n">
         <v>40561</v>
@@ -43724,7 +43724,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1495" t="n">
         <v>31435</v>
@@ -44014,7 +44014,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.321253776550293</v>
+        <v>0.321253746747971</v>
       </c>
       <c r="H1505" t="n">
         <v>17238</v>
@@ -44072,7 +44072,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.336283713579178</v>
+        <v>0.336283683776855</v>
       </c>
       <c r="H1507" t="n">
         <v>8112</v>
@@ -44101,7 +44101,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1508" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1508" t="n">
         <v>9126</v>
@@ -44362,7 +44362,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1517" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1517" t="n">
         <v>41068</v>
@@ -44391,7 +44391,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1518" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1518" t="n">
         <v>15717</v>
@@ -44565,7 +44565,7 @@
         <v>0.319514006376266</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.304346352815628</v>
+        <v>0.30434638261795</v>
       </c>
       <c r="H1524" t="n">
         <v>88728</v>
@@ -44594,7 +44594,7 @@
         <v>0.347126007080078</v>
       </c>
       <c r="G1525" t="n">
-        <v>0.330647587776184</v>
+        <v>0.330647617578506</v>
       </c>
       <c r="H1525" t="n">
         <v>83151</v>
@@ -44710,7 +44710,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1529" t="n">
-        <v>0.321253776550293</v>
+        <v>0.321253746747971</v>
       </c>
       <c r="H1529" t="n">
         <v>28393</v>
@@ -44768,7 +44768,7 @@
         <v>0.330361008644104</v>
       </c>
       <c r="G1531" t="n">
-        <v>0.314678460359573</v>
+        <v>0.314678430557251</v>
       </c>
       <c r="H1531" t="n">
         <v>50194</v>
@@ -45029,7 +45029,7 @@
         <v>0.347126007080078</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.330647587776184</v>
+        <v>0.330647617578506</v>
       </c>
       <c r="H1540" t="n">
         <v>26365</v>
@@ -45087,7 +45087,7 @@
         <v>0.333319991827011</v>
       </c>
       <c r="G1542" t="n">
-        <v>0.317496955394745</v>
+        <v>0.317496985197067</v>
       </c>
       <c r="H1542" t="n">
         <v>20280</v>
@@ -45116,7 +45116,7 @@
         <v>0.333319991827011</v>
       </c>
       <c r="G1543" t="n">
-        <v>0.317496955394745</v>
+        <v>0.317496985197067</v>
       </c>
       <c r="H1543" t="n">
         <v>41068</v>
@@ -45174,7 +45174,7 @@
         <v>0.334306001663208</v>
       </c>
       <c r="G1545" t="n">
-        <v>0.318436145782471</v>
+        <v>0.318436175584793</v>
       </c>
       <c r="H1545" t="n">
         <v>1521</v>
@@ -45203,7 +45203,7 @@
         <v>0.334306001663208</v>
       </c>
       <c r="G1546" t="n">
-        <v>0.318436145782471</v>
+        <v>0.318436175584793</v>
       </c>
       <c r="H1546" t="n">
         <v>0</v>
@@ -45232,7 +45232,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1547" t="n">
-        <v>0.309981524944305</v>
+        <v>0.309981554746628</v>
       </c>
       <c r="H1547" t="n">
         <v>12168</v>
@@ -45261,7 +45261,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.309981524944305</v>
+        <v>0.309981554746628</v>
       </c>
       <c r="H1548" t="n">
         <v>8619</v>
@@ -45522,7 +45522,7 @@
         <v>0.333319991827011</v>
       </c>
       <c r="G1557" t="n">
-        <v>0.317496955394745</v>
+        <v>0.317496985197067</v>
       </c>
       <c r="H1557" t="n">
         <v>13182</v>
@@ -45551,7 +45551,7 @@
         <v>0.366849005222321</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.349434345960617</v>
+        <v>0.349434316158295</v>
       </c>
       <c r="H1558" t="n">
         <v>454289</v>
@@ -45667,7 +45667,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.321253776550293</v>
+        <v>0.321253746747971</v>
       </c>
       <c r="H1562" t="n">
         <v>39547</v>
@@ -45696,7 +45696,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1563" t="n">
-        <v>0.309981524944305</v>
+        <v>0.309981554746628</v>
       </c>
       <c r="H1563" t="n">
         <v>19266</v>
@@ -45870,7 +45870,7 @@
         <v>0.330361008644104</v>
       </c>
       <c r="G1569" t="n">
-        <v>0.314678460359573</v>
+        <v>0.314678430557251</v>
       </c>
       <c r="H1569" t="n">
         <v>24843</v>
@@ -45899,7 +45899,7 @@
         <v>0.330361008644104</v>
       </c>
       <c r="G1570" t="n">
-        <v>0.314678460359573</v>
+        <v>0.314678430557251</v>
       </c>
       <c r="H1570" t="n">
         <v>0</v>
@@ -46015,7 +46015,7 @@
         <v>0.307680010795593</v>
       </c>
       <c r="G1574" t="n">
-        <v>0.293074160814285</v>
+        <v>0.293074131011963</v>
       </c>
       <c r="H1574" t="n">
         <v>35491</v>
@@ -46044,7 +46044,7 @@
         <v>0.301762998104095</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.287438005208969</v>
+        <v>0.287438035011292</v>
       </c>
       <c r="H1575" t="n">
         <v>19266</v>
@@ -46073,7 +46073,7 @@
         <v>0.304720997810364</v>
       </c>
       <c r="G1576" t="n">
-        <v>0.290255576372147</v>
+        <v>0.290255606174469</v>
       </c>
       <c r="H1576" t="n">
         <v>5070</v>
@@ -46276,7 +46276,7 @@
         <v>0.316554993391037</v>
       </c>
       <c r="G1583" t="n">
-        <v>0.301527827978134</v>
+        <v>0.301527798175812</v>
       </c>
       <c r="H1583" t="n">
         <v>4056</v>
@@ -46305,7 +46305,7 @@
         <v>0.304720997810364</v>
       </c>
       <c r="G1584" t="n">
-        <v>0.290255576372147</v>
+        <v>0.290255606174469</v>
       </c>
       <c r="H1584" t="n">
         <v>19773</v>
@@ -46392,7 +46392,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1587" t="n">
-        <v>0.309981524944305</v>
+        <v>0.309981554746628</v>
       </c>
       <c r="H1587" t="n">
         <v>9633</v>
@@ -46537,7 +46537,7 @@
         <v>0.323457986116409</v>
       </c>
       <c r="G1592" t="n">
-        <v>0.308103144168854</v>
+        <v>0.308103114366531</v>
       </c>
       <c r="H1592" t="n">
         <v>3042</v>
@@ -46595,7 +46595,7 @@
         <v>0.321485996246338</v>
       </c>
       <c r="G1594" t="n">
-        <v>0.306224763393402</v>
+        <v>0.30622473359108</v>
       </c>
       <c r="H1594" t="n">
         <v>12168</v>
@@ -46885,7 +46885,7 @@
         <v>0.307680010795593</v>
       </c>
       <c r="G1604" t="n">
-        <v>0.293074160814285</v>
+        <v>0.293074131011963</v>
       </c>
       <c r="H1604" t="n">
         <v>6591</v>
@@ -46914,7 +46914,7 @@
         <v>0.307680010795593</v>
       </c>
       <c r="G1605" t="n">
-        <v>0.293074160814285</v>
+        <v>0.293074131011963</v>
       </c>
       <c r="H1605" t="n">
         <v>0</v>
@@ -46943,7 +46943,7 @@
         <v>0.308665990829468</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.294013321399689</v>
+        <v>0.294013291597366</v>
       </c>
       <c r="H1606" t="n">
         <v>6084</v>
@@ -46972,7 +46972,7 @@
         <v>0.301762998104095</v>
       </c>
       <c r="G1607" t="n">
-        <v>0.287438005208969</v>
+        <v>0.287438035011292</v>
       </c>
       <c r="H1607" t="n">
         <v>6084</v>
@@ -47146,7 +47146,7 @@
         <v>0.34909799695015</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.332525968551636</v>
+        <v>0.332525998353958</v>
       </c>
       <c r="H1613" t="n">
         <v>2028</v>
@@ -47175,7 +47175,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.321253776550293</v>
+        <v>0.321253746747971</v>
       </c>
       <c r="H1614" t="n">
         <v>13689</v>
@@ -47262,7 +47262,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1617" t="n">
-        <v>0.347555905580521</v>
+        <v>0.347555935382843</v>
       </c>
       <c r="H1617" t="n">
         <v>191653</v>
@@ -47320,7 +47320,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.336283713579178</v>
+        <v>0.336283683776855</v>
       </c>
       <c r="H1619" t="n">
         <v>56279</v>
@@ -47349,7 +47349,7 @@
         <v>0.363889992237091</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.346615761518478</v>
+        <v>0.346615791320801</v>
       </c>
       <c r="H1620" t="n">
         <v>17238</v>
@@ -47407,7 +47407,7 @@
         <v>0.368820995092392</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.351312726736069</v>
+        <v>0.351312696933746</v>
       </c>
       <c r="H1622" t="n">
         <v>476598</v>
@@ -47465,7 +47465,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1624" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1624" t="n">
         <v>62363</v>
@@ -47697,7 +47697,7 @@
         <v>0.674529016017914</v>
       </c>
       <c r="G1632" t="n">
-        <v>0.642508447170258</v>
+        <v>0.642508506774902</v>
       </c>
       <c r="H1632" t="n">
         <v>674336</v>
@@ -47755,7 +47755,7 @@
         <v>0.639028012752533</v>
       </c>
       <c r="G1634" t="n">
-        <v>0.608692705631256</v>
+        <v>0.608692765235901</v>
       </c>
       <c r="H1634" t="n">
         <v>336661</v>
@@ -47871,7 +47871,7 @@
         <v>0.611415028572083</v>
       </c>
       <c r="G1638" t="n">
-        <v>0.582390546798706</v>
+        <v>0.582390606403351</v>
       </c>
       <c r="H1638" t="n">
         <v>162246</v>
@@ -47900,7 +47900,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1639" t="n">
-        <v>0.548574805259705</v>
+        <v>0.548574864864349</v>
       </c>
       <c r="H1639" t="n">
         <v>162246</v>
@@ -47987,7 +47987,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1642" t="n">
-        <v>0.548574805259705</v>
+        <v>0.548574864864349</v>
       </c>
       <c r="H1642" t="n">
         <v>111037</v>
@@ -48045,7 +48045,7 @@
         <v>0.571968972682953</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.544817090034485</v>
+        <v>0.54481703042984</v>
       </c>
       <c r="H1644" t="n">
         <v>66926</v>
@@ -48364,7 +48364,7 @@
         <v>0.702140986919403</v>
       </c>
       <c r="G1655" t="n">
-        <v>0.668809652328491</v>
+        <v>0.668809711933136</v>
       </c>
       <c r="H1655" t="n">
         <v>78081</v>
@@ -48625,7 +48625,7 @@
         <v>0.615360021591187</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.586148321628571</v>
+        <v>0.586148262023926</v>
       </c>
       <c r="H1664" t="n">
         <v>8619</v>
@@ -48712,7 +48712,7 @@
         <v>0.639028012752533</v>
       </c>
       <c r="G1667" t="n">
-        <v>0.608692705631256</v>
+        <v>0.608692765235901</v>
       </c>
       <c r="H1667" t="n">
         <v>56786</v>
@@ -48741,7 +48741,7 @@
         <v>0.64691698551178</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.616207182407379</v>
+        <v>0.616207242012024</v>
       </c>
       <c r="H1668" t="n">
         <v>59321</v>
@@ -48857,7 +48857,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.604935050010681</v>
+        <v>0.604934990406036</v>
       </c>
       <c r="H1672" t="n">
         <v>31942</v>
@@ -48915,7 +48915,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1674" t="n">
-        <v>0.604935050010681</v>
+        <v>0.604934990406036</v>
       </c>
       <c r="H1674" t="n">
         <v>70982</v>
@@ -49147,7 +49147,7 @@
         <v>0.615360021591187</v>
       </c>
       <c r="G1682" t="n">
-        <v>0.586148321628571</v>
+        <v>0.586148262023926</v>
       </c>
       <c r="H1682" t="n">
         <v>13689</v>
@@ -49176,7 +49176,7 @@
         <v>0.583802998065948</v>
       </c>
       <c r="G1683" t="n">
-        <v>0.556089282035828</v>
+        <v>0.556089341640472</v>
       </c>
       <c r="H1683" t="n">
         <v>214976</v>
@@ -49263,7 +49263,7 @@
         <v>0.571968972682953</v>
       </c>
       <c r="G1686" t="n">
-        <v>0.544817090034485</v>
+        <v>0.54481703042984</v>
       </c>
       <c r="H1686" t="n">
         <v>9126</v>
@@ -49350,7 +49350,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1689" t="n">
-        <v>0.548574805259705</v>
+        <v>0.548574864864349</v>
       </c>
       <c r="H1689" t="n">
         <v>25858</v>
@@ -49408,7 +49408,7 @@
         <v>0.595637023448944</v>
       </c>
       <c r="G1691" t="n">
-        <v>0.567361533641815</v>
+        <v>0.56736159324646</v>
       </c>
       <c r="H1691" t="n">
         <v>12675</v>
@@ -49524,7 +49524,7 @@
         <v>0.603525996208191</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.574876010417938</v>
+        <v>0.574876070022583</v>
       </c>
       <c r="H1695" t="n">
         <v>28900</v>
@@ -49582,7 +49582,7 @@
         <v>0.595637023448944</v>
       </c>
       <c r="G1697" t="n">
-        <v>0.567361533641815</v>
+        <v>0.56736159324646</v>
       </c>
       <c r="H1697" t="n">
         <v>3549</v>
@@ -49669,7 +49669,7 @@
         <v>0.607470989227295</v>
       </c>
       <c r="G1700" t="n">
-        <v>0.578633785247803</v>
+        <v>0.578633725643158</v>
       </c>
       <c r="H1700" t="n">
         <v>25351</v>
@@ -49698,7 +49698,7 @@
         <v>0.607470989227295</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.578633785247803</v>
+        <v>0.578633725643158</v>
       </c>
       <c r="H1701" t="n">
         <v>19773</v>
@@ -49727,7 +49727,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.604935050010681</v>
+        <v>0.604934990406036</v>
       </c>
       <c r="H1702" t="n">
         <v>64391</v>
@@ -49872,7 +49872,7 @@
         <v>0.662694990634918</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.631236255168915</v>
+        <v>0.63123619556427</v>
       </c>
       <c r="H1707" t="n">
         <v>123712</v>
@@ -50075,7 +50075,7 @@
         <v>0.702140986919403</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.668809652328491</v>
+        <v>0.668809711933136</v>
       </c>
       <c r="H1714" t="n">
         <v>115093</v>
@@ -50162,7 +50162,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1717" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H1717" t="n">
         <v>1126598</v>
@@ -50249,7 +50249,7 @@
         <v>0.702140986919403</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.668809652328491</v>
+        <v>0.668809711933136</v>
       </c>
       <c r="H1720" t="n">
         <v>385842</v>
@@ -50423,7 +50423,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1726" t="n">
-        <v>0.63499391078949</v>
+        <v>0.634993970394135</v>
       </c>
       <c r="H1726" t="n">
         <v>82644</v>
@@ -50481,7 +50481,7 @@
         <v>0.668612003326416</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.636872291564941</v>
+        <v>0.636872351169586</v>
       </c>
       <c r="H1728" t="n">
         <v>132332</v>
@@ -50510,7 +50510,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1729" t="n">
-        <v>0.63499391078949</v>
+        <v>0.634993970394135</v>
       </c>
       <c r="H1729" t="n">
         <v>9126</v>
@@ -50713,7 +50713,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H1736" t="n">
         <v>307254</v>
@@ -50800,7 +50800,7 @@
         <v>0.674529016017914</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.642508447170258</v>
+        <v>0.642508506774902</v>
       </c>
       <c r="H1739" t="n">
         <v>100389</v>
@@ -50887,7 +50887,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1742" t="n">
-        <v>0.63499391078949</v>
+        <v>0.634993970394135</v>
       </c>
       <c r="H1742" t="n">
         <v>41575</v>
@@ -50945,7 +50945,7 @@
         <v>0.662694990634918</v>
       </c>
       <c r="G1744" t="n">
-        <v>0.631236255168915</v>
+        <v>0.63123619556427</v>
       </c>
       <c r="H1744" t="n">
         <v>26365</v>
@@ -51119,7 +51119,7 @@
         <v>0.64691698551178</v>
       </c>
       <c r="G1750" t="n">
-        <v>0.616207182407379</v>
+        <v>0.616207242012024</v>
       </c>
       <c r="H1750" t="n">
         <v>328548</v>
@@ -51264,7 +51264,7 @@
         <v>0.694252014160156</v>
       </c>
       <c r="G1755" t="n">
-        <v>0.661295175552368</v>
+        <v>0.661295235157013</v>
       </c>
       <c r="H1755" t="n">
         <v>19773</v>
@@ -51496,7 +51496,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1763" t="n">
-        <v>0.63499391078949</v>
+        <v>0.634993970394135</v>
       </c>
       <c r="H1763" t="n">
         <v>228159</v>
@@ -51699,7 +51699,7 @@
         <v>0.69819700717926</v>
       </c>
       <c r="G1770" t="n">
-        <v>0.665052950382233</v>
+        <v>0.665052890777588</v>
       </c>
       <c r="H1770" t="n">
         <v>90249</v>
@@ -52279,7 +52279,7 @@
         <v>0.674529016017914</v>
       </c>
       <c r="G1790" t="n">
-        <v>0.642508447170258</v>
+        <v>0.642508506774902</v>
       </c>
       <c r="H1790" t="n">
         <v>5577</v>
@@ -52337,7 +52337,7 @@
         <v>0.694252014160156</v>
       </c>
       <c r="G1792" t="n">
-        <v>0.661295175552368</v>
+        <v>0.661295235157013</v>
       </c>
       <c r="H1792" t="n">
         <v>99882</v>
@@ -52656,7 +52656,7 @@
         <v>0.69819700717926</v>
       </c>
       <c r="G1803" t="n">
-        <v>0.665052950382233</v>
+        <v>0.665052890777588</v>
       </c>
       <c r="H1803" t="n">
         <v>735179</v>
@@ -52830,7 +52830,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1809" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H1809" t="n">
         <v>43603</v>
@@ -52859,7 +52859,7 @@
         <v>0.706085979938507</v>
       </c>
       <c r="G1810" t="n">
-        <v>0.672567427158356</v>
+        <v>0.672567367553711</v>
       </c>
       <c r="H1810" t="n">
         <v>60335</v>
@@ -53207,7 +53207,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H1822" t="n">
         <v>42589</v>
@@ -53265,7 +53265,7 @@
         <v>0.733698010444641</v>
       </c>
       <c r="G1824" t="n">
-        <v>0.698868691921234</v>
+        <v>0.698868632316589</v>
       </c>
       <c r="H1824" t="n">
         <v>185569</v>
@@ -53323,7 +53323,7 @@
         <v>0.729753971099854</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.695111811161041</v>
+        <v>0.695111870765686</v>
       </c>
       <c r="H1826" t="n">
         <v>63884</v>
@@ -53410,7 +53410,7 @@
         <v>0.745531976222992</v>
       </c>
       <c r="G1829" t="n">
-        <v>0.710140824317932</v>
+        <v>0.710140883922577</v>
       </c>
       <c r="H1829" t="n">
         <v>101911</v>
@@ -53439,7 +53439,7 @@
         <v>0.745531976222992</v>
       </c>
       <c r="G1830" t="n">
-        <v>0.710140824317932</v>
+        <v>0.710140883922577</v>
       </c>
       <c r="H1830" t="n">
         <v>85179</v>
@@ -53497,7 +53497,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1832" t="n">
-        <v>0.712020218372345</v>
+        <v>0.71202027797699</v>
       </c>
       <c r="H1832" t="n">
         <v>27886</v>
@@ -53555,7 +53555,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1834" t="n">
-        <v>0.712020218372345</v>
+        <v>0.71202027797699</v>
       </c>
       <c r="H1834" t="n">
         <v>23829</v>
@@ -53584,7 +53584,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G1835" t="n">
-        <v>0.702626347541809</v>
+        <v>0.702626407146454</v>
       </c>
       <c r="H1835" t="n">
         <v>106981</v>
@@ -53613,7 +53613,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.702626347541809</v>
+        <v>0.702626407146454</v>
       </c>
       <c r="H1836" t="n">
         <v>2535</v>
@@ -53642,7 +53642,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G1837" t="n">
-        <v>0.702626347541809</v>
+        <v>0.702626407146454</v>
       </c>
       <c r="H1837" t="n">
         <v>14703</v>
@@ -53700,7 +53700,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1839" t="n">
-        <v>0.712020218372345</v>
+        <v>0.71202027797699</v>
       </c>
       <c r="H1839" t="n">
         <v>37519</v>
@@ -53729,7 +53729,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.712020218372345</v>
+        <v>0.71202027797699</v>
       </c>
       <c r="H1840" t="n">
         <v>5577</v>
@@ -53990,7 +53990,7 @@
         <v>0.796811997890472</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.758986592292786</v>
+        <v>0.758986532688141</v>
       </c>
       <c r="H1849" t="n">
         <v>942043</v>
@@ -54193,7 +54193,7 @@
         <v>0.942762970924377</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.898009121417999</v>
+        <v>0.898009061813354</v>
       </c>
       <c r="H1856" t="n">
         <v>243876</v>
@@ -54338,7 +54338,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1861" t="n">
-        <v>1.089635014534</v>
+        <v>1.08963513374329</v>
       </c>
       <c r="H1861" t="n">
         <v>336661</v>
@@ -54425,7 +54425,7 @@
         <v>1.10449194908142</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.05206072330475</v>
+        <v>1.05206060409546</v>
       </c>
       <c r="H1864" t="n">
         <v>324999</v>
@@ -54512,7 +54512,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.089635014534</v>
+        <v>1.08963513374329</v>
       </c>
       <c r="H1867" t="n">
         <v>737207</v>
@@ -54599,7 +54599,7 @@
         <v>1.10449194908142</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.05206072330475</v>
+        <v>1.05206060409546</v>
       </c>
       <c r="H1870" t="n">
         <v>120163</v>
@@ -54657,7 +54657,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.089635014534</v>
+        <v>1.08963513374329</v>
       </c>
       <c r="H1872" t="n">
         <v>374180</v>
@@ -54744,7 +54744,7 @@
         <v>1.15873098373413</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.10372483730316</v>
+        <v>1.10372495651245</v>
       </c>
       <c r="H1875" t="n">
         <v>117121</v>
@@ -54773,7 +54773,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.089635014534</v>
+        <v>1.08963513374329</v>
       </c>
       <c r="H1876" t="n">
         <v>24336</v>
@@ -54860,7 +54860,7 @@
         <v>1.15873098373413</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.10372483730316</v>
+        <v>1.10372495651245</v>
       </c>
       <c r="H1879" t="n">
         <v>75038</v>
@@ -54976,7 +54976,7 @@
         <v>1.2179000377655</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.16008520126343</v>
+        <v>1.16008508205414</v>
       </c>
       <c r="H1883" t="n">
         <v>52730</v>
@@ -55324,7 +55324,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.20705246925354</v>
+        <v>1.20705235004425</v>
       </c>
       <c r="H1895" t="n">
         <v>59321</v>
@@ -55382,7 +55382,7 @@
         <v>1.25734603404999</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.19765853881836</v>
+        <v>1.19765865802765</v>
       </c>
       <c r="H1897" t="n">
         <v>146021</v>
@@ -55411,7 +55411,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.20705246925354</v>
+        <v>1.20705235004425</v>
       </c>
       <c r="H1898" t="n">
         <v>88221</v>
@@ -55440,7 +55440,7 @@
         <v>1.27213895320892</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.21174931526184</v>
+        <v>1.21174919605255</v>
       </c>
       <c r="H1899" t="n">
         <v>80616</v>
@@ -55701,7 +55701,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.20705246925354</v>
+        <v>1.20705235004425</v>
       </c>
       <c r="H1908" t="n">
         <v>396489</v>
@@ -56020,7 +56020,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H1919" t="n">
         <v>359984</v>
@@ -56049,7 +56049,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.31977272033691</v>
+        <v>1.3197728395462</v>
       </c>
       <c r="H1920" t="n">
         <v>571411</v>
@@ -56107,7 +56107,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.33386361598969</v>
+        <v>1.3338634967804</v>
       </c>
       <c r="H1922" t="n">
         <v>187090</v>
@@ -56310,7 +56310,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.30568289756775</v>
+        <v>1.30568301677704</v>
       </c>
       <c r="H1929" t="n">
         <v>545553</v>
@@ -56368,7 +56368,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.2352329492569</v>
+        <v>1.23523306846619</v>
       </c>
       <c r="H1931" t="n">
         <v>329055</v>
@@ -56397,7 +56397,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G1932" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H1932" t="n">
         <v>112558</v>
@@ -80125,6 +80125,35 @@
         <v>17500</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>3.35999989509583</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>3.44000005722046</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>3.28999996185303</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>3.33999991416931</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>3.33999991416931</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>52000</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G2" t="n">
-        <v>2.78796315193176</v>
+        <v>2.78796291351318</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -456,7 +456,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G3" t="n">
-        <v>2.78796315193176</v>
+        <v>2.78796291351318</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -485,7 +485,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78796315193176</v>
+        <v>2.78796291351318</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -514,7 +514,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G5" t="n">
-        <v>2.78796315193176</v>
+        <v>2.78796291351318</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -543,7 +543,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G6" t="n">
-        <v>2.78796315193176</v>
+        <v>2.78796291351318</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>2.90521001815796</v>
       </c>
       <c r="G32" t="n">
-        <v>2.76729679107666</v>
+        <v>2.76729702949524</v>
       </c>
       <c r="H32" t="n">
         <v>1521</v>
@@ -1355,7 +1355,7 @@
         <v>2.85984706878662</v>
       </c>
       <c r="G34" t="n">
-        <v>2.72408747673035</v>
+        <v>2.72408723831177</v>
       </c>
       <c r="H34" t="n">
         <v>5070</v>
@@ -1442,7 +1442,7 @@
         <v>2.90718293190002</v>
       </c>
       <c r="G37" t="n">
-        <v>2.76917600631714</v>
+        <v>2.76917624473572</v>
       </c>
       <c r="H37" t="n">
         <v>1014</v>
@@ -1471,7 +1471,7 @@
         <v>2.90718293190002</v>
       </c>
       <c r="G38" t="n">
-        <v>2.76917600631714</v>
+        <v>2.76917624473572</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>2.90718293190002</v>
       </c>
       <c r="G39" t="n">
-        <v>2.76917600631714</v>
+        <v>2.76917624473572</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G45" t="n">
-        <v>2.66772699356079</v>
+        <v>2.66772723197937</v>
       </c>
       <c r="H45" t="n">
         <v>2028</v>
@@ -3965,7 +3965,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G124" t="n">
-        <v>2.78796315193176</v>
+        <v>2.78796291351318</v>
       </c>
       <c r="H124" t="n">
         <v>507</v>
@@ -3994,7 +3994,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G125" t="n">
-        <v>2.78796315193176</v>
+        <v>2.78796291351318</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G126" t="n">
-        <v>2.66772699356079</v>
+        <v>2.66772723197937</v>
       </c>
       <c r="H126" t="n">
         <v>10140</v>
@@ -4052,7 +4052,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G127" t="n">
-        <v>2.66772699356079</v>
+        <v>2.66772723197937</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G128" t="n">
-        <v>2.66772699356079</v>
+        <v>2.66772723197937</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G129" t="n">
-        <v>2.66772699356079</v>
+        <v>2.66772723197937</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G130" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H130" t="n">
         <v>2028</v>
@@ -4168,7 +4168,7 @@
         <v>2.72967505455017</v>
       </c>
       <c r="G131" t="n">
-        <v>2.60009455680847</v>
+        <v>2.60009479522705</v>
       </c>
       <c r="H131" t="n">
         <v>507</v>
@@ -4197,7 +4197,7 @@
         <v>2.72967505455017</v>
       </c>
       <c r="G132" t="n">
-        <v>2.60009455680847</v>
+        <v>2.60009479522705</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4226,7 +4226,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G133" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H133" t="n">
         <v>6591</v>
@@ -4255,7 +4255,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G136" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G137" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G138" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G139" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G140" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G141" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G142" t="n">
-        <v>2.56064176559448</v>
+        <v>2.56064200401306</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>2.58372402191162</v>
       </c>
       <c r="G143" t="n">
-        <v>2.46107196807861</v>
+        <v>2.46107220649719</v>
       </c>
       <c r="H143" t="n">
         <v>1014</v>
@@ -4545,7 +4545,7 @@
         <v>2.58372402191162</v>
       </c>
       <c r="G144" t="n">
-        <v>2.46107196807861</v>
+        <v>2.46107220649719</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>2.48905301094055</v>
       </c>
       <c r="G145" t="n">
-        <v>2.37089538574219</v>
+        <v>2.37089514732361</v>
       </c>
       <c r="H145" t="n">
         <v>507</v>
@@ -4603,7 +4603,7 @@
         <v>2.48905301094055</v>
       </c>
       <c r="G146" t="n">
-        <v>2.37089538574219</v>
+        <v>2.37089514732361</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>2.35690808296204</v>
       </c>
       <c r="G148" t="n">
-        <v>2.24502325057983</v>
+        <v>2.24502348899841</v>
       </c>
       <c r="H148" t="n">
         <v>2028</v>
@@ -4835,7 +4835,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G154" t="n">
-        <v>2.47046613693237</v>
+        <v>2.47046589851379</v>
       </c>
       <c r="H154" t="n">
         <v>1014</v>
@@ -4864,7 +4864,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G155" t="n">
-        <v>2.47046613693237</v>
+        <v>2.47046589851379</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G156" t="n">
-        <v>2.47046613693237</v>
+        <v>2.47046589851379</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G157" t="n">
-        <v>2.47046613693237</v>
+        <v>2.47046589851379</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G158" t="n">
-        <v>2.47046613693237</v>
+        <v>2.47046589851379</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G159" t="n">
-        <v>2.47046613693237</v>
+        <v>2.47046589851379</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>2.56400108337402</v>
       </c>
       <c r="G173" t="n">
-        <v>2.44228553771973</v>
+        <v>2.44228529930115</v>
       </c>
       <c r="H173" t="n">
         <v>1014</v>
@@ -5618,7 +5618,7 @@
         <v>2.58372402191162</v>
       </c>
       <c r="G181" t="n">
-        <v>2.46107196807861</v>
+        <v>2.46107220649719</v>
       </c>
       <c r="H181" t="n">
         <v>2028</v>
@@ -6227,7 +6227,7 @@
         <v>2.56400108337402</v>
       </c>
       <c r="G202" t="n">
-        <v>2.44228553771973</v>
+        <v>2.44228529930115</v>
       </c>
       <c r="H202" t="n">
         <v>10140</v>
@@ -6256,7 +6256,7 @@
         <v>2.56991791725159</v>
       </c>
       <c r="G203" t="n">
-        <v>2.44792151451111</v>
+        <v>2.44792127609253</v>
       </c>
       <c r="H203" t="n">
         <v>3549</v>
@@ -6314,7 +6314,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G205" t="n">
-        <v>2.36525917053223</v>
+        <v>2.36525893211365</v>
       </c>
       <c r="H205" t="n">
         <v>2028</v>
@@ -6343,7 +6343,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G206" t="n">
-        <v>2.36525917053223</v>
+        <v>2.36525893211365</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -6372,7 +6372,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G207" t="n">
-        <v>2.36525917053223</v>
+        <v>2.36525893211365</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G208" t="n">
-        <v>2.36525917053223</v>
+        <v>2.36525893211365</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G209" t="n">
-        <v>2.36525917053223</v>
+        <v>2.36525893211365</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G210" t="n">
-        <v>2.36525917053223</v>
+        <v>2.36525893211365</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>2.46144104003906</v>
       </c>
       <c r="G214" t="n">
-        <v>2.34459400177002</v>
+        <v>2.3445942401886</v>
       </c>
       <c r="H214" t="n">
         <v>7605</v>
@@ -7242,7 +7242,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G237" t="n">
-        <v>2.2074499130249</v>
+        <v>2.20744967460632</v>
       </c>
       <c r="H237" t="n">
         <v>2028</v>
@@ -7271,7 +7271,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G238" t="n">
-        <v>2.2074499130249</v>
+        <v>2.20744967460632</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G239" t="n">
-        <v>2.2074499130249</v>
+        <v>2.20744967460632</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G240" t="n">
-        <v>2.2074499130249</v>
+        <v>2.20744967460632</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G241" t="n">
-        <v>2.2074499130249</v>
+        <v>2.20744967460632</v>
       </c>
       <c r="H241" t="n">
         <v>1521</v>
@@ -7764,7 +7764,7 @@
         <v>2.36874198913574</v>
       </c>
       <c r="G255" t="n">
-        <v>2.25629544258118</v>
+        <v>2.25629568099976</v>
       </c>
       <c r="H255" t="n">
         <v>21294</v>
@@ -7880,7 +7880,7 @@
         <v>2.17151093482971</v>
       </c>
       <c r="G259" t="n">
-        <v>2.06842708587646</v>
+        <v>2.06842732429504</v>
       </c>
       <c r="H259" t="n">
         <v>1014</v>
@@ -7909,7 +7909,7 @@
         <v>2.09853601455688</v>
       </c>
       <c r="G260" t="n">
-        <v>1.99891638755798</v>
+        <v>1.99891650676727</v>
       </c>
       <c r="H260" t="n">
         <v>5577</v>
@@ -7967,7 +7967,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G262" t="n">
-        <v>2.08345699310303</v>
+        <v>2.08345723152161</v>
       </c>
       <c r="H262" t="n">
         <v>507</v>
@@ -7996,7 +7996,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G263" t="n">
-        <v>2.08345699310303</v>
+        <v>2.08345723152161</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G264" t="n">
-        <v>2.08345699310303</v>
+        <v>2.08345723152161</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G265" t="n">
-        <v>2.08345699310303</v>
+        <v>2.08345723152161</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G266" t="n">
-        <v>2.01958155632019</v>
+        <v>2.01958131790161</v>
       </c>
       <c r="H266" t="n">
         <v>2535</v>
@@ -8112,7 +8112,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G267" t="n">
-        <v>2.01958155632019</v>
+        <v>2.01958131790161</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G280" t="n">
-        <v>2.01958155632019</v>
+        <v>2.01958131790161</v>
       </c>
       <c r="H280" t="n">
         <v>507</v>
@@ -8518,7 +8518,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G281" t="n">
-        <v>2.01958155632019</v>
+        <v>2.01958131790161</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G282" t="n">
-        <v>2.01958155632019</v>
+        <v>2.01958131790161</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G283" t="n">
-        <v>1.98200809955597</v>
+        <v>1.98200821876526</v>
       </c>
       <c r="H283" t="n">
         <v>1014</v>
@@ -8605,7 +8605,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G284" t="n">
-        <v>1.98200809955597</v>
+        <v>1.98200821876526</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G285" t="n">
-        <v>1.98200809955597</v>
+        <v>1.98200821876526</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>2.18531799316406</v>
       </c>
       <c r="G305" t="n">
-        <v>2.08157873153687</v>
+        <v>2.08157896995544</v>
       </c>
       <c r="H305" t="n">
         <v>7605</v>
@@ -9301,7 +9301,7 @@
         <v>1.98216998577118</v>
       </c>
       <c r="G308" t="n">
-        <v>1.88807439804077</v>
+        <v>1.88807451725006</v>
       </c>
       <c r="H308" t="n">
         <v>8112</v>
@@ -9330,7 +9330,7 @@
         <v>1.94272398948669</v>
       </c>
       <c r="G309" t="n">
-        <v>1.85050094127655</v>
+        <v>1.85050106048584</v>
       </c>
       <c r="H309" t="n">
         <v>1014</v>
@@ -9823,7 +9823,7 @@
         <v>2.15770506858826</v>
       </c>
       <c r="G326" t="n">
-        <v>2.05527687072754</v>
+        <v>2.05527663230896</v>
       </c>
       <c r="H326" t="n">
         <v>12675</v>
@@ -9997,7 +9997,7 @@
         <v>2.18926191329956</v>
       </c>
       <c r="G332" t="n">
-        <v>2.08533549308777</v>
+        <v>2.08533573150635</v>
       </c>
       <c r="H332" t="n">
         <v>2535</v>
@@ -10026,7 +10026,7 @@
         <v>2.18926191329956</v>
       </c>
       <c r="G333" t="n">
-        <v>2.08533549308777</v>
+        <v>2.08533573150635</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G340" t="n">
-        <v>2.02521777153015</v>
+        <v>2.02521753311157</v>
       </c>
       <c r="H340" t="n">
         <v>507</v>
@@ -10345,7 +10345,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G344" t="n">
-        <v>2.02521777153015</v>
+        <v>2.02521753311157</v>
       </c>
       <c r="H344" t="n">
         <v>2535</v>
@@ -10374,7 +10374,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G345" t="n">
-        <v>2.02521777153015</v>
+        <v>2.02521753311157</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G346" t="n">
-        <v>1.98200809955597</v>
+        <v>1.98200821876526</v>
       </c>
       <c r="H346" t="n">
         <v>3042</v>
@@ -10432,7 +10432,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G347" t="n">
-        <v>1.98200809955597</v>
+        <v>1.98200821876526</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>2.00189304351807</v>
       </c>
       <c r="G365" t="n">
-        <v>1.90686130523682</v>
+        <v>1.90686118602753</v>
       </c>
       <c r="H365" t="n">
         <v>507</v>
@@ -11041,7 +11041,7 @@
         <v>2.71981310844421</v>
       </c>
       <c r="G368" t="n">
-        <v>2.59070086479187</v>
+        <v>2.59070110321045</v>
       </c>
       <c r="H368" t="n">
         <v>70475</v>
@@ -11070,7 +11070,7 @@
         <v>2.41607809066772</v>
       </c>
       <c r="G369" t="n">
-        <v>2.30138468742371</v>
+        <v>2.30138444900513</v>
       </c>
       <c r="H369" t="n">
         <v>39040</v>
@@ -11099,7 +11099,7 @@
         <v>2.25829291343689</v>
       </c>
       <c r="G370" t="n">
-        <v>2.15108942985535</v>
+        <v>2.15108966827393</v>
       </c>
       <c r="H370" t="n">
         <v>18759</v>
@@ -11215,7 +11215,7 @@
         <v>2.17940092086792</v>
       </c>
       <c r="G374" t="n">
-        <v>2.0759425163269</v>
+        <v>2.07594275474548</v>
       </c>
       <c r="H374" t="n">
         <v>7098</v>
@@ -11273,7 +11273,7 @@
         <v>2.17940092086792</v>
       </c>
       <c r="G376" t="n">
-        <v>2.0759425163269</v>
+        <v>2.07594275474548</v>
       </c>
       <c r="H376" t="n">
         <v>3549</v>
@@ -11331,7 +11331,7 @@
         <v>2.20701289176941</v>
       </c>
       <c r="G378" t="n">
-        <v>2.10224390029907</v>
+        <v>2.10224366188049</v>
       </c>
       <c r="H378" t="n">
         <v>507</v>
@@ -11476,7 +11476,7 @@
         <v>2.44369006156921</v>
       </c>
       <c r="G383" t="n">
-        <v>2.32768559455872</v>
+        <v>2.32768583297729</v>
       </c>
       <c r="H383" t="n">
         <v>179992</v>
@@ -11505,7 +11505,7 @@
         <v>2.30957293510437</v>
       </c>
       <c r="G384" t="n">
-        <v>2.19993543624878</v>
+        <v>2.1999351978302</v>
       </c>
       <c r="H384" t="n">
         <v>109516</v>
@@ -11766,7 +11766,7 @@
         <v>2.3628249168396</v>
       </c>
       <c r="G393" t="n">
-        <v>2.25065922737122</v>
+        <v>2.25065946578979</v>
       </c>
       <c r="H393" t="n">
         <v>19266</v>
@@ -11824,7 +11824,7 @@
         <v>2.27604389190674</v>
       </c>
       <c r="G395" t="n">
-        <v>2.16799783706665</v>
+        <v>2.16799807548523</v>
       </c>
       <c r="H395" t="n">
         <v>20280</v>
@@ -11911,7 +11911,7 @@
         <v>2.10445308685303</v>
       </c>
       <c r="G398" t="n">
-        <v>2.00455260276794</v>
+        <v>2.00455284118652</v>
       </c>
       <c r="H398" t="n">
         <v>142979</v>
@@ -11940,7 +11940,7 @@
         <v>2.0472559928894</v>
       </c>
       <c r="G399" t="n">
-        <v>1.95007073879242</v>
+        <v>1.95007061958313</v>
       </c>
       <c r="H399" t="n">
         <v>25858</v>
@@ -11998,7 +11998,7 @@
         <v>2.19123506546021</v>
       </c>
       <c r="G401" t="n">
-        <v>2.08721494674683</v>
+        <v>2.08721518516541</v>
       </c>
       <c r="H401" t="n">
         <v>99882</v>
@@ -12027,7 +12027,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G402" t="n">
-        <v>2.02521777153015</v>
+        <v>2.02521753311157</v>
       </c>
       <c r="H402" t="n">
         <v>30421</v>
@@ -12056,7 +12056,7 @@
         <v>2.10839796066284</v>
       </c>
       <c r="G403" t="n">
-        <v>2.00831031799316</v>
+        <v>2.00831007957458</v>
       </c>
       <c r="H403" t="n">
         <v>20280</v>
@@ -12143,7 +12143,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G406" t="n">
-        <v>1.98200809955597</v>
+        <v>1.98200821876526</v>
       </c>
       <c r="H406" t="n">
         <v>9633</v>
@@ -12433,7 +12433,7 @@
         <v>2.00189304351807</v>
       </c>
       <c r="G416" t="n">
-        <v>1.90686130523682</v>
+        <v>1.90686118602753</v>
       </c>
       <c r="H416" t="n">
         <v>8112</v>
@@ -12462,7 +12462,7 @@
         <v>1.98019802570343</v>
       </c>
       <c r="G417" t="n">
-        <v>1.88619601726532</v>
+        <v>1.88619613647461</v>
       </c>
       <c r="H417" t="n">
         <v>4563</v>
@@ -12491,7 +12491,7 @@
         <v>2.00189304351807</v>
       </c>
       <c r="G418" t="n">
-        <v>1.90686130523682</v>
+        <v>1.90686118602753</v>
       </c>
       <c r="H418" t="n">
         <v>11661</v>
@@ -12520,7 +12520,7 @@
         <v>2.03936696052551</v>
       </c>
       <c r="G419" t="n">
-        <v>1.9425562620163</v>
+        <v>1.94255614280701</v>
       </c>
       <c r="H419" t="n">
         <v>1014</v>
@@ -12549,7 +12549,7 @@
         <v>2.03936696052551</v>
       </c>
       <c r="G420" t="n">
-        <v>1.9425562620163</v>
+        <v>1.94255614280701</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>1.98808705806732</v>
       </c>
       <c r="G421" t="n">
-        <v>1.89371061325073</v>
+        <v>1.89371073246002</v>
       </c>
       <c r="H421" t="n">
         <v>2028</v>
@@ -12607,7 +12607,7 @@
         <v>2.03936696052551</v>
       </c>
       <c r="G422" t="n">
-        <v>1.9425562620163</v>
+        <v>1.94255614280701</v>
       </c>
       <c r="H422" t="n">
         <v>5070</v>
@@ -12636,7 +12636,7 @@
         <v>2.01569890975952</v>
       </c>
       <c r="G423" t="n">
-        <v>1.92001163959503</v>
+        <v>1.92001175880432</v>
       </c>
       <c r="H423" t="n">
         <v>17745</v>
@@ -12781,7 +12781,7 @@
         <v>1.98019802570343</v>
       </c>
       <c r="G428" t="n">
-        <v>1.88619601726532</v>
+        <v>1.88619613647461</v>
       </c>
       <c r="H428" t="n">
         <v>1521</v>
@@ -12810,7 +12810,7 @@
         <v>1.98019802570343</v>
       </c>
       <c r="G429" t="n">
-        <v>1.88619601726532</v>
+        <v>1.88619613647461</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>1.91313898563385</v>
       </c>
       <c r="G434" t="n">
-        <v>1.82232046127319</v>
+        <v>1.8223203420639</v>
       </c>
       <c r="H434" t="n">
         <v>5070</v>
@@ -12984,7 +12984,7 @@
         <v>1.87960994243622</v>
       </c>
       <c r="G435" t="n">
-        <v>1.79038310050964</v>
+        <v>1.79038298130035</v>
       </c>
       <c r="H435" t="n">
         <v>44617</v>
@@ -13100,7 +13100,7 @@
         <v>1.85397005081177</v>
       </c>
       <c r="G439" t="n">
-        <v>1.76596021652222</v>
+        <v>1.76596033573151</v>
       </c>
       <c r="H439" t="n">
         <v>16731</v>
@@ -13158,7 +13158,7 @@
         <v>1.85791397094727</v>
       </c>
       <c r="G441" t="n">
-        <v>1.76971697807312</v>
+        <v>1.76971709728241</v>
       </c>
       <c r="H441" t="n">
         <v>10140</v>
@@ -13274,7 +13274,7 @@
         <v>1.77507698535919</v>
       </c>
       <c r="G445" t="n">
-        <v>1.69081234931946</v>
+        <v>1.69081246852875</v>
       </c>
       <c r="H445" t="n">
         <v>24843</v>
@@ -13303,7 +13303,7 @@
         <v>1.77507698535919</v>
       </c>
       <c r="G446" t="n">
-        <v>1.69081234931946</v>
+        <v>1.69081246852875</v>
       </c>
       <c r="H446" t="n">
         <v>12675</v>
@@ -13448,7 +13448,7 @@
         <v>1.53840005397797</v>
       </c>
       <c r="G451" t="n">
-        <v>1.46537065505981</v>
+        <v>1.4653707742691</v>
       </c>
       <c r="H451" t="n">
         <v>38533</v>
@@ -13535,7 +13535,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G454" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H454" t="n">
         <v>19266</v>
@@ -13593,7 +13593,7 @@
         <v>1.82241296768188</v>
       </c>
       <c r="G456" t="n">
-        <v>1.73590135574341</v>
+        <v>1.73590123653412</v>
       </c>
       <c r="H456" t="n">
         <v>45631</v>
@@ -13883,7 +13883,7 @@
         <v>1.47528600692749</v>
       </c>
       <c r="G466" t="n">
-        <v>1.40525281429291</v>
+        <v>1.40525269508362</v>
       </c>
       <c r="H466" t="n">
         <v>28393</v>
@@ -13941,7 +13941,7 @@
         <v>1.50684297084808</v>
       </c>
       <c r="G468" t="n">
-        <v>1.43531167507172</v>
+        <v>1.43531179428101</v>
       </c>
       <c r="H468" t="n">
         <v>35998</v>
@@ -13970,7 +13970,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G469" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H469" t="n">
         <v>31435</v>
@@ -14115,7 +14115,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G474" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H474" t="n">
         <v>7098</v>
@@ -14144,7 +14144,7 @@
         <v>1.48909294605255</v>
       </c>
       <c r="G475" t="n">
-        <v>1.41840422153473</v>
+        <v>1.41840434074402</v>
       </c>
       <c r="H475" t="n">
         <v>50702</v>
@@ -14202,7 +14202,7 @@
         <v>1.54431700706482</v>
       </c>
       <c r="G477" t="n">
-        <v>1.47100675106049</v>
+        <v>1.47100687026978</v>
       </c>
       <c r="H477" t="n">
         <v>92784</v>
@@ -14231,7 +14231,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G478" t="n">
-        <v>1.474764585495</v>
+        <v>1.47476446628571</v>
       </c>
       <c r="H478" t="n">
         <v>51716</v>
@@ -14260,7 +14260,7 @@
         <v>1.48909294605255</v>
       </c>
       <c r="G479" t="n">
-        <v>1.41840422153473</v>
+        <v>1.41840434074402</v>
       </c>
       <c r="H479" t="n">
         <v>3042</v>
@@ -14521,7 +14521,7 @@
         <v>1.49205100536346</v>
       </c>
       <c r="G488" t="n">
-        <v>1.42122185230255</v>
+        <v>1.42122197151184</v>
       </c>
       <c r="H488" t="n">
         <v>104446</v>
@@ -14550,7 +14550,7 @@
         <v>1.53840005397797</v>
       </c>
       <c r="G489" t="n">
-        <v>1.46537065505981</v>
+        <v>1.4653707742691</v>
       </c>
       <c r="H489" t="n">
         <v>117121</v>
@@ -14579,7 +14579,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G490" t="n">
-        <v>1.474764585495</v>
+        <v>1.47476446628571</v>
       </c>
       <c r="H490" t="n">
         <v>201793</v>
@@ -14637,7 +14637,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G492" t="n">
-        <v>1.44658398628235</v>
+        <v>1.44658386707306</v>
       </c>
       <c r="H492" t="n">
         <v>31435</v>
@@ -14666,7 +14666,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G493" t="n">
-        <v>1.44658398628235</v>
+        <v>1.44658386707306</v>
       </c>
       <c r="H493" t="n">
         <v>0</v>
@@ -14695,7 +14695,7 @@
         <v>1.54234504699707</v>
       </c>
       <c r="G494" t="n">
-        <v>1.46912837028503</v>
+        <v>1.46912848949432</v>
       </c>
       <c r="H494" t="n">
         <v>14196</v>
@@ -14811,7 +14811,7 @@
         <v>1.55615103244781</v>
       </c>
       <c r="G498" t="n">
-        <v>1.48227906227112</v>
+        <v>1.48227894306183</v>
       </c>
       <c r="H498" t="n">
         <v>2535</v>
@@ -14840,7 +14840,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G499" t="n">
-        <v>1.474764585495</v>
+        <v>1.47476446628571</v>
       </c>
       <c r="H499" t="n">
         <v>3549</v>
@@ -14898,7 +14898,7 @@
         <v>1.55220699310303</v>
       </c>
       <c r="G501" t="n">
-        <v>1.47852230072021</v>
+        <v>1.47852218151093</v>
       </c>
       <c r="H501" t="n">
         <v>2028</v>
@@ -14927,7 +14927,7 @@
         <v>1.50684297084808</v>
       </c>
       <c r="G502" t="n">
-        <v>1.43531167507172</v>
+        <v>1.43531179428101</v>
       </c>
       <c r="H502" t="n">
         <v>3549</v>
@@ -14985,7 +14985,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G504" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H504" t="n">
         <v>23322</v>
@@ -15014,7 +15014,7 @@
         <v>1.44175696372986</v>
       </c>
       <c r="G505" t="n">
-        <v>1.37331545352936</v>
+        <v>1.37331533432007</v>
       </c>
       <c r="H505" t="n">
         <v>8619</v>
@@ -15072,7 +15072,7 @@
         <v>1.4013249874115</v>
       </c>
       <c r="G507" t="n">
-        <v>1.33480262756348</v>
+        <v>1.33480274677277</v>
       </c>
       <c r="H507" t="n">
         <v>5070</v>
@@ -15101,7 +15101,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G508" t="n">
-        <v>1.3338634967804</v>
+        <v>1.33386361598969</v>
       </c>
       <c r="H508" t="n">
         <v>2028</v>
@@ -15304,7 +15304,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G515" t="n">
-        <v>1.3338634967804</v>
+        <v>1.33386361598969</v>
       </c>
       <c r="H515" t="n">
         <v>5577</v>
@@ -15449,7 +15449,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G520" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H520" t="n">
         <v>39040</v>
@@ -15478,7 +15478,7 @@
         <v>1.48909294605255</v>
       </c>
       <c r="G521" t="n">
-        <v>1.41840422153473</v>
+        <v>1.41840434074402</v>
       </c>
       <c r="H521" t="n">
         <v>4056</v>
@@ -15565,7 +15565,7 @@
         <v>1.5531929731369</v>
       </c>
       <c r="G524" t="n">
-        <v>1.4794614315033</v>
+        <v>1.47946131229401</v>
       </c>
       <c r="H524" t="n">
         <v>313845</v>
@@ -15623,7 +15623,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G526" t="n">
-        <v>1.474764585495</v>
+        <v>1.47476446628571</v>
       </c>
       <c r="H526" t="n">
         <v>37012</v>
@@ -15652,7 +15652,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G527" t="n">
-        <v>1.44658398628235</v>
+        <v>1.44658386707306</v>
       </c>
       <c r="H527" t="n">
         <v>17238</v>
@@ -15710,7 +15710,7 @@
         <v>1.5531929731369</v>
       </c>
       <c r="G529" t="n">
-        <v>1.4794614315033</v>
+        <v>1.47946131229401</v>
       </c>
       <c r="H529" t="n">
         <v>11154</v>
@@ -15826,7 +15826,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G533" t="n">
-        <v>1.474764585495</v>
+        <v>1.47476446628571</v>
       </c>
       <c r="H533" t="n">
         <v>20280</v>
@@ -15884,7 +15884,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G535" t="n">
-        <v>1.44658398628235</v>
+        <v>1.44658386707306</v>
       </c>
       <c r="H535" t="n">
         <v>5070</v>
@@ -15971,7 +15971,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G538" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H538" t="n">
         <v>11661</v>
@@ -16000,7 +16000,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G539" t="n">
-        <v>1.474764585495</v>
+        <v>1.47476446628571</v>
       </c>
       <c r="H539" t="n">
         <v>17238</v>
@@ -16116,7 +16116,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G543" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H543" t="n">
         <v>507</v>
@@ -16145,7 +16145,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G544" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H544" t="n">
         <v>1014</v>
@@ -16203,7 +16203,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G546" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H546" t="n">
         <v>7098</v>
@@ -16232,7 +16232,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G547" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H547" t="n">
         <v>6084</v>
@@ -16261,7 +16261,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G548" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H548" t="n">
         <v>2028</v>
@@ -16464,7 +16464,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G555" t="n">
-        <v>1.30568301677704</v>
+        <v>1.30568289756775</v>
       </c>
       <c r="H555" t="n">
         <v>9633</v>
@@ -16638,7 +16638,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G561" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H561" t="n">
         <v>4056</v>
@@ -16812,7 +16812,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G567" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H567" t="n">
         <v>24843</v>
@@ -16841,7 +16841,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G568" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H568" t="n">
         <v>2028</v>
@@ -17073,7 +17073,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G576" t="n">
-        <v>1.29629004001617</v>
+        <v>1.29629015922546</v>
       </c>
       <c r="H576" t="n">
         <v>4056</v>
@@ -17102,7 +17102,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G577" t="n">
-        <v>1.3197728395462</v>
+        <v>1.31977272033691</v>
       </c>
       <c r="H577" t="n">
         <v>6084</v>
@@ -17160,7 +17160,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G579" t="n">
-        <v>1.3197728395462</v>
+        <v>1.31977272033691</v>
       </c>
       <c r="H579" t="n">
         <v>3549</v>
@@ -17508,7 +17508,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G591" t="n">
-        <v>1.29629004001617</v>
+        <v>1.29629015922546</v>
       </c>
       <c r="H591" t="n">
         <v>17745</v>
@@ -17682,7 +17682,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G597" t="n">
-        <v>1.3197728395462</v>
+        <v>1.31977272033691</v>
       </c>
       <c r="H597" t="n">
         <v>5577</v>
@@ -17856,7 +17856,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G603" t="n">
-        <v>1.24932265281677</v>
+        <v>1.24932277202606</v>
       </c>
       <c r="H603" t="n">
         <v>1014</v>
@@ -17885,7 +17885,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G604" t="n">
-        <v>1.24932265281677</v>
+        <v>1.24932277202606</v>
       </c>
       <c r="H604" t="n">
         <v>1521</v>
@@ -17972,7 +17972,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G607" t="n">
-        <v>1.23523306846619</v>
+        <v>1.2352329492569</v>
       </c>
       <c r="H607" t="n">
         <v>15717</v>
@@ -18088,7 +18088,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G611" t="n">
-        <v>1.24932265281677</v>
+        <v>1.24932277202606</v>
       </c>
       <c r="H611" t="n">
         <v>2028</v>
@@ -18117,7 +18117,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G612" t="n">
-        <v>1.24932265281677</v>
+        <v>1.24932277202606</v>
       </c>
       <c r="H612" t="n">
         <v>1014</v>
@@ -18175,7 +18175,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G614" t="n">
-        <v>1.20705235004425</v>
+        <v>1.20705246925354</v>
       </c>
       <c r="H614" t="n">
         <v>12168</v>
@@ -18378,7 +18378,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G621" t="n">
-        <v>1.30568301677704</v>
+        <v>1.30568289756775</v>
       </c>
       <c r="H621" t="n">
         <v>16731</v>
@@ -18639,7 +18639,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G630" t="n">
-        <v>1.30568301677704</v>
+        <v>1.30568289756775</v>
       </c>
       <c r="H630" t="n">
         <v>10647</v>
@@ -18784,7 +18784,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G635" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H635" t="n">
         <v>53237</v>
@@ -18871,7 +18871,7 @@
         <v>1.85397005081177</v>
       </c>
       <c r="G638" t="n">
-        <v>1.76596021652222</v>
+        <v>1.76596033573151</v>
       </c>
       <c r="H638" t="n">
         <v>456825</v>
@@ -19074,7 +19074,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G645" t="n">
-        <v>1.474764585495</v>
+        <v>1.47476446628571</v>
       </c>
       <c r="H645" t="n">
         <v>142979</v>
@@ -19277,7 +19277,7 @@
         <v>1.56798505783081</v>
       </c>
       <c r="G652" t="n">
-        <v>1.49355137348175</v>
+        <v>1.49355125427246</v>
       </c>
       <c r="H652" t="n">
         <v>129797</v>
@@ -19393,7 +19393,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G656" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H656" t="n">
         <v>6591</v>
@@ -19451,7 +19451,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G658" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H658" t="n">
         <v>46138</v>
@@ -19509,7 +19509,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G660" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H660" t="n">
         <v>2028</v>
@@ -19567,7 +19567,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G662" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H662" t="n">
         <v>2535</v>
@@ -19596,7 +19596,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G663" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H663" t="n">
         <v>0</v>
@@ -19625,7 +19625,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G664" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H664" t="n">
         <v>0</v>
@@ -19654,7 +19654,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G665" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H665" t="n">
         <v>0</v>
@@ -19741,7 +19741,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G668" t="n">
-        <v>1.40431368350983</v>
+        <v>1.40431356430054</v>
       </c>
       <c r="H668" t="n">
         <v>17238</v>
@@ -19770,7 +19770,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G669" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H669" t="n">
         <v>30421</v>
@@ -19799,7 +19799,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G670" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H670" t="n">
         <v>3042</v>
@@ -19828,7 +19828,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G671" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H671" t="n">
         <v>9126</v>
@@ -19886,7 +19886,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G673" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H673" t="n">
         <v>4563</v>
@@ -19973,7 +19973,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G676" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H676" t="n">
         <v>20280</v>
@@ -20060,7 +20060,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G679" t="n">
-        <v>1.40901052951813</v>
+        <v>1.40901041030884</v>
       </c>
       <c r="H679" t="n">
         <v>5070</v>
@@ -20089,7 +20089,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G680" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H680" t="n">
         <v>4056</v>
@@ -20234,7 +20234,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G685" t="n">
-        <v>1.29629004001617</v>
+        <v>1.29629015922546</v>
       </c>
       <c r="H685" t="n">
         <v>5070</v>
@@ -20263,7 +20263,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G686" t="n">
-        <v>1.29629004001617</v>
+        <v>1.29629015922546</v>
       </c>
       <c r="H686" t="n">
         <v>507</v>
@@ -20408,7 +20408,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G691" t="n">
-        <v>1.3338634967804</v>
+        <v>1.33386361598969</v>
       </c>
       <c r="H691" t="n">
         <v>9633</v>
@@ -20495,7 +20495,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G694" t="n">
-        <v>1.3338634967804</v>
+        <v>1.33386361598969</v>
       </c>
       <c r="H694" t="n">
         <v>10140</v>
@@ -20553,7 +20553,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G696" t="n">
-        <v>1.39022374153137</v>
+        <v>1.39022362232208</v>
       </c>
       <c r="H696" t="n">
         <v>44110</v>
@@ -20669,7 +20669,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G700" t="n">
-        <v>1.30568301677704</v>
+        <v>1.30568289756775</v>
       </c>
       <c r="H700" t="n">
         <v>67433</v>
@@ -20698,7 +20698,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G701" t="n">
-        <v>1.23523306846619</v>
+        <v>1.2352329492569</v>
       </c>
       <c r="H701" t="n">
         <v>81123</v>
@@ -20727,7 +20727,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G702" t="n">
-        <v>1.23523306846619</v>
+        <v>1.2352329492569</v>
       </c>
       <c r="H702" t="n">
         <v>14703</v>
@@ -20872,7 +20872,7 @@
         <v>1.2179000377655</v>
       </c>
       <c r="G707" t="n">
-        <v>1.16008508205414</v>
+        <v>1.16008520126343</v>
       </c>
       <c r="H707" t="n">
         <v>17745</v>
@@ -21017,7 +21017,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G712" t="n">
-        <v>1.08963513374329</v>
+        <v>1.089635014534</v>
       </c>
       <c r="H712" t="n">
         <v>20787</v>
@@ -21075,7 +21075,7 @@
         <v>1.17845404148102</v>
       </c>
       <c r="G714" t="n">
-        <v>1.12251162528992</v>
+        <v>1.12251174449921</v>
       </c>
       <c r="H714" t="n">
         <v>32956</v>
@@ -21133,7 +21133,7 @@
         <v>1.12914597988129</v>
       </c>
       <c r="G716" t="n">
-        <v>1.07554423809052</v>
+        <v>1.0755443572998</v>
       </c>
       <c r="H716" t="n">
         <v>28393</v>
@@ -21220,7 +21220,7 @@
         <v>1.01573896408081</v>
       </c>
       <c r="G719" t="n">
-        <v>0.967520833015442</v>
+        <v>0.967520892620087</v>
       </c>
       <c r="H719" t="n">
         <v>25858</v>
@@ -21336,7 +21336,7 @@
         <v>1.11435401439667</v>
       </c>
       <c r="G723" t="n">
-        <v>1.06145465373993</v>
+        <v>1.06145453453064</v>
       </c>
       <c r="H723" t="n">
         <v>4563</v>
@@ -21365,7 +21365,7 @@
         <v>1.10449194908142</v>
       </c>
       <c r="G724" t="n">
-        <v>1.05206060409546</v>
+        <v>1.05206072330475</v>
       </c>
       <c r="H724" t="n">
         <v>3042</v>
@@ -21800,7 +21800,7 @@
         <v>0.938817977905273</v>
       </c>
       <c r="G739" t="n">
-        <v>0.89425140619278</v>
+        <v>0.894251346588135</v>
       </c>
       <c r="H739" t="n">
         <v>507</v>
@@ -21829,7 +21829,7 @@
         <v>0.938817977905273</v>
       </c>
       <c r="G740" t="n">
-        <v>0.89425140619278</v>
+        <v>0.894251346588135</v>
       </c>
       <c r="H740" t="n">
         <v>1521</v>
@@ -21887,7 +21887,7 @@
         <v>0.926985025405884</v>
       </c>
       <c r="G742" t="n">
-        <v>0.882980108261108</v>
+        <v>0.882980167865753</v>
       </c>
       <c r="H742" t="n">
         <v>11661</v>
@@ -21916,7 +21916,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G743" t="n">
-        <v>0.911159753799438</v>
+        <v>0.911159813404083</v>
       </c>
       <c r="H743" t="n">
         <v>9126</v>
@@ -21945,7 +21945,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G744" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H744" t="n">
         <v>12168</v>
@@ -22061,7 +22061,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G748" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H748" t="n">
         <v>1521</v>
@@ -22206,7 +22206,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G753" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H753" t="n">
         <v>6591</v>
@@ -22264,7 +22264,7 @@
         <v>0.926985025405884</v>
       </c>
       <c r="G755" t="n">
-        <v>0.882980108261108</v>
+        <v>0.882980167865753</v>
       </c>
       <c r="H755" t="n">
         <v>8112</v>
@@ -22322,7 +22322,7 @@
         <v>0.867815017700195</v>
       </c>
       <c r="G757" t="n">
-        <v>0.82661896944046</v>
+        <v>0.826619029045105</v>
       </c>
       <c r="H757" t="n">
         <v>3042</v>
@@ -22351,7 +22351,7 @@
         <v>0.887538015842438</v>
       </c>
       <c r="G758" t="n">
-        <v>0.845405697822571</v>
+        <v>0.845405757427216</v>
       </c>
       <c r="H758" t="n">
         <v>11154</v>
@@ -22380,7 +22380,7 @@
         <v>0.879648983478546</v>
       </c>
       <c r="G759" t="n">
-        <v>0.837891161441803</v>
+        <v>0.837891221046448</v>
       </c>
       <c r="H759" t="n">
         <v>10140</v>
@@ -22409,7 +22409,7 @@
         <v>0.887538015842438</v>
       </c>
       <c r="G760" t="n">
-        <v>0.845405697822571</v>
+        <v>0.845405757427216</v>
       </c>
       <c r="H760" t="n">
         <v>1521</v>
@@ -22699,7 +22699,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G770" t="n">
-        <v>0.911159753799438</v>
+        <v>0.911159813404083</v>
       </c>
       <c r="H770" t="n">
         <v>2028</v>
@@ -22844,7 +22844,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G775" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H775" t="n">
         <v>6591</v>
@@ -22902,7 +22902,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G777" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H777" t="n">
         <v>19266</v>
@@ -22931,7 +22931,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G778" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H778" t="n">
         <v>10140</v>
@@ -22960,7 +22960,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G779" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H779" t="n">
         <v>0</v>
@@ -22989,7 +22989,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G780" t="n">
-        <v>0.911159753799438</v>
+        <v>0.911159813404083</v>
       </c>
       <c r="H780" t="n">
         <v>1521</v>
@@ -23018,7 +23018,7 @@
         <v>0.942762970924377</v>
       </c>
       <c r="G781" t="n">
-        <v>0.898009061813354</v>
+        <v>0.898009121417999</v>
       </c>
       <c r="H781" t="n">
         <v>7098</v>
@@ -23192,7 +23192,7 @@
         <v>0.938817977905273</v>
       </c>
       <c r="G787" t="n">
-        <v>0.89425140619278</v>
+        <v>0.894251346588135</v>
       </c>
       <c r="H787" t="n">
         <v>1014</v>
@@ -23250,7 +23250,7 @@
         <v>1.01573896408081</v>
       </c>
       <c r="G789" t="n">
-        <v>0.967520833015442</v>
+        <v>0.967520892620087</v>
       </c>
       <c r="H789" t="n">
         <v>1521</v>
@@ -23279,7 +23279,7 @@
         <v>0.962486028671265</v>
       </c>
       <c r="G790" t="n">
-        <v>0.916795909404755</v>
+        <v>0.91679584980011</v>
       </c>
       <c r="H790" t="n">
         <v>32449</v>
@@ -23308,7 +23308,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G791" t="n">
-        <v>0.911159753799438</v>
+        <v>0.911159813404083</v>
       </c>
       <c r="H791" t="n">
         <v>16224</v>
@@ -23685,7 +23685,7 @@
         <v>1.09956204891205</v>
       </c>
       <c r="G804" t="n">
-        <v>1.04736483097076</v>
+        <v>1.04736471176147</v>
       </c>
       <c r="H804" t="n">
         <v>18252</v>
@@ -24236,7 +24236,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G823" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H823" t="n">
         <v>23322</v>
@@ -24265,7 +24265,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G824" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -24323,7 +24323,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G826" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H826" t="n">
         <v>3549</v>
@@ -24381,7 +24381,7 @@
         <v>0.972347974777222</v>
       </c>
       <c r="G828" t="n">
-        <v>0.926189661026001</v>
+        <v>0.926189720630646</v>
       </c>
       <c r="H828" t="n">
         <v>25858</v>
@@ -24410,7 +24410,7 @@
         <v>0.978264987468719</v>
       </c>
       <c r="G829" t="n">
-        <v>0.931825816631317</v>
+        <v>0.931825757026672</v>
       </c>
       <c r="H829" t="n">
         <v>10647</v>
@@ -24613,7 +24613,7 @@
         <v>1.04039204120636</v>
       </c>
       <c r="G836" t="n">
-        <v>0.991003572940826</v>
+        <v>0.991003632545471</v>
       </c>
       <c r="H836" t="n">
         <v>55772</v>
@@ -24700,7 +24700,7 @@
         <v>1.01573896408081</v>
       </c>
       <c r="G839" t="n">
-        <v>0.967520833015442</v>
+        <v>0.967520892620087</v>
       </c>
       <c r="H839" t="n">
         <v>14703</v>
@@ -24729,7 +24729,7 @@
         <v>0.99108499288559</v>
       </c>
       <c r="G840" t="n">
-        <v>0.944037199020386</v>
+        <v>0.944037258625031</v>
       </c>
       <c r="H840" t="n">
         <v>19773</v>
@@ -24787,7 +24787,7 @@
         <v>0.982209026813507</v>
       </c>
       <c r="G842" t="n">
-        <v>0.935582637786865</v>
+        <v>0.93558257818222</v>
       </c>
       <c r="H842" t="n">
         <v>6591</v>
@@ -24816,7 +24816,7 @@
         <v>0.982209026813507</v>
       </c>
       <c r="G843" t="n">
-        <v>0.935582637786865</v>
+        <v>0.93558257818222</v>
       </c>
       <c r="H843" t="n">
         <v>0</v>
@@ -24874,7 +24874,7 @@
         <v>0.99108499288559</v>
       </c>
       <c r="G845" t="n">
-        <v>0.944037199020386</v>
+        <v>0.944037258625031</v>
       </c>
       <c r="H845" t="n">
         <v>12168</v>
@@ -25106,7 +25106,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G853" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H853" t="n">
         <v>18759</v>
@@ -25164,7 +25164,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G855" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H855" t="n">
         <v>3549</v>
@@ -25193,7 +25193,7 @@
         <v>0.982209026813507</v>
       </c>
       <c r="G856" t="n">
-        <v>0.935582637786865</v>
+        <v>0.93558257818222</v>
       </c>
       <c r="H856" t="n">
         <v>5070</v>
@@ -25222,7 +25222,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G857" t="n">
-        <v>0.937461972236633</v>
+        <v>0.937461912631989</v>
       </c>
       <c r="H857" t="n">
         <v>12675</v>
@@ -25396,7 +25396,7 @@
         <v>0.978264987468719</v>
       </c>
       <c r="G863" t="n">
-        <v>0.931825816631317</v>
+        <v>0.931825757026672</v>
       </c>
       <c r="H863" t="n">
         <v>17745</v>
@@ -25425,7 +25425,7 @@
         <v>0.978264987468719</v>
       </c>
       <c r="G864" t="n">
-        <v>0.931825816631317</v>
+        <v>0.931825757026672</v>
       </c>
       <c r="H864" t="n">
         <v>0</v>
@@ -25512,7 +25512,7 @@
         <v>0.950652003288269</v>
       </c>
       <c r="G867" t="n">
-        <v>0.905523598194122</v>
+        <v>0.905523657798767</v>
       </c>
       <c r="H867" t="n">
         <v>9126</v>
@@ -25686,7 +25686,7 @@
         <v>0.90923398733139</v>
       </c>
       <c r="G873" t="n">
-        <v>0.866071820259094</v>
+        <v>0.866071760654449</v>
       </c>
       <c r="H873" t="n">
         <v>7098</v>
@@ -25715,7 +25715,7 @@
         <v>0.915151000022888</v>
       </c>
       <c r="G874" t="n">
-        <v>0.871707916259766</v>
+        <v>0.871707856655121</v>
       </c>
       <c r="H874" t="n">
         <v>7098</v>
@@ -25831,7 +25831,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G878" t="n">
-        <v>0.674445748329163</v>
+        <v>0.674445807933807</v>
       </c>
       <c r="H878" t="n">
         <v>31435</v>
@@ -25860,7 +25860,7 @@
         <v>0.769200026988983</v>
       </c>
       <c r="G879" t="n">
-        <v>0.732685327529907</v>
+        <v>0.732685387134552</v>
       </c>
       <c r="H879" t="n">
         <v>49687</v>
@@ -25889,7 +25889,7 @@
         <v>0.769200026988983</v>
       </c>
       <c r="G880" t="n">
-        <v>0.732685327529907</v>
+        <v>0.732685387134552</v>
       </c>
       <c r="H880" t="n">
         <v>21801</v>
@@ -26005,7 +26005,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G884" t="n">
-        <v>0.674445748329163</v>
+        <v>0.674445807933807</v>
       </c>
       <c r="H884" t="n">
         <v>10647</v>
@@ -26063,7 +26063,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G886" t="n">
-        <v>0.674445748329163</v>
+        <v>0.674445807933807</v>
       </c>
       <c r="H886" t="n">
         <v>7605</v>
@@ -26121,7 +26121,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G888" t="n">
-        <v>0.723291516304016</v>
+        <v>0.723291456699371</v>
       </c>
       <c r="H888" t="n">
         <v>12168</v>
@@ -26150,7 +26150,7 @@
         <v>0.745531976222992</v>
       </c>
       <c r="G889" t="n">
-        <v>0.710140883922577</v>
+        <v>0.710140824317932</v>
       </c>
       <c r="H889" t="n">
         <v>10647</v>
@@ -26179,7 +26179,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G890" t="n">
-        <v>0.723291516304016</v>
+        <v>0.723291456699371</v>
       </c>
       <c r="H890" t="n">
         <v>1521</v>
@@ -26208,7 +26208,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G891" t="n">
-        <v>0.723291516304016</v>
+        <v>0.723291456699371</v>
       </c>
       <c r="H891" t="n">
         <v>0</v>
@@ -26266,7 +26266,7 @@
         <v>0.77708899974823</v>
       </c>
       <c r="G893" t="n">
-        <v>0.74019980430603</v>
+        <v>0.740199863910675</v>
       </c>
       <c r="H893" t="n">
         <v>29914</v>
@@ -26353,7 +26353,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G896" t="n">
-        <v>0.723291516304016</v>
+        <v>0.723291456699371</v>
       </c>
       <c r="H896" t="n">
         <v>30928</v>
@@ -26411,7 +26411,7 @@
         <v>0.729753971099854</v>
       </c>
       <c r="G898" t="n">
-        <v>0.695111870765686</v>
+        <v>0.695111811161041</v>
       </c>
       <c r="H898" t="n">
         <v>15210</v>
@@ -26440,7 +26440,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G899" t="n">
-        <v>0.702626407146454</v>
+        <v>0.702626347541809</v>
       </c>
       <c r="H899" t="n">
         <v>52223</v>
@@ -26585,7 +26585,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G904" t="n">
-        <v>0.548574864864349</v>
+        <v>0.548574805259705</v>
       </c>
       <c r="H904" t="n">
         <v>50702</v>
@@ -26672,7 +26672,7 @@
         <v>0.508854985237122</v>
       </c>
       <c r="G907" t="n">
-        <v>0.484699159860611</v>
+        <v>0.484699130058289</v>
       </c>
       <c r="H907" t="n">
         <v>76053</v>
@@ -26817,7 +26817,7 @@
         <v>0.492091000080109</v>
       </c>
       <c r="G912" t="n">
-        <v>0.468730986118317</v>
+        <v>0.468730956315994</v>
       </c>
       <c r="H912" t="n">
         <v>19773</v>
@@ -26846,7 +26846,7 @@
         <v>0.492091000080109</v>
       </c>
       <c r="G913" t="n">
-        <v>0.468730986118317</v>
+        <v>0.468730956315994</v>
       </c>
       <c r="H913" t="n">
         <v>507</v>
@@ -26991,7 +26991,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G918" t="n">
-        <v>0.432096719741821</v>
+        <v>0.432096689939499</v>
       </c>
       <c r="H918" t="n">
         <v>18759</v>
@@ -27049,7 +27049,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G920" t="n">
-        <v>0.418945133686066</v>
+        <v>0.418945103883743</v>
       </c>
       <c r="H920" t="n">
         <v>7098</v>
@@ -27107,7 +27107,7 @@
         <v>0.481243014335632</v>
       </c>
       <c r="G922" t="n">
-        <v>0.458397954702377</v>
+        <v>0.458397924900055</v>
       </c>
       <c r="H922" t="n">
         <v>51209</v>
@@ -27194,7 +27194,7 @@
         <v>0.44574099779129</v>
       </c>
       <c r="G925" t="n">
-        <v>0.424581229686737</v>
+        <v>0.424581259489059</v>
       </c>
       <c r="H925" t="n">
         <v>198751</v>
@@ -27252,7 +27252,7 @@
         <v>0.449685990810394</v>
       </c>
       <c r="G927" t="n">
-        <v>0.428338974714279</v>
+        <v>0.428338944911957</v>
       </c>
       <c r="H927" t="n">
         <v>507</v>
@@ -27339,7 +27339,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G930" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H930" t="n">
         <v>36505</v>
@@ -27368,7 +27368,7 @@
         <v>0.469408988952637</v>
       </c>
       <c r="G931" t="n">
-        <v>0.44712570309639</v>
+        <v>0.447125673294067</v>
       </c>
       <c r="H931" t="n">
         <v>24843</v>
@@ -27571,7 +27571,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G938" t="n">
-        <v>0.494093030691147</v>
+        <v>0.494093000888824</v>
       </c>
       <c r="H938" t="n">
         <v>40561</v>
@@ -27600,7 +27600,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G939" t="n">
-        <v>0.494093030691147</v>
+        <v>0.494093000888824</v>
       </c>
       <c r="H939" t="n">
         <v>19773</v>
@@ -27629,7 +27629,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G940" t="n">
-        <v>0.494093030691147</v>
+        <v>0.494093000888824</v>
       </c>
       <c r="H940" t="n">
         <v>20787</v>
@@ -27716,7 +27716,7 @@
         <v>0.506883025169373</v>
       </c>
       <c r="G943" t="n">
-        <v>0.482820779085159</v>
+        <v>0.482820808887482</v>
       </c>
       <c r="H943" t="n">
         <v>100389</v>
@@ -27861,7 +27861,7 @@
         <v>0.489131987094879</v>
       </c>
       <c r="G948" t="n">
-        <v>0.465912401676178</v>
+        <v>0.4659124314785</v>
       </c>
       <c r="H948" t="n">
         <v>3549</v>
@@ -28035,7 +28035,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G954" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H954" t="n">
         <v>103939</v>
@@ -28064,7 +28064,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G955" t="n">
-        <v>0.419885277748108</v>
+        <v>0.41988530755043</v>
       </c>
       <c r="H955" t="n">
         <v>17238</v>
@@ -28238,7 +28238,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G961" t="n">
-        <v>0.437731862068176</v>
+        <v>0.437731891870499</v>
       </c>
       <c r="H961" t="n">
         <v>415756</v>
@@ -28296,7 +28296,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G963" t="n">
-        <v>0.462154716253281</v>
+        <v>0.462154686450958</v>
       </c>
       <c r="H963" t="n">
         <v>130811</v>
@@ -28731,7 +28731,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G978" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H978" t="n">
         <v>47659</v>
@@ -28818,7 +28818,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G981" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H981" t="n">
         <v>45631</v>
@@ -28876,7 +28876,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G983" t="n">
-        <v>0.432096719741821</v>
+        <v>0.432096689939499</v>
       </c>
       <c r="H983" t="n">
         <v>39547</v>
@@ -28992,7 +28992,7 @@
         <v>0.469408988952637</v>
       </c>
       <c r="G987" t="n">
-        <v>0.44712570309639</v>
+        <v>0.447125673294067</v>
       </c>
       <c r="H987" t="n">
         <v>6084</v>
@@ -29079,7 +29079,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G990" t="n">
-        <v>0.432096719741821</v>
+        <v>0.432096689939499</v>
       </c>
       <c r="H990" t="n">
         <v>19266</v>
@@ -29108,7 +29108,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G991" t="n">
-        <v>0.432096719741821</v>
+        <v>0.432096689939499</v>
       </c>
       <c r="H991" t="n">
         <v>19266</v>
@@ -29137,7 +29137,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G992" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H992" t="n">
         <v>9633</v>
@@ -29166,7 +29166,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G993" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H993" t="n">
         <v>104446</v>
@@ -29195,7 +29195,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G994" t="n">
-        <v>0.419885277748108</v>
+        <v>0.41988530755043</v>
       </c>
       <c r="H994" t="n">
         <v>175935</v>
@@ -29224,7 +29224,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G995" t="n">
-        <v>0.418945133686066</v>
+        <v>0.418945103883743</v>
       </c>
       <c r="H995" t="n">
         <v>67940</v>
@@ -29253,7 +29253,7 @@
         <v>0.449685990810394</v>
       </c>
       <c r="G996" t="n">
-        <v>0.428338974714279</v>
+        <v>0.428338944911957</v>
       </c>
       <c r="H996" t="n">
         <v>116107</v>
@@ -29282,7 +29282,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G997" t="n">
-        <v>0.422702848911285</v>
+        <v>0.422702878713608</v>
       </c>
       <c r="H997" t="n">
         <v>52730</v>
@@ -29398,7 +29398,7 @@
         <v>0.55224597454071</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.526030302047729</v>
+        <v>0.526030361652374</v>
       </c>
       <c r="H1001" t="n">
         <v>693096</v>
@@ -29543,7 +29543,7 @@
         <v>0.603525996208191</v>
       </c>
       <c r="G1006" t="n">
-        <v>0.574876070022583</v>
+        <v>0.574876010417938</v>
       </c>
       <c r="H1006" t="n">
         <v>259594</v>
@@ -29601,7 +29601,7 @@
         <v>0.694252014160156</v>
       </c>
       <c r="G1008" t="n">
-        <v>0.661295235157013</v>
+        <v>0.661295175552368</v>
       </c>
       <c r="H1008" t="n">
         <v>497893</v>
@@ -29717,7 +29717,7 @@
         <v>0.639028012752533</v>
       </c>
       <c r="G1012" t="n">
-        <v>0.608692765235901</v>
+        <v>0.608692705631256</v>
       </c>
       <c r="H1012" t="n">
         <v>271255</v>
@@ -29775,7 +29775,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.634993970394135</v>
+        <v>0.63499391078949</v>
       </c>
       <c r="H1014" t="n">
         <v>67433</v>
@@ -29862,7 +29862,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1017" t="n">
-        <v>0.604934990406036</v>
+        <v>0.604935050010681</v>
       </c>
       <c r="H1017" t="n">
         <v>279875</v>
@@ -29949,7 +29949,7 @@
         <v>0.611415028572083</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.582390606403351</v>
+        <v>0.582390546798706</v>
       </c>
       <c r="H1020" t="n">
         <v>99882</v>
@@ -30094,7 +30094,7 @@
         <v>0.765254974365234</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.728927612304688</v>
+        <v>0.728927552700043</v>
       </c>
       <c r="H1025" t="n">
         <v>870046</v>
@@ -30268,7 +30268,7 @@
         <v>0.706085979938507</v>
       </c>
       <c r="G1031" t="n">
-        <v>0.672567367553711</v>
+        <v>0.672567427158356</v>
       </c>
       <c r="H1031" t="n">
         <v>155148</v>
@@ -30471,7 +30471,7 @@
         <v>0.668612003326416</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.636872351169586</v>
+        <v>0.636872291564941</v>
       </c>
       <c r="H1038" t="n">
         <v>98361</v>
@@ -30616,7 +30616,7 @@
         <v>0.69819700717926</v>
       </c>
       <c r="G1043" t="n">
-        <v>0.665052890777588</v>
+        <v>0.665052950382233</v>
       </c>
       <c r="H1043" t="n">
         <v>186583</v>
@@ -30906,7 +30906,7 @@
         <v>0.550274014472961</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.524151980876923</v>
+        <v>0.524151921272278</v>
       </c>
       <c r="H1053" t="n">
         <v>205850</v>
@@ -30935,7 +30935,7 @@
         <v>0.571968972682953</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.54481703042984</v>
+        <v>0.544817090034485</v>
       </c>
       <c r="H1054" t="n">
         <v>95826</v>
@@ -30964,7 +30964,7 @@
         <v>0.55224597454071</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.526030302047729</v>
+        <v>0.526030361652374</v>
       </c>
       <c r="H1055" t="n">
         <v>104953</v>
@@ -31051,7 +31051,7 @@
         <v>0.520689010620117</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.495971411466599</v>
+        <v>0.495971381664276</v>
       </c>
       <c r="H1058" t="n">
         <v>18759</v>
@@ -31225,7 +31225,7 @@
         <v>0.36191800236702</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.344737380743027</v>
+        <v>0.344737410545349</v>
       </c>
       <c r="H1064" t="n">
         <v>127769</v>
@@ -31312,7 +31312,7 @@
         <v>0.318527013063431</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.303406238555908</v>
+        <v>0.303406208753586</v>
       </c>
       <c r="H1067" t="n">
         <v>33463</v>
@@ -31370,7 +31370,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.309981554746628</v>
+        <v>0.309981524944305</v>
       </c>
       <c r="H1069" t="n">
         <v>42082</v>
@@ -31399,7 +31399,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1070" t="n">
         <v>74531</v>
@@ -31515,7 +31515,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.345676630735397</v>
+        <v>0.345676600933075</v>
       </c>
       <c r="H1074" t="n">
         <v>38026</v>
@@ -31718,7 +31718,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.394522279500961</v>
+        <v>0.394522309303284</v>
       </c>
       <c r="H1081" t="n">
         <v>79095</v>
@@ -31776,7 +31776,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.387946963310242</v>
+        <v>0.387946993112564</v>
       </c>
       <c r="H1083" t="n">
         <v>106474</v>
@@ -31863,7 +31863,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.387946963310242</v>
+        <v>0.387946993112564</v>
       </c>
       <c r="H1086" t="n">
         <v>16224</v>
@@ -31892,7 +31892,7 @@
         <v>0.400377988815308</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.381371647119522</v>
+        <v>0.381371676921844</v>
       </c>
       <c r="H1087" t="n">
         <v>33463</v>
@@ -31921,7 +31921,7 @@
         <v>0.384600013494492</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.366342663764954</v>
+        <v>0.366342693567276</v>
       </c>
       <c r="H1088" t="n">
         <v>21294</v>
@@ -32066,7 +32066,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1093" t="n">
         <v>9633</v>
@@ -32124,7 +32124,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1095" t="n">
         <v>16224</v>
@@ -32211,7 +32211,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1098" t="n">
         <v>44617</v>
@@ -32269,7 +32269,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.336283683776855</v>
+        <v>0.336283713579178</v>
       </c>
       <c r="H1100" t="n">
         <v>250974</v>
@@ -32298,7 +32298,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.337222874164581</v>
+        <v>0.337222903966904</v>
       </c>
       <c r="H1101" t="n">
         <v>48673</v>
@@ -32356,7 +32356,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1103" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1103" t="n">
         <v>9126</v>
@@ -32385,7 +32385,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1104" t="n">
         <v>12168</v>
@@ -32443,7 +32443,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1106" t="n">
-        <v>0.337222874164581</v>
+        <v>0.337222903966904</v>
       </c>
       <c r="H1106" t="n">
         <v>25351</v>
@@ -32472,7 +32472,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1107" t="n">
         <v>7605</v>
@@ -32530,7 +32530,7 @@
         <v>0.369807004928589</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.352251887321472</v>
+        <v>0.352251917123795</v>
       </c>
       <c r="H1109" t="n">
         <v>23829</v>
@@ -32559,7 +32559,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.432096719741821</v>
+        <v>0.432096689939499</v>
       </c>
       <c r="H1110" t="n">
         <v>456825</v>
@@ -32617,7 +32617,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.39264389872551</v>
+        <v>0.392643928527832</v>
       </c>
       <c r="H1112" t="n">
         <v>188104</v>
@@ -32646,7 +32646,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.394522279500961</v>
+        <v>0.394522309303284</v>
       </c>
       <c r="H1113" t="n">
         <v>101911</v>
@@ -32704,7 +32704,7 @@
         <v>0.398405998945236</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.37949326634407</v>
+        <v>0.379493296146393</v>
       </c>
       <c r="H1115" t="n">
         <v>63377</v>
@@ -32849,7 +32849,7 @@
         <v>0.475326001644135</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.452761799097061</v>
+        <v>0.452761828899384</v>
       </c>
       <c r="H1120" t="n">
         <v>63884</v>
@@ -33110,7 +33110,7 @@
         <v>0.484201014041901</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.461215496063232</v>
+        <v>0.461215525865555</v>
       </c>
       <c r="H1129" t="n">
         <v>51209</v>
@@ -33284,7 +33284,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G1135" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H1135" t="n">
         <v>11154</v>
@@ -33342,7 +33342,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G1137" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H1137" t="n">
         <v>3549</v>
@@ -33371,7 +33371,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.462154716253281</v>
+        <v>0.462154686450958</v>
       </c>
       <c r="H1138" t="n">
         <v>16224</v>
@@ -33400,7 +33400,7 @@
         <v>0.475326001644135</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.452761799097061</v>
+        <v>0.452761828899384</v>
       </c>
       <c r="H1139" t="n">
         <v>8619</v>
@@ -33458,7 +33458,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1141" t="n">
-        <v>0.437731862068176</v>
+        <v>0.437731891870499</v>
       </c>
       <c r="H1141" t="n">
         <v>9126</v>
@@ -33516,7 +33516,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1143" t="n">
-        <v>0.548574864864349</v>
+        <v>0.548574805259705</v>
       </c>
       <c r="H1143" t="n">
         <v>882214</v>
@@ -33545,7 +33545,7 @@
         <v>0.524634003639221</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.499729096889496</v>
+        <v>0.499729126691818</v>
       </c>
       <c r="H1144" t="n">
         <v>914157</v>
@@ -33748,7 +33748,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.462154716253281</v>
+        <v>0.462154686450958</v>
       </c>
       <c r="H1151" t="n">
         <v>49687</v>
@@ -33806,7 +33806,7 @@
         <v>0.489131987094879</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.465912401676178</v>
+        <v>0.4659124314785</v>
       </c>
       <c r="H1153" t="n">
         <v>48673</v>
@@ -33980,7 +33980,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.437731862068176</v>
+        <v>0.437731891870499</v>
       </c>
       <c r="H1159" t="n">
         <v>34984</v>
@@ -34009,7 +34009,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.422702848911285</v>
+        <v>0.422702878713608</v>
       </c>
       <c r="H1160" t="n">
         <v>45124</v>
@@ -34096,7 +34096,7 @@
         <v>0.449685990810394</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.428338974714279</v>
+        <v>0.428338944911957</v>
       </c>
       <c r="H1163" t="n">
         <v>51716</v>
@@ -34241,7 +34241,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.387946963310242</v>
+        <v>0.387946993112564</v>
       </c>
       <c r="H1168" t="n">
         <v>12168</v>
@@ -34357,7 +34357,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.419885277748108</v>
+        <v>0.41988530755043</v>
       </c>
       <c r="H1172" t="n">
         <v>116107</v>
@@ -34386,7 +34386,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.422702848911285</v>
+        <v>0.422702878713608</v>
       </c>
       <c r="H1173" t="n">
         <v>52730</v>
@@ -34415,7 +34415,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.422702848911285</v>
+        <v>0.422702878713608</v>
       </c>
       <c r="H1174" t="n">
         <v>0</v>
@@ -34473,7 +34473,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.418945133686066</v>
+        <v>0.418945103883743</v>
       </c>
       <c r="H1176" t="n">
         <v>15717</v>
@@ -34502,7 +34502,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.418945133686066</v>
+        <v>0.418945103883743</v>
       </c>
       <c r="H1177" t="n">
         <v>8619</v>
@@ -34531,7 +34531,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.418945133686066</v>
+        <v>0.418945103883743</v>
       </c>
       <c r="H1178" t="n">
         <v>1014</v>
@@ -34676,7 +34676,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1183" t="n">
         <v>10140</v>
@@ -35024,7 +35024,7 @@
         <v>0.429962992668152</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.409552216529846</v>
+        <v>0.409552246332169</v>
       </c>
       <c r="H1195" t="n">
         <v>142472</v>
@@ -35053,7 +35053,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1196" t="n">
         <v>87207</v>
@@ -35256,7 +35256,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1203" t="n">
         <v>65405</v>
@@ -35314,7 +35314,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1205" t="n">
         <v>3042</v>
@@ -35401,7 +35401,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1208" t="n">
         <v>241341</v>
@@ -35430,7 +35430,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.39264389872551</v>
+        <v>0.392643928527832</v>
       </c>
       <c r="H1209" t="n">
         <v>62363</v>
@@ -35575,7 +35575,7 @@
         <v>0.429962992668152</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.409552216529846</v>
+        <v>0.409552246332169</v>
       </c>
       <c r="H1214" t="n">
         <v>40561</v>
@@ -35836,7 +35836,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1223" t="n">
         <v>77067</v>
@@ -35923,7 +35923,7 @@
         <v>0.402350008487701</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.383250087499619</v>
+        <v>0.383250057697296</v>
       </c>
       <c r="H1226" t="n">
         <v>10647</v>
@@ -36097,7 +36097,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.39264389872551</v>
+        <v>0.392643928527832</v>
       </c>
       <c r="H1232" t="n">
         <v>11154</v>
@@ -36184,7 +36184,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1235" t="n">
         <v>115093</v>
@@ -36213,7 +36213,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.394522279500961</v>
+        <v>0.394522309303284</v>
       </c>
       <c r="H1236" t="n">
         <v>85179</v>
@@ -36300,7 +36300,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.394522279500961</v>
+        <v>0.394522309303284</v>
       </c>
       <c r="H1239" t="n">
         <v>109516</v>
@@ -36329,7 +36329,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1240" t="n">
         <v>40561</v>
@@ -36358,7 +36358,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1241" t="n">
         <v>76053</v>
@@ -36416,7 +36416,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.422702848911285</v>
+        <v>0.422702878713608</v>
       </c>
       <c r="H1243" t="n">
         <v>481161</v>
@@ -36561,7 +36561,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.441489607095718</v>
+        <v>0.441489577293396</v>
       </c>
       <c r="H1248" t="n">
         <v>119149</v>
@@ -36648,7 +36648,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.494093030691147</v>
+        <v>0.494093000888824</v>
       </c>
       <c r="H1251" t="n">
         <v>617043</v>
@@ -36822,7 +36822,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.462154716253281</v>
+        <v>0.462154686450958</v>
       </c>
       <c r="H1257" t="n">
         <v>29407</v>
@@ -37054,7 +37054,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.437731862068176</v>
+        <v>0.437731891870499</v>
       </c>
       <c r="H1265" t="n">
         <v>59321</v>
@@ -37170,7 +37170,7 @@
         <v>0.44574099779129</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.424581229686737</v>
+        <v>0.424581259489059</v>
       </c>
       <c r="H1269" t="n">
         <v>12168</v>
@@ -37315,7 +37315,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.437731862068176</v>
+        <v>0.437731891870499</v>
       </c>
       <c r="H1274" t="n">
         <v>93798</v>
@@ -37431,7 +37431,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.422702848911285</v>
+        <v>0.422702878713608</v>
       </c>
       <c r="H1278" t="n">
         <v>9126</v>
@@ -37547,7 +37547,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.419885277748108</v>
+        <v>0.41988530755043</v>
       </c>
       <c r="H1282" t="n">
         <v>6084</v>
@@ -37837,7 +37837,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1292" t="n">
         <v>94305</v>
@@ -37895,7 +37895,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1294" t="n">
         <v>116107</v>
@@ -37924,7 +37924,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1295" t="n">
         <v>29407</v>
@@ -37953,7 +37953,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.394522279500961</v>
+        <v>0.394522309303284</v>
       </c>
       <c r="H1296" t="n">
         <v>84672</v>
@@ -38011,7 +38011,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1298" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1298" t="n">
         <v>76560</v>
@@ -38243,7 +38243,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1306" t="n">
         <v>4056</v>
@@ -38330,7 +38330,7 @@
         <v>0.418128997087479</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.398280024528503</v>
+        <v>0.398279994726181</v>
       </c>
       <c r="H1309" t="n">
         <v>13689</v>
@@ -38359,7 +38359,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1310" t="n">
         <v>1521</v>
@@ -38388,7 +38388,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1311" t="n">
         <v>3042</v>
@@ -38504,7 +38504,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.387946963310242</v>
+        <v>0.387946993112564</v>
       </c>
       <c r="H1315" t="n">
         <v>4563</v>
@@ -38533,7 +38533,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.387946963310242</v>
+        <v>0.387946993112564</v>
       </c>
       <c r="H1316" t="n">
         <v>0</v>
@@ -38591,7 +38591,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1318" t="n">
         <v>115600</v>
@@ -38765,7 +38765,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1324" t="n">
         <v>25858</v>
@@ -38794,7 +38794,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1325" t="n">
-        <v>0.39264389872551</v>
+        <v>0.392643928527832</v>
       </c>
       <c r="H1325" t="n">
         <v>1521</v>
@@ -38968,7 +38968,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1331" t="n">
         <v>29407</v>
@@ -38997,7 +38997,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1332" t="n">
-        <v>0.394522279500961</v>
+        <v>0.394522309303284</v>
       </c>
       <c r="H1332" t="n">
         <v>14703</v>
@@ -39026,7 +39026,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1333" t="n">
         <v>4056</v>
@@ -39113,7 +39113,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1336" t="n">
         <v>39040</v>
@@ -39142,7 +39142,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1337" t="n">
-        <v>0.39264389872551</v>
+        <v>0.392643928527832</v>
       </c>
       <c r="H1337" t="n">
         <v>11154</v>
@@ -39200,7 +39200,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1339" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1339" t="n">
         <v>2028</v>
@@ -39258,7 +39258,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1341" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1341" t="n">
         <v>10647</v>
@@ -39287,7 +39287,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1342" t="n">
         <v>0</v>
@@ -39316,7 +39316,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1343" t="n">
-        <v>0.395461469888687</v>
+        <v>0.39546149969101</v>
       </c>
       <c r="H1343" t="n">
         <v>11154</v>
@@ -39490,7 +39490,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.387946963310242</v>
+        <v>0.387946993112564</v>
       </c>
       <c r="H1349" t="n">
         <v>7098</v>
@@ -39519,7 +39519,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.394522279500961</v>
+        <v>0.394522309303284</v>
       </c>
       <c r="H1350" t="n">
         <v>19266</v>
@@ -39606,7 +39606,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1353" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1353" t="n">
         <v>41575</v>
@@ -39693,7 +39693,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.403916150331497</v>
+        <v>0.403916120529175</v>
       </c>
       <c r="H1356" t="n">
         <v>9633</v>
@@ -39722,7 +39722,7 @@
         <v>0.429962992668152</v>
       </c>
       <c r="G1357" t="n">
-        <v>0.409552216529846</v>
+        <v>0.409552246332169</v>
       </c>
       <c r="H1357" t="n">
         <v>12168</v>
@@ -39896,7 +39896,7 @@
         <v>0.398405998945236</v>
       </c>
       <c r="G1363" t="n">
-        <v>0.37949326634407</v>
+        <v>0.379493296146393</v>
       </c>
       <c r="H1363" t="n">
         <v>57293</v>
@@ -39983,7 +39983,7 @@
         <v>0.398405998945236</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.37949326634407</v>
+        <v>0.379493296146393</v>
       </c>
       <c r="H1366" t="n">
         <v>5577</v>
@@ -40041,7 +40041,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1368" t="n">
-        <v>0.387946963310242</v>
+        <v>0.387946993112564</v>
       </c>
       <c r="H1368" t="n">
         <v>7098</v>
@@ -40070,7 +40070,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1369" t="n">
         <v>49687</v>
@@ -40099,7 +40099,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1370" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1370" t="n">
         <v>171372</v>
@@ -40244,7 +40244,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1375" t="n">
         <v>56786</v>
@@ -40302,7 +40302,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1377" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1377" t="n">
         <v>23829</v>
@@ -40505,7 +40505,7 @@
         <v>0.402350008487701</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.383250087499619</v>
+        <v>0.383250057697296</v>
       </c>
       <c r="H1384" t="n">
         <v>46138</v>
@@ -40534,7 +40534,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1385" t="n">
-        <v>0.375735580921173</v>
+        <v>0.375735551118851</v>
       </c>
       <c r="H1385" t="n">
         <v>136895</v>
@@ -40621,7 +40621,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.364463329315186</v>
+        <v>0.364463359117508</v>
       </c>
       <c r="H1388" t="n">
         <v>115093</v>
@@ -40650,7 +40650,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.360706567764282</v>
+        <v>0.36070653796196</v>
       </c>
       <c r="H1389" t="n">
         <v>14703</v>
@@ -40708,7 +40708,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1391" t="n">
-        <v>0.364463329315186</v>
+        <v>0.364463359117508</v>
       </c>
       <c r="H1391" t="n">
         <v>68954</v>
@@ -40766,7 +40766,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.361645758152008</v>
+        <v>0.361645728349686</v>
       </c>
       <c r="H1393" t="n">
         <v>43096</v>
@@ -40795,7 +40795,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.360706567764282</v>
+        <v>0.36070653796196</v>
       </c>
       <c r="H1394" t="n">
         <v>37012</v>
@@ -40911,7 +40911,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1398" t="n">
-        <v>0.364463329315186</v>
+        <v>0.364463359117508</v>
       </c>
       <c r="H1398" t="n">
         <v>18759</v>
@@ -40940,7 +40940,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.364463329315186</v>
+        <v>0.364463359117508</v>
       </c>
       <c r="H1399" t="n">
         <v>0</v>
@@ -41172,7 +41172,7 @@
         <v>0.368820995092392</v>
       </c>
       <c r="G1407" t="n">
-        <v>0.351312696933746</v>
+        <v>0.351312726736069</v>
       </c>
       <c r="H1407" t="n">
         <v>23829</v>
@@ -41201,7 +41201,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.347555935382843</v>
+        <v>0.347555905580521</v>
       </c>
       <c r="H1408" t="n">
         <v>35998</v>
@@ -41288,7 +41288,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1411" t="n">
         <v>29407</v>
@@ -41375,7 +41375,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1414" t="n">
-        <v>0.337222874164581</v>
+        <v>0.337222903966904</v>
       </c>
       <c r="H1414" t="n">
         <v>21801</v>
@@ -41404,7 +41404,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.337222874164581</v>
+        <v>0.337222903966904</v>
       </c>
       <c r="H1415" t="n">
         <v>24336</v>
@@ -41433,7 +41433,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.337222874164581</v>
+        <v>0.337222903966904</v>
       </c>
       <c r="H1416" t="n">
         <v>0</v>
@@ -41462,7 +41462,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.337222874164581</v>
+        <v>0.337222903966904</v>
       </c>
       <c r="H1417" t="n">
         <v>5577</v>
@@ -41491,7 +41491,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.336283683776855</v>
+        <v>0.336283713579178</v>
       </c>
       <c r="H1418" t="n">
         <v>29407</v>
@@ -41665,7 +41665,7 @@
         <v>0.34909799695015</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.332525998353958</v>
+        <v>0.332525968551636</v>
       </c>
       <c r="H1424" t="n">
         <v>60842</v>
@@ -41752,7 +41752,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.345676630735397</v>
+        <v>0.345676600933075</v>
       </c>
       <c r="H1427" t="n">
         <v>30928</v>
@@ -41781,7 +41781,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.345676630735397</v>
+        <v>0.345676600933075</v>
       </c>
       <c r="H1428" t="n">
         <v>32956</v>
@@ -41810,7 +41810,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.345676630735397</v>
+        <v>0.345676600933075</v>
       </c>
       <c r="H1429" t="n">
         <v>0</v>
@@ -42013,7 +42013,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1436" t="n">
-        <v>0.347555935382843</v>
+        <v>0.347555905580521</v>
       </c>
       <c r="H1436" t="n">
         <v>8112</v>
@@ -42332,7 +42332,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.355070441961288</v>
+        <v>0.355070412158966</v>
       </c>
       <c r="H1447" t="n">
         <v>14196</v>
@@ -42361,7 +42361,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.355070441961288</v>
+        <v>0.355070412158966</v>
       </c>
       <c r="H1448" t="n">
         <v>31942</v>
@@ -42419,7 +42419,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1450" t="n">
-        <v>0.361645758152008</v>
+        <v>0.361645728349686</v>
       </c>
       <c r="H1450" t="n">
         <v>3549</v>
@@ -42448,7 +42448,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.361645758152008</v>
+        <v>0.361645728349686</v>
       </c>
       <c r="H1451" t="n">
         <v>0</v>
@@ -42680,7 +42680,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.364463329315186</v>
+        <v>0.364463359117508</v>
       </c>
       <c r="H1459" t="n">
         <v>120163</v>
@@ -42767,7 +42767,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1462" t="n">
-        <v>0.364463329315186</v>
+        <v>0.364463359117508</v>
       </c>
       <c r="H1462" t="n">
         <v>46645</v>
@@ -42912,7 +42912,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1467" t="n">
-        <v>0.360706567764282</v>
+        <v>0.36070653796196</v>
       </c>
       <c r="H1467" t="n">
         <v>6591</v>
@@ -42941,7 +42941,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.355070441961288</v>
+        <v>0.355070412158966</v>
       </c>
       <c r="H1468" t="n">
         <v>18759</v>
@@ -43028,7 +43028,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.347555935382843</v>
+        <v>0.347555905580521</v>
       </c>
       <c r="H1471" t="n">
         <v>5070</v>
@@ -43231,7 +43231,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1478" t="n">
-        <v>0.360706567764282</v>
+        <v>0.36070653796196</v>
       </c>
       <c r="H1478" t="n">
         <v>1521</v>
@@ -43260,7 +43260,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.361645758152008</v>
+        <v>0.361645728349686</v>
       </c>
       <c r="H1479" t="n">
         <v>5070</v>
@@ -43405,7 +43405,7 @@
         <v>0.384600013494492</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.366342663764954</v>
+        <v>0.366342693567276</v>
       </c>
       <c r="H1484" t="n">
         <v>2535</v>
@@ -43434,7 +43434,7 @@
         <v>0.384600013494492</v>
       </c>
       <c r="G1485" t="n">
-        <v>0.366342663764954</v>
+        <v>0.366342693567276</v>
       </c>
       <c r="H1485" t="n">
         <v>0</v>
@@ -43492,7 +43492,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1487" t="n">
-        <v>0.361645758152008</v>
+        <v>0.361645728349686</v>
       </c>
       <c r="H1487" t="n">
         <v>11661</v>
@@ -43521,7 +43521,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1488" t="n">
-        <v>0.355070441961288</v>
+        <v>0.355070412158966</v>
       </c>
       <c r="H1488" t="n">
         <v>17745</v>
@@ -43550,7 +43550,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1489" t="n">
-        <v>0.355070441961288</v>
+        <v>0.355070412158966</v>
       </c>
       <c r="H1489" t="n">
         <v>0</v>
@@ -43579,7 +43579,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1490" t="n">
-        <v>0.355070441961288</v>
+        <v>0.355070412158966</v>
       </c>
       <c r="H1490" t="n">
         <v>0</v>
@@ -43695,7 +43695,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.345676630735397</v>
+        <v>0.345676600933075</v>
       </c>
       <c r="H1494" t="n">
         <v>40561</v>
@@ -43724,7 +43724,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.345676630735397</v>
+        <v>0.345676600933075</v>
       </c>
       <c r="H1495" t="n">
         <v>31435</v>
@@ -44014,7 +44014,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.321253746747971</v>
+        <v>0.321253776550293</v>
       </c>
       <c r="H1505" t="n">
         <v>17238</v>
@@ -44072,7 +44072,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.336283683776855</v>
+        <v>0.336283713579178</v>
       </c>
       <c r="H1507" t="n">
         <v>8112</v>
@@ -44101,7 +44101,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1508" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1508" t="n">
         <v>9126</v>
@@ -44362,7 +44362,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1517" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1517" t="n">
         <v>41068</v>
@@ -44391,7 +44391,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1518" t="n">
-        <v>0.333465188741684</v>
+        <v>0.333465158939362</v>
       </c>
       <c r="H1518" t="n">
         <v>15717</v>
@@ -44565,7 +44565,7 @@
         <v>0.319514006376266</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.30434638261795</v>
+        <v>0.304346352815628</v>
       </c>
       <c r="H1524" t="n">
         <v>88728</v>
@@ -44594,7 +44594,7 @@
         <v>0.347126007080078</v>
       </c>
       <c r="G1525" t="n">
-        <v>0.330647617578506</v>
+        <v>0.330647587776184</v>
       </c>
       <c r="H1525" t="n">
         <v>83151</v>
@@ -44710,7 +44710,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1529" t="n">
-        <v>0.321253746747971</v>
+        <v>0.321253776550293</v>
       </c>
       <c r="H1529" t="n">
         <v>28393</v>
@@ -44768,7 +44768,7 @@
         <v>0.330361008644104</v>
       </c>
       <c r="G1531" t="n">
-        <v>0.314678430557251</v>
+        <v>0.314678460359573</v>
       </c>
       <c r="H1531" t="n">
         <v>50194</v>
@@ -45029,7 +45029,7 @@
         <v>0.347126007080078</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.330647617578506</v>
+        <v>0.330647587776184</v>
       </c>
       <c r="H1540" t="n">
         <v>26365</v>
@@ -45087,7 +45087,7 @@
         <v>0.333319991827011</v>
       </c>
       <c r="G1542" t="n">
-        <v>0.317496985197067</v>
+        <v>0.317496955394745</v>
       </c>
       <c r="H1542" t="n">
         <v>20280</v>
@@ -45116,7 +45116,7 @@
         <v>0.333319991827011</v>
       </c>
       <c r="G1543" t="n">
-        <v>0.317496985197067</v>
+        <v>0.317496955394745</v>
       </c>
       <c r="H1543" t="n">
         <v>41068</v>
@@ -45174,7 +45174,7 @@
         <v>0.334306001663208</v>
       </c>
       <c r="G1545" t="n">
-        <v>0.318436175584793</v>
+        <v>0.318436145782471</v>
       </c>
       <c r="H1545" t="n">
         <v>1521</v>
@@ -45203,7 +45203,7 @@
         <v>0.334306001663208</v>
       </c>
       <c r="G1546" t="n">
-        <v>0.318436175584793</v>
+        <v>0.318436145782471</v>
       </c>
       <c r="H1546" t="n">
         <v>0</v>
@@ -45232,7 +45232,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1547" t="n">
-        <v>0.309981554746628</v>
+        <v>0.309981524944305</v>
       </c>
       <c r="H1547" t="n">
         <v>12168</v>
@@ -45261,7 +45261,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.309981554746628</v>
+        <v>0.309981524944305</v>
       </c>
       <c r="H1548" t="n">
         <v>8619</v>
@@ -45522,7 +45522,7 @@
         <v>0.333319991827011</v>
       </c>
       <c r="G1557" t="n">
-        <v>0.317496985197067</v>
+        <v>0.317496955394745</v>
       </c>
       <c r="H1557" t="n">
         <v>13182</v>
@@ -45551,7 +45551,7 @@
         <v>0.366849005222321</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.349434316158295</v>
+        <v>0.349434345960617</v>
       </c>
       <c r="H1558" t="n">
         <v>454289</v>
@@ -45667,7 +45667,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.321253746747971</v>
+        <v>0.321253776550293</v>
       </c>
       <c r="H1562" t="n">
         <v>39547</v>
@@ -45696,7 +45696,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1563" t="n">
-        <v>0.309981554746628</v>
+        <v>0.309981524944305</v>
       </c>
       <c r="H1563" t="n">
         <v>19266</v>
@@ -45870,7 +45870,7 @@
         <v>0.330361008644104</v>
       </c>
       <c r="G1569" t="n">
-        <v>0.314678430557251</v>
+        <v>0.314678460359573</v>
       </c>
       <c r="H1569" t="n">
         <v>24843</v>
@@ -45899,7 +45899,7 @@
         <v>0.330361008644104</v>
       </c>
       <c r="G1570" t="n">
-        <v>0.314678430557251</v>
+        <v>0.314678460359573</v>
       </c>
       <c r="H1570" t="n">
         <v>0</v>
@@ -46015,7 +46015,7 @@
         <v>0.307680010795593</v>
       </c>
       <c r="G1574" t="n">
-        <v>0.293074131011963</v>
+        <v>0.293074160814285</v>
       </c>
       <c r="H1574" t="n">
         <v>35491</v>
@@ -46044,7 +46044,7 @@
         <v>0.301762998104095</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.287438035011292</v>
+        <v>0.287438005208969</v>
       </c>
       <c r="H1575" t="n">
         <v>19266</v>
@@ -46073,7 +46073,7 @@
         <v>0.304720997810364</v>
       </c>
       <c r="G1576" t="n">
-        <v>0.290255606174469</v>
+        <v>0.290255576372147</v>
       </c>
       <c r="H1576" t="n">
         <v>5070</v>
@@ -46276,7 +46276,7 @@
         <v>0.316554993391037</v>
       </c>
       <c r="G1583" t="n">
-        <v>0.301527798175812</v>
+        <v>0.301527827978134</v>
       </c>
       <c r="H1583" t="n">
         <v>4056</v>
@@ -46305,7 +46305,7 @@
         <v>0.304720997810364</v>
       </c>
       <c r="G1584" t="n">
-        <v>0.290255606174469</v>
+        <v>0.290255576372147</v>
       </c>
       <c r="H1584" t="n">
         <v>19773</v>
@@ -46392,7 +46392,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1587" t="n">
-        <v>0.309981554746628</v>
+        <v>0.309981524944305</v>
       </c>
       <c r="H1587" t="n">
         <v>9633</v>
@@ -46537,7 +46537,7 @@
         <v>0.323457986116409</v>
       </c>
       <c r="G1592" t="n">
-        <v>0.308103114366531</v>
+        <v>0.308103144168854</v>
       </c>
       <c r="H1592" t="n">
         <v>3042</v>
@@ -46595,7 +46595,7 @@
         <v>0.321485996246338</v>
       </c>
       <c r="G1594" t="n">
-        <v>0.30622473359108</v>
+        <v>0.306224763393402</v>
       </c>
       <c r="H1594" t="n">
         <v>12168</v>
@@ -46885,7 +46885,7 @@
         <v>0.307680010795593</v>
       </c>
       <c r="G1604" t="n">
-        <v>0.293074131011963</v>
+        <v>0.293074160814285</v>
       </c>
       <c r="H1604" t="n">
         <v>6591</v>
@@ -46914,7 +46914,7 @@
         <v>0.307680010795593</v>
       </c>
       <c r="G1605" t="n">
-        <v>0.293074131011963</v>
+        <v>0.293074160814285</v>
       </c>
       <c r="H1605" t="n">
         <v>0</v>
@@ -46943,7 +46943,7 @@
         <v>0.308665990829468</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.294013291597366</v>
+        <v>0.294013321399689</v>
       </c>
       <c r="H1606" t="n">
         <v>6084</v>
@@ -46972,7 +46972,7 @@
         <v>0.301762998104095</v>
       </c>
       <c r="G1607" t="n">
-        <v>0.287438035011292</v>
+        <v>0.287438005208969</v>
       </c>
       <c r="H1607" t="n">
         <v>6084</v>
@@ -47146,7 +47146,7 @@
         <v>0.34909799695015</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.332525998353958</v>
+        <v>0.332525968551636</v>
       </c>
       <c r="H1613" t="n">
         <v>2028</v>
@@ -47175,7 +47175,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.321253746747971</v>
+        <v>0.321253776550293</v>
       </c>
       <c r="H1614" t="n">
         <v>13689</v>
@@ -47262,7 +47262,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1617" t="n">
-        <v>0.347555935382843</v>
+        <v>0.347555905580521</v>
       </c>
       <c r="H1617" t="n">
         <v>191653</v>
@@ -47320,7 +47320,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.336283683776855</v>
+        <v>0.336283713579178</v>
       </c>
       <c r="H1619" t="n">
         <v>56279</v>
@@ -47349,7 +47349,7 @@
         <v>0.363889992237091</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.346615791320801</v>
+        <v>0.346615761518478</v>
       </c>
       <c r="H1620" t="n">
         <v>17238</v>
@@ -47407,7 +47407,7 @@
         <v>0.368820995092392</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.351312696933746</v>
+        <v>0.351312726736069</v>
       </c>
       <c r="H1622" t="n">
         <v>476598</v>
@@ -47465,7 +47465,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1624" t="n">
-        <v>0.364463329315186</v>
+        <v>0.364463359117508</v>
       </c>
       <c r="H1624" t="n">
         <v>62363</v>
@@ -47697,7 +47697,7 @@
         <v>0.674529016017914</v>
       </c>
       <c r="G1632" t="n">
-        <v>0.642508506774902</v>
+        <v>0.642508447170258</v>
       </c>
       <c r="H1632" t="n">
         <v>674336</v>
@@ -47755,7 +47755,7 @@
         <v>0.639028012752533</v>
       </c>
       <c r="G1634" t="n">
-        <v>0.608692765235901</v>
+        <v>0.608692705631256</v>
       </c>
       <c r="H1634" t="n">
         <v>336661</v>
@@ -47871,7 +47871,7 @@
         <v>0.611415028572083</v>
       </c>
       <c r="G1638" t="n">
-        <v>0.582390606403351</v>
+        <v>0.582390546798706</v>
       </c>
       <c r="H1638" t="n">
         <v>162246</v>
@@ -47900,7 +47900,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1639" t="n">
-        <v>0.548574864864349</v>
+        <v>0.548574805259705</v>
       </c>
       <c r="H1639" t="n">
         <v>162246</v>
@@ -47987,7 +47987,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1642" t="n">
-        <v>0.548574864864349</v>
+        <v>0.548574805259705</v>
       </c>
       <c r="H1642" t="n">
         <v>111037</v>
@@ -48045,7 +48045,7 @@
         <v>0.571968972682953</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.54481703042984</v>
+        <v>0.544817090034485</v>
       </c>
       <c r="H1644" t="n">
         <v>66926</v>
@@ -48364,7 +48364,7 @@
         <v>0.702140986919403</v>
       </c>
       <c r="G1655" t="n">
-        <v>0.668809711933136</v>
+        <v>0.668809652328491</v>
       </c>
       <c r="H1655" t="n">
         <v>78081</v>
@@ -48625,7 +48625,7 @@
         <v>0.615360021591187</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.586148262023926</v>
+        <v>0.586148321628571</v>
       </c>
       <c r="H1664" t="n">
         <v>8619</v>
@@ -48712,7 +48712,7 @@
         <v>0.639028012752533</v>
       </c>
       <c r="G1667" t="n">
-        <v>0.608692765235901</v>
+        <v>0.608692705631256</v>
       </c>
       <c r="H1667" t="n">
         <v>56786</v>
@@ -48741,7 +48741,7 @@
         <v>0.64691698551178</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.616207242012024</v>
+        <v>0.616207182407379</v>
       </c>
       <c r="H1668" t="n">
         <v>59321</v>
@@ -48857,7 +48857,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.604934990406036</v>
+        <v>0.604935050010681</v>
       </c>
       <c r="H1672" t="n">
         <v>31942</v>
@@ -48915,7 +48915,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1674" t="n">
-        <v>0.604934990406036</v>
+        <v>0.604935050010681</v>
       </c>
       <c r="H1674" t="n">
         <v>70982</v>
@@ -49147,7 +49147,7 @@
         <v>0.615360021591187</v>
       </c>
       <c r="G1682" t="n">
-        <v>0.586148262023926</v>
+        <v>0.586148321628571</v>
       </c>
       <c r="H1682" t="n">
         <v>13689</v>
@@ -49176,7 +49176,7 @@
         <v>0.583802998065948</v>
       </c>
       <c r="G1683" t="n">
-        <v>0.556089341640472</v>
+        <v>0.556089282035828</v>
       </c>
       <c r="H1683" t="n">
         <v>214976</v>
@@ -49263,7 +49263,7 @@
         <v>0.571968972682953</v>
       </c>
       <c r="G1686" t="n">
-        <v>0.54481703042984</v>
+        <v>0.544817090034485</v>
       </c>
       <c r="H1686" t="n">
         <v>9126</v>
@@ -49350,7 +49350,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1689" t="n">
-        <v>0.548574864864349</v>
+        <v>0.548574805259705</v>
       </c>
       <c r="H1689" t="n">
         <v>25858</v>
@@ -49408,7 +49408,7 @@
         <v>0.595637023448944</v>
       </c>
       <c r="G1691" t="n">
-        <v>0.56736159324646</v>
+        <v>0.567361533641815</v>
       </c>
       <c r="H1691" t="n">
         <v>12675</v>
@@ -49524,7 +49524,7 @@
         <v>0.603525996208191</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.574876070022583</v>
+        <v>0.574876010417938</v>
       </c>
       <c r="H1695" t="n">
         <v>28900</v>
@@ -49582,7 +49582,7 @@
         <v>0.595637023448944</v>
       </c>
       <c r="G1697" t="n">
-        <v>0.56736159324646</v>
+        <v>0.567361533641815</v>
       </c>
       <c r="H1697" t="n">
         <v>3549</v>
@@ -49669,7 +49669,7 @@
         <v>0.607470989227295</v>
       </c>
       <c r="G1700" t="n">
-        <v>0.578633725643158</v>
+        <v>0.578633785247803</v>
       </c>
       <c r="H1700" t="n">
         <v>25351</v>
@@ -49698,7 +49698,7 @@
         <v>0.607470989227295</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.578633725643158</v>
+        <v>0.578633785247803</v>
       </c>
       <c r="H1701" t="n">
         <v>19773</v>
@@ -49727,7 +49727,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.604934990406036</v>
+        <v>0.604935050010681</v>
       </c>
       <c r="H1702" t="n">
         <v>64391</v>
@@ -49872,7 +49872,7 @@
         <v>0.662694990634918</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.63123619556427</v>
+        <v>0.631236255168915</v>
       </c>
       <c r="H1707" t="n">
         <v>123712</v>
@@ -50075,7 +50075,7 @@
         <v>0.702140986919403</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.668809711933136</v>
+        <v>0.668809652328491</v>
       </c>
       <c r="H1714" t="n">
         <v>115093</v>
@@ -50162,7 +50162,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1717" t="n">
-        <v>0.674445748329163</v>
+        <v>0.674445807933807</v>
       </c>
       <c r="H1717" t="n">
         <v>1126598</v>
@@ -50249,7 +50249,7 @@
         <v>0.702140986919403</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.668809711933136</v>
+        <v>0.668809652328491</v>
       </c>
       <c r="H1720" t="n">
         <v>385842</v>
@@ -50423,7 +50423,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1726" t="n">
-        <v>0.634993970394135</v>
+        <v>0.63499391078949</v>
       </c>
       <c r="H1726" t="n">
         <v>82644</v>
@@ -50481,7 +50481,7 @@
         <v>0.668612003326416</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.636872351169586</v>
+        <v>0.636872291564941</v>
       </c>
       <c r="H1728" t="n">
         <v>132332</v>
@@ -50510,7 +50510,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1729" t="n">
-        <v>0.634993970394135</v>
+        <v>0.63499391078949</v>
       </c>
       <c r="H1729" t="n">
         <v>9126</v>
@@ -50713,7 +50713,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.674445748329163</v>
+        <v>0.674445807933807</v>
       </c>
       <c r="H1736" t="n">
         <v>307254</v>
@@ -50800,7 +50800,7 @@
         <v>0.674529016017914</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.642508506774902</v>
+        <v>0.642508447170258</v>
       </c>
       <c r="H1739" t="n">
         <v>100389</v>
@@ -50887,7 +50887,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1742" t="n">
-        <v>0.634993970394135</v>
+        <v>0.63499391078949</v>
       </c>
       <c r="H1742" t="n">
         <v>41575</v>
@@ -50945,7 +50945,7 @@
         <v>0.662694990634918</v>
       </c>
       <c r="G1744" t="n">
-        <v>0.63123619556427</v>
+        <v>0.631236255168915</v>
       </c>
       <c r="H1744" t="n">
         <v>26365</v>
@@ -51119,7 +51119,7 @@
         <v>0.64691698551178</v>
       </c>
       <c r="G1750" t="n">
-        <v>0.616207242012024</v>
+        <v>0.616207182407379</v>
       </c>
       <c r="H1750" t="n">
         <v>328548</v>
@@ -51264,7 +51264,7 @@
         <v>0.694252014160156</v>
       </c>
       <c r="G1755" t="n">
-        <v>0.661295235157013</v>
+        <v>0.661295175552368</v>
       </c>
       <c r="H1755" t="n">
         <v>19773</v>
@@ -51496,7 +51496,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1763" t="n">
-        <v>0.634993970394135</v>
+        <v>0.63499391078949</v>
       </c>
       <c r="H1763" t="n">
         <v>228159</v>
@@ -51699,7 +51699,7 @@
         <v>0.69819700717926</v>
       </c>
       <c r="G1770" t="n">
-        <v>0.665052890777588</v>
+        <v>0.665052950382233</v>
       </c>
       <c r="H1770" t="n">
         <v>90249</v>
@@ -52279,7 +52279,7 @@
         <v>0.674529016017914</v>
       </c>
       <c r="G1790" t="n">
-        <v>0.642508506774902</v>
+        <v>0.642508447170258</v>
       </c>
       <c r="H1790" t="n">
         <v>5577</v>
@@ -52337,7 +52337,7 @@
         <v>0.694252014160156</v>
       </c>
       <c r="G1792" t="n">
-        <v>0.661295235157013</v>
+        <v>0.661295175552368</v>
       </c>
       <c r="H1792" t="n">
         <v>99882</v>
@@ -52656,7 +52656,7 @@
         <v>0.69819700717926</v>
       </c>
       <c r="G1803" t="n">
-        <v>0.665052890777588</v>
+        <v>0.665052950382233</v>
       </c>
       <c r="H1803" t="n">
         <v>735179</v>
@@ -52830,7 +52830,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1809" t="n">
-        <v>0.674445748329163</v>
+        <v>0.674445807933807</v>
       </c>
       <c r="H1809" t="n">
         <v>43603</v>
@@ -52859,7 +52859,7 @@
         <v>0.706085979938507</v>
       </c>
       <c r="G1810" t="n">
-        <v>0.672567367553711</v>
+        <v>0.672567427158356</v>
       </c>
       <c r="H1810" t="n">
         <v>60335</v>
@@ -53207,7 +53207,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.674445748329163</v>
+        <v>0.674445807933807</v>
       </c>
       <c r="H1822" t="n">
         <v>42589</v>
@@ -53265,7 +53265,7 @@
         <v>0.733698010444641</v>
       </c>
       <c r="G1824" t="n">
-        <v>0.698868632316589</v>
+        <v>0.698868691921234</v>
       </c>
       <c r="H1824" t="n">
         <v>185569</v>
@@ -53323,7 +53323,7 @@
         <v>0.729753971099854</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.695111870765686</v>
+        <v>0.695111811161041</v>
       </c>
       <c r="H1826" t="n">
         <v>63884</v>
@@ -53410,7 +53410,7 @@
         <v>0.745531976222992</v>
       </c>
       <c r="G1829" t="n">
-        <v>0.710140883922577</v>
+        <v>0.710140824317932</v>
       </c>
       <c r="H1829" t="n">
         <v>101911</v>
@@ -53439,7 +53439,7 @@
         <v>0.745531976222992</v>
       </c>
       <c r="G1830" t="n">
-        <v>0.710140883922577</v>
+        <v>0.710140824317932</v>
       </c>
       <c r="H1830" t="n">
         <v>85179</v>
@@ -53497,7 +53497,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1832" t="n">
-        <v>0.71202027797699</v>
+        <v>0.712020218372345</v>
       </c>
       <c r="H1832" t="n">
         <v>27886</v>
@@ -53555,7 +53555,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1834" t="n">
-        <v>0.71202027797699</v>
+        <v>0.712020218372345</v>
       </c>
       <c r="H1834" t="n">
         <v>23829</v>
@@ -53584,7 +53584,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G1835" t="n">
-        <v>0.702626407146454</v>
+        <v>0.702626347541809</v>
       </c>
       <c r="H1835" t="n">
         <v>106981</v>
@@ -53613,7 +53613,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.702626407146454</v>
+        <v>0.702626347541809</v>
       </c>
       <c r="H1836" t="n">
         <v>2535</v>
@@ -53642,7 +53642,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G1837" t="n">
-        <v>0.702626407146454</v>
+        <v>0.702626347541809</v>
       </c>
       <c r="H1837" t="n">
         <v>14703</v>
@@ -53700,7 +53700,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1839" t="n">
-        <v>0.71202027797699</v>
+        <v>0.712020218372345</v>
       </c>
       <c r="H1839" t="n">
         <v>37519</v>
@@ -53729,7 +53729,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.71202027797699</v>
+        <v>0.712020218372345</v>
       </c>
       <c r="H1840" t="n">
         <v>5577</v>
@@ -53990,7 +53990,7 @@
         <v>0.796811997890472</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.758986532688141</v>
+        <v>0.758986592292786</v>
       </c>
       <c r="H1849" t="n">
         <v>942043</v>
@@ -54193,7 +54193,7 @@
         <v>0.942762970924377</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.898009061813354</v>
+        <v>0.898009121417999</v>
       </c>
       <c r="H1856" t="n">
         <v>243876</v>
@@ -54338,7 +54338,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1861" t="n">
-        <v>1.08963513374329</v>
+        <v>1.089635014534</v>
       </c>
       <c r="H1861" t="n">
         <v>336661</v>
@@ -54425,7 +54425,7 @@
         <v>1.10449194908142</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.05206060409546</v>
+        <v>1.05206072330475</v>
       </c>
       <c r="H1864" t="n">
         <v>324999</v>
@@ -54512,7 +54512,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.08963513374329</v>
+        <v>1.089635014534</v>
       </c>
       <c r="H1867" t="n">
         <v>737207</v>
@@ -54599,7 +54599,7 @@
         <v>1.10449194908142</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.05206060409546</v>
+        <v>1.05206072330475</v>
       </c>
       <c r="H1870" t="n">
         <v>120163</v>
@@ -54657,7 +54657,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.08963513374329</v>
+        <v>1.089635014534</v>
       </c>
       <c r="H1872" t="n">
         <v>374180</v>
@@ -54744,7 +54744,7 @@
         <v>1.15873098373413</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.10372495651245</v>
+        <v>1.10372483730316</v>
       </c>
       <c r="H1875" t="n">
         <v>117121</v>
@@ -54773,7 +54773,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.08963513374329</v>
+        <v>1.089635014534</v>
       </c>
       <c r="H1876" t="n">
         <v>24336</v>
@@ -54860,7 +54860,7 @@
         <v>1.15873098373413</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.10372495651245</v>
+        <v>1.10372483730316</v>
       </c>
       <c r="H1879" t="n">
         <v>75038</v>
@@ -54976,7 +54976,7 @@
         <v>1.2179000377655</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.16008508205414</v>
+        <v>1.16008520126343</v>
       </c>
       <c r="H1883" t="n">
         <v>52730</v>
@@ -55324,7 +55324,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.20705235004425</v>
+        <v>1.20705246925354</v>
       </c>
       <c r="H1895" t="n">
         <v>59321</v>
@@ -55382,7 +55382,7 @@
         <v>1.25734603404999</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.19765865802765</v>
+        <v>1.19765853881836</v>
       </c>
       <c r="H1897" t="n">
         <v>146021</v>
@@ -55411,7 +55411,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.20705235004425</v>
+        <v>1.20705246925354</v>
       </c>
       <c r="H1898" t="n">
         <v>88221</v>
@@ -55440,7 +55440,7 @@
         <v>1.27213895320892</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.21174919605255</v>
+        <v>1.21174931526184</v>
       </c>
       <c r="H1899" t="n">
         <v>80616</v>
@@ -55701,7 +55701,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.20705235004425</v>
+        <v>1.20705246925354</v>
       </c>
       <c r="H1908" t="n">
         <v>396489</v>
@@ -56020,7 +56020,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.24932265281677</v>
+        <v>1.24932277202606</v>
       </c>
       <c r="H1919" t="n">
         <v>359984</v>
@@ -56049,7 +56049,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.3197728395462</v>
+        <v>1.31977272033691</v>
       </c>
       <c r="H1920" t="n">
         <v>571411</v>
@@ -56107,7 +56107,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.3338634967804</v>
+        <v>1.33386361598969</v>
       </c>
       <c r="H1922" t="n">
         <v>187090</v>
@@ -56310,7 +56310,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.30568301677704</v>
+        <v>1.30568289756775</v>
       </c>
       <c r="H1929" t="n">
         <v>545553</v>
@@ -56368,7 +56368,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.23523306846619</v>
+        <v>1.2352329492569</v>
       </c>
       <c r="H1931" t="n">
         <v>329055</v>
@@ -56397,7 +56397,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G1932" t="n">
-        <v>1.24932265281677</v>
+        <v>1.24932277202606</v>
       </c>
       <c r="H1932" t="n">
         <v>112558</v>
@@ -80154,6 +80154,35 @@
         <v>52000</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>3.35999989509583</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>3.4300000667572</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>3.35999989509583</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>17500</v>
+      </c>
+      <c r="I2752" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -80168,7 +80168,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="D2752" t="n">
-        <v>3.4300000667572</v>
+        <v>3.44000005722046</v>
       </c>
       <c r="E2752" t="n">
         <v>3.35999989509583</v>
@@ -80183,6 +80183,35 @@
         <v>17500</v>
       </c>
       <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>3.41000008583069</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>3.4300000667572</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I2753" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CDG.MI.xlsx
+++ b/data/CDG.MI.xlsx
@@ -427,7 +427,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G2" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -456,7 +456,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G3" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -485,7 +485,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G4" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -514,7 +514,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G5" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -543,7 +543,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G6" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>2.90521001815796</v>
       </c>
       <c r="G32" t="n">
-        <v>2.76729702949524</v>
+        <v>2.76729679107666</v>
       </c>
       <c r="H32" t="n">
         <v>1521</v>
@@ -1355,7 +1355,7 @@
         <v>2.85984706878662</v>
       </c>
       <c r="G34" t="n">
-        <v>2.72408723831177</v>
+        <v>2.72408747673035</v>
       </c>
       <c r="H34" t="n">
         <v>5070</v>
@@ -1442,7 +1442,7 @@
         <v>2.90718293190002</v>
       </c>
       <c r="G37" t="n">
-        <v>2.76917624473572</v>
+        <v>2.76917600631714</v>
       </c>
       <c r="H37" t="n">
         <v>1014</v>
@@ -1471,7 +1471,7 @@
         <v>2.90718293190002</v>
       </c>
       <c r="G38" t="n">
-        <v>2.76917624473572</v>
+        <v>2.76917600631714</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>2.90718293190002</v>
       </c>
       <c r="G39" t="n">
-        <v>2.76917624473572</v>
+        <v>2.76917600631714</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G45" t="n">
-        <v>2.66772723197937</v>
+        <v>2.66772699356079</v>
       </c>
       <c r="H45" t="n">
         <v>2028</v>
@@ -3965,7 +3965,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G124" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H124" t="n">
         <v>507</v>
@@ -3994,7 +3994,7 @@
         <v>2.9269061088562</v>
       </c>
       <c r="G125" t="n">
-        <v>2.78796291351318</v>
+        <v>2.78796315193176</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G126" t="n">
-        <v>2.66772723197937</v>
+        <v>2.66772699356079</v>
       </c>
       <c r="H126" t="n">
         <v>10140</v>
@@ -4052,7 +4052,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G127" t="n">
-        <v>2.66772723197937</v>
+        <v>2.66772699356079</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G128" t="n">
-        <v>2.66772723197937</v>
+        <v>2.66772699356079</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>2.80067801475525</v>
       </c>
       <c r="G129" t="n">
-        <v>2.66772723197937</v>
+        <v>2.66772699356079</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G130" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H130" t="n">
         <v>2028</v>
@@ -4168,7 +4168,7 @@
         <v>2.72967505455017</v>
       </c>
       <c r="G131" t="n">
-        <v>2.60009479522705</v>
+        <v>2.60009455680847</v>
       </c>
       <c r="H131" t="n">
         <v>507</v>
@@ -4197,7 +4197,7 @@
         <v>2.72967505455017</v>
       </c>
       <c r="G132" t="n">
-        <v>2.60009479522705</v>
+        <v>2.60009455680847</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4226,7 +4226,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G133" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H133" t="n">
         <v>6591</v>
@@ -4255,7 +4255,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G134" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G135" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G136" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G137" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G138" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G139" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G140" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G141" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>2.68825602531433</v>
       </c>
       <c r="G142" t="n">
-        <v>2.56064200401306</v>
+        <v>2.56064176559448</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>2.58372402191162</v>
       </c>
       <c r="G143" t="n">
-        <v>2.46107220649719</v>
+        <v>2.46107196807861</v>
       </c>
       <c r="H143" t="n">
         <v>1014</v>
@@ -4545,7 +4545,7 @@
         <v>2.58372402191162</v>
       </c>
       <c r="G144" t="n">
-        <v>2.46107220649719</v>
+        <v>2.46107196807861</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>2.48905301094055</v>
       </c>
       <c r="G145" t="n">
-        <v>2.37089514732361</v>
+        <v>2.37089538574219</v>
       </c>
       <c r="H145" t="n">
         <v>507</v>
@@ -4603,7 +4603,7 @@
         <v>2.48905301094055</v>
       </c>
       <c r="G146" t="n">
-        <v>2.37089514732361</v>
+        <v>2.37089538574219</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>2.35690808296204</v>
       </c>
       <c r="G148" t="n">
-        <v>2.24502348899841</v>
+        <v>2.24502325057983</v>
       </c>
       <c r="H148" t="n">
         <v>2028</v>
@@ -4835,7 +4835,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G154" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H154" t="n">
         <v>1014</v>
@@ -4864,7 +4864,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G155" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G156" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G157" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G158" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>2.59358596801758</v>
       </c>
       <c r="G159" t="n">
-        <v>2.47046589851379</v>
+        <v>2.47046613693237</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>2.56400108337402</v>
       </c>
       <c r="G173" t="n">
-        <v>2.44228529930115</v>
+        <v>2.44228553771973</v>
       </c>
       <c r="H173" t="n">
         <v>1014</v>
@@ -5618,7 +5618,7 @@
         <v>2.58372402191162</v>
       </c>
       <c r="G181" t="n">
-        <v>2.46107220649719</v>
+        <v>2.46107196807861</v>
       </c>
       <c r="H181" t="n">
         <v>2028</v>
@@ -6227,7 +6227,7 @@
         <v>2.56400108337402</v>
       </c>
       <c r="G202" t="n">
-        <v>2.44228529930115</v>
+        <v>2.44228553771973</v>
       </c>
       <c r="H202" t="n">
         <v>10140</v>
@@ -6256,7 +6256,7 @@
         <v>2.56991791725159</v>
       </c>
       <c r="G203" t="n">
-        <v>2.44792127609253</v>
+        <v>2.44792151451111</v>
       </c>
       <c r="H203" t="n">
         <v>3549</v>
@@ -6314,7 +6314,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G205" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H205" t="n">
         <v>2028</v>
@@ -6343,7 +6343,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G206" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -6372,7 +6372,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G207" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G208" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G209" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>2.48313593864441</v>
       </c>
       <c r="G210" t="n">
-        <v>2.36525893211365</v>
+        <v>2.36525917053223</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>2.46144104003906</v>
       </c>
       <c r="G214" t="n">
-        <v>2.3445942401886</v>
+        <v>2.34459400177002</v>
       </c>
       <c r="H214" t="n">
         <v>7605</v>
@@ -7242,7 +7242,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G237" t="n">
-        <v>2.20744967460632</v>
+        <v>2.2074499130249</v>
       </c>
       <c r="H237" t="n">
         <v>2028</v>
@@ -7271,7 +7271,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G238" t="n">
-        <v>2.20744967460632</v>
+        <v>2.2074499130249</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G239" t="n">
-        <v>2.20744967460632</v>
+        <v>2.2074499130249</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G240" t="n">
-        <v>2.20744967460632</v>
+        <v>2.2074499130249</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>2.31746196746826</v>
       </c>
       <c r="G241" t="n">
-        <v>2.20744967460632</v>
+        <v>2.2074499130249</v>
       </c>
       <c r="H241" t="n">
         <v>1521</v>
@@ -7764,7 +7764,7 @@
         <v>2.36874198913574</v>
       </c>
       <c r="G255" t="n">
-        <v>2.25629568099976</v>
+        <v>2.25629544258118</v>
       </c>
       <c r="H255" t="n">
         <v>21294</v>
@@ -7880,7 +7880,7 @@
         <v>2.17151093482971</v>
       </c>
       <c r="G259" t="n">
-        <v>2.06842732429504</v>
+        <v>2.06842708587646</v>
       </c>
       <c r="H259" t="n">
         <v>1014</v>
@@ -7909,7 +7909,7 @@
         <v>2.09853601455688</v>
       </c>
       <c r="G260" t="n">
-        <v>1.99891650676727</v>
+        <v>1.99891638755798</v>
       </c>
       <c r="H260" t="n">
         <v>5577</v>
@@ -7967,7 +7967,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G262" t="n">
-        <v>2.08345723152161</v>
+        <v>2.08345699310303</v>
       </c>
       <c r="H262" t="n">
         <v>507</v>
@@ -7996,7 +7996,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G263" t="n">
-        <v>2.08345723152161</v>
+        <v>2.08345699310303</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G264" t="n">
-        <v>2.08345723152161</v>
+        <v>2.08345699310303</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>2.18728995323181</v>
       </c>
       <c r="G265" t="n">
-        <v>2.08345723152161</v>
+        <v>2.08345699310303</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G266" t="n">
-        <v>2.01958131790161</v>
+        <v>2.01958155632019</v>
       </c>
       <c r="H266" t="n">
         <v>2535</v>
@@ -8112,7 +8112,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G267" t="n">
-        <v>2.01958131790161</v>
+        <v>2.01958155632019</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G280" t="n">
-        <v>2.01958131790161</v>
+        <v>2.01958155632019</v>
       </c>
       <c r="H280" t="n">
         <v>507</v>
@@ -8518,7 +8518,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G281" t="n">
-        <v>2.01958131790161</v>
+        <v>2.01958155632019</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>2.12023091316223</v>
       </c>
       <c r="G282" t="n">
-        <v>2.01958131790161</v>
+        <v>2.01958155632019</v>
       </c>
       <c r="H282" t="n">
         <v>0</v>
@@ -8576,7 +8576,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G283" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H283" t="n">
         <v>1014</v>
@@ -8605,7 +8605,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G284" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G285" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H285" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>2.18531799316406</v>
       </c>
       <c r="G305" t="n">
-        <v>2.08157896995544</v>
+        <v>2.08157873153687</v>
       </c>
       <c r="H305" t="n">
         <v>7605</v>
@@ -9301,7 +9301,7 @@
         <v>1.98216998577118</v>
       </c>
       <c r="G308" t="n">
-        <v>1.88807451725006</v>
+        <v>1.88807439804077</v>
       </c>
       <c r="H308" t="n">
         <v>8112</v>
@@ -9330,7 +9330,7 @@
         <v>1.94272398948669</v>
       </c>
       <c r="G309" t="n">
-        <v>1.85050106048584</v>
+        <v>1.85050094127655</v>
       </c>
       <c r="H309" t="n">
         <v>1014</v>
@@ -9823,7 +9823,7 @@
         <v>2.15770506858826</v>
       </c>
       <c r="G326" t="n">
-        <v>2.05527663230896</v>
+        <v>2.05527687072754</v>
       </c>
       <c r="H326" t="n">
         <v>12675</v>
@@ -9997,7 +9997,7 @@
         <v>2.18926191329956</v>
       </c>
       <c r="G332" t="n">
-        <v>2.08533573150635</v>
+        <v>2.08533549308777</v>
       </c>
       <c r="H332" t="n">
         <v>2535</v>
@@ -10026,7 +10026,7 @@
         <v>2.18926191329956</v>
       </c>
       <c r="G333" t="n">
-        <v>2.08533573150635</v>
+        <v>2.08533549308777</v>
       </c>
       <c r="H333" t="n">
         <v>0</v>
@@ -10229,7 +10229,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G340" t="n">
-        <v>2.02521753311157</v>
+        <v>2.02521777153015</v>
       </c>
       <c r="H340" t="n">
         <v>507</v>
@@ -10345,7 +10345,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G344" t="n">
-        <v>2.02521753311157</v>
+        <v>2.02521777153015</v>
       </c>
       <c r="H344" t="n">
         <v>2535</v>
@@ -10374,7 +10374,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G345" t="n">
-        <v>2.02521753311157</v>
+        <v>2.02521777153015</v>
       </c>
       <c r="H345" t="n">
         <v>0</v>
@@ -10403,7 +10403,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G346" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H346" t="n">
         <v>3042</v>
@@ -10432,7 +10432,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G347" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H347" t="n">
         <v>0</v>
@@ -10954,7 +10954,7 @@
         <v>2.00189304351807</v>
       </c>
       <c r="G365" t="n">
-        <v>1.90686118602753</v>
+        <v>1.90686130523682</v>
       </c>
       <c r="H365" t="n">
         <v>507</v>
@@ -11041,7 +11041,7 @@
         <v>2.71981310844421</v>
       </c>
       <c r="G368" t="n">
-        <v>2.59070110321045</v>
+        <v>2.59070086479187</v>
       </c>
       <c r="H368" t="n">
         <v>70475</v>
@@ -11070,7 +11070,7 @@
         <v>2.41607809066772</v>
       </c>
       <c r="G369" t="n">
-        <v>2.30138444900513</v>
+        <v>2.30138468742371</v>
       </c>
       <c r="H369" t="n">
         <v>39040</v>
@@ -11099,7 +11099,7 @@
         <v>2.25829291343689</v>
       </c>
       <c r="G370" t="n">
-        <v>2.15108966827393</v>
+        <v>2.15108942985535</v>
       </c>
       <c r="H370" t="n">
         <v>18759</v>
@@ -11215,7 +11215,7 @@
         <v>2.17940092086792</v>
       </c>
       <c r="G374" t="n">
-        <v>2.07594275474548</v>
+        <v>2.0759425163269</v>
       </c>
       <c r="H374" t="n">
         <v>7098</v>
@@ -11273,7 +11273,7 @@
         <v>2.17940092086792</v>
       </c>
       <c r="G376" t="n">
-        <v>2.07594275474548</v>
+        <v>2.0759425163269</v>
       </c>
       <c r="H376" t="n">
         <v>3549</v>
@@ -11331,7 +11331,7 @@
         <v>2.20701289176941</v>
       </c>
       <c r="G378" t="n">
-        <v>2.10224366188049</v>
+        <v>2.10224390029907</v>
       </c>
       <c r="H378" t="n">
         <v>507</v>
@@ -11476,7 +11476,7 @@
         <v>2.44369006156921</v>
       </c>
       <c r="G383" t="n">
-        <v>2.32768583297729</v>
+        <v>2.32768559455872</v>
       </c>
       <c r="H383" t="n">
         <v>179992</v>
@@ -11505,7 +11505,7 @@
         <v>2.30957293510437</v>
       </c>
       <c r="G384" t="n">
-        <v>2.1999351978302</v>
+        <v>2.19993543624878</v>
       </c>
       <c r="H384" t="n">
         <v>109516</v>
@@ -11766,7 +11766,7 @@
         <v>2.3628249168396</v>
       </c>
       <c r="G393" t="n">
-        <v>2.25065946578979</v>
+        <v>2.25065922737122</v>
       </c>
       <c r="H393" t="n">
         <v>19266</v>
@@ -11824,7 +11824,7 @@
         <v>2.27604389190674</v>
       </c>
       <c r="G395" t="n">
-        <v>2.16799807548523</v>
+        <v>2.16799783706665</v>
       </c>
       <c r="H395" t="n">
         <v>20280</v>
@@ -11911,7 +11911,7 @@
         <v>2.10445308685303</v>
       </c>
       <c r="G398" t="n">
-        <v>2.00455284118652</v>
+        <v>2.00455260276794</v>
       </c>
       <c r="H398" t="n">
         <v>142979</v>
@@ -11940,7 +11940,7 @@
         <v>2.0472559928894</v>
       </c>
       <c r="G399" t="n">
-        <v>1.95007061958313</v>
+        <v>1.95007073879242</v>
       </c>
       <c r="H399" t="n">
         <v>25858</v>
@@ -11998,7 +11998,7 @@
         <v>2.19123506546021</v>
       </c>
       <c r="G401" t="n">
-        <v>2.08721518516541</v>
+        <v>2.08721494674683</v>
       </c>
       <c r="H401" t="n">
         <v>99882</v>
@@ -12027,7 +12027,7 @@
         <v>2.12614798545837</v>
       </c>
       <c r="G402" t="n">
-        <v>2.02521753311157</v>
+        <v>2.02521777153015</v>
       </c>
       <c r="H402" t="n">
         <v>30421</v>
@@ -12056,7 +12056,7 @@
         <v>2.10839796066284</v>
       </c>
       <c r="G403" t="n">
-        <v>2.00831007957458</v>
+        <v>2.00831031799316</v>
       </c>
       <c r="H403" t="n">
         <v>20280</v>
@@ -12143,7 +12143,7 @@
         <v>2.08078503608704</v>
       </c>
       <c r="G406" t="n">
-        <v>1.98200821876526</v>
+        <v>1.98200809955597</v>
       </c>
       <c r="H406" t="n">
         <v>9633</v>
@@ -12433,7 +12433,7 @@
         <v>2.00189304351807</v>
       </c>
       <c r="G416" t="n">
-        <v>1.90686118602753</v>
+        <v>1.90686130523682</v>
       </c>
       <c r="H416" t="n">
         <v>8112</v>
@@ -12462,7 +12462,7 @@
         <v>1.98019802570343</v>
       </c>
       <c r="G417" t="n">
-        <v>1.88619613647461</v>
+        <v>1.88619601726532</v>
       </c>
       <c r="H417" t="n">
         <v>4563</v>
@@ -12491,7 +12491,7 @@
         <v>2.00189304351807</v>
       </c>
       <c r="G418" t="n">
-        <v>1.90686118602753</v>
+        <v>1.90686130523682</v>
       </c>
       <c r="H418" t="n">
         <v>11661</v>
@@ -12520,7 +12520,7 @@
         <v>2.03936696052551</v>
       </c>
       <c r="G419" t="n">
-        <v>1.94255614280701</v>
+        <v>1.9425562620163</v>
       </c>
       <c r="H419" t="n">
         <v>1014</v>
@@ -12549,7 +12549,7 @@
         <v>2.03936696052551</v>
       </c>
       <c r="G420" t="n">
-        <v>1.94255614280701</v>
+        <v>1.9425562620163</v>
       </c>
       <c r="H420" t="n">
         <v>0</v>
@@ -12578,7 +12578,7 @@
         <v>1.98808705806732</v>
       </c>
       <c r="G421" t="n">
-        <v>1.89371073246002</v>
+        <v>1.89371061325073</v>
       </c>
       <c r="H421" t="n">
         <v>2028</v>
@@ -12607,7 +12607,7 @@
         <v>2.03936696052551</v>
       </c>
       <c r="G422" t="n">
-        <v>1.94255614280701</v>
+        <v>1.9425562620163</v>
       </c>
       <c r="H422" t="n">
         <v>5070</v>
@@ -12636,7 +12636,7 @@
         <v>2.01569890975952</v>
       </c>
       <c r="G423" t="n">
-        <v>1.92001175880432</v>
+        <v>1.92001163959503</v>
       </c>
       <c r="H423" t="n">
         <v>17745</v>
@@ -12781,7 +12781,7 @@
         <v>1.98019802570343</v>
       </c>
       <c r="G428" t="n">
-        <v>1.88619613647461</v>
+        <v>1.88619601726532</v>
       </c>
       <c r="H428" t="n">
         <v>1521</v>
@@ -12810,7 +12810,7 @@
         <v>1.98019802570343</v>
       </c>
       <c r="G429" t="n">
-        <v>1.88619613647461</v>
+        <v>1.88619601726532</v>
       </c>
       <c r="H429" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>1.91313898563385</v>
       </c>
       <c r="G434" t="n">
-        <v>1.8223203420639</v>
+        <v>1.82232046127319</v>
       </c>
       <c r="H434" t="n">
         <v>5070</v>
@@ -12984,7 +12984,7 @@
         <v>1.87960994243622</v>
       </c>
       <c r="G435" t="n">
-        <v>1.79038298130035</v>
+        <v>1.79038310050964</v>
       </c>
       <c r="H435" t="n">
         <v>44617</v>
@@ -13100,7 +13100,7 @@
         <v>1.85397005081177</v>
       </c>
       <c r="G439" t="n">
-        <v>1.76596033573151</v>
+        <v>1.76596021652222</v>
       </c>
       <c r="H439" t="n">
         <v>16731</v>
@@ -13158,7 +13158,7 @@
         <v>1.85791397094727</v>
       </c>
       <c r="G441" t="n">
-        <v>1.76971709728241</v>
+        <v>1.76971697807312</v>
       </c>
       <c r="H441" t="n">
         <v>10140</v>
@@ -13274,7 +13274,7 @@
         <v>1.77507698535919</v>
       </c>
       <c r="G445" t="n">
-        <v>1.69081246852875</v>
+        <v>1.69081234931946</v>
       </c>
       <c r="H445" t="n">
         <v>24843</v>
@@ -13303,7 +13303,7 @@
         <v>1.77507698535919</v>
       </c>
       <c r="G446" t="n">
-        <v>1.69081246852875</v>
+        <v>1.69081234931946</v>
       </c>
       <c r="H446" t="n">
         <v>12675</v>
@@ -13448,7 +13448,7 @@
         <v>1.53840005397797</v>
       </c>
       <c r="G451" t="n">
-        <v>1.4653707742691</v>
+        <v>1.46537065505981</v>
       </c>
       <c r="H451" t="n">
         <v>38533</v>
@@ -13535,7 +13535,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G454" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H454" t="n">
         <v>19266</v>
@@ -13593,7 +13593,7 @@
         <v>1.82241296768188</v>
       </c>
       <c r="G456" t="n">
-        <v>1.73590123653412</v>
+        <v>1.73590135574341</v>
       </c>
       <c r="H456" t="n">
         <v>45631</v>
@@ -13883,7 +13883,7 @@
         <v>1.47528600692749</v>
       </c>
       <c r="G466" t="n">
-        <v>1.40525269508362</v>
+        <v>1.40525281429291</v>
       </c>
       <c r="H466" t="n">
         <v>28393</v>
@@ -13941,7 +13941,7 @@
         <v>1.50684297084808</v>
       </c>
       <c r="G468" t="n">
-        <v>1.43531179428101</v>
+        <v>1.43531167507172</v>
       </c>
       <c r="H468" t="n">
         <v>35998</v>
@@ -13970,7 +13970,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G469" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H469" t="n">
         <v>31435</v>
@@ -14115,7 +14115,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G474" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H474" t="n">
         <v>7098</v>
@@ -14144,7 +14144,7 @@
         <v>1.48909294605255</v>
       </c>
       <c r="G475" t="n">
-        <v>1.41840434074402</v>
+        <v>1.41840422153473</v>
       </c>
       <c r="H475" t="n">
         <v>50702</v>
@@ -14202,7 +14202,7 @@
         <v>1.54431700706482</v>
       </c>
       <c r="G477" t="n">
-        <v>1.47100687026978</v>
+        <v>1.47100675106049</v>
       </c>
       <c r="H477" t="n">
         <v>92784</v>
@@ -14231,7 +14231,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G478" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H478" t="n">
         <v>51716</v>
@@ -14260,7 +14260,7 @@
         <v>1.48909294605255</v>
       </c>
       <c r="G479" t="n">
-        <v>1.41840434074402</v>
+        <v>1.41840422153473</v>
       </c>
       <c r="H479" t="n">
         <v>3042</v>
@@ -14521,7 +14521,7 @@
         <v>1.49205100536346</v>
       </c>
       <c r="G488" t="n">
-        <v>1.42122197151184</v>
+        <v>1.42122185230255</v>
       </c>
       <c r="H488" t="n">
         <v>104446</v>
@@ -14550,7 +14550,7 @@
         <v>1.53840005397797</v>
       </c>
       <c r="G489" t="n">
-        <v>1.4653707742691</v>
+        <v>1.46537065505981</v>
       </c>
       <c r="H489" t="n">
         <v>117121</v>
@@ -14579,7 +14579,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G490" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H490" t="n">
         <v>201793</v>
@@ -14637,7 +14637,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G492" t="n">
-        <v>1.44658386707306</v>
+        <v>1.44658398628235</v>
       </c>
       <c r="H492" t="n">
         <v>31435</v>
@@ -14666,7 +14666,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G493" t="n">
-        <v>1.44658386707306</v>
+        <v>1.44658398628235</v>
       </c>
       <c r="H493" t="n">
         <v>0</v>
@@ -14695,7 +14695,7 @@
         <v>1.54234504699707</v>
       </c>
       <c r="G494" t="n">
-        <v>1.46912848949432</v>
+        <v>1.46912837028503</v>
       </c>
       <c r="H494" t="n">
         <v>14196</v>
@@ -14811,7 +14811,7 @@
         <v>1.55615103244781</v>
       </c>
       <c r="G498" t="n">
-        <v>1.48227894306183</v>
+        <v>1.48227906227112</v>
       </c>
       <c r="H498" t="n">
         <v>2535</v>
@@ -14840,7 +14840,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G499" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H499" t="n">
         <v>3549</v>
@@ -14898,7 +14898,7 @@
         <v>1.55220699310303</v>
       </c>
       <c r="G501" t="n">
-        <v>1.47852218151093</v>
+        <v>1.47852230072021</v>
       </c>
       <c r="H501" t="n">
         <v>2028</v>
@@ -14927,7 +14927,7 @@
         <v>1.50684297084808</v>
       </c>
       <c r="G502" t="n">
-        <v>1.43531179428101</v>
+        <v>1.43531167507172</v>
       </c>
       <c r="H502" t="n">
         <v>3549</v>
@@ -14985,7 +14985,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G504" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H504" t="n">
         <v>23322</v>
@@ -15014,7 +15014,7 @@
         <v>1.44175696372986</v>
       </c>
       <c r="G505" t="n">
-        <v>1.37331533432007</v>
+        <v>1.37331545352936</v>
       </c>
       <c r="H505" t="n">
         <v>8619</v>
@@ -15072,7 +15072,7 @@
         <v>1.4013249874115</v>
       </c>
       <c r="G507" t="n">
-        <v>1.33480274677277</v>
+        <v>1.33480262756348</v>
       </c>
       <c r="H507" t="n">
         <v>5070</v>
@@ -15101,7 +15101,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G508" t="n">
-        <v>1.33386361598969</v>
+        <v>1.3338634967804</v>
       </c>
       <c r="H508" t="n">
         <v>2028</v>
@@ -15304,7 +15304,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G515" t="n">
-        <v>1.33386361598969</v>
+        <v>1.3338634967804</v>
       </c>
       <c r="H515" t="n">
         <v>5577</v>
@@ -15449,7 +15449,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G520" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H520" t="n">
         <v>39040</v>
@@ -15478,7 +15478,7 @@
         <v>1.48909294605255</v>
       </c>
       <c r="G521" t="n">
-        <v>1.41840434074402</v>
+        <v>1.41840422153473</v>
       </c>
       <c r="H521" t="n">
         <v>4056</v>
@@ -15565,7 +15565,7 @@
         <v>1.5531929731369</v>
       </c>
       <c r="G524" t="n">
-        <v>1.47946131229401</v>
+        <v>1.4794614315033</v>
       </c>
       <c r="H524" t="n">
         <v>313845</v>
@@ -15623,7 +15623,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G526" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H526" t="n">
         <v>37012</v>
@@ -15652,7 +15652,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G527" t="n">
-        <v>1.44658386707306</v>
+        <v>1.44658398628235</v>
       </c>
       <c r="H527" t="n">
         <v>17238</v>
@@ -15710,7 +15710,7 @@
         <v>1.5531929731369</v>
       </c>
       <c r="G529" t="n">
-        <v>1.47946131229401</v>
+        <v>1.4794614315033</v>
       </c>
       <c r="H529" t="n">
         <v>11154</v>
@@ -15826,7 +15826,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G533" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H533" t="n">
         <v>20280</v>
@@ -15884,7 +15884,7 @@
         <v>1.51867699623108</v>
       </c>
       <c r="G535" t="n">
-        <v>1.44658386707306</v>
+        <v>1.44658398628235</v>
       </c>
       <c r="H535" t="n">
         <v>5070</v>
@@ -15971,7 +15971,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G538" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H538" t="n">
         <v>11661</v>
@@ -16000,7 +16000,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G539" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H539" t="n">
         <v>17238</v>
@@ -16116,7 +16116,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G543" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H543" t="n">
         <v>507</v>
@@ -16145,7 +16145,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G544" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H544" t="n">
         <v>1014</v>
@@ -16203,7 +16203,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G546" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H546" t="n">
         <v>7098</v>
@@ -16232,7 +16232,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G547" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H547" t="n">
         <v>6084</v>
@@ -16261,7 +16261,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G548" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H548" t="n">
         <v>2028</v>
@@ -16464,7 +16464,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G555" t="n">
-        <v>1.30568289756775</v>
+        <v>1.30568301677704</v>
       </c>
       <c r="H555" t="n">
         <v>9633</v>
@@ -16638,7 +16638,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G561" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H561" t="n">
         <v>4056</v>
@@ -16812,7 +16812,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G567" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H567" t="n">
         <v>24843</v>
@@ -16841,7 +16841,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G568" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H568" t="n">
         <v>2028</v>
@@ -17073,7 +17073,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G576" t="n">
-        <v>1.29629015922546</v>
+        <v>1.29629004001617</v>
       </c>
       <c r="H576" t="n">
         <v>4056</v>
@@ -17102,7 +17102,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G577" t="n">
-        <v>1.31977272033691</v>
+        <v>1.3197728395462</v>
       </c>
       <c r="H577" t="n">
         <v>6084</v>
@@ -17160,7 +17160,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G579" t="n">
-        <v>1.31977272033691</v>
+        <v>1.3197728395462</v>
       </c>
       <c r="H579" t="n">
         <v>3549</v>
@@ -17508,7 +17508,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G591" t="n">
-        <v>1.29629015922546</v>
+        <v>1.29629004001617</v>
       </c>
       <c r="H591" t="n">
         <v>17745</v>
@@ -17682,7 +17682,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G597" t="n">
-        <v>1.31977272033691</v>
+        <v>1.3197728395462</v>
       </c>
       <c r="H597" t="n">
         <v>5577</v>
@@ -17856,7 +17856,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G603" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H603" t="n">
         <v>1014</v>
@@ -17885,7 +17885,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G604" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H604" t="n">
         <v>1521</v>
@@ -17972,7 +17972,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G607" t="n">
-        <v>1.2352329492569</v>
+        <v>1.23523306846619</v>
       </c>
       <c r="H607" t="n">
         <v>15717</v>
@@ -18088,7 +18088,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G611" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H611" t="n">
         <v>2028</v>
@@ -18117,7 +18117,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G612" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H612" t="n">
         <v>1014</v>
@@ -18175,7 +18175,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G614" t="n">
-        <v>1.20705246925354</v>
+        <v>1.20705235004425</v>
       </c>
       <c r="H614" t="n">
         <v>12168</v>
@@ -18378,7 +18378,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G621" t="n">
-        <v>1.30568289756775</v>
+        <v>1.30568301677704</v>
       </c>
       <c r="H621" t="n">
         <v>16731</v>
@@ -18639,7 +18639,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G630" t="n">
-        <v>1.30568289756775</v>
+        <v>1.30568301677704</v>
       </c>
       <c r="H630" t="n">
         <v>10647</v>
@@ -18784,7 +18784,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G635" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H635" t="n">
         <v>53237</v>
@@ -18871,7 +18871,7 @@
         <v>1.85397005081177</v>
       </c>
       <c r="G638" t="n">
-        <v>1.76596033573151</v>
+        <v>1.76596021652222</v>
       </c>
       <c r="H638" t="n">
         <v>456825</v>
@@ -19074,7 +19074,7 @@
         <v>1.54826200008392</v>
       </c>
       <c r="G645" t="n">
-        <v>1.47476446628571</v>
+        <v>1.474764585495</v>
       </c>
       <c r="H645" t="n">
         <v>142979</v>
@@ -19277,7 +19277,7 @@
         <v>1.56798505783081</v>
       </c>
       <c r="G652" t="n">
-        <v>1.49355125427246</v>
+        <v>1.49355137348175</v>
       </c>
       <c r="H652" t="n">
         <v>129797</v>
@@ -19393,7 +19393,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G656" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H656" t="n">
         <v>6591</v>
@@ -19451,7 +19451,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G658" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H658" t="n">
         <v>46138</v>
@@ -19509,7 +19509,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G660" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H660" t="n">
         <v>2028</v>
@@ -19567,7 +19567,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G662" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H662" t="n">
         <v>2535</v>
@@ -19596,7 +19596,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G663" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H663" t="n">
         <v>0</v>
@@ -19625,7 +19625,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G664" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H664" t="n">
         <v>0</v>
@@ -19654,7 +19654,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G665" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H665" t="n">
         <v>0</v>
@@ -19741,7 +19741,7 @@
         <v>1.47430002689362</v>
       </c>
       <c r="G668" t="n">
-        <v>1.40431356430054</v>
+        <v>1.40431368350983</v>
       </c>
       <c r="H668" t="n">
         <v>17238</v>
@@ -19770,7 +19770,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G669" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H669" t="n">
         <v>30421</v>
@@ -19799,7 +19799,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G670" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H670" t="n">
         <v>3042</v>
@@ -19828,7 +19828,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G671" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H671" t="n">
         <v>9126</v>
@@ -19886,7 +19886,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G673" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H673" t="n">
         <v>4563</v>
@@ -19973,7 +19973,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G676" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H676" t="n">
         <v>20280</v>
@@ -20060,7 +20060,7 @@
         <v>1.47923099994659</v>
       </c>
       <c r="G679" t="n">
-        <v>1.40901041030884</v>
+        <v>1.40901052951813</v>
       </c>
       <c r="H679" t="n">
         <v>5070</v>
@@ -20089,7 +20089,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G680" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H680" t="n">
         <v>4056</v>
@@ -20234,7 +20234,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G685" t="n">
-        <v>1.29629015922546</v>
+        <v>1.29629004001617</v>
       </c>
       <c r="H685" t="n">
         <v>5070</v>
@@ -20263,7 +20263,7 @@
         <v>1.36089301109314</v>
       </c>
       <c r="G686" t="n">
-        <v>1.29629015922546</v>
+        <v>1.29629004001617</v>
       </c>
       <c r="H686" t="n">
         <v>507</v>
@@ -20408,7 +20408,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G691" t="n">
-        <v>1.33386361598969</v>
+        <v>1.3338634967804</v>
       </c>
       <c r="H691" t="n">
         <v>9633</v>
@@ -20495,7 +20495,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G694" t="n">
-        <v>1.33386361598969</v>
+        <v>1.3338634967804</v>
       </c>
       <c r="H694" t="n">
         <v>10140</v>
@@ -20553,7 +20553,7 @@
         <v>1.45950794219971</v>
       </c>
       <c r="G696" t="n">
-        <v>1.39022362232208</v>
+        <v>1.39022374153137</v>
       </c>
       <c r="H696" t="n">
         <v>44110</v>
@@ -20669,7 +20669,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G700" t="n">
-        <v>1.30568289756775</v>
+        <v>1.30568301677704</v>
       </c>
       <c r="H700" t="n">
         <v>67433</v>
@@ -20698,7 +20698,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G701" t="n">
-        <v>1.2352329492569</v>
+        <v>1.23523306846619</v>
       </c>
       <c r="H701" t="n">
         <v>81123</v>
@@ -20727,7 +20727,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G702" t="n">
-        <v>1.2352329492569</v>
+        <v>1.23523306846619</v>
       </c>
       <c r="H702" t="n">
         <v>14703</v>
@@ -20872,7 +20872,7 @@
         <v>1.2179000377655</v>
       </c>
       <c r="G707" t="n">
-        <v>1.16008520126343</v>
+        <v>1.16008508205414</v>
       </c>
       <c r="H707" t="n">
         <v>17745</v>
@@ -21017,7 +21017,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G712" t="n">
-        <v>1.089635014534</v>
+        <v>1.08963513374329</v>
       </c>
       <c r="H712" t="n">
         <v>20787</v>
@@ -21075,7 +21075,7 @@
         <v>1.17845404148102</v>
       </c>
       <c r="G714" t="n">
-        <v>1.12251174449921</v>
+        <v>1.12251162528992</v>
       </c>
       <c r="H714" t="n">
         <v>32956</v>
@@ -21133,7 +21133,7 @@
         <v>1.12914597988129</v>
       </c>
       <c r="G716" t="n">
-        <v>1.0755443572998</v>
+        <v>1.07554423809052</v>
       </c>
       <c r="H716" t="n">
         <v>28393</v>
@@ -21220,7 +21220,7 @@
         <v>1.01573896408081</v>
       </c>
       <c r="G719" t="n">
-        <v>0.967520892620087</v>
+        <v>0.967520833015442</v>
       </c>
       <c r="H719" t="n">
         <v>25858</v>
@@ -21336,7 +21336,7 @@
         <v>1.11435401439667</v>
       </c>
       <c r="G723" t="n">
-        <v>1.06145453453064</v>
+        <v>1.06145465373993</v>
       </c>
       <c r="H723" t="n">
         <v>4563</v>
@@ -21365,7 +21365,7 @@
         <v>1.10449194908142</v>
       </c>
       <c r="G724" t="n">
-        <v>1.05206072330475</v>
+        <v>1.05206060409546</v>
       </c>
       <c r="H724" t="n">
         <v>3042</v>
@@ -21800,7 +21800,7 @@
         <v>0.938817977905273</v>
       </c>
       <c r="G739" t="n">
-        <v>0.894251346588135</v>
+        <v>0.89425140619278</v>
       </c>
       <c r="H739" t="n">
         <v>507</v>
@@ -21829,7 +21829,7 @@
         <v>0.938817977905273</v>
       </c>
       <c r="G740" t="n">
-        <v>0.894251346588135</v>
+        <v>0.89425140619278</v>
       </c>
       <c r="H740" t="n">
         <v>1521</v>
@@ -21887,7 +21887,7 @@
         <v>0.926985025405884</v>
       </c>
       <c r="G742" t="n">
-        <v>0.882980167865753</v>
+        <v>0.882980108261108</v>
       </c>
       <c r="H742" t="n">
         <v>11661</v>
@@ -21916,7 +21916,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G743" t="n">
-        <v>0.911159813404083</v>
+        <v>0.911159753799438</v>
       </c>
       <c r="H743" t="n">
         <v>9126</v>
@@ -21945,7 +21945,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G744" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H744" t="n">
         <v>12168</v>
@@ -22061,7 +22061,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G748" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H748" t="n">
         <v>1521</v>
@@ -22206,7 +22206,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G753" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H753" t="n">
         <v>6591</v>
@@ -22264,7 +22264,7 @@
         <v>0.926985025405884</v>
       </c>
       <c r="G755" t="n">
-        <v>0.882980167865753</v>
+        <v>0.882980108261108</v>
       </c>
       <c r="H755" t="n">
         <v>8112</v>
@@ -22322,7 +22322,7 @@
         <v>0.867815017700195</v>
       </c>
       <c r="G757" t="n">
-        <v>0.826619029045105</v>
+        <v>0.82661896944046</v>
       </c>
       <c r="H757" t="n">
         <v>3042</v>
@@ -22351,7 +22351,7 @@
         <v>0.887538015842438</v>
       </c>
       <c r="G758" t="n">
-        <v>0.845405757427216</v>
+        <v>0.845405697822571</v>
       </c>
       <c r="H758" t="n">
         <v>11154</v>
@@ -22380,7 +22380,7 @@
         <v>0.879648983478546</v>
       </c>
       <c r="G759" t="n">
-        <v>0.837891221046448</v>
+        <v>0.837891161441803</v>
       </c>
       <c r="H759" t="n">
         <v>10140</v>
@@ -22409,7 +22409,7 @@
         <v>0.887538015842438</v>
       </c>
       <c r="G760" t="n">
-        <v>0.845405757427216</v>
+        <v>0.845405697822571</v>
       </c>
       <c r="H760" t="n">
         <v>1521</v>
@@ -22699,7 +22699,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G770" t="n">
-        <v>0.911159813404083</v>
+        <v>0.911159753799438</v>
       </c>
       <c r="H770" t="n">
         <v>2028</v>
@@ -22844,7 +22844,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G775" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H775" t="n">
         <v>6591</v>
@@ -22902,7 +22902,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G777" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H777" t="n">
         <v>19266</v>
@@ -22931,7 +22931,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G778" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H778" t="n">
         <v>10140</v>
@@ -22960,7 +22960,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G779" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H779" t="n">
         <v>0</v>
@@ -22989,7 +22989,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G780" t="n">
-        <v>0.911159813404083</v>
+        <v>0.911159753799438</v>
       </c>
       <c r="H780" t="n">
         <v>1521</v>
@@ -23018,7 +23018,7 @@
         <v>0.942762970924377</v>
       </c>
       <c r="G781" t="n">
-        <v>0.898009121417999</v>
+        <v>0.898009061813354</v>
       </c>
       <c r="H781" t="n">
         <v>7098</v>
@@ -23192,7 +23192,7 @@
         <v>0.938817977905273</v>
       </c>
       <c r="G787" t="n">
-        <v>0.894251346588135</v>
+        <v>0.89425140619278</v>
       </c>
       <c r="H787" t="n">
         <v>1014</v>
@@ -23250,7 +23250,7 @@
         <v>1.01573896408081</v>
       </c>
       <c r="G789" t="n">
-        <v>0.967520892620087</v>
+        <v>0.967520833015442</v>
       </c>
       <c r="H789" t="n">
         <v>1521</v>
@@ -23279,7 +23279,7 @@
         <v>0.962486028671265</v>
       </c>
       <c r="G790" t="n">
-        <v>0.91679584980011</v>
+        <v>0.916795909404755</v>
       </c>
       <c r="H790" t="n">
         <v>32449</v>
@@ -23308,7 +23308,7 @@
         <v>0.956569015979767</v>
       </c>
       <c r="G791" t="n">
-        <v>0.911159813404083</v>
+        <v>0.911159753799438</v>
       </c>
       <c r="H791" t="n">
         <v>16224</v>
@@ -23685,7 +23685,7 @@
         <v>1.09956204891205</v>
       </c>
       <c r="G804" t="n">
-        <v>1.04736471176147</v>
+        <v>1.04736483097076</v>
       </c>
       <c r="H804" t="n">
         <v>18252</v>
@@ -24236,7 +24236,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G823" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H823" t="n">
         <v>23322</v>
@@ -24265,7 +24265,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G824" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H824" t="n">
         <v>0</v>
@@ -24323,7 +24323,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G826" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H826" t="n">
         <v>3549</v>
@@ -24381,7 +24381,7 @@
         <v>0.972347974777222</v>
       </c>
       <c r="G828" t="n">
-        <v>0.926189720630646</v>
+        <v>0.926189661026001</v>
       </c>
       <c r="H828" t="n">
         <v>25858</v>
@@ -24410,7 +24410,7 @@
         <v>0.978264987468719</v>
       </c>
       <c r="G829" t="n">
-        <v>0.931825757026672</v>
+        <v>0.931825816631317</v>
       </c>
       <c r="H829" t="n">
         <v>10647</v>
@@ -24613,7 +24613,7 @@
         <v>1.04039204120636</v>
       </c>
       <c r="G836" t="n">
-        <v>0.991003632545471</v>
+        <v>0.991003572940826</v>
       </c>
       <c r="H836" t="n">
         <v>55772</v>
@@ -24700,7 +24700,7 @@
         <v>1.01573896408081</v>
       </c>
       <c r="G839" t="n">
-        <v>0.967520892620087</v>
+        <v>0.967520833015442</v>
       </c>
       <c r="H839" t="n">
         <v>14703</v>
@@ -24729,7 +24729,7 @@
         <v>0.99108499288559</v>
       </c>
       <c r="G840" t="n">
-        <v>0.944037258625031</v>
+        <v>0.944037199020386</v>
       </c>
       <c r="H840" t="n">
         <v>19773</v>
@@ -24787,7 +24787,7 @@
         <v>0.982209026813507</v>
       </c>
       <c r="G842" t="n">
-        <v>0.93558257818222</v>
+        <v>0.935582637786865</v>
       </c>
       <c r="H842" t="n">
         <v>6591</v>
@@ -24816,7 +24816,7 @@
         <v>0.982209026813507</v>
       </c>
       <c r="G843" t="n">
-        <v>0.93558257818222</v>
+        <v>0.935582637786865</v>
       </c>
       <c r="H843" t="n">
         <v>0</v>
@@ -24874,7 +24874,7 @@
         <v>0.99108499288559</v>
       </c>
       <c r="G845" t="n">
-        <v>0.944037258625031</v>
+        <v>0.944037199020386</v>
       </c>
       <c r="H845" t="n">
         <v>12168</v>
@@ -25106,7 +25106,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G853" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H853" t="n">
         <v>18759</v>
@@ -25164,7 +25164,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G855" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H855" t="n">
         <v>3549</v>
@@ -25193,7 +25193,7 @@
         <v>0.982209026813507</v>
       </c>
       <c r="G856" t="n">
-        <v>0.93558257818222</v>
+        <v>0.935582637786865</v>
       </c>
       <c r="H856" t="n">
         <v>5070</v>
@@ -25222,7 +25222,7 @@
         <v>0.984182000160217</v>
       </c>
       <c r="G857" t="n">
-        <v>0.937461912631989</v>
+        <v>0.937461972236633</v>
       </c>
       <c r="H857" t="n">
         <v>12675</v>
@@ -25396,7 +25396,7 @@
         <v>0.978264987468719</v>
       </c>
       <c r="G863" t="n">
-        <v>0.931825757026672</v>
+        <v>0.931825816631317</v>
       </c>
       <c r="H863" t="n">
         <v>17745</v>
@@ -25425,7 +25425,7 @@
         <v>0.978264987468719</v>
       </c>
       <c r="G864" t="n">
-        <v>0.931825757026672</v>
+        <v>0.931825816631317</v>
       </c>
       <c r="H864" t="n">
         <v>0</v>
@@ -25512,7 +25512,7 @@
         <v>0.950652003288269</v>
       </c>
       <c r="G867" t="n">
-        <v>0.905523657798767</v>
+        <v>0.905523598194122</v>
       </c>
       <c r="H867" t="n">
         <v>9126</v>
@@ -25686,7 +25686,7 @@
         <v>0.90923398733139</v>
       </c>
       <c r="G873" t="n">
-        <v>0.866071760654449</v>
+        <v>0.866071820259094</v>
       </c>
       <c r="H873" t="n">
         <v>7098</v>
@@ -25715,7 +25715,7 @@
         <v>0.915151000022888</v>
       </c>
       <c r="G874" t="n">
-        <v>0.871707856655121</v>
+        <v>0.871707916259766</v>
       </c>
       <c r="H874" t="n">
         <v>7098</v>
@@ -25831,7 +25831,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G878" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H878" t="n">
         <v>31435</v>
@@ -25860,7 +25860,7 @@
         <v>0.769200026988983</v>
       </c>
       <c r="G879" t="n">
-        <v>0.732685387134552</v>
+        <v>0.732685327529907</v>
       </c>
       <c r="H879" t="n">
         <v>49687</v>
@@ -25889,7 +25889,7 @@
         <v>0.769200026988983</v>
       </c>
       <c r="G880" t="n">
-        <v>0.732685387134552</v>
+        <v>0.732685327529907</v>
       </c>
       <c r="H880" t="n">
         <v>21801</v>
@@ -26005,7 +26005,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G884" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H884" t="n">
         <v>10647</v>
@@ -26063,7 +26063,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G886" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H886" t="n">
         <v>7605</v>
@@ -26121,7 +26121,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G888" t="n">
-        <v>0.723291456699371</v>
+        <v>0.723291516304016</v>
       </c>
       <c r="H888" t="n">
         <v>12168</v>
@@ -26150,7 +26150,7 @@
         <v>0.745531976222992</v>
       </c>
       <c r="G889" t="n">
-        <v>0.710140824317932</v>
+        <v>0.710140883922577</v>
       </c>
       <c r="H889" t="n">
         <v>10647</v>
@@ -26179,7 +26179,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G890" t="n">
-        <v>0.723291456699371</v>
+        <v>0.723291516304016</v>
       </c>
       <c r="H890" t="n">
         <v>1521</v>
@@ -26208,7 +26208,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G891" t="n">
-        <v>0.723291456699371</v>
+        <v>0.723291516304016</v>
       </c>
       <c r="H891" t="n">
         <v>0</v>
@@ -26266,7 +26266,7 @@
         <v>0.77708899974823</v>
       </c>
       <c r="G893" t="n">
-        <v>0.740199863910675</v>
+        <v>0.74019980430603</v>
       </c>
       <c r="H893" t="n">
         <v>29914</v>
@@ -26353,7 +26353,7 @@
         <v>0.759338021278381</v>
       </c>
       <c r="G896" t="n">
-        <v>0.723291456699371</v>
+        <v>0.723291516304016</v>
       </c>
       <c r="H896" t="n">
         <v>30928</v>
@@ -26411,7 +26411,7 @@
         <v>0.729753971099854</v>
       </c>
       <c r="G898" t="n">
-        <v>0.695111811161041</v>
+        <v>0.695111870765686</v>
       </c>
       <c r="H898" t="n">
         <v>15210</v>
@@ -26440,7 +26440,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G899" t="n">
-        <v>0.702626347541809</v>
+        <v>0.702626407146454</v>
       </c>
       <c r="H899" t="n">
         <v>52223</v>
@@ -26585,7 +26585,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G904" t="n">
-        <v>0.548574805259705</v>
+        <v>0.548574864864349</v>
       </c>
       <c r="H904" t="n">
         <v>50702</v>
@@ -26672,7 +26672,7 @@
         <v>0.508854985237122</v>
       </c>
       <c r="G907" t="n">
-        <v>0.484699130058289</v>
+        <v>0.484699159860611</v>
       </c>
       <c r="H907" t="n">
         <v>76053</v>
@@ -26817,7 +26817,7 @@
         <v>0.492091000080109</v>
       </c>
       <c r="G912" t="n">
-        <v>0.468730956315994</v>
+        <v>0.468730986118317</v>
       </c>
       <c r="H912" t="n">
         <v>19773</v>
@@ -26846,7 +26846,7 @@
         <v>0.492091000080109</v>
       </c>
       <c r="G913" t="n">
-        <v>0.468730956315994</v>
+        <v>0.468730986118317</v>
       </c>
       <c r="H913" t="n">
         <v>507</v>
@@ -26991,7 +26991,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G918" t="n">
-        <v>0.432096689939499</v>
+        <v>0.432096719741821</v>
       </c>
       <c r="H918" t="n">
         <v>18759</v>
@@ -27049,7 +27049,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G920" t="n">
-        <v>0.418945103883743</v>
+        <v>0.418945133686066</v>
       </c>
       <c r="H920" t="n">
         <v>7098</v>
@@ -27107,7 +27107,7 @@
         <v>0.481243014335632</v>
       </c>
       <c r="G922" t="n">
-        <v>0.458397924900055</v>
+        <v>0.458397954702377</v>
       </c>
       <c r="H922" t="n">
         <v>51209</v>
@@ -27194,7 +27194,7 @@
         <v>0.44574099779129</v>
       </c>
       <c r="G925" t="n">
-        <v>0.424581259489059</v>
+        <v>0.424581229686737</v>
       </c>
       <c r="H925" t="n">
         <v>198751</v>
@@ -27252,7 +27252,7 @@
         <v>0.449685990810394</v>
       </c>
       <c r="G927" t="n">
-        <v>0.428338944911957</v>
+        <v>0.428338974714279</v>
       </c>
       <c r="H927" t="n">
         <v>507</v>
@@ -27339,7 +27339,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G930" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H930" t="n">
         <v>36505</v>
@@ -27368,7 +27368,7 @@
         <v>0.469408988952637</v>
       </c>
       <c r="G931" t="n">
-        <v>0.447125673294067</v>
+        <v>0.44712570309639</v>
       </c>
       <c r="H931" t="n">
         <v>24843</v>
@@ -27571,7 +27571,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G938" t="n">
-        <v>0.494093000888824</v>
+        <v>0.494093030691147</v>
       </c>
       <c r="H938" t="n">
         <v>40561</v>
@@ -27600,7 +27600,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G939" t="n">
-        <v>0.494093000888824</v>
+        <v>0.494093030691147</v>
       </c>
       <c r="H939" t="n">
         <v>19773</v>
@@ -27629,7 +27629,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G940" t="n">
-        <v>0.494093000888824</v>
+        <v>0.494093030691147</v>
       </c>
       <c r="H940" t="n">
         <v>20787</v>
@@ -27716,7 +27716,7 @@
         <v>0.506883025169373</v>
       </c>
       <c r="G943" t="n">
-        <v>0.482820808887482</v>
+        <v>0.482820779085159</v>
       </c>
       <c r="H943" t="n">
         <v>100389</v>
@@ -27861,7 +27861,7 @@
         <v>0.489131987094879</v>
       </c>
       <c r="G948" t="n">
-        <v>0.4659124314785</v>
+        <v>0.465912401676178</v>
       </c>
       <c r="H948" t="n">
         <v>3549</v>
@@ -28035,7 +28035,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G954" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H954" t="n">
         <v>103939</v>
@@ -28064,7 +28064,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G955" t="n">
-        <v>0.41988530755043</v>
+        <v>0.419885277748108</v>
       </c>
       <c r="H955" t="n">
         <v>17238</v>
@@ -28238,7 +28238,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G961" t="n">
-        <v>0.437731891870499</v>
+        <v>0.437731862068176</v>
       </c>
       <c r="H961" t="n">
         <v>415756</v>
@@ -28296,7 +28296,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G963" t="n">
-        <v>0.462154686450958</v>
+        <v>0.462154716253281</v>
       </c>
       <c r="H963" t="n">
         <v>130811</v>
@@ -28731,7 +28731,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G978" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H978" t="n">
         <v>47659</v>
@@ -28818,7 +28818,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G981" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H981" t="n">
         <v>45631</v>
@@ -28876,7 +28876,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G983" t="n">
-        <v>0.432096689939499</v>
+        <v>0.432096719741821</v>
       </c>
       <c r="H983" t="n">
         <v>39547</v>
@@ -28992,7 +28992,7 @@
         <v>0.469408988952637</v>
       </c>
       <c r="G987" t="n">
-        <v>0.447125673294067</v>
+        <v>0.44712570309639</v>
       </c>
       <c r="H987" t="n">
         <v>6084</v>
@@ -29079,7 +29079,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G990" t="n">
-        <v>0.432096689939499</v>
+        <v>0.432096719741821</v>
       </c>
       <c r="H990" t="n">
         <v>19266</v>
@@ -29108,7 +29108,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G991" t="n">
-        <v>0.432096689939499</v>
+        <v>0.432096719741821</v>
       </c>
       <c r="H991" t="n">
         <v>19266</v>
@@ -29137,7 +29137,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G992" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H992" t="n">
         <v>9633</v>
@@ -29166,7 +29166,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G993" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H993" t="n">
         <v>104446</v>
@@ -29195,7 +29195,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G994" t="n">
-        <v>0.41988530755043</v>
+        <v>0.419885277748108</v>
       </c>
       <c r="H994" t="n">
         <v>175935</v>
@@ -29224,7 +29224,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G995" t="n">
-        <v>0.418945103883743</v>
+        <v>0.418945133686066</v>
       </c>
       <c r="H995" t="n">
         <v>67940</v>
@@ -29253,7 +29253,7 @@
         <v>0.449685990810394</v>
       </c>
       <c r="G996" t="n">
-        <v>0.428338944911957</v>
+        <v>0.428338974714279</v>
       </c>
       <c r="H996" t="n">
         <v>116107</v>
@@ -29282,7 +29282,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G997" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H997" t="n">
         <v>52730</v>
@@ -29398,7 +29398,7 @@
         <v>0.55224597454071</v>
       </c>
       <c r="G1001" t="n">
-        <v>0.526030361652374</v>
+        <v>0.526030302047729</v>
       </c>
       <c r="H1001" t="n">
         <v>693096</v>
@@ -29543,7 +29543,7 @@
         <v>0.603525996208191</v>
       </c>
       <c r="G1006" t="n">
-        <v>0.574876010417938</v>
+        <v>0.574876070022583</v>
       </c>
       <c r="H1006" t="n">
         <v>259594</v>
@@ -29601,7 +29601,7 @@
         <v>0.694252014160156</v>
       </c>
       <c r="G1008" t="n">
-        <v>0.661295175552368</v>
+        <v>0.661295235157013</v>
       </c>
       <c r="H1008" t="n">
         <v>497893</v>
@@ -29717,7 +29717,7 @@
         <v>0.639028012752533</v>
       </c>
       <c r="G1012" t="n">
-        <v>0.608692705631256</v>
+        <v>0.608692765235901</v>
       </c>
       <c r="H1012" t="n">
         <v>271255</v>
@@ -29775,7 +29775,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1014" t="n">
-        <v>0.63499391078949</v>
+        <v>0.634993970394135</v>
       </c>
       <c r="H1014" t="n">
         <v>67433</v>
@@ -29862,7 +29862,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1017" t="n">
-        <v>0.604935050010681</v>
+        <v>0.604934990406036</v>
       </c>
       <c r="H1017" t="n">
         <v>279875</v>
@@ -29949,7 +29949,7 @@
         <v>0.611415028572083</v>
       </c>
       <c r="G1020" t="n">
-        <v>0.582390546798706</v>
+        <v>0.582390606403351</v>
       </c>
       <c r="H1020" t="n">
         <v>99882</v>
@@ -30094,7 +30094,7 @@
         <v>0.765254974365234</v>
       </c>
       <c r="G1025" t="n">
-        <v>0.728927552700043</v>
+        <v>0.728927612304688</v>
       </c>
       <c r="H1025" t="n">
         <v>870046</v>
@@ -30268,7 +30268,7 @@
         <v>0.706085979938507</v>
       </c>
       <c r="G1031" t="n">
-        <v>0.672567427158356</v>
+        <v>0.672567367553711</v>
       </c>
       <c r="H1031" t="n">
         <v>155148</v>
@@ -30471,7 +30471,7 @@
         <v>0.668612003326416</v>
       </c>
       <c r="G1038" t="n">
-        <v>0.636872291564941</v>
+        <v>0.636872351169586</v>
       </c>
       <c r="H1038" t="n">
         <v>98361</v>
@@ -30616,7 +30616,7 @@
         <v>0.69819700717926</v>
       </c>
       <c r="G1043" t="n">
-        <v>0.665052950382233</v>
+        <v>0.665052890777588</v>
       </c>
       <c r="H1043" t="n">
         <v>186583</v>
@@ -30906,7 +30906,7 @@
         <v>0.550274014472961</v>
       </c>
       <c r="G1053" t="n">
-        <v>0.524151921272278</v>
+        <v>0.524151980876923</v>
       </c>
       <c r="H1053" t="n">
         <v>205850</v>
@@ -30935,7 +30935,7 @@
         <v>0.571968972682953</v>
       </c>
       <c r="G1054" t="n">
-        <v>0.544817090034485</v>
+        <v>0.54481703042984</v>
       </c>
       <c r="H1054" t="n">
         <v>95826</v>
@@ -30964,7 +30964,7 @@
         <v>0.55224597454071</v>
       </c>
       <c r="G1055" t="n">
-        <v>0.526030361652374</v>
+        <v>0.526030302047729</v>
       </c>
       <c r="H1055" t="n">
         <v>104953</v>
@@ -31051,7 +31051,7 @@
         <v>0.520689010620117</v>
       </c>
       <c r="G1058" t="n">
-        <v>0.495971381664276</v>
+        <v>0.495971411466599</v>
       </c>
       <c r="H1058" t="n">
         <v>18759</v>
@@ -31225,7 +31225,7 @@
         <v>0.36191800236702</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.344737410545349</v>
+        <v>0.344737380743027</v>
       </c>
       <c r="H1064" t="n">
         <v>127769</v>
@@ -31312,7 +31312,7 @@
         <v>0.318527013063431</v>
       </c>
       <c r="G1067" t="n">
-        <v>0.303406208753586</v>
+        <v>0.303406238555908</v>
       </c>
       <c r="H1067" t="n">
         <v>33463</v>
@@ -31370,7 +31370,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.309981524944305</v>
+        <v>0.309981554746628</v>
       </c>
       <c r="H1069" t="n">
         <v>42082</v>
@@ -31399,7 +31399,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1070" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1070" t="n">
         <v>74531</v>
@@ -31515,7 +31515,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1074" t="n">
         <v>38026</v>
@@ -31718,7 +31718,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1081" t="n">
         <v>79095</v>
@@ -31776,7 +31776,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1083" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1083" t="n">
         <v>106474</v>
@@ -31863,7 +31863,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1086" t="n">
         <v>16224</v>
@@ -31892,7 +31892,7 @@
         <v>0.400377988815308</v>
       </c>
       <c r="G1087" t="n">
-        <v>0.381371676921844</v>
+        <v>0.381371647119522</v>
       </c>
       <c r="H1087" t="n">
         <v>33463</v>
@@ -31921,7 +31921,7 @@
         <v>0.384600013494492</v>
       </c>
       <c r="G1088" t="n">
-        <v>0.366342693567276</v>
+        <v>0.366342663764954</v>
       </c>
       <c r="H1088" t="n">
         <v>21294</v>
@@ -32066,7 +32066,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1093" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1093" t="n">
         <v>9633</v>
@@ -32124,7 +32124,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1095" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1095" t="n">
         <v>16224</v>
@@ -32211,7 +32211,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1098" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1098" t="n">
         <v>44617</v>
@@ -32269,7 +32269,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.336283713579178</v>
+        <v>0.336283683776855</v>
       </c>
       <c r="H1100" t="n">
         <v>250974</v>
@@ -32298,7 +32298,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1101" t="n">
         <v>48673</v>
@@ -32356,7 +32356,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1103" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1103" t="n">
         <v>9126</v>
@@ -32385,7 +32385,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1104" t="n">
         <v>12168</v>
@@ -32443,7 +32443,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1106" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1106" t="n">
         <v>25351</v>
@@ -32472,7 +32472,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1107" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1107" t="n">
         <v>7605</v>
@@ -32530,7 +32530,7 @@
         <v>0.369807004928589</v>
       </c>
       <c r="G1109" t="n">
-        <v>0.352251917123795</v>
+        <v>0.352251887321472</v>
       </c>
       <c r="H1109" t="n">
         <v>23829</v>
@@ -32559,7 +32559,7 @@
         <v>0.453631013631821</v>
       </c>
       <c r="G1110" t="n">
-        <v>0.432096689939499</v>
+        <v>0.432096719741821</v>
       </c>
       <c r="H1110" t="n">
         <v>456825</v>
@@ -32617,7 +32617,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.392643928527832</v>
+        <v>0.39264389872551</v>
       </c>
       <c r="H1112" t="n">
         <v>188104</v>
@@ -32646,7 +32646,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1113" t="n">
         <v>101911</v>
@@ -32704,7 +32704,7 @@
         <v>0.398405998945236</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.379493296146393</v>
+        <v>0.37949326634407</v>
       </c>
       <c r="H1115" t="n">
         <v>63377</v>
@@ -32849,7 +32849,7 @@
         <v>0.475326001644135</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.452761828899384</v>
+        <v>0.452761799097061</v>
       </c>
       <c r="H1120" t="n">
         <v>63884</v>
@@ -33110,7 +33110,7 @@
         <v>0.484201014041901</v>
       </c>
       <c r="G1129" t="n">
-        <v>0.461215525865555</v>
+        <v>0.461215496063232</v>
       </c>
       <c r="H1129" t="n">
         <v>51209</v>
@@ -33284,7 +33284,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G1135" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H1135" t="n">
         <v>11154</v>
@@ -33342,7 +33342,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G1137" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H1137" t="n">
         <v>3549</v>
@@ -33371,7 +33371,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.462154686450958</v>
+        <v>0.462154716253281</v>
       </c>
       <c r="H1138" t="n">
         <v>16224</v>
@@ -33400,7 +33400,7 @@
         <v>0.475326001644135</v>
       </c>
       <c r="G1139" t="n">
-        <v>0.452761828899384</v>
+        <v>0.452761799097061</v>
       </c>
       <c r="H1139" t="n">
         <v>8619</v>
@@ -33458,7 +33458,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1141" t="n">
-        <v>0.437731891870499</v>
+        <v>0.437731862068176</v>
       </c>
       <c r="H1141" t="n">
         <v>9126</v>
@@ -33516,7 +33516,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1143" t="n">
-        <v>0.548574805259705</v>
+        <v>0.548574864864349</v>
       </c>
       <c r="H1143" t="n">
         <v>882214</v>
@@ -33545,7 +33545,7 @@
         <v>0.524634003639221</v>
       </c>
       <c r="G1144" t="n">
-        <v>0.499729126691818</v>
+        <v>0.499729096889496</v>
       </c>
       <c r="H1144" t="n">
         <v>914157</v>
@@ -33748,7 +33748,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G1151" t="n">
-        <v>0.462154686450958</v>
+        <v>0.462154716253281</v>
       </c>
       <c r="H1151" t="n">
         <v>49687</v>
@@ -33806,7 +33806,7 @@
         <v>0.489131987094879</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.4659124314785</v>
+        <v>0.465912401676178</v>
       </c>
       <c r="H1153" t="n">
         <v>48673</v>
@@ -33980,7 +33980,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1159" t="n">
-        <v>0.437731891870499</v>
+        <v>0.437731862068176</v>
       </c>
       <c r="H1159" t="n">
         <v>34984</v>
@@ -34009,7 +34009,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1160" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H1160" t="n">
         <v>45124</v>
@@ -34096,7 +34096,7 @@
         <v>0.449685990810394</v>
       </c>
       <c r="G1163" t="n">
-        <v>0.428338944911957</v>
+        <v>0.428338974714279</v>
       </c>
       <c r="H1163" t="n">
         <v>51716</v>
@@ -34241,7 +34241,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1168" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1168" t="n">
         <v>12168</v>
@@ -34357,7 +34357,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.41988530755043</v>
+        <v>0.419885277748108</v>
       </c>
       <c r="H1172" t="n">
         <v>116107</v>
@@ -34386,7 +34386,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1173" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H1173" t="n">
         <v>52730</v>
@@ -34415,7 +34415,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H1174" t="n">
         <v>0</v>
@@ -34473,7 +34473,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.418945103883743</v>
+        <v>0.418945133686066</v>
       </c>
       <c r="H1176" t="n">
         <v>15717</v>
@@ -34502,7 +34502,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G1177" t="n">
-        <v>0.418945103883743</v>
+        <v>0.418945133686066</v>
       </c>
       <c r="H1177" t="n">
         <v>8619</v>
@@ -34531,7 +34531,7 @@
         <v>0.439823985099792</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.418945103883743</v>
+        <v>0.418945133686066</v>
       </c>
       <c r="H1178" t="n">
         <v>1014</v>
@@ -34676,7 +34676,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1183" t="n">
         <v>10140</v>
@@ -35024,7 +35024,7 @@
         <v>0.429962992668152</v>
       </c>
       <c r="G1195" t="n">
-        <v>0.409552246332169</v>
+        <v>0.409552216529846</v>
       </c>
       <c r="H1195" t="n">
         <v>142472</v>
@@ -35053,7 +35053,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1196" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1196" t="n">
         <v>87207</v>
@@ -35256,7 +35256,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1203" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1203" t="n">
         <v>65405</v>
@@ -35314,7 +35314,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1205" t="n">
         <v>3042</v>
@@ -35401,7 +35401,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1208" t="n">
         <v>241341</v>
@@ -35430,7 +35430,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1209" t="n">
-        <v>0.392643928527832</v>
+        <v>0.39264389872551</v>
       </c>
       <c r="H1209" t="n">
         <v>62363</v>
@@ -35575,7 +35575,7 @@
         <v>0.429962992668152</v>
       </c>
       <c r="G1214" t="n">
-        <v>0.409552246332169</v>
+        <v>0.409552216529846</v>
       </c>
       <c r="H1214" t="n">
         <v>40561</v>
@@ -35836,7 +35836,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1223" t="n">
         <v>77067</v>
@@ -35923,7 +35923,7 @@
         <v>0.402350008487701</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.383250057697296</v>
+        <v>0.383250087499619</v>
       </c>
       <c r="H1226" t="n">
         <v>10647</v>
@@ -36097,7 +36097,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1232" t="n">
-        <v>0.392643928527832</v>
+        <v>0.39264389872551</v>
       </c>
       <c r="H1232" t="n">
         <v>11154</v>
@@ -36184,7 +36184,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1235" t="n">
         <v>115093</v>
@@ -36213,7 +36213,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1236" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1236" t="n">
         <v>85179</v>
@@ -36300,7 +36300,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1239" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1239" t="n">
         <v>109516</v>
@@ -36329,7 +36329,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1240" t="n">
         <v>40561</v>
@@ -36358,7 +36358,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1241" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1241" t="n">
         <v>76053</v>
@@ -36416,7 +36416,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1243" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H1243" t="n">
         <v>481161</v>
@@ -36561,7 +36561,7 @@
         <v>0.463492006063461</v>
       </c>
       <c r="G1248" t="n">
-        <v>0.441489577293396</v>
+        <v>0.441489607095718</v>
       </c>
       <c r="H1248" t="n">
         <v>119149</v>
@@ -36648,7 +36648,7 @@
         <v>0.518716990947723</v>
       </c>
       <c r="G1251" t="n">
-        <v>0.494093000888824</v>
+        <v>0.494093030691147</v>
       </c>
       <c r="H1251" t="n">
         <v>617043</v>
@@ -36822,7 +36822,7 @@
         <v>0.485186994075775</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.462154686450958</v>
+        <v>0.462154716253281</v>
       </c>
       <c r="H1257" t="n">
         <v>29407</v>
@@ -37054,7 +37054,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1265" t="n">
-        <v>0.437731891870499</v>
+        <v>0.437731862068176</v>
       </c>
       <c r="H1265" t="n">
         <v>59321</v>
@@ -37170,7 +37170,7 @@
         <v>0.44574099779129</v>
       </c>
       <c r="G1269" t="n">
-        <v>0.424581259489059</v>
+        <v>0.424581229686737</v>
       </c>
       <c r="H1269" t="n">
         <v>12168</v>
@@ -37315,7 +37315,7 @@
         <v>0.459547013044357</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.437731891870499</v>
+        <v>0.437731862068176</v>
       </c>
       <c r="H1274" t="n">
         <v>93798</v>
@@ -37431,7 +37431,7 @@
         <v>0.443769007921219</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.422702878713608</v>
+        <v>0.422702848911285</v>
       </c>
       <c r="H1278" t="n">
         <v>9126</v>
@@ -37547,7 +37547,7 @@
         <v>0.440811008214951</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.41988530755043</v>
+        <v>0.419885277748108</v>
       </c>
       <c r="H1282" t="n">
         <v>6084</v>
@@ -37837,7 +37837,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1292" t="n">
         <v>94305</v>
@@ -37895,7 +37895,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1294" t="n">
         <v>116107</v>
@@ -37924,7 +37924,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1295" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1295" t="n">
         <v>29407</v>
@@ -37953,7 +37953,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1296" t="n">
         <v>84672</v>
@@ -38011,7 +38011,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1298" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1298" t="n">
         <v>76560</v>
@@ -38243,7 +38243,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1306" t="n">
         <v>4056</v>
@@ -38330,7 +38330,7 @@
         <v>0.418128997087479</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.398279994726181</v>
+        <v>0.398280024528503</v>
       </c>
       <c r="H1309" t="n">
         <v>13689</v>
@@ -38359,7 +38359,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1310" t="n">
         <v>1521</v>
@@ -38388,7 +38388,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1311" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1311" t="n">
         <v>3042</v>
@@ -38504,7 +38504,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1315" t="n">
         <v>4563</v>
@@ -38533,7 +38533,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1316" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1316" t="n">
         <v>0</v>
@@ -38591,7 +38591,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1318" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1318" t="n">
         <v>115600</v>
@@ -38765,7 +38765,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1324" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1324" t="n">
         <v>25858</v>
@@ -38794,7 +38794,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1325" t="n">
-        <v>0.392643928527832</v>
+        <v>0.39264389872551</v>
       </c>
       <c r="H1325" t="n">
         <v>1521</v>
@@ -38968,7 +38968,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1331" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1331" t="n">
         <v>29407</v>
@@ -38997,7 +38997,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1332" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1332" t="n">
         <v>14703</v>
@@ -39026,7 +39026,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1333" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1333" t="n">
         <v>4056</v>
@@ -39113,7 +39113,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1336" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1336" t="n">
         <v>39040</v>
@@ -39142,7 +39142,7 @@
         <v>0.412212014198303</v>
       </c>
       <c r="G1337" t="n">
-        <v>0.392643928527832</v>
+        <v>0.39264389872551</v>
       </c>
       <c r="H1337" t="n">
         <v>11154</v>
@@ -39200,7 +39200,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1339" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1339" t="n">
         <v>2028</v>
@@ -39258,7 +39258,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1341" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1341" t="n">
         <v>10647</v>
@@ -39287,7 +39287,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1342" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1342" t="n">
         <v>0</v>
@@ -39316,7 +39316,7 @@
         <v>0.415170013904572</v>
       </c>
       <c r="G1343" t="n">
-        <v>0.39546149969101</v>
+        <v>0.395461469888687</v>
       </c>
       <c r="H1343" t="n">
         <v>11154</v>
@@ -39490,7 +39490,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1349" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1349" t="n">
         <v>7098</v>
@@ -39519,7 +39519,7 @@
         <v>0.414184004068375</v>
       </c>
       <c r="G1350" t="n">
-        <v>0.394522309303284</v>
+        <v>0.394522279500961</v>
       </c>
       <c r="H1350" t="n">
         <v>19266</v>
@@ -39606,7 +39606,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1353" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1353" t="n">
         <v>41575</v>
@@ -39693,7 +39693,7 @@
         <v>0.424046009778976</v>
       </c>
       <c r="G1356" t="n">
-        <v>0.403916120529175</v>
+        <v>0.403916150331497</v>
       </c>
       <c r="H1356" t="n">
         <v>9633</v>
@@ -39722,7 +39722,7 @@
         <v>0.429962992668152</v>
       </c>
       <c r="G1357" t="n">
-        <v>0.409552246332169</v>
+        <v>0.409552216529846</v>
       </c>
       <c r="H1357" t="n">
         <v>12168</v>
@@ -39896,7 +39896,7 @@
         <v>0.398405998945236</v>
       </c>
       <c r="G1363" t="n">
-        <v>0.379493296146393</v>
+        <v>0.37949326634407</v>
       </c>
       <c r="H1363" t="n">
         <v>57293</v>
@@ -39983,7 +39983,7 @@
         <v>0.398405998945236</v>
       </c>
       <c r="G1366" t="n">
-        <v>0.379493296146393</v>
+        <v>0.37949326634407</v>
       </c>
       <c r="H1366" t="n">
         <v>5577</v>
@@ -40041,7 +40041,7 @@
         <v>0.407281011343002</v>
       </c>
       <c r="G1368" t="n">
-        <v>0.387946993112564</v>
+        <v>0.387946963310242</v>
       </c>
       <c r="H1368" t="n">
         <v>7098</v>
@@ -40070,7 +40070,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1369" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1369" t="n">
         <v>49687</v>
@@ -40099,7 +40099,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1370" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1370" t="n">
         <v>171372</v>
@@ -40244,7 +40244,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1375" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1375" t="n">
         <v>56786</v>
@@ -40302,7 +40302,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1377" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1377" t="n">
         <v>23829</v>
@@ -40505,7 +40505,7 @@
         <v>0.402350008487701</v>
       </c>
       <c r="G1384" t="n">
-        <v>0.383250057697296</v>
+        <v>0.383250087499619</v>
       </c>
       <c r="H1384" t="n">
         <v>46138</v>
@@ -40534,7 +40534,7 @@
         <v>0.394461005926132</v>
       </c>
       <c r="G1385" t="n">
-        <v>0.375735551118851</v>
+        <v>0.375735580921173</v>
       </c>
       <c r="H1385" t="n">
         <v>136895</v>
@@ -40621,7 +40621,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1388" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1388" t="n">
         <v>115093</v>
@@ -40650,7 +40650,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1389" t="n">
-        <v>0.36070653796196</v>
+        <v>0.360706567764282</v>
       </c>
       <c r="H1389" t="n">
         <v>14703</v>
@@ -40708,7 +40708,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1391" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1391" t="n">
         <v>68954</v>
@@ -40766,7 +40766,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1393" t="n">
-        <v>0.361645728349686</v>
+        <v>0.361645758152008</v>
       </c>
       <c r="H1393" t="n">
         <v>43096</v>
@@ -40795,7 +40795,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1394" t="n">
-        <v>0.36070653796196</v>
+        <v>0.360706567764282</v>
       </c>
       <c r="H1394" t="n">
         <v>37012</v>
@@ -40911,7 +40911,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1398" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1398" t="n">
         <v>18759</v>
@@ -40940,7 +40940,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1399" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1399" t="n">
         <v>0</v>
@@ -41172,7 +41172,7 @@
         <v>0.368820995092392</v>
       </c>
       <c r="G1407" t="n">
-        <v>0.351312726736069</v>
+        <v>0.351312696933746</v>
       </c>
       <c r="H1407" t="n">
         <v>23829</v>
@@ -41201,7 +41201,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1408" t="n">
-        <v>0.347555905580521</v>
+        <v>0.347555935382843</v>
       </c>
       <c r="H1408" t="n">
         <v>35998</v>
@@ -41288,7 +41288,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1411" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1411" t="n">
         <v>29407</v>
@@ -41375,7 +41375,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1414" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1414" t="n">
         <v>21801</v>
@@ -41404,7 +41404,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1415" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1415" t="n">
         <v>24336</v>
@@ -41433,7 +41433,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1416" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1416" t="n">
         <v>0</v>
@@ -41462,7 +41462,7 @@
         <v>0.35402899980545</v>
       </c>
       <c r="G1417" t="n">
-        <v>0.337222903966904</v>
+        <v>0.337222874164581</v>
       </c>
       <c r="H1417" t="n">
         <v>5577</v>
@@ -41491,7 +41491,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1418" t="n">
-        <v>0.336283713579178</v>
+        <v>0.336283683776855</v>
       </c>
       <c r="H1418" t="n">
         <v>29407</v>
@@ -41665,7 +41665,7 @@
         <v>0.34909799695015</v>
       </c>
       <c r="G1424" t="n">
-        <v>0.332525968551636</v>
+        <v>0.332525998353958</v>
       </c>
       <c r="H1424" t="n">
         <v>60842</v>
@@ -41752,7 +41752,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1427" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1427" t="n">
         <v>30928</v>
@@ -41781,7 +41781,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1428" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1428" t="n">
         <v>32956</v>
@@ -41810,7 +41810,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1429" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1429" t="n">
         <v>0</v>
@@ -42013,7 +42013,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1436" t="n">
-        <v>0.347555905580521</v>
+        <v>0.347555935382843</v>
       </c>
       <c r="H1436" t="n">
         <v>8112</v>
@@ -42332,7 +42332,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1447" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1447" t="n">
         <v>14196</v>
@@ -42361,7 +42361,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1448" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1448" t="n">
         <v>31942</v>
@@ -42419,7 +42419,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1450" t="n">
-        <v>0.361645728349686</v>
+        <v>0.361645758152008</v>
       </c>
       <c r="H1450" t="n">
         <v>3549</v>
@@ -42448,7 +42448,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1451" t="n">
-        <v>0.361645728349686</v>
+        <v>0.361645758152008</v>
       </c>
       <c r="H1451" t="n">
         <v>0</v>
@@ -42680,7 +42680,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1459" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1459" t="n">
         <v>120163</v>
@@ -42767,7 +42767,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1462" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1462" t="n">
         <v>46645</v>
@@ -42912,7 +42912,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1467" t="n">
-        <v>0.36070653796196</v>
+        <v>0.360706567764282</v>
       </c>
       <c r="H1467" t="n">
         <v>6591</v>
@@ -42941,7 +42941,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1468" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1468" t="n">
         <v>18759</v>
@@ -43028,7 +43028,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1471" t="n">
-        <v>0.347555905580521</v>
+        <v>0.347555935382843</v>
       </c>
       <c r="H1471" t="n">
         <v>5070</v>
@@ -43231,7 +43231,7 @@
         <v>0.378683000802994</v>
       </c>
       <c r="G1478" t="n">
-        <v>0.36070653796196</v>
+        <v>0.360706567764282</v>
       </c>
       <c r="H1478" t="n">
         <v>1521</v>
@@ -43260,7 +43260,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1479" t="n">
-        <v>0.361645728349686</v>
+        <v>0.361645758152008</v>
       </c>
       <c r="H1479" t="n">
         <v>5070</v>
@@ -43405,7 +43405,7 @@
         <v>0.384600013494492</v>
       </c>
       <c r="G1484" t="n">
-        <v>0.366342693567276</v>
+        <v>0.366342663764954</v>
       </c>
       <c r="H1484" t="n">
         <v>2535</v>
@@ -43434,7 +43434,7 @@
         <v>0.384600013494492</v>
       </c>
       <c r="G1485" t="n">
-        <v>0.366342693567276</v>
+        <v>0.366342663764954</v>
       </c>
       <c r="H1485" t="n">
         <v>0</v>
@@ -43492,7 +43492,7 @@
         <v>0.379669010639191</v>
       </c>
       <c r="G1487" t="n">
-        <v>0.361645728349686</v>
+        <v>0.361645758152008</v>
       </c>
       <c r="H1487" t="n">
         <v>11661</v>
@@ -43521,7 +43521,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1488" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1488" t="n">
         <v>17745</v>
@@ -43550,7 +43550,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1489" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1489" t="n">
         <v>0</v>
@@ -43579,7 +43579,7 @@
         <v>0.372765988111496</v>
       </c>
       <c r="G1490" t="n">
-        <v>0.355070412158966</v>
+        <v>0.355070441961288</v>
       </c>
       <c r="H1490" t="n">
         <v>0</v>
@@ -43695,7 +43695,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1494" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1494" t="n">
         <v>40561</v>
@@ -43724,7 +43724,7 @@
         <v>0.362904012203217</v>
       </c>
       <c r="G1495" t="n">
-        <v>0.345676600933075</v>
+        <v>0.345676630735397</v>
       </c>
       <c r="H1495" t="n">
         <v>31435</v>
@@ -44014,7 +44014,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1505" t="n">
-        <v>0.321253776550293</v>
+        <v>0.321253746747971</v>
       </c>
       <c r="H1505" t="n">
         <v>17238</v>
@@ -44072,7 +44072,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1507" t="n">
-        <v>0.336283713579178</v>
+        <v>0.336283683776855</v>
       </c>
       <c r="H1507" t="n">
         <v>8112</v>
@@ -44101,7 +44101,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1508" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1508" t="n">
         <v>9126</v>
@@ -44362,7 +44362,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1517" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1517" t="n">
         <v>41068</v>
@@ -44391,7 +44391,7 @@
         <v>0.350084006786346</v>
       </c>
       <c r="G1518" t="n">
-        <v>0.333465158939362</v>
+        <v>0.333465188741684</v>
       </c>
       <c r="H1518" t="n">
         <v>15717</v>
@@ -44565,7 +44565,7 @@
         <v>0.319514006376266</v>
       </c>
       <c r="G1524" t="n">
-        <v>0.304346352815628</v>
+        <v>0.30434638261795</v>
       </c>
       <c r="H1524" t="n">
         <v>88728</v>
@@ -44594,7 +44594,7 @@
         <v>0.347126007080078</v>
       </c>
       <c r="G1525" t="n">
-        <v>0.330647587776184</v>
+        <v>0.330647617578506</v>
       </c>
       <c r="H1525" t="n">
         <v>83151</v>
@@ -44710,7 +44710,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1529" t="n">
-        <v>0.321253776550293</v>
+        <v>0.321253746747971</v>
       </c>
       <c r="H1529" t="n">
         <v>28393</v>
@@ -44768,7 +44768,7 @@
         <v>0.330361008644104</v>
       </c>
       <c r="G1531" t="n">
-        <v>0.314678460359573</v>
+        <v>0.314678430557251</v>
       </c>
       <c r="H1531" t="n">
         <v>50194</v>
@@ -45029,7 +45029,7 @@
         <v>0.347126007080078</v>
       </c>
       <c r="G1540" t="n">
-        <v>0.330647587776184</v>
+        <v>0.330647617578506</v>
       </c>
       <c r="H1540" t="n">
         <v>26365</v>
@@ -45087,7 +45087,7 @@
         <v>0.333319991827011</v>
       </c>
       <c r="G1542" t="n">
-        <v>0.317496955394745</v>
+        <v>0.317496985197067</v>
       </c>
       <c r="H1542" t="n">
         <v>20280</v>
@@ -45116,7 +45116,7 @@
         <v>0.333319991827011</v>
       </c>
       <c r="G1543" t="n">
-        <v>0.317496955394745</v>
+        <v>0.317496985197067</v>
       </c>
       <c r="H1543" t="n">
         <v>41068</v>
@@ -45174,7 +45174,7 @@
         <v>0.334306001663208</v>
       </c>
       <c r="G1545" t="n">
-        <v>0.318436145782471</v>
+        <v>0.318436175584793</v>
       </c>
       <c r="H1545" t="n">
         <v>1521</v>
@@ -45203,7 +45203,7 @@
         <v>0.334306001663208</v>
       </c>
       <c r="G1546" t="n">
-        <v>0.318436145782471</v>
+        <v>0.318436175584793</v>
       </c>
       <c r="H1546" t="n">
         <v>0</v>
@@ -45232,7 +45232,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1547" t="n">
-        <v>0.309981524944305</v>
+        <v>0.309981554746628</v>
       </c>
       <c r="H1547" t="n">
         <v>12168</v>
@@ -45261,7 +45261,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1548" t="n">
-        <v>0.309981524944305</v>
+        <v>0.309981554746628</v>
       </c>
       <c r="H1548" t="n">
         <v>8619</v>
@@ -45522,7 +45522,7 @@
         <v>0.333319991827011</v>
       </c>
       <c r="G1557" t="n">
-        <v>0.317496955394745</v>
+        <v>0.317496985197067</v>
       </c>
       <c r="H1557" t="n">
         <v>13182</v>
@@ -45551,7 +45551,7 @@
         <v>0.366849005222321</v>
       </c>
       <c r="G1558" t="n">
-        <v>0.349434345960617</v>
+        <v>0.349434316158295</v>
       </c>
       <c r="H1558" t="n">
         <v>454289</v>
@@ -45667,7 +45667,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1562" t="n">
-        <v>0.321253776550293</v>
+        <v>0.321253746747971</v>
       </c>
       <c r="H1562" t="n">
         <v>39547</v>
@@ -45696,7 +45696,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1563" t="n">
-        <v>0.309981524944305</v>
+        <v>0.309981554746628</v>
       </c>
       <c r="H1563" t="n">
         <v>19266</v>
@@ -45870,7 +45870,7 @@
         <v>0.330361008644104</v>
       </c>
       <c r="G1569" t="n">
-        <v>0.314678460359573</v>
+        <v>0.314678430557251</v>
       </c>
       <c r="H1569" t="n">
         <v>24843</v>
@@ -45899,7 +45899,7 @@
         <v>0.330361008644104</v>
       </c>
       <c r="G1570" t="n">
-        <v>0.314678460359573</v>
+        <v>0.314678430557251</v>
       </c>
       <c r="H1570" t="n">
         <v>0</v>
@@ -46015,7 +46015,7 @@
         <v>0.307680010795593</v>
       </c>
       <c r="G1574" t="n">
-        <v>0.293074160814285</v>
+        <v>0.293074131011963</v>
       </c>
       <c r="H1574" t="n">
         <v>35491</v>
@@ -46044,7 +46044,7 @@
         <v>0.301762998104095</v>
       </c>
       <c r="G1575" t="n">
-        <v>0.287438005208969</v>
+        <v>0.287438035011292</v>
       </c>
       <c r="H1575" t="n">
         <v>19266</v>
@@ -46073,7 +46073,7 @@
         <v>0.304720997810364</v>
       </c>
       <c r="G1576" t="n">
-        <v>0.290255576372147</v>
+        <v>0.290255606174469</v>
       </c>
       <c r="H1576" t="n">
         <v>5070</v>
@@ -46276,7 +46276,7 @@
         <v>0.316554993391037</v>
       </c>
       <c r="G1583" t="n">
-        <v>0.301527827978134</v>
+        <v>0.301527798175812</v>
       </c>
       <c r="H1583" t="n">
         <v>4056</v>
@@ -46305,7 +46305,7 @@
         <v>0.304720997810364</v>
       </c>
       <c r="G1584" t="n">
-        <v>0.290255576372147</v>
+        <v>0.290255606174469</v>
       </c>
       <c r="H1584" t="n">
         <v>19773</v>
@@ -46392,7 +46392,7 @@
         <v>0.325430005788803</v>
       </c>
       <c r="G1587" t="n">
-        <v>0.309981524944305</v>
+        <v>0.309981554746628</v>
       </c>
       <c r="H1587" t="n">
         <v>9633</v>
@@ -46537,7 +46537,7 @@
         <v>0.323457986116409</v>
       </c>
       <c r="G1592" t="n">
-        <v>0.308103144168854</v>
+        <v>0.308103114366531</v>
       </c>
       <c r="H1592" t="n">
         <v>3042</v>
@@ -46595,7 +46595,7 @@
         <v>0.321485996246338</v>
       </c>
       <c r="G1594" t="n">
-        <v>0.306224763393402</v>
+        <v>0.30622473359108</v>
       </c>
       <c r="H1594" t="n">
         <v>12168</v>
@@ -46885,7 +46885,7 @@
         <v>0.307680010795593</v>
       </c>
       <c r="G1604" t="n">
-        <v>0.293074160814285</v>
+        <v>0.293074131011963</v>
       </c>
       <c r="H1604" t="n">
         <v>6591</v>
@@ -46914,7 +46914,7 @@
         <v>0.307680010795593</v>
       </c>
       <c r="G1605" t="n">
-        <v>0.293074160814285</v>
+        <v>0.293074131011963</v>
       </c>
       <c r="H1605" t="n">
         <v>0</v>
@@ -46943,7 +46943,7 @@
         <v>0.308665990829468</v>
       </c>
       <c r="G1606" t="n">
-        <v>0.294013321399689</v>
+        <v>0.294013291597366</v>
       </c>
       <c r="H1606" t="n">
         <v>6084</v>
@@ -46972,7 +46972,7 @@
         <v>0.301762998104095</v>
       </c>
       <c r="G1607" t="n">
-        <v>0.287438005208969</v>
+        <v>0.287438035011292</v>
       </c>
       <c r="H1607" t="n">
         <v>6084</v>
@@ -47146,7 +47146,7 @@
         <v>0.34909799695015</v>
       </c>
       <c r="G1613" t="n">
-        <v>0.332525968551636</v>
+        <v>0.332525998353958</v>
       </c>
       <c r="H1613" t="n">
         <v>2028</v>
@@ -47175,7 +47175,7 @@
         <v>0.337264001369476</v>
       </c>
       <c r="G1614" t="n">
-        <v>0.321253776550293</v>
+        <v>0.321253746747971</v>
       </c>
       <c r="H1614" t="n">
         <v>13689</v>
@@ -47262,7 +47262,7 @@
         <v>0.364876985549927</v>
       </c>
       <c r="G1617" t="n">
-        <v>0.347555905580521</v>
+        <v>0.347555935382843</v>
       </c>
       <c r="H1617" t="n">
         <v>191653</v>
@@ -47320,7 +47320,7 @@
         <v>0.353042989969254</v>
       </c>
       <c r="G1619" t="n">
-        <v>0.336283713579178</v>
+        <v>0.336283683776855</v>
       </c>
       <c r="H1619" t="n">
         <v>56279</v>
@@ -47349,7 +47349,7 @@
         <v>0.363889992237091</v>
       </c>
       <c r="G1620" t="n">
-        <v>0.346615761518478</v>
+        <v>0.346615791320801</v>
       </c>
       <c r="H1620" t="n">
         <v>17238</v>
@@ -47407,7 +47407,7 @@
         <v>0.368820995092392</v>
       </c>
       <c r="G1622" t="n">
-        <v>0.351312726736069</v>
+        <v>0.351312696933746</v>
       </c>
       <c r="H1622" t="n">
         <v>476598</v>
@@ -47465,7 +47465,7 @@
         <v>0.382627010345459</v>
       </c>
       <c r="G1624" t="n">
-        <v>0.364463359117508</v>
+        <v>0.364463329315186</v>
       </c>
       <c r="H1624" t="n">
         <v>62363</v>
@@ -47697,7 +47697,7 @@
         <v>0.674529016017914</v>
       </c>
       <c r="G1632" t="n">
-        <v>0.642508447170258</v>
+        <v>0.642508506774902</v>
       </c>
       <c r="H1632" t="n">
         <v>674336</v>
@@ -47755,7 +47755,7 @@
         <v>0.639028012752533</v>
       </c>
       <c r="G1634" t="n">
-        <v>0.608692705631256</v>
+        <v>0.608692765235901</v>
       </c>
       <c r="H1634" t="n">
         <v>336661</v>
@@ -47871,7 +47871,7 @@
         <v>0.611415028572083</v>
       </c>
       <c r="G1638" t="n">
-        <v>0.582390546798706</v>
+        <v>0.582390606403351</v>
       </c>
       <c r="H1638" t="n">
         <v>162246</v>
@@ -47900,7 +47900,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1639" t="n">
-        <v>0.548574805259705</v>
+        <v>0.548574864864349</v>
       </c>
       <c r="H1639" t="n">
         <v>162246</v>
@@ -47987,7 +47987,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1642" t="n">
-        <v>0.548574805259705</v>
+        <v>0.548574864864349</v>
       </c>
       <c r="H1642" t="n">
         <v>111037</v>
@@ -48045,7 +48045,7 @@
         <v>0.571968972682953</v>
       </c>
       <c r="G1644" t="n">
-        <v>0.544817090034485</v>
+        <v>0.54481703042984</v>
       </c>
       <c r="H1644" t="n">
         <v>66926</v>
@@ -48364,7 +48364,7 @@
         <v>0.702140986919403</v>
       </c>
       <c r="G1655" t="n">
-        <v>0.668809652328491</v>
+        <v>0.668809711933136</v>
       </c>
       <c r="H1655" t="n">
         <v>78081</v>
@@ -48625,7 +48625,7 @@
         <v>0.615360021591187</v>
       </c>
       <c r="G1664" t="n">
-        <v>0.586148321628571</v>
+        <v>0.586148262023926</v>
       </c>
       <c r="H1664" t="n">
         <v>8619</v>
@@ -48712,7 +48712,7 @@
         <v>0.639028012752533</v>
       </c>
       <c r="G1667" t="n">
-        <v>0.608692705631256</v>
+        <v>0.608692765235901</v>
       </c>
       <c r="H1667" t="n">
         <v>56786</v>
@@ -48741,7 +48741,7 @@
         <v>0.64691698551178</v>
       </c>
       <c r="G1668" t="n">
-        <v>0.616207182407379</v>
+        <v>0.616207242012024</v>
       </c>
       <c r="H1668" t="n">
         <v>59321</v>
@@ -48857,7 +48857,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1672" t="n">
-        <v>0.604935050010681</v>
+        <v>0.604934990406036</v>
       </c>
       <c r="H1672" t="n">
         <v>31942</v>
@@ -48915,7 +48915,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1674" t="n">
-        <v>0.604935050010681</v>
+        <v>0.604934990406036</v>
       </c>
       <c r="H1674" t="n">
         <v>70982</v>
@@ -49147,7 +49147,7 @@
         <v>0.615360021591187</v>
       </c>
       <c r="G1682" t="n">
-        <v>0.586148321628571</v>
+        <v>0.586148262023926</v>
       </c>
       <c r="H1682" t="n">
         <v>13689</v>
@@ -49176,7 +49176,7 @@
         <v>0.583802998065948</v>
       </c>
       <c r="G1683" t="n">
-        <v>0.556089282035828</v>
+        <v>0.556089341640472</v>
       </c>
       <c r="H1683" t="n">
         <v>214976</v>
@@ -49263,7 +49263,7 @@
         <v>0.571968972682953</v>
       </c>
       <c r="G1686" t="n">
-        <v>0.544817090034485</v>
+        <v>0.54481703042984</v>
       </c>
       <c r="H1686" t="n">
         <v>9126</v>
@@ -49350,7 +49350,7 @@
         <v>0.575914025306702</v>
       </c>
       <c r="G1689" t="n">
-        <v>0.548574805259705</v>
+        <v>0.548574864864349</v>
       </c>
       <c r="H1689" t="n">
         <v>25858</v>
@@ -49408,7 +49408,7 @@
         <v>0.595637023448944</v>
       </c>
       <c r="G1691" t="n">
-        <v>0.567361533641815</v>
+        <v>0.56736159324646</v>
       </c>
       <c r="H1691" t="n">
         <v>12675</v>
@@ -49524,7 +49524,7 @@
         <v>0.603525996208191</v>
       </c>
       <c r="G1695" t="n">
-        <v>0.574876010417938</v>
+        <v>0.574876070022583</v>
       </c>
       <c r="H1695" t="n">
         <v>28900</v>
@@ -49582,7 +49582,7 @@
         <v>0.595637023448944</v>
       </c>
       <c r="G1697" t="n">
-        <v>0.567361533641815</v>
+        <v>0.56736159324646</v>
       </c>
       <c r="H1697" t="n">
         <v>3549</v>
@@ -49669,7 +49669,7 @@
         <v>0.607470989227295</v>
       </c>
       <c r="G1700" t="n">
-        <v>0.578633785247803</v>
+        <v>0.578633725643158</v>
       </c>
       <c r="H1700" t="n">
         <v>25351</v>
@@ -49698,7 +49698,7 @@
         <v>0.607470989227295</v>
       </c>
       <c r="G1701" t="n">
-        <v>0.578633785247803</v>
+        <v>0.578633725643158</v>
       </c>
       <c r="H1701" t="n">
         <v>19773</v>
@@ -49727,7 +49727,7 @@
         <v>0.635083019733429</v>
       </c>
       <c r="G1702" t="n">
-        <v>0.604935050010681</v>
+        <v>0.604934990406036</v>
       </c>
       <c r="H1702" t="n">
         <v>64391</v>
@@ -49872,7 +49872,7 @@
         <v>0.662694990634918</v>
       </c>
       <c r="G1707" t="n">
-        <v>0.631236255168915</v>
+        <v>0.63123619556427</v>
       </c>
       <c r="H1707" t="n">
         <v>123712</v>
@@ -50075,7 +50075,7 @@
         <v>0.702140986919403</v>
       </c>
       <c r="G1714" t="n">
-        <v>0.668809652328491</v>
+        <v>0.668809711933136</v>
       </c>
       <c r="H1714" t="n">
         <v>115093</v>
@@ -50162,7 +50162,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1717" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H1717" t="n">
         <v>1126598</v>
@@ -50249,7 +50249,7 @@
         <v>0.702140986919403</v>
       </c>
       <c r="G1720" t="n">
-        <v>0.668809652328491</v>
+        <v>0.668809711933136</v>
       </c>
       <c r="H1720" t="n">
         <v>385842</v>
@@ -50423,7 +50423,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1726" t="n">
-        <v>0.63499391078949</v>
+        <v>0.634993970394135</v>
       </c>
       <c r="H1726" t="n">
         <v>82644</v>
@@ -50481,7 +50481,7 @@
         <v>0.668612003326416</v>
       </c>
       <c r="G1728" t="n">
-        <v>0.636872291564941</v>
+        <v>0.636872351169586</v>
       </c>
       <c r="H1728" t="n">
         <v>132332</v>
@@ -50510,7 +50510,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1729" t="n">
-        <v>0.63499391078949</v>
+        <v>0.634993970394135</v>
       </c>
       <c r="H1729" t="n">
         <v>9126</v>
@@ -50713,7 +50713,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1736" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H1736" t="n">
         <v>307254</v>
@@ -50800,7 +50800,7 @@
         <v>0.674529016017914</v>
       </c>
       <c r="G1739" t="n">
-        <v>0.642508447170258</v>
+        <v>0.642508506774902</v>
       </c>
       <c r="H1739" t="n">
         <v>100389</v>
@@ -50887,7 +50887,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1742" t="n">
-        <v>0.63499391078949</v>
+        <v>0.634993970394135</v>
       </c>
       <c r="H1742" t="n">
         <v>41575</v>
@@ -50945,7 +50945,7 @@
         <v>0.662694990634918</v>
       </c>
       <c r="G1744" t="n">
-        <v>0.631236255168915</v>
+        <v>0.63123619556427</v>
       </c>
       <c r="H1744" t="n">
         <v>26365</v>
@@ -51119,7 +51119,7 @@
         <v>0.64691698551178</v>
       </c>
       <c r="G1750" t="n">
-        <v>0.616207182407379</v>
+        <v>0.616207242012024</v>
       </c>
       <c r="H1750" t="n">
         <v>328548</v>
@@ -51264,7 +51264,7 @@
         <v>0.694252014160156</v>
       </c>
       <c r="G1755" t="n">
-        <v>0.661295175552368</v>
+        <v>0.661295235157013</v>
       </c>
       <c r="H1755" t="n">
         <v>19773</v>
@@ -51496,7 +51496,7 @@
         <v>0.666639983654022</v>
       </c>
       <c r="G1763" t="n">
-        <v>0.63499391078949</v>
+        <v>0.634993970394135</v>
       </c>
       <c r="H1763" t="n">
         <v>228159</v>
@@ -51699,7 +51699,7 @@
         <v>0.69819700717926</v>
       </c>
       <c r="G1770" t="n">
-        <v>0.665052950382233</v>
+        <v>0.665052890777588</v>
       </c>
       <c r="H1770" t="n">
         <v>90249</v>
@@ -52279,7 +52279,7 @@
         <v>0.674529016017914</v>
       </c>
       <c r="G1790" t="n">
-        <v>0.642508447170258</v>
+        <v>0.642508506774902</v>
       </c>
       <c r="H1790" t="n">
         <v>5577</v>
@@ -52337,7 +52337,7 @@
         <v>0.694252014160156</v>
       </c>
       <c r="G1792" t="n">
-        <v>0.661295175552368</v>
+        <v>0.661295235157013</v>
       </c>
       <c r="H1792" t="n">
         <v>99882</v>
@@ -52656,7 +52656,7 @@
         <v>0.69819700717926</v>
       </c>
       <c r="G1803" t="n">
-        <v>0.665052950382233</v>
+        <v>0.665052890777588</v>
       </c>
       <c r="H1803" t="n">
         <v>735179</v>
@@ -52830,7 +52830,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1809" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H1809" t="n">
         <v>43603</v>
@@ -52859,7 +52859,7 @@
         <v>0.706085979938507</v>
       </c>
       <c r="G1810" t="n">
-        <v>0.672567427158356</v>
+        <v>0.672567367553711</v>
       </c>
       <c r="H1810" t="n">
         <v>60335</v>
@@ -53207,7 +53207,7 @@
         <v>0.708057999610901</v>
       </c>
       <c r="G1822" t="n">
-        <v>0.674445807933807</v>
+        <v>0.674445748329163</v>
       </c>
       <c r="H1822" t="n">
         <v>42589</v>
@@ -53265,7 +53265,7 @@
         <v>0.733698010444641</v>
       </c>
       <c r="G1824" t="n">
-        <v>0.698868691921234</v>
+        <v>0.698868632316589</v>
       </c>
       <c r="H1824" t="n">
         <v>185569</v>
@@ -53323,7 +53323,7 @@
         <v>0.729753971099854</v>
       </c>
       <c r="G1826" t="n">
-        <v>0.695111811161041</v>
+        <v>0.695111870765686</v>
       </c>
       <c r="H1826" t="n">
         <v>63884</v>
@@ -53410,7 +53410,7 @@
         <v>0.745531976222992</v>
       </c>
       <c r="G1829" t="n">
-        <v>0.710140824317932</v>
+        <v>0.710140883922577</v>
       </c>
       <c r="H1829" t="n">
         <v>101911</v>
@@ -53439,7 +53439,7 @@
         <v>0.745531976222992</v>
       </c>
       <c r="G1830" t="n">
-        <v>0.710140824317932</v>
+        <v>0.710140883922577</v>
       </c>
       <c r="H1830" t="n">
         <v>85179</v>
@@ -53497,7 +53497,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1832" t="n">
-        <v>0.712020218372345</v>
+        <v>0.71202027797699</v>
       </c>
       <c r="H1832" t="n">
         <v>27886</v>
@@ -53555,7 +53555,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1834" t="n">
-        <v>0.712020218372345</v>
+        <v>0.71202027797699</v>
       </c>
       <c r="H1834" t="n">
         <v>23829</v>
@@ -53584,7 +53584,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G1835" t="n">
-        <v>0.702626347541809</v>
+        <v>0.702626407146454</v>
       </c>
       <c r="H1835" t="n">
         <v>106981</v>
@@ -53613,7 +53613,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G1836" t="n">
-        <v>0.702626347541809</v>
+        <v>0.702626407146454</v>
       </c>
       <c r="H1836" t="n">
         <v>2535</v>
@@ -53642,7 +53642,7 @@
         <v>0.737643003463745</v>
       </c>
       <c r="G1837" t="n">
-        <v>0.702626347541809</v>
+        <v>0.702626407146454</v>
       </c>
       <c r="H1837" t="n">
         <v>14703</v>
@@ -53700,7 +53700,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1839" t="n">
-        <v>0.712020218372345</v>
+        <v>0.71202027797699</v>
       </c>
       <c r="H1839" t="n">
         <v>37519</v>
@@ -53729,7 +53729,7 @@
         <v>0.747505009174347</v>
       </c>
       <c r="G1840" t="n">
-        <v>0.712020218372345</v>
+        <v>0.71202027797699</v>
       </c>
       <c r="H1840" t="n">
         <v>5577</v>
@@ -53990,7 +53990,7 @@
         <v>0.796811997890472</v>
       </c>
       <c r="G1849" t="n">
-        <v>0.758986592292786</v>
+        <v>0.758986532688141</v>
       </c>
       <c r="H1849" t="n">
         <v>942043</v>
@@ -54193,7 +54193,7 @@
         <v>0.942762970924377</v>
       </c>
       <c r="G1856" t="n">
-        <v>0.898009121417999</v>
+        <v>0.898009061813354</v>
       </c>
       <c r="H1856" t="n">
         <v>243876</v>
@@ -54338,7 +54338,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1861" t="n">
-        <v>1.089635014534</v>
+        <v>1.08963513374329</v>
       </c>
       <c r="H1861" t="n">
         <v>336661</v>
@@ -54425,7 +54425,7 @@
         <v>1.10449194908142</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.05206072330475</v>
+        <v>1.05206060409546</v>
       </c>
       <c r="H1864" t="n">
         <v>324999</v>
@@ -54512,7 +54512,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.089635014534</v>
+        <v>1.08963513374329</v>
       </c>
       <c r="H1867" t="n">
         <v>737207</v>
@@ -54599,7 +54599,7 @@
         <v>1.10449194908142</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.05206072330475</v>
+        <v>1.05206060409546</v>
       </c>
       <c r="H1870" t="n">
         <v>120163</v>
@@ -54657,7 +54657,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.089635014534</v>
+        <v>1.08963513374329</v>
       </c>
       <c r="H1872" t="n">
         <v>374180</v>
@@ -54744,7 +54744,7 @@
         <v>1.15873098373413</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.10372483730316</v>
+        <v>1.10372495651245</v>
       </c>
       <c r="H1875" t="n">
         <v>117121</v>
@@ -54773,7 +54773,7 @@
         <v>1.14393901824951</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.089635014534</v>
+        <v>1.08963513374329</v>
       </c>
       <c r="H1876" t="n">
         <v>24336</v>
@@ -54860,7 +54860,7 @@
         <v>1.15873098373413</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.10372483730316</v>
+        <v>1.10372495651245</v>
       </c>
       <c r="H1879" t="n">
         <v>75038</v>
@@ -54976,7 +54976,7 @@
         <v>1.2179000377655</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.16008520126343</v>
+        <v>1.16008508205414</v>
       </c>
       <c r="H1883" t="n">
         <v>52730</v>
@@ -55324,7 +55324,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.20705246925354</v>
+        <v>1.20705235004425</v>
       </c>
       <c r="H1895" t="n">
         <v>59321</v>
@@ -55382,7 +55382,7 @@
         <v>1.25734603404999</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.19765853881836</v>
+        <v>1.19765865802765</v>
       </c>
       <c r="H1897" t="n">
         <v>146021</v>
@@ -55411,7 +55411,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.20705246925354</v>
+        <v>1.20705235004425</v>
       </c>
       <c r="H1898" t="n">
         <v>88221</v>
@@ -55440,7 +55440,7 @@
         <v>1.27213895320892</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.21174931526184</v>
+        <v>1.21174919605255</v>
       </c>
       <c r="H1899" t="n">
         <v>80616</v>
@@ -55701,7 +55701,7 @@
         <v>1.26720798015594</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.20705246925354</v>
+        <v>1.20705235004425</v>
       </c>
       <c r="H1908" t="n">
         <v>396489</v>
@@ -56020,7 +56020,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H1919" t="n">
         <v>359984</v>
@@ -56049,7 +56049,7 @@
         <v>1.3855459690094</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.31977272033691</v>
+        <v>1.3197728395462</v>
       </c>
       <c r="H1920" t="n">
         <v>571411</v>
@@ -56107,7 +56107,7 @@
         <v>1.40033900737762</v>
       </c>
       <c r="G1922" t="n">
-        <v>1.33386361598969</v>
+        <v>1.3338634967804</v>
       </c>
       <c r="H1922" t="n">
         <v>187090</v>
@@ -56310,7 +56310,7 @@
         <v>1.37075400352478</v>
       </c>
       <c r="G1929" t="n">
-        <v>1.30568289756775</v>
+        <v>1.30568301677704</v>
       </c>
       <c r="H1929" t="n">
         <v>545553</v>
@@ -56368,7 +56368,7 @@
         <v>1.29679298400879</v>
       </c>
       <c r="G1931" t="n">
-        <v>1.2352329492569</v>
+        <v>1.23523306846619</v>
       </c>
       <c r="H1931" t="n">
         <v>329055</v>
@@ -56397,7 +56397,7 @@
         <v>1.31158494949341</v>
       </c>
       <c r="G1932" t="n">
-        <v>1.24932277202606</v>
+        <v>1.24932265281677</v>
       </c>
       <c r="H1932" t="n">
         <v>112558</v>
@@ -80212,6 +80212,35 @@
         <v>6500</v>
       </c>
       <c r="I2753" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2754" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C2754" t="n">
+        <v>3.41000008583069</v>
+      </c>
+      <c r="D2754" t="n">
+        <v>3.41000008583069</v>
+      </c>
+      <c r="E2754" t="n">
+        <v>3.41000008583069</v>
+      </c>
+      <c r="F2754" t="n">
+        <v>3.41000008583069</v>
+      </c>
+      <c r="G2754" t="n">
+        <v>3.41000008583069</v>
+      </c>
+      <c r="H2754" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I2754" t="s">
         <v>9</v>
       </c>
     </row>
